--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -939,6 +939,9 @@
   <si>
     <t>['62', '83']</t>
   </si>
+  <si>
+    <t>['1', '61']</t>
+  </si>
 </sst>
 </file>
 
@@ -1299,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2663,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ7">
         <v>0.9</v>
@@ -3078,7 +3081,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ9">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -5753,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
         <v>0.8</v>
@@ -6168,7 +6171,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -9464,7 +9467,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -10491,7 +10494,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ45">
         <v>0.44</v>
@@ -13996,7 +13999,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -15026,7 +15029,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -16259,7 +16262,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ73">
         <v>2.4</v>
@@ -17495,7 +17498,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79">
         <v>1.22</v>
@@ -18734,7 +18737,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ85">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -21409,7 +21412,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ98">
         <v>0.9</v>
@@ -23884,7 +23887,7 @@
         <v>1</v>
       </c>
       <c r="AQ110">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24705,7 +24708,7 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ114">
         <v>1.4</v>
@@ -28004,7 +28007,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ130">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28413,7 +28416,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ132">
         <v>1.2</v>
@@ -32330,7 +32333,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ151">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR151">
         <v>1.15</v>
@@ -32533,7 +32536,7 @@
         <v>1.13</v>
       </c>
       <c r="AP152">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ152">
         <v>1.2</v>
@@ -33151,7 +33154,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ155">
         <v>1.56</v>
@@ -36732,6 +36735,212 @@
       </c>
       <c r="BP172">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7468529</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45688.69791666666</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>75</v>
+      </c>
+      <c r="H173" t="s">
+        <v>83</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>90</v>
+      </c>
+      <c r="P173" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q173">
+        <v>4.33</v>
+      </c>
+      <c r="R173">
+        <v>2.3</v>
+      </c>
+      <c r="S173">
+        <v>2.4</v>
+      </c>
+      <c r="T173">
+        <v>1.33</v>
+      </c>
+      <c r="U173">
+        <v>3.25</v>
+      </c>
+      <c r="V173">
+        <v>2.5</v>
+      </c>
+      <c r="W173">
+        <v>1.5</v>
+      </c>
+      <c r="X173">
+        <v>6</v>
+      </c>
+      <c r="Y173">
+        <v>1.13</v>
+      </c>
+      <c r="Z173">
+        <v>4.02</v>
+      </c>
+      <c r="AA173">
+        <v>3.94</v>
+      </c>
+      <c r="AB173">
+        <v>1.82</v>
+      </c>
+      <c r="AC173">
+        <v>1.03</v>
+      </c>
+      <c r="AD173">
+        <v>15</v>
+      </c>
+      <c r="AE173">
+        <v>1.22</v>
+      </c>
+      <c r="AF173">
+        <v>4.33</v>
+      </c>
+      <c r="AG173">
+        <v>1.68</v>
+      </c>
+      <c r="AH173">
+        <v>2.2</v>
+      </c>
+      <c r="AI173">
+        <v>1.62</v>
+      </c>
+      <c r="AJ173">
+        <v>2.2</v>
+      </c>
+      <c r="AK173">
+        <v>1.93</v>
+      </c>
+      <c r="AL173">
+        <v>1.26</v>
+      </c>
+      <c r="AM173">
+        <v>1.23</v>
+      </c>
+      <c r="AN173">
+        <v>1.2</v>
+      </c>
+      <c r="AO173">
+        <v>1.78</v>
+      </c>
+      <c r="AP173">
+        <v>1.09</v>
+      </c>
+      <c r="AQ173">
+        <v>1.9</v>
+      </c>
+      <c r="AR173">
+        <v>1.44</v>
+      </c>
+      <c r="AS173">
+        <v>1.43</v>
+      </c>
+      <c r="AT173">
+        <v>2.87</v>
+      </c>
+      <c r="AU173">
+        <v>4</v>
+      </c>
+      <c r="AV173">
+        <v>7</v>
+      </c>
+      <c r="AW173">
+        <v>12</v>
+      </c>
+      <c r="AX173">
+        <v>12</v>
+      </c>
+      <c r="AY173">
+        <v>18</v>
+      </c>
+      <c r="AZ173">
+        <v>25</v>
+      </c>
+      <c r="BA173">
+        <v>4</v>
+      </c>
+      <c r="BB173">
+        <v>5</v>
+      </c>
+      <c r="BC173">
+        <v>9</v>
+      </c>
+      <c r="BD173">
+        <v>2.65</v>
+      </c>
+      <c r="BE173">
+        <v>6.5</v>
+      </c>
+      <c r="BF173">
+        <v>1.58</v>
+      </c>
+      <c r="BG173">
+        <v>1.32</v>
+      </c>
+      <c r="BH173">
+        <v>3.05</v>
+      </c>
+      <c r="BI173">
+        <v>1.55</v>
+      </c>
+      <c r="BJ173">
+        <v>2.25</v>
+      </c>
+      <c r="BK173">
+        <v>1.9</v>
+      </c>
+      <c r="BL173">
+        <v>1.79</v>
+      </c>
+      <c r="BM173">
+        <v>2.4</v>
+      </c>
+      <c r="BN173">
+        <v>1.49</v>
+      </c>
+      <c r="BO173">
+        <v>3.15</v>
+      </c>
+      <c r="BP173">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,18 @@
     <t>['7', '51']</t>
   </si>
   <si>
+    <t>['50', '71']</t>
+  </si>
+  <si>
+    <t>['35', '57', '63', '65']</t>
+  </si>
+  <si>
+    <t>['32', '63', '72', '78']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -847,9 +859,6 @@
     <t>['23', '61']</t>
   </si>
   <si>
-    <t>['85']</t>
-  </si>
-  <si>
     <t>['44', '54']</t>
   </si>
   <si>
@@ -941,6 +950,12 @@
   </si>
   <si>
     <t>['1', '61']</t>
+  </si>
+  <si>
+    <t>['29', '57', '62', '89', '90+7']</t>
+  </si>
+  <si>
+    <t>['38', '45+7']</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,7 +1573,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1639,7 +1654,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ2">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1764,7 +1779,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1842,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ3">
         <v>2.4</v>
@@ -1970,7 +1985,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2254,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2382,7 +2397,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2463,7 +2478,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2588,7 +2603,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2872,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8">
         <v>0.8</v>
@@ -3618,7 +3633,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3902,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ13">
         <v>1.2</v>
@@ -4030,7 +4045,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4442,7 +4457,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4729,7 +4744,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ17">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5060,7 +5075,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5266,7 +5281,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5550,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5678,7 +5693,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5884,7 +5899,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -5962,7 +5977,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ23">
         <v>2.4</v>
@@ -6090,7 +6105,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6168,7 +6183,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ24">
         <v>1.9</v>
@@ -6296,7 +6311,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6377,7 +6392,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6583,7 +6598,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ26">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6708,7 +6723,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6914,7 +6929,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6992,10 +7007,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ28">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7407,7 +7422,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -7532,7 +7547,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8150,7 +8165,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8356,7 +8371,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8640,7 +8655,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36">
         <v>0.78</v>
@@ -9055,7 +9070,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ38">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9180,7 +9195,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9258,7 +9273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ39">
         <v>0.9</v>
@@ -9386,7 +9401,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9673,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -9876,7 +9891,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ42">
         <v>0.78</v>
@@ -10082,7 +10097,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ43">
         <v>1.22</v>
@@ -10210,7 +10225,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10416,7 +10431,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10497,7 +10512,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ45">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10622,7 +10637,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11034,7 +11049,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11321,7 +11336,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11446,7 +11461,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11652,7 +11667,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11730,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ51">
         <v>0.33</v>
@@ -11858,7 +11873,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11936,7 +11951,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52">
         <v>1.3</v>
@@ -12064,7 +12079,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12145,7 +12160,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ53">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12270,7 +12285,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12888,7 +12903,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -12969,7 +12984,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ57">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13172,7 +13187,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ58">
         <v>1.22</v>
@@ -13300,7 +13315,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13790,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ61">
         <v>0.78</v>
@@ -13918,7 +13933,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14124,7 +14139,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14330,7 +14345,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14411,7 +14426,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ64">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -14614,7 +14629,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ65">
         <v>1.4</v>
@@ -14820,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ66">
         <v>0.11</v>
@@ -14948,7 +14963,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15154,7 +15169,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15360,7 +15375,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15566,7 +15581,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15644,7 +15659,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ70">
         <v>1.2</v>
@@ -15772,7 +15787,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15853,7 +15868,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -15978,7 +15993,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16184,7 +16199,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16596,7 +16611,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16677,7 +16692,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ75">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16802,7 +16817,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17008,7 +17023,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17214,7 +17229,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17295,7 +17310,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ78">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17420,7 +17435,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17626,7 +17641,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18038,7 +18053,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18119,7 +18134,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ82">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18322,7 +18337,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ83">
         <v>1.2</v>
@@ -18528,7 +18543,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ84">
         <v>1.3</v>
@@ -18862,7 +18877,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18940,10 +18955,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19352,7 +19367,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
         <v>1.33</v>
@@ -19892,7 +19907,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20098,7 +20113,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20179,7 +20194,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ92">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20304,7 +20319,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20510,7 +20525,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20716,7 +20731,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20797,7 +20812,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ95">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -20922,7 +20937,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21128,7 +21143,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21334,7 +21349,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21540,7 +21555,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21827,7 +21842,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ100">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -21952,7 +21967,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22030,7 +22045,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ101">
         <v>0.9</v>
@@ -22364,7 +22379,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23060,7 +23075,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ106">
         <v>0.11</v>
@@ -23394,7 +23409,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23600,7 +23615,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23806,7 +23821,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24093,7 +24108,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24218,7 +24233,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24296,7 +24311,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ112">
         <v>0.9</v>
@@ -24630,7 +24645,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24836,7 +24851,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25120,10 +25135,10 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ116">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25248,7 +25263,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25329,7 +25344,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -25454,7 +25469,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25738,7 +25753,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ119">
         <v>0.9</v>
@@ -25947,7 +25962,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ120">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26150,7 +26165,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ121">
         <v>1.22</v>
@@ -26278,7 +26293,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26484,7 +26499,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27308,7 +27323,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27592,10 +27607,10 @@
         <v>0.14</v>
       </c>
       <c r="AP128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ128">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27720,7 +27735,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27926,7 +27941,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28338,7 +28353,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28419,7 +28434,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ132">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28544,7 +28559,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28828,7 +28843,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ134">
         <v>0.8</v>
@@ -29368,7 +29383,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29446,10 +29461,10 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ137">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29574,7 +29589,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29780,7 +29795,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29986,7 +30001,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30064,7 +30079,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30685,7 +30700,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -31016,7 +31031,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31222,7 +31237,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31634,7 +31649,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31712,7 +31727,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ148">
         <v>1.3</v>
@@ -31840,7 +31855,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -31921,7 +31936,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32046,7 +32061,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32252,7 +32267,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32458,7 +32473,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32664,7 +32679,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32742,7 +32757,7 @@
         <v>0.63</v>
       </c>
       <c r="AP153">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ153">
         <v>0.9</v>
@@ -32951,7 +32966,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ154">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR154">
         <v>2.26</v>
@@ -33076,7 +33091,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33360,10 +33375,10 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ156">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33488,7 +33503,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33569,7 +33584,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ157">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AR157">
         <v>1.67</v>
@@ -33694,7 +33709,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34393,7 +34408,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ161">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR161">
         <v>1.21</v>
@@ -34724,7 +34739,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35011,7 +35026,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ164">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35136,7 +35151,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35214,7 +35229,7 @@
         <v>0.13</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ165">
         <v>0.11</v>
@@ -35548,7 +35563,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35754,7 +35769,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35960,7 +35975,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36166,7 +36181,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36244,7 +36259,7 @@
         <v>0</v>
       </c>
       <c r="AP170">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ170">
         <v>0.33</v>
@@ -36784,7 +36799,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -36941,6 +36956,830 @@
       </c>
       <c r="BP173">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7468528</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45689.54166666666</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>71</v>
+      </c>
+      <c r="H174" t="s">
+        <v>79</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>5</v>
+      </c>
+      <c r="N174">
+        <v>7</v>
+      </c>
+      <c r="O174" t="s">
+        <v>214</v>
+      </c>
+      <c r="P174" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q174">
+        <v>5.25</v>
+      </c>
+      <c r="R174">
+        <v>2.4</v>
+      </c>
+      <c r="S174">
+        <v>1.93</v>
+      </c>
+      <c r="T174">
+        <v>1.28</v>
+      </c>
+      <c r="U174">
+        <v>3.4</v>
+      </c>
+      <c r="V174">
+        <v>2.25</v>
+      </c>
+      <c r="W174">
+        <v>1.57</v>
+      </c>
+      <c r="X174">
+        <v>5</v>
+      </c>
+      <c r="Y174">
+        <v>1.14</v>
+      </c>
+      <c r="Z174">
+        <v>6.2</v>
+      </c>
+      <c r="AA174">
+        <v>4.75</v>
+      </c>
+      <c r="AB174">
+        <v>1.51</v>
+      </c>
+      <c r="AC174">
+        <v>1.02</v>
+      </c>
+      <c r="AD174">
+        <v>19</v>
+      </c>
+      <c r="AE174">
+        <v>1.18</v>
+      </c>
+      <c r="AF174">
+        <v>5</v>
+      </c>
+      <c r="AG174">
+        <v>1.57</v>
+      </c>
+      <c r="AH174">
+        <v>2.25</v>
+      </c>
+      <c r="AI174">
+        <v>1.7</v>
+      </c>
+      <c r="AJ174">
+        <v>2</v>
+      </c>
+      <c r="AK174">
+        <v>2.55</v>
+      </c>
+      <c r="AL174">
+        <v>1.19</v>
+      </c>
+      <c r="AM174">
+        <v>1.13</v>
+      </c>
+      <c r="AN174">
+        <v>2.11</v>
+      </c>
+      <c r="AO174">
+        <v>2.33</v>
+      </c>
+      <c r="AP174">
+        <v>1.9</v>
+      </c>
+      <c r="AQ174">
+        <v>2.4</v>
+      </c>
+      <c r="AR174">
+        <v>1.46</v>
+      </c>
+      <c r="AS174">
+        <v>2.17</v>
+      </c>
+      <c r="AT174">
+        <v>3.63</v>
+      </c>
+      <c r="AU174">
+        <v>8</v>
+      </c>
+      <c r="AV174">
+        <v>8</v>
+      </c>
+      <c r="AW174">
+        <v>7</v>
+      </c>
+      <c r="AX174">
+        <v>7</v>
+      </c>
+      <c r="AY174">
+        <v>19</v>
+      </c>
+      <c r="AZ174">
+        <v>18</v>
+      </c>
+      <c r="BA174">
+        <v>4</v>
+      </c>
+      <c r="BB174">
+        <v>7</v>
+      </c>
+      <c r="BC174">
+        <v>11</v>
+      </c>
+      <c r="BD174">
+        <v>3.8</v>
+      </c>
+      <c r="BE174">
+        <v>6.75</v>
+      </c>
+      <c r="BF174">
+        <v>1.33</v>
+      </c>
+      <c r="BG174">
+        <v>1.44</v>
+      </c>
+      <c r="BH174">
+        <v>2.55</v>
+      </c>
+      <c r="BI174">
+        <v>1.76</v>
+      </c>
+      <c r="BJ174">
+        <v>1.94</v>
+      </c>
+      <c r="BK174">
+        <v>2.2</v>
+      </c>
+      <c r="BL174">
+        <v>1.58</v>
+      </c>
+      <c r="BM174">
+        <v>2.85</v>
+      </c>
+      <c r="BN174">
+        <v>1.36</v>
+      </c>
+      <c r="BO174">
+        <v>3.8</v>
+      </c>
+      <c r="BP174">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7468535</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45689.625</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>73</v>
+      </c>
+      <c r="H175" t="s">
+        <v>74</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>3</v>
+      </c>
+      <c r="L175">
+        <v>4</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>6</v>
+      </c>
+      <c r="O175" t="s">
+        <v>215</v>
+      </c>
+      <c r="P175" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q175">
+        <v>1.73</v>
+      </c>
+      <c r="R175">
+        <v>2.75</v>
+      </c>
+      <c r="S175">
+        <v>7</v>
+      </c>
+      <c r="T175">
+        <v>1.25</v>
+      </c>
+      <c r="U175">
+        <v>3.75</v>
+      </c>
+      <c r="V175">
+        <v>2.1</v>
+      </c>
+      <c r="W175">
+        <v>1.67</v>
+      </c>
+      <c r="X175">
+        <v>4.5</v>
+      </c>
+      <c r="Y175">
+        <v>1.18</v>
+      </c>
+      <c r="Z175">
+        <v>1.36</v>
+      </c>
+      <c r="AA175">
+        <v>5.7</v>
+      </c>
+      <c r="AB175">
+        <v>7.9</v>
+      </c>
+      <c r="AC175">
+        <v>1.01</v>
+      </c>
+      <c r="AD175">
+        <v>17</v>
+      </c>
+      <c r="AE175">
+        <v>1.13</v>
+      </c>
+      <c r="AF175">
+        <v>6</v>
+      </c>
+      <c r="AG175">
+        <v>1.4</v>
+      </c>
+      <c r="AH175">
+        <v>2.82</v>
+      </c>
+      <c r="AI175">
+        <v>1.75</v>
+      </c>
+      <c r="AJ175">
+        <v>2</v>
+      </c>
+      <c r="AK175">
+        <v>1.09</v>
+      </c>
+      <c r="AL175">
+        <v>1.15</v>
+      </c>
+      <c r="AM175">
+        <v>3.1</v>
+      </c>
+      <c r="AN175">
+        <v>2</v>
+      </c>
+      <c r="AO175">
+        <v>0.44</v>
+      </c>
+      <c r="AP175">
+        <v>2.09</v>
+      </c>
+      <c r="AQ175">
+        <v>0.4</v>
+      </c>
+      <c r="AR175">
+        <v>1.59</v>
+      </c>
+      <c r="AS175">
+        <v>1.2</v>
+      </c>
+      <c r="AT175">
+        <v>2.79</v>
+      </c>
+      <c r="AU175">
+        <v>8</v>
+      </c>
+      <c r="AV175">
+        <v>8</v>
+      </c>
+      <c r="AW175">
+        <v>4</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>13</v>
+      </c>
+      <c r="AZ175">
+        <v>14</v>
+      </c>
+      <c r="BA175">
+        <v>5</v>
+      </c>
+      <c r="BB175">
+        <v>4</v>
+      </c>
+      <c r="BC175">
+        <v>9</v>
+      </c>
+      <c r="BD175">
+        <v>1.25</v>
+      </c>
+      <c r="BE175">
+        <v>8</v>
+      </c>
+      <c r="BF175">
+        <v>4.3</v>
+      </c>
+      <c r="BG175">
+        <v>1.29</v>
+      </c>
+      <c r="BH175">
+        <v>3.15</v>
+      </c>
+      <c r="BI175">
+        <v>1.5</v>
+      </c>
+      <c r="BJ175">
+        <v>2.38</v>
+      </c>
+      <c r="BK175">
+        <v>1.81</v>
+      </c>
+      <c r="BL175">
+        <v>1.88</v>
+      </c>
+      <c r="BM175">
+        <v>2.25</v>
+      </c>
+      <c r="BN175">
+        <v>1.55</v>
+      </c>
+      <c r="BO175">
+        <v>2.9</v>
+      </c>
+      <c r="BP175">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7468530</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45689.71180555555</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>81</v>
+      </c>
+      <c r="H176" t="s">
+        <v>82</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>2</v>
+      </c>
+      <c r="L176">
+        <v>4</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>5</v>
+      </c>
+      <c r="O176" t="s">
+        <v>216</v>
+      </c>
+      <c r="P176" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q176">
+        <v>1.91</v>
+      </c>
+      <c r="R176">
+        <v>2.4</v>
+      </c>
+      <c r="S176">
+        <v>7.5</v>
+      </c>
+      <c r="T176">
+        <v>1.36</v>
+      </c>
+      <c r="U176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>2.63</v>
+      </c>
+      <c r="W176">
+        <v>1.44</v>
+      </c>
+      <c r="X176">
+        <v>7</v>
+      </c>
+      <c r="Y176">
+        <v>1.1</v>
+      </c>
+      <c r="Z176">
+        <v>1.36</v>
+      </c>
+      <c r="AA176">
+        <v>5.4</v>
+      </c>
+      <c r="AB176">
+        <v>8.5</v>
+      </c>
+      <c r="AC176">
+        <v>1.03</v>
+      </c>
+      <c r="AD176">
+        <v>13</v>
+      </c>
+      <c r="AE176">
+        <v>1.26</v>
+      </c>
+      <c r="AF176">
+        <v>4</v>
+      </c>
+      <c r="AG176">
+        <v>1.83</v>
+      </c>
+      <c r="AH176">
+        <v>1.98</v>
+      </c>
+      <c r="AI176">
+        <v>2.05</v>
+      </c>
+      <c r="AJ176">
+        <v>1.7</v>
+      </c>
+      <c r="AK176">
+        <v>1.08</v>
+      </c>
+      <c r="AL176">
+        <v>1.17</v>
+      </c>
+      <c r="AM176">
+        <v>3</v>
+      </c>
+      <c r="AN176">
+        <v>2</v>
+      </c>
+      <c r="AO176">
+        <v>0.2</v>
+      </c>
+      <c r="AP176">
+        <v>2.1</v>
+      </c>
+      <c r="AQ176">
+        <v>0.18</v>
+      </c>
+      <c r="AR176">
+        <v>1.38</v>
+      </c>
+      <c r="AS176">
+        <v>0.99</v>
+      </c>
+      <c r="AT176">
+        <v>2.37</v>
+      </c>
+      <c r="AU176">
+        <v>14</v>
+      </c>
+      <c r="AV176">
+        <v>3</v>
+      </c>
+      <c r="AW176">
+        <v>18</v>
+      </c>
+      <c r="AX176">
+        <v>7</v>
+      </c>
+      <c r="AY176">
+        <v>37</v>
+      </c>
+      <c r="AZ176">
+        <v>12</v>
+      </c>
+      <c r="BA176">
+        <v>7</v>
+      </c>
+      <c r="BB176">
+        <v>1</v>
+      </c>
+      <c r="BC176">
+        <v>8</v>
+      </c>
+      <c r="BD176">
+        <v>1.23</v>
+      </c>
+      <c r="BE176">
+        <v>8</v>
+      </c>
+      <c r="BF176">
+        <v>4.6</v>
+      </c>
+      <c r="BG176">
+        <v>1.4</v>
+      </c>
+      <c r="BH176">
+        <v>2.7</v>
+      </c>
+      <c r="BI176">
+        <v>1.66</v>
+      </c>
+      <c r="BJ176">
+        <v>2.07</v>
+      </c>
+      <c r="BK176">
+        <v>2.05</v>
+      </c>
+      <c r="BL176">
+        <v>1.67</v>
+      </c>
+      <c r="BM176">
+        <v>2.65</v>
+      </c>
+      <c r="BN176">
+        <v>1.41</v>
+      </c>
+      <c r="BO176">
+        <v>3.4</v>
+      </c>
+      <c r="BP176">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7468533</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>76</v>
+      </c>
+      <c r="H177" t="s">
+        <v>86</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>2</v>
+      </c>
+      <c r="O177" t="s">
+        <v>217</v>
+      </c>
+      <c r="P177" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q177">
+        <v>3.1</v>
+      </c>
+      <c r="R177">
+        <v>2.2</v>
+      </c>
+      <c r="S177">
+        <v>3.4</v>
+      </c>
+      <c r="T177">
+        <v>1.4</v>
+      </c>
+      <c r="U177">
+        <v>2.75</v>
+      </c>
+      <c r="V177">
+        <v>2.75</v>
+      </c>
+      <c r="W177">
+        <v>1.4</v>
+      </c>
+      <c r="X177">
+        <v>8</v>
+      </c>
+      <c r="Y177">
+        <v>1.08</v>
+      </c>
+      <c r="Z177">
+        <v>2.42</v>
+      </c>
+      <c r="AA177">
+        <v>3.62</v>
+      </c>
+      <c r="AB177">
+        <v>2.89</v>
+      </c>
+      <c r="AC177">
+        <v>1.06</v>
+      </c>
+      <c r="AD177">
+        <v>11</v>
+      </c>
+      <c r="AE177">
+        <v>1.3</v>
+      </c>
+      <c r="AF177">
+        <v>3.6</v>
+      </c>
+      <c r="AG177">
+        <v>1.89</v>
+      </c>
+      <c r="AH177">
+        <v>1.92</v>
+      </c>
+      <c r="AI177">
+        <v>1.7</v>
+      </c>
+      <c r="AJ177">
+        <v>2.05</v>
+      </c>
+      <c r="AK177">
+        <v>1.41</v>
+      </c>
+      <c r="AL177">
+        <v>1.3</v>
+      </c>
+      <c r="AM177">
+        <v>1.55</v>
+      </c>
+      <c r="AN177">
+        <v>1.4</v>
+      </c>
+      <c r="AO177">
+        <v>1.2</v>
+      </c>
+      <c r="AP177">
+        <v>1.36</v>
+      </c>
+      <c r="AQ177">
+        <v>1.18</v>
+      </c>
+      <c r="AR177">
+        <v>1.51</v>
+      </c>
+      <c r="AS177">
+        <v>1.47</v>
+      </c>
+      <c r="AT177">
+        <v>2.98</v>
+      </c>
+      <c r="AU177">
+        <v>5</v>
+      </c>
+      <c r="AV177">
+        <v>5</v>
+      </c>
+      <c r="AW177">
+        <v>10</v>
+      </c>
+      <c r="AX177">
+        <v>10</v>
+      </c>
+      <c r="AY177">
+        <v>19</v>
+      </c>
+      <c r="AZ177">
+        <v>16</v>
+      </c>
+      <c r="BA177">
+        <v>7</v>
+      </c>
+      <c r="BB177">
+        <v>2</v>
+      </c>
+      <c r="BC177">
+        <v>9</v>
+      </c>
+      <c r="BD177">
+        <v>1.79</v>
+      </c>
+      <c r="BE177">
+        <v>6.4</v>
+      </c>
+      <c r="BF177">
+        <v>2.23</v>
+      </c>
+      <c r="BG177">
+        <v>1.37</v>
+      </c>
+      <c r="BH177">
+        <v>2.8</v>
+      </c>
+      <c r="BI177">
+        <v>1.64</v>
+      </c>
+      <c r="BJ177">
+        <v>2.1</v>
+      </c>
+      <c r="BK177">
+        <v>2.04</v>
+      </c>
+      <c r="BL177">
+        <v>1.67</v>
+      </c>
+      <c r="BM177">
+        <v>2.65</v>
+      </c>
+      <c r="BN177">
+        <v>1.41</v>
+      </c>
+      <c r="BO177">
+        <v>3.45</v>
+      </c>
+      <c r="BP177">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,12 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['61', '64', '85']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -956,6 +962,12 @@
   </si>
   <si>
     <t>['38', '45+7']</t>
+  </si>
+  <si>
+    <t>['42', '70']</t>
+  </si>
+  <si>
+    <t>['53', '72']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1585,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1779,7 +1791,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1985,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2063,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ4">
         <v>1.4</v>
@@ -2397,7 +2409,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2603,7 +2615,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2684,7 +2696,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ7">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2890,7 +2902,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3093,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9">
         <v>1.9</v>
@@ -3299,10 +3311,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ10">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3633,7 +3645,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4045,7 +4057,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4126,7 +4138,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ14">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4457,7 +4469,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5075,7 +5087,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5153,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -5281,7 +5293,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5362,7 +5374,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5693,7 +5705,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5774,7 +5786,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -5899,7 +5911,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6105,7 +6117,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6311,7 +6323,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6389,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ25">
         <v>1.18</v>
@@ -6723,7 +6735,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6801,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ27">
         <v>0.11</v>
@@ -6929,7 +6941,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7419,7 +7431,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>1.18</v>
@@ -7547,7 +7559,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8037,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33">
         <v>0.33</v>
@@ -8165,7 +8177,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8371,7 +8383,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8658,7 +8670,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -8864,7 +8876,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ37">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -9195,7 +9207,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9276,7 +9288,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ39">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9401,7 +9413,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9479,7 +9491,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
         <v>1.9</v>
@@ -9685,7 +9697,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ41">
         <v>2.4</v>
@@ -9894,7 +9906,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10225,7 +10237,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10303,10 +10315,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ44">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10431,7 +10443,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10637,7 +10649,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11049,7 +11061,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11461,7 +11473,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11667,7 +11679,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11873,7 +11885,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11954,7 +11966,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR52">
         <v>1.24</v>
@@ -12079,7 +12091,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12285,7 +12297,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12363,7 +12375,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12775,7 +12787,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56">
         <v>1.2</v>
@@ -12903,7 +12915,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13315,7 +13327,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13393,7 +13405,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ59">
         <v>1.56</v>
@@ -13602,7 +13614,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -13808,7 +13820,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ61">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -13933,7 +13945,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14139,7 +14151,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14217,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ63">
         <v>0.33</v>
@@ -14345,7 +14357,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14963,7 +14975,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15169,7 +15181,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15250,7 +15262,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ68">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15375,7 +15387,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15456,7 +15468,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ69">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR69">
         <v>1.32</v>
@@ -15581,7 +15593,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15787,7 +15799,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15993,7 +16005,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16199,7 +16211,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16483,10 +16495,10 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ74">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16611,7 +16623,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16689,7 +16701,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ75">
         <v>0.18</v>
@@ -16817,7 +16829,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16895,7 +16907,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ76">
         <v>0.9</v>
@@ -17023,7 +17035,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17229,7 +17241,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17435,7 +17447,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17641,7 +17653,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17722,7 +17734,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -18053,7 +18065,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18131,7 +18143,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ82">
         <v>2.4</v>
@@ -18546,7 +18558,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ84">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18877,7 +18889,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19164,7 +19176,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ87">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19907,7 +19919,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20113,7 +20125,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20191,7 +20203,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ92">
         <v>0.4</v>
@@ -20319,7 +20331,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20525,7 +20537,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20606,7 +20618,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -20731,7 +20743,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20809,7 +20821,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ95">
         <v>2.4</v>
@@ -20937,7 +20949,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21143,7 +21155,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21221,7 +21233,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
         <v>1.22</v>
@@ -21349,7 +21361,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21555,7 +21567,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21967,7 +21979,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22379,7 +22391,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22869,10 +22881,10 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ105">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR105">
         <v>1.09</v>
@@ -23409,7 +23421,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23490,7 +23502,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ108">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23615,7 +23627,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23696,7 +23708,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ109">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23821,7 +23833,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23899,7 +23911,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ110">
         <v>1.9</v>
@@ -24105,7 +24117,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
         <v>0.18</v>
@@ -24314,7 +24326,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ112">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24520,7 +24532,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ113">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24645,7 +24657,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24851,7 +24863,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25263,7 +25275,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25469,7 +25481,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25547,7 +25559,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ118">
         <v>1.56</v>
@@ -26293,7 +26305,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26374,7 +26386,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ122">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26499,7 +26511,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26577,10 +26589,10 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ123">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27323,7 +27335,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27735,7 +27747,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27813,7 +27825,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ129">
         <v>1.4</v>
@@ -27941,7 +27953,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28225,7 +28237,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ131">
         <v>1.56</v>
@@ -28353,7 +28365,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28559,7 +28571,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28640,7 +28652,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ133">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -28846,7 +28858,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ134">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29049,7 +29061,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.2</v>
@@ -29258,7 +29270,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ136">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR136">
         <v>2.35</v>
@@ -29383,7 +29395,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29589,7 +29601,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29795,7 +29807,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30001,7 +30013,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30082,7 +30094,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ140">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -30903,7 +30915,7 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ144">
         <v>0.9</v>
@@ -31109,10 +31121,10 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ145">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31237,7 +31249,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31649,7 +31661,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31730,7 +31742,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ148">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR148">
         <v>1.48</v>
@@ -31855,7 +31867,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -31933,7 +31945,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ149">
         <v>1.18</v>
@@ -32061,7 +32073,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32139,7 +32151,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ150">
         <v>2.4</v>
@@ -32267,7 +32279,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32473,7 +32485,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32679,7 +32691,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32760,7 +32772,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ153">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33091,7 +33103,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33503,7 +33515,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33709,7 +33721,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33787,7 +33799,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ158">
         <v>0.9</v>
@@ -34202,7 +34214,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ160">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34405,7 +34417,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ161">
         <v>0.4</v>
@@ -34611,10 +34623,10 @@
         <v>0.75</v>
       </c>
       <c r="AP162">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ162">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -34739,7 +34751,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34817,10 +34829,10 @@
         <v>0.89</v>
       </c>
       <c r="AP163">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ163">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR163">
         <v>1.45</v>
@@ -35151,7 +35163,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35563,7 +35575,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35769,7 +35781,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35975,7 +35987,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36056,7 +36068,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ169">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR169">
         <v>1.4</v>
@@ -36181,7 +36193,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36799,7 +36811,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37005,7 +37017,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37211,7 +37223,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37623,7 +37635,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37780,6 +37792,830 @@
       </c>
       <c r="BP177">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7468534</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45690.55208333334</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>78</v>
+      </c>
+      <c r="H178" t="s">
+        <v>84</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>178</v>
+      </c>
+      <c r="P178" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q178">
+        <v>2.75</v>
+      </c>
+      <c r="R178">
+        <v>2.2</v>
+      </c>
+      <c r="S178">
+        <v>4</v>
+      </c>
+      <c r="T178">
+        <v>1.4</v>
+      </c>
+      <c r="U178">
+        <v>2.75</v>
+      </c>
+      <c r="V178">
+        <v>2.75</v>
+      </c>
+      <c r="W178">
+        <v>1.4</v>
+      </c>
+      <c r="X178">
+        <v>8</v>
+      </c>
+      <c r="Y178">
+        <v>1.08</v>
+      </c>
+      <c r="Z178">
+        <v>2.15</v>
+      </c>
+      <c r="AA178">
+        <v>3.64</v>
+      </c>
+      <c r="AB178">
+        <v>3.38</v>
+      </c>
+      <c r="AC178">
+        <v>1.05</v>
+      </c>
+      <c r="AD178">
+        <v>11</v>
+      </c>
+      <c r="AE178">
+        <v>1.3</v>
+      </c>
+      <c r="AF178">
+        <v>3.6</v>
+      </c>
+      <c r="AG178">
+        <v>1.89</v>
+      </c>
+      <c r="AH178">
+        <v>1.92</v>
+      </c>
+      <c r="AI178">
+        <v>1.75</v>
+      </c>
+      <c r="AJ178">
+        <v>2</v>
+      </c>
+      <c r="AK178">
+        <v>1.32</v>
+      </c>
+      <c r="AL178">
+        <v>1.29</v>
+      </c>
+      <c r="AM178">
+        <v>1.68</v>
+      </c>
+      <c r="AN178">
+        <v>1.6</v>
+      </c>
+      <c r="AO178">
+        <v>0.9</v>
+      </c>
+      <c r="AP178">
+        <v>1.73</v>
+      </c>
+      <c r="AQ178">
+        <v>0.82</v>
+      </c>
+      <c r="AR178">
+        <v>1.61</v>
+      </c>
+      <c r="AS178">
+        <v>1.26</v>
+      </c>
+      <c r="AT178">
+        <v>2.87</v>
+      </c>
+      <c r="AU178">
+        <v>4</v>
+      </c>
+      <c r="AV178">
+        <v>4</v>
+      </c>
+      <c r="AW178">
+        <v>7</v>
+      </c>
+      <c r="AX178">
+        <v>3</v>
+      </c>
+      <c r="AY178">
+        <v>14</v>
+      </c>
+      <c r="AZ178">
+        <v>8</v>
+      </c>
+      <c r="BA178">
+        <v>6</v>
+      </c>
+      <c r="BB178">
+        <v>2</v>
+      </c>
+      <c r="BC178">
+        <v>8</v>
+      </c>
+      <c r="BD178">
+        <v>1.49</v>
+      </c>
+      <c r="BE178">
+        <v>6.4</v>
+      </c>
+      <c r="BF178">
+        <v>2.9</v>
+      </c>
+      <c r="BG178">
+        <v>1.48</v>
+      </c>
+      <c r="BH178">
+        <v>2.45</v>
+      </c>
+      <c r="BI178">
+        <v>1.8</v>
+      </c>
+      <c r="BJ178">
+        <v>1.88</v>
+      </c>
+      <c r="BK178">
+        <v>2.28</v>
+      </c>
+      <c r="BL178">
+        <v>1.55</v>
+      </c>
+      <c r="BM178">
+        <v>2.95</v>
+      </c>
+      <c r="BN178">
+        <v>1.33</v>
+      </c>
+      <c r="BO178">
+        <v>3.95</v>
+      </c>
+      <c r="BP178">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7468532</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45690.55208333334</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>77</v>
+      </c>
+      <c r="H179" t="s">
+        <v>70</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>2</v>
+      </c>
+      <c r="O179" t="s">
+        <v>105</v>
+      </c>
+      <c r="P179" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q179">
+        <v>2.75</v>
+      </c>
+      <c r="R179">
+        <v>2.05</v>
+      </c>
+      <c r="S179">
+        <v>4.5</v>
+      </c>
+      <c r="T179">
+        <v>1.5</v>
+      </c>
+      <c r="U179">
+        <v>2.5</v>
+      </c>
+      <c r="V179">
+        <v>3.4</v>
+      </c>
+      <c r="W179">
+        <v>1.3</v>
+      </c>
+      <c r="X179">
+        <v>10</v>
+      </c>
+      <c r="Y179">
+        <v>1.06</v>
+      </c>
+      <c r="Z179">
+        <v>2.06</v>
+      </c>
+      <c r="AA179">
+        <v>3.51</v>
+      </c>
+      <c r="AB179">
+        <v>3.78</v>
+      </c>
+      <c r="AC179">
+        <v>1.08</v>
+      </c>
+      <c r="AD179">
+        <v>8.5</v>
+      </c>
+      <c r="AE179">
+        <v>1.42</v>
+      </c>
+      <c r="AF179">
+        <v>2.9</v>
+      </c>
+      <c r="AG179">
+        <v>2.1</v>
+      </c>
+      <c r="AH179">
+        <v>1.7</v>
+      </c>
+      <c r="AI179">
+        <v>1.95</v>
+      </c>
+      <c r="AJ179">
+        <v>1.8</v>
+      </c>
+      <c r="AK179">
+        <v>1.25</v>
+      </c>
+      <c r="AL179">
+        <v>1.32</v>
+      </c>
+      <c r="AM179">
+        <v>1.77</v>
+      </c>
+      <c r="AN179">
+        <v>1.11</v>
+      </c>
+      <c r="AO179">
+        <v>0.78</v>
+      </c>
+      <c r="AP179">
+        <v>1.1</v>
+      </c>
+      <c r="AQ179">
+        <v>0.8</v>
+      </c>
+      <c r="AR179">
+        <v>1.27</v>
+      </c>
+      <c r="AS179">
+        <v>0.9</v>
+      </c>
+      <c r="AT179">
+        <v>2.17</v>
+      </c>
+      <c r="AU179">
+        <v>4</v>
+      </c>
+      <c r="AV179">
+        <v>5</v>
+      </c>
+      <c r="AW179">
+        <v>12</v>
+      </c>
+      <c r="AX179">
+        <v>8</v>
+      </c>
+      <c r="AY179">
+        <v>16</v>
+      </c>
+      <c r="AZ179">
+        <v>14</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>2</v>
+      </c>
+      <c r="BC179">
+        <v>6</v>
+      </c>
+      <c r="BD179">
+        <v>1.58</v>
+      </c>
+      <c r="BE179">
+        <v>6.4</v>
+      </c>
+      <c r="BF179">
+        <v>2.65</v>
+      </c>
+      <c r="BG179">
+        <v>1.43</v>
+      </c>
+      <c r="BH179">
+        <v>2.55</v>
+      </c>
+      <c r="BI179">
+        <v>1.73</v>
+      </c>
+      <c r="BJ179">
+        <v>1.97</v>
+      </c>
+      <c r="BK179">
+        <v>2.18</v>
+      </c>
+      <c r="BL179">
+        <v>1.58</v>
+      </c>
+      <c r="BM179">
+        <v>2.8</v>
+      </c>
+      <c r="BN179">
+        <v>1.36</v>
+      </c>
+      <c r="BO179">
+        <v>3.8</v>
+      </c>
+      <c r="BP179">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7468531</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45690.55208333334</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>72</v>
+      </c>
+      <c r="H180" t="s">
+        <v>85</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>2</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>218</v>
+      </c>
+      <c r="P180" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q180">
+        <v>2.88</v>
+      </c>
+      <c r="R180">
+        <v>2.1</v>
+      </c>
+      <c r="S180">
+        <v>4</v>
+      </c>
+      <c r="T180">
+        <v>1.44</v>
+      </c>
+      <c r="U180">
+        <v>2.63</v>
+      </c>
+      <c r="V180">
+        <v>3.25</v>
+      </c>
+      <c r="W180">
+        <v>1.33</v>
+      </c>
+      <c r="X180">
+        <v>9</v>
+      </c>
+      <c r="Y180">
+        <v>1.07</v>
+      </c>
+      <c r="Z180">
+        <v>2.19</v>
+      </c>
+      <c r="AA180">
+        <v>3.45</v>
+      </c>
+      <c r="AB180">
+        <v>3.5</v>
+      </c>
+      <c r="AC180">
+        <v>1.06</v>
+      </c>
+      <c r="AD180">
+        <v>10</v>
+      </c>
+      <c r="AE180">
+        <v>1.33</v>
+      </c>
+      <c r="AF180">
+        <v>3.3</v>
+      </c>
+      <c r="AG180">
+        <v>2</v>
+      </c>
+      <c r="AH180">
+        <v>1.75</v>
+      </c>
+      <c r="AI180">
+        <v>1.8</v>
+      </c>
+      <c r="AJ180">
+        <v>1.95</v>
+      </c>
+      <c r="AK180">
+        <v>1.3</v>
+      </c>
+      <c r="AL180">
+        <v>1.31</v>
+      </c>
+      <c r="AM180">
+        <v>1.68</v>
+      </c>
+      <c r="AN180">
+        <v>1</v>
+      </c>
+      <c r="AO180">
+        <v>0.8</v>
+      </c>
+      <c r="AP180">
+        <v>0.91</v>
+      </c>
+      <c r="AQ180">
+        <v>1</v>
+      </c>
+      <c r="AR180">
+        <v>1.22</v>
+      </c>
+      <c r="AS180">
+        <v>1.12</v>
+      </c>
+      <c r="AT180">
+        <v>2.34</v>
+      </c>
+      <c r="AU180">
+        <v>3</v>
+      </c>
+      <c r="AV180">
+        <v>8</v>
+      </c>
+      <c r="AW180">
+        <v>13</v>
+      </c>
+      <c r="AX180">
+        <v>4</v>
+      </c>
+      <c r="AY180">
+        <v>20</v>
+      </c>
+      <c r="AZ180">
+        <v>14</v>
+      </c>
+      <c r="BA180">
+        <v>9</v>
+      </c>
+      <c r="BB180">
+        <v>3</v>
+      </c>
+      <c r="BC180">
+        <v>12</v>
+      </c>
+      <c r="BD180">
+        <v>1.73</v>
+      </c>
+      <c r="BE180">
+        <v>6.4</v>
+      </c>
+      <c r="BF180">
+        <v>2.33</v>
+      </c>
+      <c r="BG180">
+        <v>1.3</v>
+      </c>
+      <c r="BH180">
+        <v>3.15</v>
+      </c>
+      <c r="BI180">
+        <v>1.52</v>
+      </c>
+      <c r="BJ180">
+        <v>2.33</v>
+      </c>
+      <c r="BK180">
+        <v>1.86</v>
+      </c>
+      <c r="BL180">
+        <v>1.82</v>
+      </c>
+      <c r="BM180">
+        <v>2.35</v>
+      </c>
+      <c r="BN180">
+        <v>1.5</v>
+      </c>
+      <c r="BO180">
+        <v>3.05</v>
+      </c>
+      <c r="BP180">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7468527</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45690.69791666666</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>87</v>
+      </c>
+      <c r="H181" t="s">
+        <v>80</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>3</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>5</v>
+      </c>
+      <c r="O181" t="s">
+        <v>219</v>
+      </c>
+      <c r="P181" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q181">
+        <v>2.5</v>
+      </c>
+      <c r="R181">
+        <v>2.4</v>
+      </c>
+      <c r="S181">
+        <v>3.75</v>
+      </c>
+      <c r="T181">
+        <v>1.29</v>
+      </c>
+      <c r="U181">
+        <v>3.5</v>
+      </c>
+      <c r="V181">
+        <v>2.38</v>
+      </c>
+      <c r="W181">
+        <v>1.53</v>
+      </c>
+      <c r="X181">
+        <v>5.5</v>
+      </c>
+      <c r="Y181">
+        <v>1.14</v>
+      </c>
+      <c r="Z181">
+        <v>2.03</v>
+      </c>
+      <c r="AA181">
+        <v>4</v>
+      </c>
+      <c r="AB181">
+        <v>3.45</v>
+      </c>
+      <c r="AC181">
+        <v>1.02</v>
+      </c>
+      <c r="AD181">
+        <v>17</v>
+      </c>
+      <c r="AE181">
+        <v>1.18</v>
+      </c>
+      <c r="AF181">
+        <v>5</v>
+      </c>
+      <c r="AG181">
+        <v>1.56</v>
+      </c>
+      <c r="AH181">
+        <v>2.33</v>
+      </c>
+      <c r="AI181">
+        <v>1.53</v>
+      </c>
+      <c r="AJ181">
+        <v>2.38</v>
+      </c>
+      <c r="AK181">
+        <v>1.3</v>
+      </c>
+      <c r="AL181">
+        <v>1.26</v>
+      </c>
+      <c r="AM181">
+        <v>1.78</v>
+      </c>
+      <c r="AN181">
+        <v>1.44</v>
+      </c>
+      <c r="AO181">
+        <v>1.3</v>
+      </c>
+      <c r="AP181">
+        <v>1.6</v>
+      </c>
+      <c r="AQ181">
+        <v>1.18</v>
+      </c>
+      <c r="AR181">
+        <v>1.5</v>
+      </c>
+      <c r="AS181">
+        <v>1.29</v>
+      </c>
+      <c r="AT181">
+        <v>2.79</v>
+      </c>
+      <c r="AU181">
+        <v>12</v>
+      </c>
+      <c r="AV181">
+        <v>5</v>
+      </c>
+      <c r="AW181">
+        <v>8</v>
+      </c>
+      <c r="AX181">
+        <v>6</v>
+      </c>
+      <c r="AY181">
+        <v>20</v>
+      </c>
+      <c r="AZ181">
+        <v>13</v>
+      </c>
+      <c r="BA181">
+        <v>6</v>
+      </c>
+      <c r="BB181">
+        <v>2</v>
+      </c>
+      <c r="BC181">
+        <v>8</v>
+      </c>
+      <c r="BD181">
+        <v>1.79</v>
+      </c>
+      <c r="BE181">
+        <v>6.4</v>
+      </c>
+      <c r="BF181">
+        <v>2.23</v>
+      </c>
+      <c r="BG181">
+        <v>1.43</v>
+      </c>
+      <c r="BH181">
+        <v>2.6</v>
+      </c>
+      <c r="BI181">
+        <v>1.71</v>
+      </c>
+      <c r="BJ181">
+        <v>2</v>
+      </c>
+      <c r="BK181">
+        <v>2.14</v>
+      </c>
+      <c r="BL181">
+        <v>1.61</v>
+      </c>
+      <c r="BM181">
+        <v>2.75</v>
+      </c>
+      <c r="BN181">
+        <v>1.38</v>
+      </c>
+      <c r="BO181">
+        <v>3.65</v>
+      </c>
+      <c r="BP181">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -969,6 +969,9 @@
   <si>
     <t>['53', '72']</t>
   </si>
+  <si>
+    <t>['9', '90+6']</t>
+  </si>
 </sst>
 </file>
 
@@ -1329,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4344,7 +4347,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ15">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4753,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>0.4</v>
@@ -7846,7 +7849,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ32">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
         <v>2.81</v>
@@ -8461,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -10936,7 +10939,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ47">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR47">
         <v>1.61</v>
@@ -12169,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
         <v>0.18</v>
@@ -15877,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>1.18</v>
@@ -16910,7 +16913,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ76">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR76">
         <v>1.01</v>
@@ -19997,7 +20000,7 @@
         <v>2.4</v>
       </c>
       <c r="AP91">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
         <v>2.4</v>
@@ -21442,7 +21445,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ98">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR98">
         <v>1.3</v>
@@ -22060,7 +22063,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ101">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -23499,7 +23502,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
         <v>0.8</v>
@@ -25768,7 +25771,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ119">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR119">
         <v>1.36</v>
@@ -27207,7 +27210,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>0.11</v>
@@ -30918,7 +30921,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ144">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR144">
         <v>1.26</v>
@@ -31327,7 +31330,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
         <v>1.56</v>
@@ -33802,7 +33805,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ158">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR158">
         <v>1.48</v>
@@ -35862,7 +35865,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ168">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR168">
         <v>1.13</v>
@@ -36065,7 +36068,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ169">
         <v>1.18</v>
@@ -38615,6 +38618,212 @@
         <v>3.65</v>
       </c>
       <c r="BP181">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7468537</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45695.625</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>85</v>
+      </c>
+      <c r="H182" t="s">
+        <v>71</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>2</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182" t="s">
+        <v>90</v>
+      </c>
+      <c r="P182" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q182">
+        <v>3.3</v>
+      </c>
+      <c r="R182">
+        <v>2</v>
+      </c>
+      <c r="S182">
+        <v>3.6</v>
+      </c>
+      <c r="T182">
+        <v>1.5</v>
+      </c>
+      <c r="U182">
+        <v>2.65</v>
+      </c>
+      <c r="V182">
+        <v>3.25</v>
+      </c>
+      <c r="W182">
+        <v>1.33</v>
+      </c>
+      <c r="X182">
+        <v>8.5</v>
+      </c>
+      <c r="Y182">
+        <v>1.06</v>
+      </c>
+      <c r="Z182">
+        <v>2.5</v>
+      </c>
+      <c r="AA182">
+        <v>3.1</v>
+      </c>
+      <c r="AB182">
+        <v>2.9</v>
+      </c>
+      <c r="AC182">
+        <v>1.08</v>
+      </c>
+      <c r="AD182">
+        <v>8.5</v>
+      </c>
+      <c r="AE182">
+        <v>1.4</v>
+      </c>
+      <c r="AF182">
+        <v>3</v>
+      </c>
+      <c r="AG182">
+        <v>2.2</v>
+      </c>
+      <c r="AH182">
+        <v>1.61</v>
+      </c>
+      <c r="AI182">
+        <v>1.9</v>
+      </c>
+      <c r="AJ182">
+        <v>1.9</v>
+      </c>
+      <c r="AK182">
+        <v>1.42</v>
+      </c>
+      <c r="AL182">
+        <v>1.3</v>
+      </c>
+      <c r="AM182">
+        <v>1.55</v>
+      </c>
+      <c r="AN182">
+        <v>1.11</v>
+      </c>
+      <c r="AO182">
+        <v>0.9</v>
+      </c>
+      <c r="AP182">
+        <v>1</v>
+      </c>
+      <c r="AQ182">
+        <v>1.09</v>
+      </c>
+      <c r="AR182">
+        <v>1.39</v>
+      </c>
+      <c r="AS182">
+        <v>1.39</v>
+      </c>
+      <c r="AT182">
+        <v>2.78</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>7</v>
+      </c>
+      <c r="AW182">
+        <v>11</v>
+      </c>
+      <c r="AX182">
+        <v>5</v>
+      </c>
+      <c r="AY182">
+        <v>18</v>
+      </c>
+      <c r="AZ182">
+        <v>13</v>
+      </c>
+      <c r="BA182">
+        <v>12</v>
+      </c>
+      <c r="BB182">
+        <v>4</v>
+      </c>
+      <c r="BC182">
+        <v>16</v>
+      </c>
+      <c r="BD182">
+        <v>1.81</v>
+      </c>
+      <c r="BE182">
+        <v>6.25</v>
+      </c>
+      <c r="BF182">
+        <v>2.23</v>
+      </c>
+      <c r="BG182">
+        <v>1.41</v>
+      </c>
+      <c r="BH182">
+        <v>2.65</v>
+      </c>
+      <c r="BI182">
+        <v>1.68</v>
+      </c>
+      <c r="BJ182">
+        <v>2.02</v>
+      </c>
+      <c r="BK182">
+        <v>2.1</v>
+      </c>
+      <c r="BL182">
+        <v>1.64</v>
+      </c>
+      <c r="BM182">
+        <v>2.7</v>
+      </c>
+      <c r="BN182">
+        <v>1.38</v>
+      </c>
+      <c r="BO182">
+        <v>3.65</v>
+      </c>
+      <c r="BP182">
         <v>1.23</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,9 @@
     <t>['61', '64', '85']</t>
   </si>
   <si>
+    <t>['6', '54', '57', '90']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1332,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1588,7 +1591,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1794,7 +1797,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2000,7 +2003,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2412,7 +2415,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2618,7 +2621,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3520,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ11">
         <v>0.33</v>
@@ -3648,7 +3651,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3729,7 +3732,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ12">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4060,7 +4063,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4472,7 +4475,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5090,7 +5093,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5296,7 +5299,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5708,7 +5711,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5914,7 +5917,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6120,7 +6123,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6326,7 +6329,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6738,7 +6741,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6944,7 +6947,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7562,7 +7565,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7643,7 +7646,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ31">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -7846,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ32">
         <v>1.09</v>
@@ -8180,7 +8183,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8386,7 +8389,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9210,7 +9213,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9416,7 +9419,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10240,7 +10243,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10446,7 +10449,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10652,7 +10655,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11064,7 +11067,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11142,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ48">
         <v>0.11</v>
@@ -11476,7 +11479,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11682,7 +11685,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11888,7 +11891,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12094,7 +12097,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12300,7 +12303,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12918,7 +12921,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13330,7 +13333,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13411,7 +13414,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ59">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -13948,7 +13951,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14154,7 +14157,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14360,7 +14363,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14978,7 +14981,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15184,7 +15187,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15262,7 +15265,7 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ68">
         <v>0.82</v>
@@ -15390,7 +15393,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15596,7 +15599,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15802,7 +15805,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16008,7 +16011,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16214,7 +16217,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16626,7 +16629,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16832,7 +16835,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17038,7 +17041,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17244,7 +17247,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17450,7 +17453,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17656,7 +17659,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17943,7 +17946,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ81">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18068,7 +18071,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18764,7 +18767,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ85">
         <v>1.9</v>
@@ -18892,7 +18895,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19922,7 +19925,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20128,7 +20131,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20334,7 +20337,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20415,7 +20418,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20540,7 +20543,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20746,7 +20749,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20952,7 +20955,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21158,7 +21161,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21364,7 +21367,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21570,7 +21573,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21982,7 +21985,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22266,7 +22269,7 @@
         <v>1.4</v>
       </c>
       <c r="AP102">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ102">
         <v>1.22</v>
@@ -22394,7 +22397,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23424,7 +23427,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23630,7 +23633,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23836,7 +23839,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24532,7 +24535,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24660,7 +24663,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24866,7 +24869,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25278,7 +25281,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25484,7 +25487,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25565,7 +25568,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ118">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -26308,7 +26311,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26514,7 +26517,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27338,7 +27341,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27750,7 +27753,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27956,7 +27959,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28243,7 +28246,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ131">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -28368,7 +28371,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28574,7 +28577,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29270,7 +29273,7 @@
         <v>1.71</v>
       </c>
       <c r="AP136">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ136">
         <v>1.18</v>
@@ -29398,7 +29401,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29604,7 +29607,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29810,7 +29813,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30016,7 +30019,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -31252,7 +31255,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31333,7 +31336,7 @@
         <v>1</v>
       </c>
       <c r="AQ146">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -31664,7 +31667,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31870,7 +31873,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32076,7 +32079,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32282,7 +32285,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32488,7 +32491,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32694,7 +32697,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32978,7 +32981,7 @@
         <v>0.13</v>
       </c>
       <c r="AP154">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ154">
         <v>0.18</v>
@@ -33106,7 +33109,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33187,7 +33190,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ155">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR155">
         <v>1.44</v>
@@ -33518,7 +33521,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33724,7 +33727,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34754,7 +34757,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35166,7 +35169,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35578,7 +35581,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35656,7 +35659,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ167">
         <v>1.33</v>
@@ -35784,7 +35787,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35990,7 +35993,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36196,7 +36199,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36814,7 +36817,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37020,7 +37023,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37226,7 +37229,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37638,7 +37641,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38256,7 +38259,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38462,7 +38465,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38668,7 +38671,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38825,6 +38828,212 @@
       </c>
       <c r="BP182">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7468541</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45695.71180555555</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>79</v>
+      </c>
+      <c r="H183" t="s">
+        <v>73</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>2</v>
+      </c>
+      <c r="L183">
+        <v>4</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>5</v>
+      </c>
+      <c r="O183" t="s">
+        <v>220</v>
+      </c>
+      <c r="P183" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q183">
+        <v>1.91</v>
+      </c>
+      <c r="R183">
+        <v>2.75</v>
+      </c>
+      <c r="S183">
+        <v>5.5</v>
+      </c>
+      <c r="T183">
+        <v>1.22</v>
+      </c>
+      <c r="U183">
+        <v>4</v>
+      </c>
+      <c r="V183">
+        <v>2</v>
+      </c>
+      <c r="W183">
+        <v>1.73</v>
+      </c>
+      <c r="X183">
+        <v>4.33</v>
+      </c>
+      <c r="Y183">
+        <v>1.2</v>
+      </c>
+      <c r="Z183">
+        <v>1.5</v>
+      </c>
+      <c r="AA183">
+        <v>5.1</v>
+      </c>
+      <c r="AB183">
+        <v>5.8</v>
+      </c>
+      <c r="AC183">
+        <v>1.01</v>
+      </c>
+      <c r="AD183">
+        <v>15</v>
+      </c>
+      <c r="AE183">
+        <v>1.11</v>
+      </c>
+      <c r="AF183">
+        <v>6.5</v>
+      </c>
+      <c r="AG183">
+        <v>1.4</v>
+      </c>
+      <c r="AH183">
+        <v>2.9</v>
+      </c>
+      <c r="AI183">
+        <v>1.53</v>
+      </c>
+      <c r="AJ183">
+        <v>2.38</v>
+      </c>
+      <c r="AK183">
+        <v>1.14</v>
+      </c>
+      <c r="AL183">
+        <v>1.17</v>
+      </c>
+      <c r="AM183">
+        <v>2.6</v>
+      </c>
+      <c r="AN183">
+        <v>2.6</v>
+      </c>
+      <c r="AO183">
+        <v>1.56</v>
+      </c>
+      <c r="AP183">
+        <v>2.64</v>
+      </c>
+      <c r="AQ183">
+        <v>1.4</v>
+      </c>
+      <c r="AR183">
+        <v>2.35</v>
+      </c>
+      <c r="AS183">
+        <v>1.67</v>
+      </c>
+      <c r="AT183">
+        <v>4.02</v>
+      </c>
+      <c r="AU183">
+        <v>8</v>
+      </c>
+      <c r="AV183">
+        <v>4</v>
+      </c>
+      <c r="AW183">
+        <v>9</v>
+      </c>
+      <c r="AX183">
+        <v>6</v>
+      </c>
+      <c r="AY183">
+        <v>20</v>
+      </c>
+      <c r="AZ183">
+        <v>12</v>
+      </c>
+      <c r="BA183">
+        <v>1</v>
+      </c>
+      <c r="BB183">
+        <v>1</v>
+      </c>
+      <c r="BC183">
+        <v>2</v>
+      </c>
+      <c r="BD183">
+        <v>1.26</v>
+      </c>
+      <c r="BE183">
+        <v>7.5</v>
+      </c>
+      <c r="BF183">
+        <v>4.1</v>
+      </c>
+      <c r="BG183">
+        <v>1.29</v>
+      </c>
+      <c r="BH183">
+        <v>3.2</v>
+      </c>
+      <c r="BI183">
+        <v>1.49</v>
+      </c>
+      <c r="BJ183">
+        <v>2.4</v>
+      </c>
+      <c r="BK183">
+        <v>1.8</v>
+      </c>
+      <c r="BL183">
+        <v>1.88</v>
+      </c>
+      <c r="BM183">
+        <v>2.23</v>
+      </c>
+      <c r="BN183">
+        <v>1.56</v>
+      </c>
+      <c r="BO183">
+        <v>2.85</v>
+      </c>
+      <c r="BP183">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,12 @@
     <t>['6', '54', '57', '90']</t>
   </si>
   <si>
+    <t>['10', '64']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -974,6 +980,12 @@
   </si>
   <si>
     <t>['9', '90+6']</t>
+  </si>
+  <si>
+    <t>['38', '56']</t>
+  </si>
+  <si>
+    <t>['15', '84']</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1591,7 +1603,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1797,7 +1809,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2003,7 +2015,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2415,7 +2427,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2621,7 +2633,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3114,7 +3126,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3651,7 +3663,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3935,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ13">
         <v>1.2</v>
@@ -4063,7 +4075,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4141,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4475,7 +4487,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4556,7 +4568,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4965,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18">
         <v>1.22</v>
@@ -5093,7 +5105,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5299,7 +5311,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5711,7 +5723,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5917,7 +5929,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6123,7 +6135,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6204,7 +6216,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ24">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -6329,7 +6341,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6741,7 +6753,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6822,7 +6834,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ27">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR27">
         <v>0.32</v>
@@ -6947,7 +6959,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7025,7 +7037,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ28">
         <v>2.4</v>
@@ -7231,7 +7243,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
         <v>1.4</v>
@@ -7565,7 +7577,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8183,7 +8195,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8389,7 +8401,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8676,7 +8688,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -9085,7 +9097,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ38">
         <v>0.18</v>
@@ -9213,7 +9225,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9291,7 +9303,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ39">
         <v>0.82</v>
@@ -9419,7 +9431,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9500,7 +9512,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9912,7 +9924,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10243,7 +10255,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10449,7 +10461,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10655,7 +10667,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11067,7 +11079,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11148,7 +11160,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ48">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR48">
         <v>2.56</v>
@@ -11479,7 +11491,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11685,7 +11697,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11891,7 +11903,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12097,7 +12109,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12303,7 +12315,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12921,7 +12933,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -12999,7 +13011,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>0.4</v>
@@ -13205,7 +13217,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ58">
         <v>1.22</v>
@@ -13333,7 +13345,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13826,7 +13838,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -13951,7 +13963,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14032,7 +14044,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14157,7 +14169,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14363,7 +14375,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14441,7 +14453,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ64">
         <v>2.4</v>
@@ -14856,7 +14868,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ66">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -14981,7 +14993,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15059,10 +15071,10 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -15187,7 +15199,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15393,7 +15405,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15599,7 +15611,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15805,7 +15817,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16011,7 +16023,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16217,7 +16229,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16504,7 +16516,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ74">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16629,7 +16641,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16835,7 +16847,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17041,7 +17053,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17247,7 +17259,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17453,7 +17465,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17659,7 +17671,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17943,7 +17955,7 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ81">
         <v>1.4</v>
@@ -18071,7 +18083,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18561,7 +18573,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ84">
         <v>1.18</v>
@@ -18770,7 +18782,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ85">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -18895,7 +18907,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19179,7 +19191,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87">
         <v>0.82</v>
@@ -19594,7 +19606,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ89">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR89">
         <v>1.39</v>
@@ -19925,7 +19937,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20131,7 +20143,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20337,7 +20349,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20543,7 +20555,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20749,7 +20761,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20955,7 +20967,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21033,7 +21045,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ96">
         <v>1.4</v>
@@ -21161,7 +21173,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21367,7 +21379,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21573,7 +21585,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21985,7 +21997,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22397,7 +22409,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22681,7 +22693,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ104">
         <v>0.33</v>
@@ -23093,10 +23105,10 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ106">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR106">
         <v>1.43</v>
@@ -23427,7 +23439,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23508,7 +23520,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23633,7 +23645,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23711,7 +23723,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ109">
         <v>0.82</v>
@@ -23839,7 +23851,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23920,7 +23932,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ110">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24663,7 +24675,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24869,7 +24881,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25281,7 +25293,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25487,7 +25499,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25771,7 +25783,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ119">
         <v>1.09</v>
@@ -26311,7 +26323,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26389,10 +26401,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ122">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26517,7 +26529,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27216,7 +27228,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR126">
         <v>1.51</v>
@@ -27341,7 +27353,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27419,7 +27431,7 @@
         <v>2.57</v>
       </c>
       <c r="AP127">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ127">
         <v>2.4</v>
@@ -27753,7 +27765,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27959,7 +27971,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28040,7 +28052,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ130">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28371,7 +28383,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28577,7 +28589,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29401,7 +29413,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29607,7 +29619,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29685,10 +29697,10 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ138">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR138">
         <v>1.63</v>
@@ -29813,7 +29825,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29891,7 +29903,7 @@
         <v>1.57</v>
       </c>
       <c r="AP139">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ139">
         <v>1.33</v>
@@ -30019,7 +30031,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30097,7 +30109,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -31130,7 +31142,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ145">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31255,7 +31267,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31667,7 +31679,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31873,7 +31885,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32079,7 +32091,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32285,7 +32297,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32366,7 +32378,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ151">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR151">
         <v>1.15</v>
@@ -32491,7 +32503,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32697,7 +32709,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33109,7 +33121,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33393,7 +33405,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ156">
         <v>1.18</v>
@@ -33521,7 +33533,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33727,7 +33739,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34217,7 +34229,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ160">
         <v>1</v>
@@ -34632,7 +34644,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ162">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -34757,7 +34769,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35169,7 +35181,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35250,7 +35262,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ165">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR165">
         <v>1.5</v>
@@ -35581,7 +35593,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35787,7 +35799,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35993,7 +36005,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36199,7 +36211,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36689,7 +36701,7 @@
         <v>2.67</v>
       </c>
       <c r="AP172">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ172">
         <v>2.4</v>
@@ -36817,7 +36829,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -36898,7 +36910,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ173">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37023,7 +37035,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37229,7 +37241,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37513,7 +37525,7 @@
         <v>0.2</v>
       </c>
       <c r="AP176">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ176">
         <v>0.18</v>
@@ -37641,7 +37653,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38134,7 +38146,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ179">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR179">
         <v>1.27</v>
@@ -38259,7 +38271,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38465,7 +38477,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38671,7 +38683,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39034,6 +39046,624 @@
       </c>
       <c r="BP183">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7468543</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45696.54166666666</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>86</v>
+      </c>
+      <c r="H184" t="s">
+        <v>83</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>2</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>2</v>
+      </c>
+      <c r="O184" t="s">
+        <v>221</v>
+      </c>
+      <c r="P184" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q184">
+        <v>3</v>
+      </c>
+      <c r="R184">
+        <v>2.2</v>
+      </c>
+      <c r="S184">
+        <v>3.5</v>
+      </c>
+      <c r="T184">
+        <v>1.36</v>
+      </c>
+      <c r="U184">
+        <v>3</v>
+      </c>
+      <c r="V184">
+        <v>2.75</v>
+      </c>
+      <c r="W184">
+        <v>1.4</v>
+      </c>
+      <c r="X184">
+        <v>7</v>
+      </c>
+      <c r="Y184">
+        <v>1.1</v>
+      </c>
+      <c r="Z184">
+        <v>2.4</v>
+      </c>
+      <c r="AA184">
+        <v>3.47</v>
+      </c>
+      <c r="AB184">
+        <v>3.03</v>
+      </c>
+      <c r="AC184">
+        <v>1.05</v>
+      </c>
+      <c r="AD184">
+        <v>12</v>
+      </c>
+      <c r="AE184">
+        <v>1.28</v>
+      </c>
+      <c r="AF184">
+        <v>3.75</v>
+      </c>
+      <c r="AG184">
+        <v>1.81</v>
+      </c>
+      <c r="AH184">
+        <v>2.01</v>
+      </c>
+      <c r="AI184">
+        <v>1.67</v>
+      </c>
+      <c r="AJ184">
+        <v>2.1</v>
+      </c>
+      <c r="AK184">
+        <v>1.4</v>
+      </c>
+      <c r="AL184">
+        <v>1.28</v>
+      </c>
+      <c r="AM184">
+        <v>1.6</v>
+      </c>
+      <c r="AN184">
+        <v>2.33</v>
+      </c>
+      <c r="AO184">
+        <v>1.9</v>
+      </c>
+      <c r="AP184">
+        <v>2.4</v>
+      </c>
+      <c r="AQ184">
+        <v>1.73</v>
+      </c>
+      <c r="AR184">
+        <v>1.58</v>
+      </c>
+      <c r="AS184">
+        <v>1.49</v>
+      </c>
+      <c r="AT184">
+        <v>3.07</v>
+      </c>
+      <c r="AU184">
+        <v>10</v>
+      </c>
+      <c r="AV184">
+        <v>4</v>
+      </c>
+      <c r="AW184">
+        <v>7</v>
+      </c>
+      <c r="AX184">
+        <v>8</v>
+      </c>
+      <c r="AY184">
+        <v>20</v>
+      </c>
+      <c r="AZ184">
+        <v>15</v>
+      </c>
+      <c r="BA184">
+        <v>7</v>
+      </c>
+      <c r="BB184">
+        <v>3</v>
+      </c>
+      <c r="BC184">
+        <v>10</v>
+      </c>
+      <c r="BD184">
+        <v>1.95</v>
+      </c>
+      <c r="BE184">
+        <v>6.4</v>
+      </c>
+      <c r="BF184">
+        <v>2.05</v>
+      </c>
+      <c r="BG184">
+        <v>1.29</v>
+      </c>
+      <c r="BH184">
+        <v>3.15</v>
+      </c>
+      <c r="BI184">
+        <v>1.5</v>
+      </c>
+      <c r="BJ184">
+        <v>2.38</v>
+      </c>
+      <c r="BK184">
+        <v>1.82</v>
+      </c>
+      <c r="BL184">
+        <v>1.86</v>
+      </c>
+      <c r="BM184">
+        <v>2.3</v>
+      </c>
+      <c r="BN184">
+        <v>1.54</v>
+      </c>
+      <c r="BO184">
+        <v>2.9</v>
+      </c>
+      <c r="BP184">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7468539</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45696.625</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>81</v>
+      </c>
+      <c r="H185" t="s">
+        <v>70</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>2</v>
+      </c>
+      <c r="N185">
+        <v>3</v>
+      </c>
+      <c r="O185" t="s">
+        <v>222</v>
+      </c>
+      <c r="P185" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q185">
+        <v>1.83</v>
+      </c>
+      <c r="R185">
+        <v>2.38</v>
+      </c>
+      <c r="S185">
+        <v>8.5</v>
+      </c>
+      <c r="T185">
+        <v>1.36</v>
+      </c>
+      <c r="U185">
+        <v>3</v>
+      </c>
+      <c r="V185">
+        <v>2.75</v>
+      </c>
+      <c r="W185">
+        <v>1.4</v>
+      </c>
+      <c r="X185">
+        <v>7</v>
+      </c>
+      <c r="Y185">
+        <v>1.1</v>
+      </c>
+      <c r="Z185">
+        <v>1.4</v>
+      </c>
+      <c r="AA185">
+        <v>5</v>
+      </c>
+      <c r="AB185">
+        <v>8.4</v>
+      </c>
+      <c r="AC185">
+        <v>1.04</v>
+      </c>
+      <c r="AD185">
+        <v>13</v>
+      </c>
+      <c r="AE185">
+        <v>1.28</v>
+      </c>
+      <c r="AF185">
+        <v>3.75</v>
+      </c>
+      <c r="AG185">
+        <v>1.87</v>
+      </c>
+      <c r="AH185">
+        <v>1.94</v>
+      </c>
+      <c r="AI185">
+        <v>2.2</v>
+      </c>
+      <c r="AJ185">
+        <v>1.62</v>
+      </c>
+      <c r="AK185">
+        <v>1.04</v>
+      </c>
+      <c r="AL185">
+        <v>1.14</v>
+      </c>
+      <c r="AM185">
+        <v>3.3</v>
+      </c>
+      <c r="AN185">
+        <v>2.1</v>
+      </c>
+      <c r="AO185">
+        <v>0.8</v>
+      </c>
+      <c r="AP185">
+        <v>1.91</v>
+      </c>
+      <c r="AQ185">
+        <v>1</v>
+      </c>
+      <c r="AR185">
+        <v>1.58</v>
+      </c>
+      <c r="AS185">
+        <v>0.96</v>
+      </c>
+      <c r="AT185">
+        <v>2.54</v>
+      </c>
+      <c r="AU185">
+        <v>7</v>
+      </c>
+      <c r="AV185">
+        <v>9</v>
+      </c>
+      <c r="AW185">
+        <v>10</v>
+      </c>
+      <c r="AX185">
+        <v>5</v>
+      </c>
+      <c r="AY185">
+        <v>17</v>
+      </c>
+      <c r="AZ185">
+        <v>14</v>
+      </c>
+      <c r="BA185">
+        <v>8</v>
+      </c>
+      <c r="BB185">
+        <v>10</v>
+      </c>
+      <c r="BC185">
+        <v>18</v>
+      </c>
+      <c r="BD185">
+        <v>1.24</v>
+      </c>
+      <c r="BE185">
+        <v>7.5</v>
+      </c>
+      <c r="BF185">
+        <v>4.4</v>
+      </c>
+      <c r="BG185">
+        <v>1.38</v>
+      </c>
+      <c r="BH185">
+        <v>2.7</v>
+      </c>
+      <c r="BI185">
+        <v>1.66</v>
+      </c>
+      <c r="BJ185">
+        <v>2.07</v>
+      </c>
+      <c r="BK185">
+        <v>2.04</v>
+      </c>
+      <c r="BL185">
+        <v>1.68</v>
+      </c>
+      <c r="BM185">
+        <v>2.55</v>
+      </c>
+      <c r="BN185">
+        <v>1.43</v>
+      </c>
+      <c r="BO185">
+        <v>3.4</v>
+      </c>
+      <c r="BP185">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7468540</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45696.71180555555</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>82</v>
+      </c>
+      <c r="H186" t="s">
+        <v>78</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>90</v>
+      </c>
+      <c r="P186" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q186">
+        <v>3.75</v>
+      </c>
+      <c r="R186">
+        <v>2.1</v>
+      </c>
+      <c r="S186">
+        <v>2.88</v>
+      </c>
+      <c r="T186">
+        <v>1.4</v>
+      </c>
+      <c r="U186">
+        <v>2.75</v>
+      </c>
+      <c r="V186">
+        <v>3</v>
+      </c>
+      <c r="W186">
+        <v>1.36</v>
+      </c>
+      <c r="X186">
+        <v>8</v>
+      </c>
+      <c r="Y186">
+        <v>1.08</v>
+      </c>
+      <c r="Z186">
+        <v>3.25</v>
+      </c>
+      <c r="AA186">
+        <v>3.47</v>
+      </c>
+      <c r="AB186">
+        <v>2.29</v>
+      </c>
+      <c r="AC186">
+        <v>1.06</v>
+      </c>
+      <c r="AD186">
+        <v>10</v>
+      </c>
+      <c r="AE186">
+        <v>1.33</v>
+      </c>
+      <c r="AF186">
+        <v>3.4</v>
+      </c>
+      <c r="AG186">
+        <v>1.89</v>
+      </c>
+      <c r="AH186">
+        <v>1.92</v>
+      </c>
+      <c r="AI186">
+        <v>1.75</v>
+      </c>
+      <c r="AJ186">
+        <v>2</v>
+      </c>
+      <c r="AK186">
+        <v>1.68</v>
+      </c>
+      <c r="AL186">
+        <v>1.28</v>
+      </c>
+      <c r="AM186">
+        <v>1.35</v>
+      </c>
+      <c r="AN186">
+        <v>1.78</v>
+      </c>
+      <c r="AO186">
+        <v>0.11</v>
+      </c>
+      <c r="AP186">
+        <v>1.6</v>
+      </c>
+      <c r="AQ186">
+        <v>0.4</v>
+      </c>
+      <c r="AR186">
+        <v>1.27</v>
+      </c>
+      <c r="AS186">
+        <v>1.2</v>
+      </c>
+      <c r="AT186">
+        <v>2.47</v>
+      </c>
+      <c r="AU186">
+        <v>4</v>
+      </c>
+      <c r="AV186">
+        <v>8</v>
+      </c>
+      <c r="AW186">
+        <v>6</v>
+      </c>
+      <c r="AX186">
+        <v>11</v>
+      </c>
+      <c r="AY186">
+        <v>12</v>
+      </c>
+      <c r="AZ186">
+        <v>21</v>
+      </c>
+      <c r="BA186">
+        <v>2</v>
+      </c>
+      <c r="BB186">
+        <v>4</v>
+      </c>
+      <c r="BC186">
+        <v>6</v>
+      </c>
+      <c r="BD186">
+        <v>2.5</v>
+      </c>
+      <c r="BE186">
+        <v>6.4</v>
+      </c>
+      <c r="BF186">
+        <v>1.65</v>
+      </c>
+      <c r="BG186">
+        <v>1.41</v>
+      </c>
+      <c r="BH186">
+        <v>2.65</v>
+      </c>
+      <c r="BI186">
+        <v>1.68</v>
+      </c>
+      <c r="BJ186">
+        <v>2.04</v>
+      </c>
+      <c r="BK186">
+        <v>2.08</v>
+      </c>
+      <c r="BL186">
+        <v>1.65</v>
+      </c>
+      <c r="BM186">
+        <v>2.65</v>
+      </c>
+      <c r="BN186">
+        <v>1.4</v>
+      </c>
+      <c r="BO186">
+        <v>3.55</v>
+      </c>
+      <c r="BP186">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,15 @@
     <t>['90+7']</t>
   </si>
   <si>
+    <t>['36', '68', '79', '90+3']</t>
+  </si>
+  <si>
+    <t>['62', '73']</t>
+  </si>
+  <si>
+    <t>['45+2', '69']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -986,6 +995,12 @@
   </si>
   <si>
     <t>['15', '84']</t>
+  </si>
+  <si>
+    <t>['68', '89']</t>
+  </si>
+  <si>
+    <t>['69', '74']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1618,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1809,7 +1824,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1890,7 +1905,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ3">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2015,7 +2030,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2427,7 +2442,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2505,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>1.18</v>
@@ -2633,7 +2648,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3123,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>1.73</v>
@@ -3538,7 +3553,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ11">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3663,7 +3678,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3741,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -4075,7 +4090,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4487,7 +4502,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4565,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16">
         <v>0.4</v>
@@ -4980,7 +4995,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5105,7 +5120,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5186,7 +5201,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5311,7 +5326,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5389,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>0.82</v>
@@ -5723,7 +5738,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5929,7 +5944,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6010,7 +6025,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ23">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR23">
         <v>1.52</v>
@@ -6135,7 +6150,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6341,7 +6356,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6419,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>1.18</v>
@@ -6753,7 +6768,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6959,7 +6974,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7577,7 +7592,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7655,7 +7670,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ31">
         <v>1.4</v>
@@ -8070,7 +8085,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ33">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR33">
         <v>2.21</v>
@@ -8195,7 +8210,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8273,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ34">
         <v>1.2</v>
@@ -8401,7 +8416,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8482,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.39</v>
@@ -9225,7 +9240,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9431,7 +9446,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10130,7 +10145,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10255,7 +10270,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10333,7 +10348,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10461,7 +10476,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10667,7 +10682,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10745,10 +10760,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR46">
         <v>1.4</v>
@@ -10951,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ47">
         <v>1.09</v>
@@ -11079,7 +11094,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11491,7 +11506,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11697,7 +11712,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11778,7 +11793,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ51">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11903,7 +11918,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12109,7 +12124,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12315,7 +12330,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12393,10 +12408,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR54">
         <v>1.25</v>
@@ -12599,10 +12614,10 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ55">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR55">
         <v>1.26</v>
@@ -12933,7 +12948,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13220,7 +13235,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13345,7 +13360,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13629,7 +13644,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13963,7 +13978,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14041,7 +14056,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
         <v>1.73</v>
@@ -14169,7 +14184,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14250,7 +14265,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ63">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR63">
         <v>0.8100000000000001</v>
@@ -14375,7 +14390,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14993,7 +15008,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15199,7 +15214,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15405,7 +15420,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15611,7 +15626,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15817,7 +15832,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16023,7 +16038,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16101,10 +16116,10 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16229,7 +16244,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16310,7 +16325,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16641,7 +16656,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16719,7 +16734,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
         <v>0.18</v>
@@ -16847,7 +16862,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17053,7 +17068,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17259,7 +17274,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17337,7 +17352,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.4</v>
@@ -17465,7 +17480,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17546,7 +17561,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -17671,7 +17686,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17749,7 +17764,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -18083,7 +18098,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18907,7 +18922,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19400,7 +19415,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR88">
         <v>1.33</v>
@@ -19603,7 +19618,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ89">
         <v>0.4</v>
@@ -19812,7 +19827,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ90">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR90">
         <v>1.17</v>
@@ -19937,7 +19952,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20018,7 +20033,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -20143,7 +20158,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20349,7 +20364,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20427,7 +20442,7 @@
         <v>2.25</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ93">
         <v>1.4</v>
@@ -20555,7 +20570,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20761,7 +20776,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20839,7 +20854,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
         <v>2.4</v>
@@ -20967,7 +20982,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21173,7 +21188,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21254,7 +21269,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21379,7 +21394,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21585,7 +21600,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21666,7 +21681,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR99">
         <v>1.18</v>
@@ -21869,7 +21884,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.18</v>
@@ -21997,7 +22012,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22284,7 +22299,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ102">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22409,7 +22424,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22490,7 +22505,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ103">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR103">
         <v>1.68</v>
@@ -22696,7 +22711,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23311,7 +23326,7 @@
         <v>1.2</v>
       </c>
       <c r="AP107">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107">
         <v>1.2</v>
@@ -23439,7 +23454,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23645,7 +23660,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23851,7 +23866,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24675,7 +24690,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24881,7 +24896,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25293,7 +25308,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25371,7 +25386,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.18</v>
@@ -25499,7 +25514,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25989,7 +26004,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ120">
         <v>2.4</v>
@@ -26198,7 +26213,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ121">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26323,7 +26338,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26529,7 +26544,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26607,7 +26622,7 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ123">
         <v>1.18</v>
@@ -26816,7 +26831,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ124">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR124">
         <v>1.73</v>
@@ -27019,10 +27034,10 @@
         <v>1.67</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27353,7 +27368,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27434,7 +27449,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ127">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR127">
         <v>1.3</v>
@@ -27765,7 +27780,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27971,7 +27986,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28049,7 +28064,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ130">
         <v>1.73</v>
@@ -28383,7 +28398,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28589,7 +28604,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29413,7 +29428,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29619,7 +29634,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29825,7 +29840,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29906,7 +29921,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ139">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR139">
         <v>1.2</v>
@@ -30031,7 +30046,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30315,10 +30330,10 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -30524,7 +30539,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ142">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -30727,7 +30742,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ143">
         <v>0.4</v>
@@ -30933,7 +30948,7 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
         <v>1.09</v>
@@ -31267,7 +31282,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31551,7 +31566,7 @@
         <v>1.63</v>
       </c>
       <c r="AP147">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ147">
         <v>1.4</v>
@@ -31679,7 +31694,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31885,7 +31900,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32091,7 +32106,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32172,7 +32187,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ150">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR150">
         <v>1.57</v>
@@ -32297,7 +32312,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32503,7 +32518,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32709,7 +32724,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33121,7 +33136,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33533,7 +33548,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33739,7 +33754,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34023,10 +34038,10 @@
         <v>1.25</v>
       </c>
       <c r="AP159">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34435,7 +34450,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ161">
         <v>0.4</v>
@@ -34769,7 +34784,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35053,7 +35068,7 @@
         <v>0.11</v>
       </c>
       <c r="AP164">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ164">
         <v>0.18</v>
@@ -35181,7 +35196,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35465,7 +35480,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ166">
         <v>1.4</v>
@@ -35593,7 +35608,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35674,7 +35689,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ167">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR167">
         <v>2.34</v>
@@ -35799,7 +35814,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36005,7 +36020,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36211,7 +36226,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36292,7 +36307,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ170">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR170">
         <v>1.48</v>
@@ -36704,7 +36719,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ172">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR172">
         <v>1.58</v>
@@ -36829,7 +36844,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37035,7 +37050,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37241,7 +37256,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37653,7 +37668,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38143,7 +38158,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38271,7 +38286,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38477,7 +38492,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38683,7 +38698,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39301,7 +39316,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39507,7 +39522,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39664,6 +39679,830 @@
       </c>
       <c r="BP186">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7468542</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>80</v>
+      </c>
+      <c r="H187" t="s">
+        <v>72</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>4</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>4</v>
+      </c>
+      <c r="O187" t="s">
+        <v>223</v>
+      </c>
+      <c r="P187" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q187">
+        <v>2</v>
+      </c>
+      <c r="R187">
+        <v>2.5</v>
+      </c>
+      <c r="S187">
+        <v>5.5</v>
+      </c>
+      <c r="T187">
+        <v>1.29</v>
+      </c>
+      <c r="U187">
+        <v>3.5</v>
+      </c>
+      <c r="V187">
+        <v>2.25</v>
+      </c>
+      <c r="W187">
+        <v>1.57</v>
+      </c>
+      <c r="X187">
+        <v>5.5</v>
+      </c>
+      <c r="Y187">
+        <v>1.14</v>
+      </c>
+      <c r="Z187">
+        <v>1.57</v>
+      </c>
+      <c r="AA187">
+        <v>4.6</v>
+      </c>
+      <c r="AB187">
+        <v>5.5</v>
+      </c>
+      <c r="AC187">
+        <v>1.01</v>
+      </c>
+      <c r="AD187">
+        <v>21</v>
+      </c>
+      <c r="AE187">
+        <v>1.17</v>
+      </c>
+      <c r="AF187">
+        <v>5</v>
+      </c>
+      <c r="AG187">
+        <v>1.75</v>
+      </c>
+      <c r="AH187">
+        <v>1.95</v>
+      </c>
+      <c r="AI187">
+        <v>1.67</v>
+      </c>
+      <c r="AJ187">
+        <v>2.1</v>
+      </c>
+      <c r="AK187">
+        <v>1.16</v>
+      </c>
+      <c r="AL187">
+        <v>1.2</v>
+      </c>
+      <c r="AM187">
+        <v>2.37</v>
+      </c>
+      <c r="AN187">
+        <v>1.89</v>
+      </c>
+      <c r="AO187">
+        <v>1.33</v>
+      </c>
+      <c r="AP187">
+        <v>2</v>
+      </c>
+      <c r="AQ187">
+        <v>1.2</v>
+      </c>
+      <c r="AR187">
+        <v>1.71</v>
+      </c>
+      <c r="AS187">
+        <v>1.29</v>
+      </c>
+      <c r="AT187">
+        <v>3</v>
+      </c>
+      <c r="AU187">
+        <v>9</v>
+      </c>
+      <c r="AV187">
+        <v>3</v>
+      </c>
+      <c r="AW187">
+        <v>6</v>
+      </c>
+      <c r="AX187">
+        <v>6</v>
+      </c>
+      <c r="AY187">
+        <v>18</v>
+      </c>
+      <c r="AZ187">
+        <v>12</v>
+      </c>
+      <c r="BA187">
+        <v>6</v>
+      </c>
+      <c r="BB187">
+        <v>6</v>
+      </c>
+      <c r="BC187">
+        <v>12</v>
+      </c>
+      <c r="BD187">
+        <v>1.46</v>
+      </c>
+      <c r="BE187">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF187">
+        <v>3.4</v>
+      </c>
+      <c r="BG187">
+        <v>1.22</v>
+      </c>
+      <c r="BH187">
+        <v>3.5</v>
+      </c>
+      <c r="BI187">
+        <v>1.44</v>
+      </c>
+      <c r="BJ187">
+        <v>2.51</v>
+      </c>
+      <c r="BK187">
+        <v>1.79</v>
+      </c>
+      <c r="BL187">
+        <v>1.92</v>
+      </c>
+      <c r="BM187">
+        <v>2.27</v>
+      </c>
+      <c r="BN187">
+        <v>1.53</v>
+      </c>
+      <c r="BO187">
+        <v>2.97</v>
+      </c>
+      <c r="BP187">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7468536</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45697.55208333334</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>74</v>
+      </c>
+      <c r="H188" t="s">
+        <v>76</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>2</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
+      </c>
+      <c r="N188">
+        <v>4</v>
+      </c>
+      <c r="O188" t="s">
+        <v>224</v>
+      </c>
+      <c r="P188" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q188">
+        <v>3.6</v>
+      </c>
+      <c r="R188">
+        <v>2.1</v>
+      </c>
+      <c r="S188">
+        <v>3</v>
+      </c>
+      <c r="T188">
+        <v>1.4</v>
+      </c>
+      <c r="U188">
+        <v>2.75</v>
+      </c>
+      <c r="V188">
+        <v>3</v>
+      </c>
+      <c r="W188">
+        <v>1.36</v>
+      </c>
+      <c r="X188">
+        <v>8</v>
+      </c>
+      <c r="Y188">
+        <v>1.08</v>
+      </c>
+      <c r="Z188">
+        <v>3.41</v>
+      </c>
+      <c r="AA188">
+        <v>3.5</v>
+      </c>
+      <c r="AB188">
+        <v>2.19</v>
+      </c>
+      <c r="AC188">
+        <v>1.06</v>
+      </c>
+      <c r="AD188">
+        <v>10</v>
+      </c>
+      <c r="AE188">
+        <v>1.33</v>
+      </c>
+      <c r="AF188">
+        <v>3.4</v>
+      </c>
+      <c r="AG188">
+        <v>1.89</v>
+      </c>
+      <c r="AH188">
+        <v>1.92</v>
+      </c>
+      <c r="AI188">
+        <v>1.75</v>
+      </c>
+      <c r="AJ188">
+        <v>2</v>
+      </c>
+      <c r="AK188">
+        <v>1.62</v>
+      </c>
+      <c r="AL188">
+        <v>1.3</v>
+      </c>
+      <c r="AM188">
+        <v>1.35</v>
+      </c>
+      <c r="AN188">
+        <v>1.9</v>
+      </c>
+      <c r="AO188">
+        <v>1.22</v>
+      </c>
+      <c r="AP188">
+        <v>1.82</v>
+      </c>
+      <c r="AQ188">
+        <v>1.2</v>
+      </c>
+      <c r="AR188">
+        <v>1.32</v>
+      </c>
+      <c r="AS188">
+        <v>1.21</v>
+      </c>
+      <c r="AT188">
+        <v>2.53</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>4</v>
+      </c>
+      <c r="AW188">
+        <v>6</v>
+      </c>
+      <c r="AX188">
+        <v>4</v>
+      </c>
+      <c r="AY188">
+        <v>13</v>
+      </c>
+      <c r="AZ188">
+        <v>9</v>
+      </c>
+      <c r="BA188">
+        <v>3</v>
+      </c>
+      <c r="BB188">
+        <v>5</v>
+      </c>
+      <c r="BC188">
+        <v>8</v>
+      </c>
+      <c r="BD188">
+        <v>2.27</v>
+      </c>
+      <c r="BE188">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF188">
+        <v>1.9</v>
+      </c>
+      <c r="BG188">
+        <v>1.3</v>
+      </c>
+      <c r="BH188">
+        <v>2.97</v>
+      </c>
+      <c r="BI188">
+        <v>1.58</v>
+      </c>
+      <c r="BJ188">
+        <v>2.17</v>
+      </c>
+      <c r="BK188">
+        <v>2.02</v>
+      </c>
+      <c r="BL188">
+        <v>1.71</v>
+      </c>
+      <c r="BM188">
+        <v>2.64</v>
+      </c>
+      <c r="BN188">
+        <v>1.4</v>
+      </c>
+      <c r="BO188">
+        <v>3.58</v>
+      </c>
+      <c r="BP188">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7468538</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45697.55208333334</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>84</v>
+      </c>
+      <c r="H189" t="s">
+        <v>75</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>225</v>
+      </c>
+      <c r="P189" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q189">
+        <v>2.3</v>
+      </c>
+      <c r="R189">
+        <v>2.38</v>
+      </c>
+      <c r="S189">
+        <v>4.5</v>
+      </c>
+      <c r="T189">
+        <v>1.3</v>
+      </c>
+      <c r="U189">
+        <v>3.4</v>
+      </c>
+      <c r="V189">
+        <v>2.5</v>
+      </c>
+      <c r="W189">
+        <v>1.5</v>
+      </c>
+      <c r="X189">
+        <v>6</v>
+      </c>
+      <c r="Y189">
+        <v>1.13</v>
+      </c>
+      <c r="Z189">
+        <v>1.77</v>
+      </c>
+      <c r="AA189">
+        <v>4.1</v>
+      </c>
+      <c r="AB189">
+        <v>4.4</v>
+      </c>
+      <c r="AC189">
+        <v>1.03</v>
+      </c>
+      <c r="AD189">
+        <v>15</v>
+      </c>
+      <c r="AE189">
+        <v>1.22</v>
+      </c>
+      <c r="AF189">
+        <v>4.33</v>
+      </c>
+      <c r="AG189">
+        <v>1.61</v>
+      </c>
+      <c r="AH189">
+        <v>2.2</v>
+      </c>
+      <c r="AI189">
+        <v>1.67</v>
+      </c>
+      <c r="AJ189">
+        <v>2.1</v>
+      </c>
+      <c r="AK189">
+        <v>1.21</v>
+      </c>
+      <c r="AL189">
+        <v>1.23</v>
+      </c>
+      <c r="AM189">
+        <v>2.05</v>
+      </c>
+      <c r="AN189">
+        <v>2</v>
+      </c>
+      <c r="AO189">
+        <v>0.33</v>
+      </c>
+      <c r="AP189">
+        <v>2.1</v>
+      </c>
+      <c r="AQ189">
+        <v>0.3</v>
+      </c>
+      <c r="AR189">
+        <v>1.26</v>
+      </c>
+      <c r="AS189">
+        <v>1.17</v>
+      </c>
+      <c r="AT189">
+        <v>2.43</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>17</v>
+      </c>
+      <c r="AX189">
+        <v>10</v>
+      </c>
+      <c r="AY189">
+        <v>29</v>
+      </c>
+      <c r="AZ189">
+        <v>15</v>
+      </c>
+      <c r="BA189">
+        <v>6</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>1.64</v>
+      </c>
+      <c r="BE189">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF189">
+        <v>2.76</v>
+      </c>
+      <c r="BG189">
+        <v>1.28</v>
+      </c>
+      <c r="BH189">
+        <v>3.05</v>
+      </c>
+      <c r="BI189">
+        <v>1.56</v>
+      </c>
+      <c r="BJ189">
+        <v>2.21</v>
+      </c>
+      <c r="BK189">
+        <v>1.98</v>
+      </c>
+      <c r="BL189">
+        <v>1.74</v>
+      </c>
+      <c r="BM189">
+        <v>2.57</v>
+      </c>
+      <c r="BN189">
+        <v>1.42</v>
+      </c>
+      <c r="BO189">
+        <v>3.5</v>
+      </c>
+      <c r="BP189">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7468662</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45697.69791666666</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>77</v>
+      </c>
+      <c r="H190" t="s">
+        <v>87</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>2</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>90</v>
+      </c>
+      <c r="P190" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q190">
+        <v>5.5</v>
+      </c>
+      <c r="R190">
+        <v>2.25</v>
+      </c>
+      <c r="S190">
+        <v>2.2</v>
+      </c>
+      <c r="T190">
+        <v>1.36</v>
+      </c>
+      <c r="U190">
+        <v>3</v>
+      </c>
+      <c r="V190">
+        <v>2.75</v>
+      </c>
+      <c r="W190">
+        <v>1.4</v>
+      </c>
+      <c r="X190">
+        <v>7</v>
+      </c>
+      <c r="Y190">
+        <v>1.1</v>
+      </c>
+      <c r="Z190">
+        <v>5.4</v>
+      </c>
+      <c r="AA190">
+        <v>4.1</v>
+      </c>
+      <c r="AB190">
+        <v>1.66</v>
+      </c>
+      <c r="AC190">
+        <v>1.04</v>
+      </c>
+      <c r="AD190">
+        <v>13</v>
+      </c>
+      <c r="AE190">
+        <v>1.28</v>
+      </c>
+      <c r="AF190">
+        <v>3.75</v>
+      </c>
+      <c r="AG190">
+        <v>1.84</v>
+      </c>
+      <c r="AH190">
+        <v>1.97</v>
+      </c>
+      <c r="AI190">
+        <v>1.91</v>
+      </c>
+      <c r="AJ190">
+        <v>1.91</v>
+      </c>
+      <c r="AK190">
+        <v>2.2</v>
+      </c>
+      <c r="AL190">
+        <v>1.24</v>
+      </c>
+      <c r="AM190">
+        <v>1.16</v>
+      </c>
+      <c r="AN190">
+        <v>1.1</v>
+      </c>
+      <c r="AO190">
+        <v>2.4</v>
+      </c>
+      <c r="AP190">
+        <v>1</v>
+      </c>
+      <c r="AQ190">
+        <v>2.45</v>
+      </c>
+      <c r="AR190">
+        <v>1.31</v>
+      </c>
+      <c r="AS190">
+        <v>1.43</v>
+      </c>
+      <c r="AT190">
+        <v>2.74</v>
+      </c>
+      <c r="AU190">
+        <v>0</v>
+      </c>
+      <c r="AV190">
+        <v>9</v>
+      </c>
+      <c r="AW190">
+        <v>7</v>
+      </c>
+      <c r="AX190">
+        <v>8</v>
+      </c>
+      <c r="AY190">
+        <v>8</v>
+      </c>
+      <c r="AZ190">
+        <v>20</v>
+      </c>
+      <c r="BA190">
+        <v>1</v>
+      </c>
+      <c r="BB190">
+        <v>7</v>
+      </c>
+      <c r="BC190">
+        <v>8</v>
+      </c>
+      <c r="BD190">
+        <v>3.56</v>
+      </c>
+      <c r="BE190">
+        <v>8.9</v>
+      </c>
+      <c r="BF190">
+        <v>1.44</v>
+      </c>
+      <c r="BG190">
+        <v>1.41</v>
+      </c>
+      <c r="BH190">
+        <v>2.6</v>
+      </c>
+      <c r="BI190">
+        <v>1.76</v>
+      </c>
+      <c r="BJ190">
+        <v>1.95</v>
+      </c>
+      <c r="BK190">
+        <v>2.25</v>
+      </c>
+      <c r="BL190">
+        <v>1.54</v>
+      </c>
+      <c r="BM190">
+        <v>3.04</v>
+      </c>
+      <c r="BN190">
+        <v>1.29</v>
+      </c>
+      <c r="BO190">
+        <v>4.3</v>
+      </c>
+      <c r="BP190">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="331">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,9 @@
     <t>['45+2', '69']</t>
   </si>
   <si>
+    <t>['60', '79']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1001,6 +1004,9 @@
   </si>
   <si>
     <t>['69', '74']</t>
+  </si>
+  <si>
+    <t>['18', '74']</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1618,7 +1624,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1824,7 +1830,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1902,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ3">
         <v>2.45</v>
@@ -2030,7 +2036,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2442,7 +2448,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2648,7 +2654,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3678,7 +3684,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4090,7 +4096,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4502,7 +4508,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4789,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5120,7 +5126,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5326,7 +5332,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5610,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21">
         <v>0.18</v>
@@ -5738,7 +5744,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5944,7 +5950,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6150,7 +6156,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6356,7 +6362,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6643,7 +6649,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ26">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6768,7 +6774,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6974,7 +6980,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7592,7 +7598,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8210,7 +8216,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8416,7 +8422,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9240,7 +9246,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9446,7 +9452,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10142,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -10270,7 +10276,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10476,7 +10482,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10557,7 +10563,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ45">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10682,7 +10688,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11094,7 +11100,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11506,7 +11512,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11712,7 +11718,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11918,7 +11924,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12124,7 +12130,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12330,7 +12336,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12948,7 +12954,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13029,7 +13035,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13360,7 +13366,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13850,7 +13856,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13978,7 +13984,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14184,7 +14190,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14390,7 +14396,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14880,7 +14886,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ66">
         <v>0.4</v>
@@ -15008,7 +15014,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15214,7 +15220,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15420,7 +15426,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15626,7 +15632,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15832,7 +15838,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16038,7 +16044,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16244,7 +16250,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16656,7 +16662,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16862,7 +16868,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17068,7 +17074,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17274,7 +17280,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17355,7 +17361,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17480,7 +17486,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17686,7 +17692,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18098,7 +18104,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18922,7 +18928,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19000,7 +19006,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ86">
         <v>1.18</v>
@@ -19952,7 +19958,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20158,7 +20164,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20239,7 +20245,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ92">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20364,7 +20370,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20570,7 +20576,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20776,7 +20782,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20982,7 +20988,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21188,7 +21194,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21394,7 +21400,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21600,7 +21606,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22012,7 +22018,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22424,7 +22430,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23454,7 +23460,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23660,7 +23666,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23866,7 +23872,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24356,7 +24362,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ112">
         <v>0.82</v>
@@ -24690,7 +24696,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24896,7 +24902,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25183,7 +25189,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ116">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25308,7 +25314,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25514,7 +25520,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26338,7 +26344,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26544,7 +26550,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27368,7 +27374,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27780,7 +27786,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27986,7 +27992,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28398,7 +28404,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28604,7 +28610,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28888,7 +28894,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29428,7 +29434,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29634,7 +29640,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29840,7 +29846,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30046,7 +30052,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30745,7 +30751,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ143">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -31282,7 +31288,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31694,7 +31700,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31772,7 +31778,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ148">
         <v>1.18</v>
@@ -31900,7 +31906,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32106,7 +32112,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32312,7 +32318,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32518,7 +32524,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32724,7 +32730,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33136,7 +33142,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33548,7 +33554,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33754,7 +33760,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34453,7 +34459,7 @@
         <v>1</v>
       </c>
       <c r="AQ161">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR161">
         <v>1.21</v>
@@ -34784,7 +34790,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35196,7 +35202,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35608,7 +35614,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35814,7 +35820,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36020,7 +36026,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36226,7 +36232,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36844,7 +36850,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37050,7 +37056,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37128,7 +37134,7 @@
         <v>2.33</v>
       </c>
       <c r="AP174">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ174">
         <v>2.4</v>
@@ -37256,7 +37262,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37337,7 +37343,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ175">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR175">
         <v>1.59</v>
@@ -37668,7 +37674,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38286,7 +38292,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38492,7 +38498,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38698,7 +38704,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39316,7 +39322,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39522,7 +39528,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39934,7 +39940,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40346,7 +40352,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40503,6 +40509,212 @@
       </c>
       <c r="BP190">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7468548</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>71</v>
+      </c>
+      <c r="H191" t="s">
+        <v>74</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>2</v>
+      </c>
+      <c r="N191">
+        <v>4</v>
+      </c>
+      <c r="O191" t="s">
+        <v>226</v>
+      </c>
+      <c r="P191" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q191">
+        <v>2.75</v>
+      </c>
+      <c r="R191">
+        <v>2.2</v>
+      </c>
+      <c r="S191">
+        <v>4</v>
+      </c>
+      <c r="T191">
+        <v>1.4</v>
+      </c>
+      <c r="U191">
+        <v>2.75</v>
+      </c>
+      <c r="V191">
+        <v>2.75</v>
+      </c>
+      <c r="W191">
+        <v>1.4</v>
+      </c>
+      <c r="X191">
+        <v>8</v>
+      </c>
+      <c r="Y191">
+        <v>1.08</v>
+      </c>
+      <c r="Z191">
+        <v>1.92</v>
+      </c>
+      <c r="AA191">
+        <v>3.77</v>
+      </c>
+      <c r="AB191">
+        <v>4</v>
+      </c>
+      <c r="AC191">
+        <v>1.06</v>
+      </c>
+      <c r="AD191">
+        <v>11</v>
+      </c>
+      <c r="AE191">
+        <v>1.3</v>
+      </c>
+      <c r="AF191">
+        <v>3.6</v>
+      </c>
+      <c r="AG191">
+        <v>1.82</v>
+      </c>
+      <c r="AH191">
+        <v>2</v>
+      </c>
+      <c r="AI191">
+        <v>1.7</v>
+      </c>
+      <c r="AJ191">
+        <v>2.05</v>
+      </c>
+      <c r="AK191">
+        <v>1.29</v>
+      </c>
+      <c r="AL191">
+        <v>1.29</v>
+      </c>
+      <c r="AM191">
+        <v>1.75</v>
+      </c>
+      <c r="AN191">
+        <v>1.9</v>
+      </c>
+      <c r="AO191">
+        <v>0.4</v>
+      </c>
+      <c r="AP191">
+        <v>1.82</v>
+      </c>
+      <c r="AQ191">
+        <v>0.45</v>
+      </c>
+      <c r="AR191">
+        <v>1.49</v>
+      </c>
+      <c r="AS191">
+        <v>1.25</v>
+      </c>
+      <c r="AT191">
+        <v>2.74</v>
+      </c>
+      <c r="AU191">
+        <v>10</v>
+      </c>
+      <c r="AV191">
+        <v>6</v>
+      </c>
+      <c r="AW191">
+        <v>10</v>
+      </c>
+      <c r="AX191">
+        <v>6</v>
+      </c>
+      <c r="AY191">
+        <v>23</v>
+      </c>
+      <c r="AZ191">
+        <v>15</v>
+      </c>
+      <c r="BA191">
+        <v>6</v>
+      </c>
+      <c r="BB191">
+        <v>4</v>
+      </c>
+      <c r="BC191">
+        <v>10</v>
+      </c>
+      <c r="BD191">
+        <v>1.61</v>
+      </c>
+      <c r="BE191">
+        <v>6.1</v>
+      </c>
+      <c r="BF191">
+        <v>2.63</v>
+      </c>
+      <c r="BG191">
+        <v>1.5</v>
+      </c>
+      <c r="BH191">
+        <v>2.4</v>
+      </c>
+      <c r="BI191">
+        <v>1.84</v>
+      </c>
+      <c r="BJ191">
+        <v>1.84</v>
+      </c>
+      <c r="BK191">
+        <v>2.33</v>
+      </c>
+      <c r="BL191">
+        <v>1.52</v>
+      </c>
+      <c r="BM191">
+        <v>3.05</v>
+      </c>
+      <c r="BN191">
+        <v>1.3</v>
+      </c>
+      <c r="BO191">
+        <v>4.1</v>
+      </c>
+      <c r="BP191">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,12 @@
     <t>['60', '79']</t>
   </si>
   <si>
+    <t>['27', '50', '58', '60', '77']</t>
+  </si>
+  <si>
+    <t>['44', '45', '49', '54', '64', '81', '90+5']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1007,6 +1013,9 @@
   </si>
   <si>
     <t>['18', '74']</t>
+  </si>
+  <si>
+    <t>['79']</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1624,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1705,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ2">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1830,7 +1839,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2036,7 +2045,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2320,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ5">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2448,7 +2457,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2654,7 +2663,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2938,10 +2947,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3684,7 +3693,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4096,7 +4105,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4508,7 +4517,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5126,7 +5135,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5204,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ19">
         <v>1.2</v>
@@ -5332,7 +5341,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5619,7 +5628,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5744,7 +5753,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5825,7 +5834,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -5950,7 +5959,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6028,7 +6037,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23">
         <v>2.45</v>
@@ -6156,7 +6165,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6234,7 +6243,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ24">
         <v>1.73</v>
@@ -6362,7 +6371,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6774,7 +6783,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6980,7 +6989,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7061,7 +7070,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ28">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7470,7 +7479,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ30">
         <v>1.18</v>
@@ -7598,7 +7607,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8216,7 +8225,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8422,7 +8431,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8706,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -9121,7 +9130,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ38">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9246,7 +9255,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9452,7 +9461,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9739,7 +9748,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ41">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -9942,7 +9951,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10276,7 +10285,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10357,7 +10366,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10482,7 +10491,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10688,7 +10697,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11100,7 +11109,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11512,7 +11521,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11718,7 +11727,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11796,7 +11805,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ51">
         <v>0.3</v>
@@ -11924,7 +11933,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12002,7 +12011,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
         <v>1.18</v>
@@ -12130,7 +12139,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12211,7 +12220,7 @@
         <v>1</v>
       </c>
       <c r="AQ53">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12336,7 +12345,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12826,7 +12835,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56">
         <v>1.2</v>
@@ -12954,7 +12963,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13366,7 +13375,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13653,7 +13662,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -13984,7 +13993,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14190,7 +14199,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14396,7 +14405,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14477,7 +14486,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ64">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -14680,7 +14689,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ65">
         <v>1.4</v>
@@ -15014,7 +15023,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15220,7 +15229,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15426,7 +15435,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15632,7 +15641,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15710,7 +15719,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
         <v>1.2</v>
@@ -15838,7 +15847,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16044,7 +16053,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16250,7 +16259,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16662,7 +16671,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16743,7 +16752,7 @@
         <v>1</v>
       </c>
       <c r="AQ75">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16868,7 +16877,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17074,7 +17083,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17280,7 +17289,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17486,7 +17495,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17692,7 +17701,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17773,7 +17782,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -18104,7 +18113,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18182,10 +18191,10 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ82">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18388,7 +18397,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ83">
         <v>1.2</v>
@@ -18928,7 +18937,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19418,7 +19427,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
         <v>1.2</v>
@@ -19958,7 +19967,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20164,7 +20173,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20242,7 +20251,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ92">
         <v>0.45</v>
@@ -20370,7 +20379,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20576,7 +20585,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20657,7 +20666,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -20782,7 +20791,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20863,7 +20872,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -20988,7 +20997,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21194,7 +21203,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21400,7 +21409,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21606,7 +21615,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21893,7 +21902,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22018,7 +22027,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22096,7 +22105,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ101">
         <v>1.09</v>
@@ -22430,7 +22439,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23460,7 +23469,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23666,7 +23675,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23872,7 +23881,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24159,7 +24168,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ111">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24571,7 +24580,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24696,7 +24705,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24902,7 +24911,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25186,7 +25195,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ116">
         <v>0.45</v>
@@ -25314,7 +25323,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25520,7 +25529,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25598,7 +25607,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ118">
         <v>1.4</v>
@@ -26013,7 +26022,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ120">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26216,7 +26225,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ121">
         <v>1.2</v>
@@ -26344,7 +26353,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26550,7 +26559,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27374,7 +27383,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27658,10 +27667,10 @@
         <v>0.14</v>
       </c>
       <c r="AP128">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ128">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27786,7 +27795,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27864,7 +27873,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129">
         <v>1.4</v>
@@ -27992,7 +28001,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28404,7 +28413,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28610,7 +28619,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28897,7 +28906,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29434,7 +29443,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29512,10 +29521,10 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ137">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29640,7 +29649,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29846,7 +29855,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30052,7 +30061,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30133,7 +30142,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -31160,7 +31169,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ145">
         <v>1</v>
@@ -31288,7 +31297,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31700,7 +31709,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31906,7 +31915,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32112,7 +32121,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32318,7 +32327,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32524,7 +32533,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32730,7 +32739,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32808,7 +32817,7 @@
         <v>0.63</v>
       </c>
       <c r="AP153">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ153">
         <v>0.82</v>
@@ -33017,7 +33026,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ154">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR154">
         <v>2.26</v>
@@ -33142,7 +33151,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33554,7 +33563,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33635,7 +33644,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ157">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR157">
         <v>1.67</v>
@@ -33760,7 +33769,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34253,7 +34262,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ160">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34790,7 +34799,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34868,7 +34877,7 @@
         <v>0.89</v>
       </c>
       <c r="AP163">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ163">
         <v>0.82</v>
@@ -35077,7 +35086,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ164">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35202,7 +35211,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35280,7 +35289,7 @@
         <v>0.13</v>
       </c>
       <c r="AP165">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ165">
         <v>0.4</v>
@@ -35614,7 +35623,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35820,7 +35829,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36026,7 +36035,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -36232,7 +36241,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36310,7 +36319,7 @@
         <v>0</v>
       </c>
       <c r="AP170">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ170">
         <v>0.3</v>
@@ -36850,7 +36859,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37056,7 +37065,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37137,7 +37146,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR174">
         <v>1.46</v>
@@ -37262,7 +37271,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37340,7 +37349,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ175">
         <v>0.45</v>
@@ -37549,7 +37558,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ176">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR176">
         <v>1.38</v>
@@ -37674,7 +37683,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37752,7 +37761,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ177">
         <v>1.18</v>
@@ -38292,7 +38301,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38373,7 +38382,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR180">
         <v>1.22</v>
@@ -38498,7 +38507,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38576,7 +38585,7 @@
         <v>1.3</v>
       </c>
       <c r="AP181">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ181">
         <v>1.18</v>
@@ -38704,7 +38713,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39322,7 +39331,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39528,7 +39537,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39940,7 +39949,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40352,7 +40361,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40558,7 +40567,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40715,6 +40724,624 @@
       </c>
       <c r="BP191">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7468545</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45703.54166666666</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>87</v>
+      </c>
+      <c r="H192" t="s">
+        <v>82</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>5</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>6</v>
+      </c>
+      <c r="O192" t="s">
+        <v>227</v>
+      </c>
+      <c r="P192" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q192">
+        <v>1.67</v>
+      </c>
+      <c r="R192">
+        <v>2.75</v>
+      </c>
+      <c r="S192">
+        <v>8</v>
+      </c>
+      <c r="T192">
+        <v>1.25</v>
+      </c>
+      <c r="U192">
+        <v>3.75</v>
+      </c>
+      <c r="V192">
+        <v>2.2</v>
+      </c>
+      <c r="W192">
+        <v>1.62</v>
+      </c>
+      <c r="X192">
+        <v>5</v>
+      </c>
+      <c r="Y192">
+        <v>1.17</v>
+      </c>
+      <c r="Z192">
+        <v>1.3</v>
+      </c>
+      <c r="AA192">
+        <v>6.2</v>
+      </c>
+      <c r="AB192">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC192">
+        <v>1.01</v>
+      </c>
+      <c r="AD192">
+        <v>21</v>
+      </c>
+      <c r="AE192">
+        <v>1.15</v>
+      </c>
+      <c r="AF192">
+        <v>5.5</v>
+      </c>
+      <c r="AG192">
+        <v>1.44</v>
+      </c>
+      <c r="AH192">
+        <v>2.67</v>
+      </c>
+      <c r="AI192">
+        <v>1.91</v>
+      </c>
+      <c r="AJ192">
+        <v>1.91</v>
+      </c>
+      <c r="AK192">
+        <v>1.06</v>
+      </c>
+      <c r="AL192">
+        <v>1.13</v>
+      </c>
+      <c r="AM192">
+        <v>3.5</v>
+      </c>
+      <c r="AN192">
+        <v>1.6</v>
+      </c>
+      <c r="AO192">
+        <v>0.18</v>
+      </c>
+      <c r="AP192">
+        <v>1.73</v>
+      </c>
+      <c r="AQ192">
+        <v>0.17</v>
+      </c>
+      <c r="AR192">
+        <v>1.6</v>
+      </c>
+      <c r="AS192">
+        <v>0.99</v>
+      </c>
+      <c r="AT192">
+        <v>2.59</v>
+      </c>
+      <c r="AU192">
+        <v>14</v>
+      </c>
+      <c r="AV192">
+        <v>3</v>
+      </c>
+      <c r="AW192">
+        <v>17</v>
+      </c>
+      <c r="AX192">
+        <v>6</v>
+      </c>
+      <c r="AY192">
+        <v>34</v>
+      </c>
+      <c r="AZ192">
+        <v>11</v>
+      </c>
+      <c r="BA192">
+        <v>14</v>
+      </c>
+      <c r="BB192">
+        <v>3</v>
+      </c>
+      <c r="BC192">
+        <v>17</v>
+      </c>
+      <c r="BD192">
+        <v>1.16</v>
+      </c>
+      <c r="BE192">
+        <v>9</v>
+      </c>
+      <c r="BF192">
+        <v>5.6</v>
+      </c>
+      <c r="BG192">
+        <v>1.33</v>
+      </c>
+      <c r="BH192">
+        <v>2.95</v>
+      </c>
+      <c r="BI192">
+        <v>1.57</v>
+      </c>
+      <c r="BJ192">
+        <v>2.23</v>
+      </c>
+      <c r="BK192">
+        <v>1.92</v>
+      </c>
+      <c r="BL192">
+        <v>1.77</v>
+      </c>
+      <c r="BM192">
+        <v>2.4</v>
+      </c>
+      <c r="BN192">
+        <v>1.49</v>
+      </c>
+      <c r="BO192">
+        <v>3.05</v>
+      </c>
+      <c r="BP192">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7468552</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45703.625</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>73</v>
+      </c>
+      <c r="H193" t="s">
+        <v>85</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>3</v>
+      </c>
+      <c r="L193">
+        <v>7</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>8</v>
+      </c>
+      <c r="O193" t="s">
+        <v>228</v>
+      </c>
+      <c r="P193" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q193">
+        <v>2.1</v>
+      </c>
+      <c r="R193">
+        <v>2.4</v>
+      </c>
+      <c r="S193">
+        <v>5.5</v>
+      </c>
+      <c r="T193">
+        <v>1.3</v>
+      </c>
+      <c r="U193">
+        <v>3.4</v>
+      </c>
+      <c r="V193">
+        <v>2.5</v>
+      </c>
+      <c r="W193">
+        <v>1.5</v>
+      </c>
+      <c r="X193">
+        <v>6</v>
+      </c>
+      <c r="Y193">
+        <v>1.13</v>
+      </c>
+      <c r="Z193">
+        <v>1.56</v>
+      </c>
+      <c r="AA193">
+        <v>4.5</v>
+      </c>
+      <c r="AB193">
+        <v>5.8</v>
+      </c>
+      <c r="AC193">
+        <v>1.03</v>
+      </c>
+      <c r="AD193">
+        <v>17</v>
+      </c>
+      <c r="AE193">
+        <v>1.2</v>
+      </c>
+      <c r="AF193">
+        <v>4.5</v>
+      </c>
+      <c r="AG193">
+        <v>1.67</v>
+      </c>
+      <c r="AH193">
+        <v>2.1</v>
+      </c>
+      <c r="AI193">
+        <v>1.7</v>
+      </c>
+      <c r="AJ193">
+        <v>2.05</v>
+      </c>
+      <c r="AK193">
+        <v>1.15</v>
+      </c>
+      <c r="AL193">
+        <v>1.21</v>
+      </c>
+      <c r="AM193">
+        <v>2.4</v>
+      </c>
+      <c r="AN193">
+        <v>2.09</v>
+      </c>
+      <c r="AO193">
+        <v>1</v>
+      </c>
+      <c r="AP193">
+        <v>2.17</v>
+      </c>
+      <c r="AQ193">
+        <v>0.92</v>
+      </c>
+      <c r="AR193">
+        <v>1.6</v>
+      </c>
+      <c r="AS193">
+        <v>1.16</v>
+      </c>
+      <c r="AT193">
+        <v>2.76</v>
+      </c>
+      <c r="AU193">
+        <v>13</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
+        <v>12</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>27</v>
+      </c>
+      <c r="AZ193">
+        <v>8</v>
+      </c>
+      <c r="BA193">
+        <v>9</v>
+      </c>
+      <c r="BB193">
+        <v>1</v>
+      </c>
+      <c r="BC193">
+        <v>10</v>
+      </c>
+      <c r="BD193">
+        <v>1.49</v>
+      </c>
+      <c r="BE193">
+        <v>6.75</v>
+      </c>
+      <c r="BF193">
+        <v>2.95</v>
+      </c>
+      <c r="BG193">
+        <v>1.3</v>
+      </c>
+      <c r="BH193">
+        <v>3.05</v>
+      </c>
+      <c r="BI193">
+        <v>1.54</v>
+      </c>
+      <c r="BJ193">
+        <v>2.3</v>
+      </c>
+      <c r="BK193">
+        <v>1.88</v>
+      </c>
+      <c r="BL193">
+        <v>1.81</v>
+      </c>
+      <c r="BM193">
+        <v>2.38</v>
+      </c>
+      <c r="BN193">
+        <v>1.5</v>
+      </c>
+      <c r="BO193">
+        <v>3.05</v>
+      </c>
+      <c r="BP193">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7468544</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45703.71180555555</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>76</v>
+      </c>
+      <c r="H194" t="s">
+        <v>79</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
+        <v>90</v>
+      </c>
+      <c r="P194" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q194">
+        <v>5.5</v>
+      </c>
+      <c r="R194">
+        <v>2.5</v>
+      </c>
+      <c r="S194">
+        <v>2</v>
+      </c>
+      <c r="T194">
+        <v>1.29</v>
+      </c>
+      <c r="U194">
+        <v>3.5</v>
+      </c>
+      <c r="V194">
+        <v>2.25</v>
+      </c>
+      <c r="W194">
+        <v>1.57</v>
+      </c>
+      <c r="X194">
+        <v>5.5</v>
+      </c>
+      <c r="Y194">
+        <v>1.14</v>
+      </c>
+      <c r="Z194">
+        <v>6</v>
+      </c>
+      <c r="AA194">
+        <v>4.75</v>
+      </c>
+      <c r="AB194">
+        <v>1.53</v>
+      </c>
+      <c r="AC194">
+        <v>1.02</v>
+      </c>
+      <c r="AD194">
+        <v>19</v>
+      </c>
+      <c r="AE194">
+        <v>1.18</v>
+      </c>
+      <c r="AF194">
+        <v>5</v>
+      </c>
+      <c r="AG194">
+        <v>1.52</v>
+      </c>
+      <c r="AH194">
+        <v>2.43</v>
+      </c>
+      <c r="AI194">
+        <v>1.67</v>
+      </c>
+      <c r="AJ194">
+        <v>2.1</v>
+      </c>
+      <c r="AK194">
+        <v>2.5</v>
+      </c>
+      <c r="AL194">
+        <v>1.19</v>
+      </c>
+      <c r="AM194">
+        <v>1.14</v>
+      </c>
+      <c r="AN194">
+        <v>1.36</v>
+      </c>
+      <c r="AO194">
+        <v>2.4</v>
+      </c>
+      <c r="AP194">
+        <v>1.25</v>
+      </c>
+      <c r="AQ194">
+        <v>2.45</v>
+      </c>
+      <c r="AR194">
+        <v>1.53</v>
+      </c>
+      <c r="AS194">
+        <v>2.14</v>
+      </c>
+      <c r="AT194">
+        <v>3.67</v>
+      </c>
+      <c r="AU194">
+        <v>5</v>
+      </c>
+      <c r="AV194">
+        <v>7</v>
+      </c>
+      <c r="AW194">
+        <v>10</v>
+      </c>
+      <c r="AX194">
+        <v>14</v>
+      </c>
+      <c r="AY194">
+        <v>17</v>
+      </c>
+      <c r="AZ194">
+        <v>25</v>
+      </c>
+      <c r="BA194">
+        <v>5</v>
+      </c>
+      <c r="BB194">
+        <v>2</v>
+      </c>
+      <c r="BC194">
+        <v>7</v>
+      </c>
+      <c r="BD194">
+        <v>3.3</v>
+      </c>
+      <c r="BE194">
+        <v>6.75</v>
+      </c>
+      <c r="BF194">
+        <v>1.42</v>
+      </c>
+      <c r="BG194">
+        <v>1.35</v>
+      </c>
+      <c r="BH194">
+        <v>2.9</v>
+      </c>
+      <c r="BI194">
+        <v>1.58</v>
+      </c>
+      <c r="BJ194">
+        <v>2.18</v>
+      </c>
+      <c r="BK194">
+        <v>1.96</v>
+      </c>
+      <c r="BL194">
+        <v>1.73</v>
+      </c>
+      <c r="BM194">
+        <v>2.5</v>
+      </c>
+      <c r="BN194">
+        <v>1.46</v>
+      </c>
+      <c r="BO194">
+        <v>3.3</v>
+      </c>
+      <c r="BP194">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1017,6 +1017,18 @@
   <si>
     <t>['79']</t>
   </si>
+  <si>
+    <t>['3', '50', '53', '73']</t>
+  </si>
+  <si>
+    <t>['16', '18', '90+4']</t>
+  </si>
+  <si>
+    <t>['81', '90+6']</t>
+  </si>
+  <si>
+    <t>['80', '86']</t>
+  </si>
 </sst>
 </file>
 
@@ -1377,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1711,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ2">
         <v>2.45</v>
@@ -2123,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2538,7 +2550,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2741,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3359,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3980,7 +3992,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ13">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4389,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15">
         <v>1.09</v>
@@ -5422,7 +5434,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5831,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>0.92</v>
@@ -6452,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6655,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ26">
         <v>0.45</v>
@@ -6861,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ27">
         <v>0.4</v>
@@ -7276,7 +7288,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR29">
         <v>1.65</v>
@@ -7482,7 +7494,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ30">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -8097,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ33">
         <v>0.3</v>
@@ -8306,7 +8318,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ34">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8921,10 +8933,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ37">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -9336,7 +9348,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ39">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9539,7 +9551,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ40">
         <v>1.73</v>
@@ -9745,7 +9757,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ41">
         <v>2.45</v>
@@ -10569,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>0.45</v>
@@ -11393,10 +11405,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ49">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11599,10 +11611,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ50">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR50">
         <v>1.41</v>
@@ -12014,7 +12026,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ52">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.24</v>
@@ -12838,7 +12850,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -13453,7 +13465,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ59">
         <v>1.4</v>
@@ -14277,7 +14289,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ63">
         <v>0.3</v>
@@ -14692,7 +14704,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ65">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR65">
         <v>1.54</v>
@@ -15310,7 +15322,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ68">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15513,10 +15525,10 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ69">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR69">
         <v>1.32</v>
@@ -15722,7 +15734,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
         <v>1.25</v>
@@ -15928,7 +15940,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -16337,7 +16349,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ73">
         <v>2.45</v>
@@ -16543,7 +16555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16955,7 +16967,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ76">
         <v>1.09</v>
@@ -17161,10 +17173,10 @@
         <v>1.75</v>
       </c>
       <c r="AP77">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ77">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR77">
         <v>1.98</v>
@@ -17573,7 +17585,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1.2</v>
@@ -18400,7 +18412,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ83">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR83">
         <v>1.55</v>
@@ -18606,7 +18618,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ84">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -19018,7 +19030,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19224,7 +19236,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ87">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19839,7 +19851,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ90">
         <v>0.3</v>
@@ -20663,7 +20675,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ94">
         <v>0.92</v>
@@ -21078,7 +21090,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ96">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR96">
         <v>1.64</v>
@@ -21281,7 +21293,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ97">
         <v>1.2</v>
@@ -21487,7 +21499,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
         <v>1.09</v>
@@ -21693,7 +21705,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ99">
         <v>1.2</v>
@@ -22517,7 +22529,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103">
         <v>2.45</v>
@@ -22929,10 +22941,10 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ105">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.09</v>
@@ -23344,7 +23356,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ107">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR107">
         <v>1.49</v>
@@ -23756,7 +23768,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ109">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23959,7 +23971,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ110">
         <v>1.73</v>
@@ -24165,7 +24177,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ111">
         <v>0.17</v>
@@ -24374,7 +24386,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ112">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24783,10 +24795,10 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR114">
         <v>1.36</v>
@@ -24989,10 +25001,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25404,7 +25416,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -26640,7 +26652,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26843,7 +26855,7 @@
         <v>0</v>
       </c>
       <c r="AP124">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
         <v>0.3</v>
@@ -27876,7 +27888,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR129">
         <v>1.4</v>
@@ -28285,7 +28297,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ131">
         <v>1.4</v>
@@ -28491,10 +28503,10 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28697,10 +28709,10 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ133">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -29109,10 +29121,10 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.64</v>
@@ -29318,7 +29330,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ136">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>2.35</v>
@@ -30551,7 +30563,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -31584,7 +31596,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR147">
         <v>1.33</v>
@@ -31790,7 +31802,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ148">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR148">
         <v>1.48</v>
@@ -31993,10 +32005,10 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ149">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32199,7 +32211,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ150">
         <v>2.45</v>
@@ -32405,7 +32417,7 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ151">
         <v>1.73</v>
@@ -32611,10 +32623,10 @@
         <v>1.13</v>
       </c>
       <c r="AP152">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ152">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR152">
         <v>1.44</v>
@@ -32820,7 +32832,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33229,7 +33241,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
         <v>1.4</v>
@@ -33438,7 +33450,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ156">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33641,7 +33653,7 @@
         <v>2.25</v>
       </c>
       <c r="AP157">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ157">
         <v>2.45</v>
@@ -33847,7 +33859,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ158">
         <v>1.09</v>
@@ -34671,7 +34683,7 @@
         <v>0.75</v>
       </c>
       <c r="AP162">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34880,7 +34892,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ163">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.45</v>
@@ -35498,7 +35510,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ166">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR166">
         <v>1.19</v>
@@ -35907,7 +35919,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ168">
         <v>1.09</v>
@@ -36116,7 +36128,7 @@
         <v>1</v>
       </c>
       <c r="AQ169">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR169">
         <v>1.4</v>
@@ -36525,10 +36537,10 @@
         <v>1.33</v>
       </c>
       <c r="AP171">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ171">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR171">
         <v>1.64</v>
@@ -36937,7 +36949,7 @@
         <v>1.78</v>
       </c>
       <c r="AP173">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>1.73</v>
@@ -37764,7 +37776,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ177">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR177">
         <v>1.51</v>
@@ -37967,10 +37979,10 @@
         <v>0.9</v>
       </c>
       <c r="AP178">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ178">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.61</v>
@@ -38379,7 +38391,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ180">
         <v>0.92</v>
@@ -38588,7 +38600,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ181">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR181">
         <v>1.5</v>
@@ -41342,6 +41354,1036 @@
       </c>
       <c r="BP194">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7468546</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>75</v>
+      </c>
+      <c r="H195" t="s">
+        <v>80</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>4</v>
+      </c>
+      <c r="N195">
+        <v>5</v>
+      </c>
+      <c r="O195" t="s">
+        <v>138</v>
+      </c>
+      <c r="P195" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q195">
+        <v>4.5</v>
+      </c>
+      <c r="R195">
+        <v>2.5</v>
+      </c>
+      <c r="S195">
+        <v>2.2</v>
+      </c>
+      <c r="T195">
+        <v>1.25</v>
+      </c>
+      <c r="U195">
+        <v>3.75</v>
+      </c>
+      <c r="V195">
+        <v>2.25</v>
+      </c>
+      <c r="W195">
+        <v>1.57</v>
+      </c>
+      <c r="X195">
+        <v>5.5</v>
+      </c>
+      <c r="Y195">
+        <v>1.14</v>
+      </c>
+      <c r="Z195">
+        <v>4.5</v>
+      </c>
+      <c r="AA195">
+        <v>4.2</v>
+      </c>
+      <c r="AB195">
+        <v>1.73</v>
+      </c>
+      <c r="AC195">
+        <v>1.01</v>
+      </c>
+      <c r="AD195">
+        <v>21</v>
+      </c>
+      <c r="AE195">
+        <v>1.16</v>
+      </c>
+      <c r="AF195">
+        <v>5.5</v>
+      </c>
+      <c r="AG195">
+        <v>1.47</v>
+      </c>
+      <c r="AH195">
+        <v>2.57</v>
+      </c>
+      <c r="AI195">
+        <v>1.53</v>
+      </c>
+      <c r="AJ195">
+        <v>2.38</v>
+      </c>
+      <c r="AK195">
+        <v>2.15</v>
+      </c>
+      <c r="AL195">
+        <v>1.22</v>
+      </c>
+      <c r="AM195">
+        <v>1.2</v>
+      </c>
+      <c r="AN195">
+        <v>1.09</v>
+      </c>
+      <c r="AO195">
+        <v>1.18</v>
+      </c>
+      <c r="AP195">
+        <v>1</v>
+      </c>
+      <c r="AQ195">
+        <v>1.33</v>
+      </c>
+      <c r="AR195">
+        <v>1.46</v>
+      </c>
+      <c r="AS195">
+        <v>1.29</v>
+      </c>
+      <c r="AT195">
+        <v>2.75</v>
+      </c>
+      <c r="AU195">
+        <v>6</v>
+      </c>
+      <c r="AV195">
+        <v>7</v>
+      </c>
+      <c r="AW195">
+        <v>7</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>18</v>
+      </c>
+      <c r="AZ195">
+        <v>13</v>
+      </c>
+      <c r="BA195">
+        <v>7</v>
+      </c>
+      <c r="BB195">
+        <v>4</v>
+      </c>
+      <c r="BC195">
+        <v>11</v>
+      </c>
+      <c r="BD195">
+        <v>2.97</v>
+      </c>
+      <c r="BE195">
+        <v>9.1</v>
+      </c>
+      <c r="BF195">
+        <v>1.56</v>
+      </c>
+      <c r="BG195">
+        <v>1.2</v>
+      </c>
+      <c r="BH195">
+        <v>3.68</v>
+      </c>
+      <c r="BI195">
+        <v>1.41</v>
+      </c>
+      <c r="BJ195">
+        <v>2.6</v>
+      </c>
+      <c r="BK195">
+        <v>1.74</v>
+      </c>
+      <c r="BL195">
+        <v>1.98</v>
+      </c>
+      <c r="BM195">
+        <v>2.19</v>
+      </c>
+      <c r="BN195">
+        <v>1.57</v>
+      </c>
+      <c r="BO195">
+        <v>2.88</v>
+      </c>
+      <c r="BP195">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7468551</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45704.55208333334</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>70</v>
+      </c>
+      <c r="H196" t="s">
+        <v>86</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="K196">
+        <v>3</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>3</v>
+      </c>
+      <c r="N196">
+        <v>4</v>
+      </c>
+      <c r="O196" t="s">
+        <v>91</v>
+      </c>
+      <c r="P196" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q196">
+        <v>5.5</v>
+      </c>
+      <c r="R196">
+        <v>2.25</v>
+      </c>
+      <c r="S196">
+        <v>2.2</v>
+      </c>
+      <c r="T196">
+        <v>1.36</v>
+      </c>
+      <c r="U196">
+        <v>3</v>
+      </c>
+      <c r="V196">
+        <v>2.63</v>
+      </c>
+      <c r="W196">
+        <v>1.44</v>
+      </c>
+      <c r="X196">
+        <v>7</v>
+      </c>
+      <c r="Y196">
+        <v>1.1</v>
+      </c>
+      <c r="Z196">
+        <v>5.4</v>
+      </c>
+      <c r="AA196">
+        <v>4.1</v>
+      </c>
+      <c r="AB196">
+        <v>1.65</v>
+      </c>
+      <c r="AC196">
+        <v>1.05</v>
+      </c>
+      <c r="AD196">
+        <v>10</v>
+      </c>
+      <c r="AE196">
+        <v>1.27</v>
+      </c>
+      <c r="AF196">
+        <v>3.94</v>
+      </c>
+      <c r="AG196">
+        <v>1.86</v>
+      </c>
+      <c r="AH196">
+        <v>1.95</v>
+      </c>
+      <c r="AI196">
+        <v>1.8</v>
+      </c>
+      <c r="AJ196">
+        <v>1.95</v>
+      </c>
+      <c r="AK196">
+        <v>2.2</v>
+      </c>
+      <c r="AL196">
+        <v>1.24</v>
+      </c>
+      <c r="AM196">
+        <v>1.16</v>
+      </c>
+      <c r="AN196">
+        <v>0.6</v>
+      </c>
+      <c r="AO196">
+        <v>1.18</v>
+      </c>
+      <c r="AP196">
+        <v>0.55</v>
+      </c>
+      <c r="AQ196">
+        <v>1.33</v>
+      </c>
+      <c r="AR196">
+        <v>1.12</v>
+      </c>
+      <c r="AS196">
+        <v>1.47</v>
+      </c>
+      <c r="AT196">
+        <v>2.59</v>
+      </c>
+      <c r="AU196">
+        <v>5</v>
+      </c>
+      <c r="AV196">
+        <v>6</v>
+      </c>
+      <c r="AW196">
+        <v>11</v>
+      </c>
+      <c r="AX196">
+        <v>4</v>
+      </c>
+      <c r="AY196">
+        <v>16</v>
+      </c>
+      <c r="AZ196">
+        <v>11</v>
+      </c>
+      <c r="BA196">
+        <v>6</v>
+      </c>
+      <c r="BB196">
+        <v>2</v>
+      </c>
+      <c r="BC196">
+        <v>8</v>
+      </c>
+      <c r="BD196">
+        <v>3.22</v>
+      </c>
+      <c r="BE196">
+        <v>9.1</v>
+      </c>
+      <c r="BF196">
+        <v>1.5</v>
+      </c>
+      <c r="BG196">
+        <v>1.24</v>
+      </c>
+      <c r="BH196">
+        <v>3.34</v>
+      </c>
+      <c r="BI196">
+        <v>1.48</v>
+      </c>
+      <c r="BJ196">
+        <v>2.4</v>
+      </c>
+      <c r="BK196">
+        <v>1.85</v>
+      </c>
+      <c r="BL196">
+        <v>1.85</v>
+      </c>
+      <c r="BM196">
+        <v>2.38</v>
+      </c>
+      <c r="BN196">
+        <v>1.49</v>
+      </c>
+      <c r="BO196">
+        <v>3.14</v>
+      </c>
+      <c r="BP196">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7468547</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45704.55208333334</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>83</v>
+      </c>
+      <c r="H197" t="s">
+        <v>84</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
+      <c r="N197">
+        <v>2</v>
+      </c>
+      <c r="O197" t="s">
+        <v>90</v>
+      </c>
+      <c r="P197" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q197">
+        <v>2.3</v>
+      </c>
+      <c r="R197">
+        <v>2.3</v>
+      </c>
+      <c r="S197">
+        <v>4.75</v>
+      </c>
+      <c r="T197">
+        <v>1.33</v>
+      </c>
+      <c r="U197">
+        <v>3.25</v>
+      </c>
+      <c r="V197">
+        <v>2.63</v>
+      </c>
+      <c r="W197">
+        <v>1.44</v>
+      </c>
+      <c r="X197">
+        <v>6.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.11</v>
+      </c>
+      <c r="Z197">
+        <v>1.75</v>
+      </c>
+      <c r="AA197">
+        <v>4.1</v>
+      </c>
+      <c r="AB197">
+        <v>4.6</v>
+      </c>
+      <c r="AC197">
+        <v>1.04</v>
+      </c>
+      <c r="AD197">
+        <v>11</v>
+      </c>
+      <c r="AE197">
+        <v>1.24</v>
+      </c>
+      <c r="AF197">
+        <v>3.8</v>
+      </c>
+      <c r="AG197">
+        <v>1.73</v>
+      </c>
+      <c r="AH197">
+        <v>2</v>
+      </c>
+      <c r="AI197">
+        <v>1.67</v>
+      </c>
+      <c r="AJ197">
+        <v>2.1</v>
+      </c>
+      <c r="AK197">
+        <v>1.21</v>
+      </c>
+      <c r="AL197">
+        <v>1.25</v>
+      </c>
+      <c r="AM197">
+        <v>2.05</v>
+      </c>
+      <c r="AN197">
+        <v>1.4</v>
+      </c>
+      <c r="AO197">
+        <v>0.82</v>
+      </c>
+      <c r="AP197">
+        <v>1.27</v>
+      </c>
+      <c r="AQ197">
+        <v>1</v>
+      </c>
+      <c r="AR197">
+        <v>1.69</v>
+      </c>
+      <c r="AS197">
+        <v>1.23</v>
+      </c>
+      <c r="AT197">
+        <v>2.92</v>
+      </c>
+      <c r="AU197">
+        <v>0</v>
+      </c>
+      <c r="AV197">
+        <v>5</v>
+      </c>
+      <c r="AW197">
+        <v>8</v>
+      </c>
+      <c r="AX197">
+        <v>9</v>
+      </c>
+      <c r="AY197">
+        <v>10</v>
+      </c>
+      <c r="AZ197">
+        <v>17</v>
+      </c>
+      <c r="BA197">
+        <v>7</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>10</v>
+      </c>
+      <c r="BD197">
+        <v>1.32</v>
+      </c>
+      <c r="BE197">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF197">
+        <v>4.4</v>
+      </c>
+      <c r="BG197">
+        <v>1.39</v>
+      </c>
+      <c r="BH197">
+        <v>2.67</v>
+      </c>
+      <c r="BI197">
+        <v>1.73</v>
+      </c>
+      <c r="BJ197">
+        <v>1.99</v>
+      </c>
+      <c r="BK197">
+        <v>2.19</v>
+      </c>
+      <c r="BL197">
+        <v>1.57</v>
+      </c>
+      <c r="BM197">
+        <v>2.92</v>
+      </c>
+      <c r="BN197">
+        <v>1.31</v>
+      </c>
+      <c r="BO197">
+        <v>4.2</v>
+      </c>
+      <c r="BP197">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7468550</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45704.55208333334</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>72</v>
+      </c>
+      <c r="H198" t="s">
+        <v>77</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
+        <v>90</v>
+      </c>
+      <c r="P198" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q198">
+        <v>2.6</v>
+      </c>
+      <c r="R198">
+        <v>2.2</v>
+      </c>
+      <c r="S198">
+        <v>4.33</v>
+      </c>
+      <c r="T198">
+        <v>1.4</v>
+      </c>
+      <c r="U198">
+        <v>2.75</v>
+      </c>
+      <c r="V198">
+        <v>3</v>
+      </c>
+      <c r="W198">
+        <v>1.36</v>
+      </c>
+      <c r="X198">
+        <v>8</v>
+      </c>
+      <c r="Y198">
+        <v>1.08</v>
+      </c>
+      <c r="Z198">
+        <v>1.99</v>
+      </c>
+      <c r="AA198">
+        <v>3.5</v>
+      </c>
+      <c r="AB198">
+        <v>4.1</v>
+      </c>
+      <c r="AC198">
+        <v>1.06</v>
+      </c>
+      <c r="AD198">
+        <v>9</v>
+      </c>
+      <c r="AE198">
+        <v>1.32</v>
+      </c>
+      <c r="AF198">
+        <v>3.56</v>
+      </c>
+      <c r="AG198">
+        <v>1.98</v>
+      </c>
+      <c r="AH198">
+        <v>1.84</v>
+      </c>
+      <c r="AI198">
+        <v>1.8</v>
+      </c>
+      <c r="AJ198">
+        <v>1.95</v>
+      </c>
+      <c r="AK198">
+        <v>1.25</v>
+      </c>
+      <c r="AL198">
+        <v>1.29</v>
+      </c>
+      <c r="AM198">
+        <v>1.82</v>
+      </c>
+      <c r="AN198">
+        <v>0.91</v>
+      </c>
+      <c r="AO198">
+        <v>1.2</v>
+      </c>
+      <c r="AP198">
+        <v>0.83</v>
+      </c>
+      <c r="AQ198">
+        <v>1.36</v>
+      </c>
+      <c r="AR198">
+        <v>1.26</v>
+      </c>
+      <c r="AS198">
+        <v>1.07</v>
+      </c>
+      <c r="AT198">
+        <v>2.33</v>
+      </c>
+      <c r="AU198">
+        <v>5</v>
+      </c>
+      <c r="AV198">
+        <v>3</v>
+      </c>
+      <c r="AW198">
+        <v>10</v>
+      </c>
+      <c r="AX198">
+        <v>6</v>
+      </c>
+      <c r="AY198">
+        <v>19</v>
+      </c>
+      <c r="AZ198">
+        <v>10</v>
+      </c>
+      <c r="BA198">
+        <v>1</v>
+      </c>
+      <c r="BB198">
+        <v>4</v>
+      </c>
+      <c r="BC198">
+        <v>5</v>
+      </c>
+      <c r="BD198">
+        <v>1.46</v>
+      </c>
+      <c r="BE198">
+        <v>8.9</v>
+      </c>
+      <c r="BF198">
+        <v>3.44</v>
+      </c>
+      <c r="BG198">
+        <v>1.32</v>
+      </c>
+      <c r="BH198">
+        <v>2.88</v>
+      </c>
+      <c r="BI198">
+        <v>1.6</v>
+      </c>
+      <c r="BJ198">
+        <v>2.14</v>
+      </c>
+      <c r="BK198">
+        <v>2.06</v>
+      </c>
+      <c r="BL198">
+        <v>1.68</v>
+      </c>
+      <c r="BM198">
+        <v>2.71</v>
+      </c>
+      <c r="BN198">
+        <v>1.38</v>
+      </c>
+      <c r="BO198">
+        <v>3.72</v>
+      </c>
+      <c r="BP198">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7468549</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45704.69791666666</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>78</v>
+      </c>
+      <c r="H199" t="s">
+        <v>81</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>90</v>
+      </c>
+      <c r="P199" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q199">
+        <v>3.2</v>
+      </c>
+      <c r="R199">
+        <v>2.1</v>
+      </c>
+      <c r="S199">
+        <v>3.4</v>
+      </c>
+      <c r="T199">
+        <v>1.4</v>
+      </c>
+      <c r="U199">
+        <v>2.75</v>
+      </c>
+      <c r="V199">
+        <v>3</v>
+      </c>
+      <c r="W199">
+        <v>1.36</v>
+      </c>
+      <c r="X199">
+        <v>8</v>
+      </c>
+      <c r="Y199">
+        <v>1.08</v>
+      </c>
+      <c r="Z199">
+        <v>2.54</v>
+      </c>
+      <c r="AA199">
+        <v>3.36</v>
+      </c>
+      <c r="AB199">
+        <v>2.91</v>
+      </c>
+      <c r="AC199">
+        <v>1.06</v>
+      </c>
+      <c r="AD199">
+        <v>10</v>
+      </c>
+      <c r="AE199">
+        <v>1.33</v>
+      </c>
+      <c r="AF199">
+        <v>3.4</v>
+      </c>
+      <c r="AG199">
+        <v>2.01</v>
+      </c>
+      <c r="AH199">
+        <v>1.81</v>
+      </c>
+      <c r="AI199">
+        <v>1.75</v>
+      </c>
+      <c r="AJ199">
+        <v>2</v>
+      </c>
+      <c r="AK199">
+        <v>1.43</v>
+      </c>
+      <c r="AL199">
+        <v>1.31</v>
+      </c>
+      <c r="AM199">
+        <v>1.5</v>
+      </c>
+      <c r="AN199">
+        <v>1.73</v>
+      </c>
+      <c r="AO199">
+        <v>1.4</v>
+      </c>
+      <c r="AP199">
+        <v>1.58</v>
+      </c>
+      <c r="AQ199">
+        <v>1.55</v>
+      </c>
+      <c r="AR199">
+        <v>1.59</v>
+      </c>
+      <c r="AS199">
+        <v>1.5</v>
+      </c>
+      <c r="AT199">
+        <v>3.09</v>
+      </c>
+      <c r="AU199">
+        <v>3</v>
+      </c>
+      <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
+        <v>2</v>
+      </c>
+      <c r="AX199">
+        <v>12</v>
+      </c>
+      <c r="AY199">
+        <v>6</v>
+      </c>
+      <c r="AZ199">
+        <v>23</v>
+      </c>
+      <c r="BA199">
+        <v>4</v>
+      </c>
+      <c r="BB199">
+        <v>8</v>
+      </c>
+      <c r="BC199">
+        <v>12</v>
+      </c>
+      <c r="BD199">
+        <v>1.99</v>
+      </c>
+      <c r="BE199">
+        <v>8.1</v>
+      </c>
+      <c r="BF199">
+        <v>2.17</v>
+      </c>
+      <c r="BG199">
+        <v>1.42</v>
+      </c>
+      <c r="BH199">
+        <v>2.57</v>
+      </c>
+      <c r="BI199">
+        <v>1.78</v>
+      </c>
+      <c r="BJ199">
+        <v>1.93</v>
+      </c>
+      <c r="BK199">
+        <v>2.28</v>
+      </c>
+      <c r="BL199">
+        <v>1.53</v>
+      </c>
+      <c r="BM199">
+        <v>3.08</v>
+      </c>
+      <c r="BN199">
+        <v>1.28</v>
+      </c>
+      <c r="BO199">
+        <v>4.4</v>
+      </c>
+      <c r="BP199">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,9 @@
     <t>['44', '45', '49', '54', '64', '81', '90+5']</t>
   </si>
   <si>
+    <t>['10']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -974,9 +977,6 @@
   </si>
   <si>
     <t>['25']</t>
-  </si>
-  <si>
-    <t>['10']</t>
   </si>
   <si>
     <t>['62', '83']</t>
@@ -1389,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1645,7 +1645,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1851,7 +1851,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2057,7 +2057,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2469,7 +2469,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2675,7 +2675,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3371,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3705,7 +3705,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4117,7 +4117,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4529,7 +4529,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5147,7 +5147,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5228,7 +5228,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ19">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5353,7 +5353,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5765,7 +5765,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5971,7 +5971,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6177,7 +6177,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6383,7 +6383,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6795,7 +6795,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7001,7 +7001,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7619,7 +7619,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ33">
         <v>0.3</v>
@@ -8237,7 +8237,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8443,7 +8443,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8524,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
         <v>1.39</v>
@@ -9267,7 +9267,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9473,7 +9473,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9551,7 +9551,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ40">
         <v>1.73</v>
@@ -10297,7 +10297,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10503,7 +10503,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10709,7 +10709,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11121,7 +11121,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11533,7 +11533,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11739,7 +11739,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11945,7 +11945,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12151,7 +12151,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12357,7 +12357,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12438,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR54">
         <v>1.25</v>
@@ -12975,7 +12975,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13387,7 +13387,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13465,7 +13465,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ59">
         <v>1.4</v>
@@ -14005,7 +14005,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14211,7 +14211,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14417,7 +14417,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15035,7 +15035,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15241,7 +15241,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15447,7 +15447,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15653,7 +15653,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15859,7 +15859,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16065,7 +16065,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16146,7 +16146,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ72">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16271,7 +16271,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16555,7 +16555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16683,7 +16683,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16889,7 +16889,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17095,7 +17095,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17301,7 +17301,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17507,7 +17507,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17713,7 +17713,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18125,7 +18125,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18949,7 +18949,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19442,7 +19442,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR88">
         <v>1.33</v>
@@ -19979,7 +19979,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20185,7 +20185,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20391,7 +20391,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20597,7 +20597,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20803,7 +20803,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21009,7 +21009,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21215,7 +21215,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21293,7 +21293,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ97">
         <v>1.2</v>
@@ -21421,7 +21421,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21627,7 +21627,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21708,7 +21708,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ99">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR99">
         <v>1.18</v>
@@ -22039,7 +22039,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22451,7 +22451,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23481,7 +23481,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23687,7 +23687,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23893,7 +23893,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24177,7 +24177,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ111">
         <v>0.17</v>
@@ -24717,7 +24717,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24923,7 +24923,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25335,7 +25335,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25541,7 +25541,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26365,7 +26365,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26571,7 +26571,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27064,7 +27064,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27395,7 +27395,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27807,7 +27807,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28013,7 +28013,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28425,7 +28425,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28631,7 +28631,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29121,7 +29121,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ135">
         <v>1.36</v>
@@ -29455,7 +29455,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29661,7 +29661,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29867,7 +29867,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29948,7 +29948,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ139">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR139">
         <v>1.2</v>
@@ -30073,7 +30073,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -31309,7 +31309,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31721,7 +31721,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31927,7 +31927,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32133,7 +32133,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32211,7 +32211,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ150">
         <v>2.45</v>
@@ -32339,7 +32339,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32545,7 +32545,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32751,7 +32751,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33163,7 +33163,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33575,7 +33575,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33781,7 +33781,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33859,7 +33859,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ158">
         <v>1.09</v>
@@ -34811,7 +34811,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35223,7 +35223,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35635,7 +35635,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35716,7 +35716,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ167">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR167">
         <v>2.34</v>
@@ -35841,7 +35841,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36047,7 +36047,7 @@
         <v>105</v>
       </c>
       <c r="P169" t="s">
-        <v>320</v>
+        <v>229</v>
       </c>
       <c r="Q169">
         <v>3.75</v>
@@ -37695,7 +37695,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37979,7 +37979,7 @@
         <v>0.9</v>
       </c>
       <c r="AP178">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -39836,7 +39836,7 @@
         <v>2</v>
       </c>
       <c r="AQ187">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR187">
         <v>1.71</v>
@@ -41197,7 +41197,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -42305,7 +42305,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ199">
         <v>1.55</v>
@@ -42384,6 +42384,212 @@
       </c>
       <c r="BP199">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7468553</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>78</v>
+      </c>
+      <c r="H200" t="s">
+        <v>72</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
+        <v>229</v>
+      </c>
+      <c r="P200" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q200">
+        <v>2.4</v>
+      </c>
+      <c r="R200">
+        <v>2.2</v>
+      </c>
+      <c r="S200">
+        <v>5</v>
+      </c>
+      <c r="T200">
+        <v>1.4</v>
+      </c>
+      <c r="U200">
+        <v>2.75</v>
+      </c>
+      <c r="V200">
+        <v>3</v>
+      </c>
+      <c r="W200">
+        <v>1.36</v>
+      </c>
+      <c r="X200">
+        <v>8</v>
+      </c>
+      <c r="Y200">
+        <v>1.08</v>
+      </c>
+      <c r="Z200">
+        <v>1.8</v>
+      </c>
+      <c r="AA200">
+        <v>3.7</v>
+      </c>
+      <c r="AB200">
+        <v>4.75</v>
+      </c>
+      <c r="AC200">
+        <v>1.06</v>
+      </c>
+      <c r="AD200">
+        <v>10</v>
+      </c>
+      <c r="AE200">
+        <v>1.35</v>
+      </c>
+      <c r="AF200">
+        <v>3.25</v>
+      </c>
+      <c r="AG200">
+        <v>2.02</v>
+      </c>
+      <c r="AH200">
+        <v>1.8</v>
+      </c>
+      <c r="AI200">
+        <v>1.91</v>
+      </c>
+      <c r="AJ200">
+        <v>1.91</v>
+      </c>
+      <c r="AK200">
+        <v>1.2</v>
+      </c>
+      <c r="AL200">
+        <v>1.27</v>
+      </c>
+      <c r="AM200">
+        <v>2</v>
+      </c>
+      <c r="AN200">
+        <v>1.58</v>
+      </c>
+      <c r="AO200">
+        <v>1.2</v>
+      </c>
+      <c r="AP200">
+        <v>1.69</v>
+      </c>
+      <c r="AQ200">
+        <v>1.09</v>
+      </c>
+      <c r="AR200">
+        <v>1.51</v>
+      </c>
+      <c r="AS200">
+        <v>1.26</v>
+      </c>
+      <c r="AT200">
+        <v>2.77</v>
+      </c>
+      <c r="AU200">
+        <v>6</v>
+      </c>
+      <c r="AV200">
+        <v>0</v>
+      </c>
+      <c r="AW200">
+        <v>21</v>
+      </c>
+      <c r="AX200">
+        <v>4</v>
+      </c>
+      <c r="AY200">
+        <v>38</v>
+      </c>
+      <c r="AZ200">
+        <v>6</v>
+      </c>
+      <c r="BA200">
+        <v>9</v>
+      </c>
+      <c r="BB200">
+        <v>2</v>
+      </c>
+      <c r="BC200">
+        <v>11</v>
+      </c>
+      <c r="BD200">
+        <v>1.5</v>
+      </c>
+      <c r="BE200">
+        <v>6.75</v>
+      </c>
+      <c r="BF200">
+        <v>2.9</v>
+      </c>
+      <c r="BG200">
+        <v>1.44</v>
+      </c>
+      <c r="BH200">
+        <v>2.55</v>
+      </c>
+      <c r="BI200">
+        <v>1.73</v>
+      </c>
+      <c r="BJ200">
+        <v>1.96</v>
+      </c>
+      <c r="BK200">
+        <v>2.18</v>
+      </c>
+      <c r="BL200">
+        <v>1.58</v>
+      </c>
+      <c r="BM200">
+        <v>2.8</v>
+      </c>
+      <c r="BN200">
+        <v>1.37</v>
+      </c>
+      <c r="BO200">
+        <v>3.7</v>
+      </c>
+      <c r="BP200">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,15 @@
     <t>['10']</t>
   </si>
   <si>
+    <t>['22', '42']</t>
+  </si>
+  <si>
+    <t>['36', '52', '73']</t>
+  </si>
+  <si>
+    <t>['34', '77', '90+1']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1028,6 +1037,9 @@
   </si>
   <si>
     <t>['80', '86']</t>
+  </si>
+  <si>
+    <t>['7', '17', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1645,7 +1657,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1851,7 +1863,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1932,7 +1944,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ3">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2057,7 +2069,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2469,7 +2481,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2547,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6">
         <v>1.33</v>
@@ -2675,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3705,7 +3717,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3786,7 +3798,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3989,10 +4001,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4117,7 +4129,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4195,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4529,7 +4541,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5147,7 +5159,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5353,7 +5365,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5765,7 +5777,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5971,7 +5983,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6052,7 +6064,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ23">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR23">
         <v>1.52</v>
@@ -6177,7 +6189,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6383,7 +6395,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6795,7 +6807,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7001,7 +7013,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7079,7 +7091,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>2.45</v>
@@ -7285,7 +7297,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ29">
         <v>1.55</v>
@@ -7619,7 +7631,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7697,10 +7709,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ31">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -8237,7 +8249,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8318,7 +8330,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8443,7 +8455,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9267,7 +9279,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9345,7 +9357,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9473,7 +9485,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10297,7 +10309,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10503,7 +10515,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10709,7 +10721,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10790,7 +10802,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR46">
         <v>1.4</v>
@@ -10993,7 +11005,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ47">
         <v>1.09</v>
@@ -11121,7 +11133,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11533,7 +11545,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11739,7 +11751,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11945,7 +11957,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12151,7 +12163,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12357,7 +12369,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12644,7 +12656,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ55">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR55">
         <v>1.26</v>
@@ -12850,7 +12862,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ56">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12975,7 +12987,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13053,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ57">
         <v>0.45</v>
@@ -13259,7 +13271,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1.2</v>
@@ -13387,7 +13399,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13468,7 +13480,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ59">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -14005,7 +14017,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14211,7 +14223,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14417,7 +14429,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15035,7 +15047,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15113,7 +15125,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ67">
         <v>1.73</v>
@@ -15241,7 +15253,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15447,7 +15459,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15653,7 +15665,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15734,7 +15746,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.25</v>
@@ -15859,7 +15871,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16065,7 +16077,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16143,7 +16155,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ72">
         <v>1.09</v>
@@ -16271,7 +16283,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16352,7 +16364,7 @@
         <v>1</v>
       </c>
       <c r="AQ73">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16683,7 +16695,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16889,7 +16901,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17095,7 +17107,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17301,7 +17313,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17507,7 +17519,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17713,7 +17725,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18000,7 +18012,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ81">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18125,7 +18137,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18412,7 +18424,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.55</v>
@@ -18615,7 +18627,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18949,7 +18961,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19233,7 +19245,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19645,7 +19657,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ89">
         <v>0.4</v>
@@ -19979,7 +19991,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20060,7 +20072,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -20185,7 +20197,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20391,7 +20403,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20472,7 +20484,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ93">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20597,7 +20609,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20803,7 +20815,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21009,7 +21021,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21215,7 +21227,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21421,7 +21433,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21627,7 +21639,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22039,7 +22051,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22451,7 +22463,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22532,7 +22544,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ103">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR103">
         <v>1.68</v>
@@ -22735,7 +22747,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ104">
         <v>0.3</v>
@@ -23147,7 +23159,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.4</v>
@@ -23353,10 +23365,10 @@
         <v>1.2</v>
       </c>
       <c r="AP107">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.49</v>
@@ -23481,7 +23493,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23687,7 +23699,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23893,7 +23905,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24717,7 +24729,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24923,7 +24935,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25004,7 +25016,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25335,7 +25347,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25541,7 +25553,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25622,7 +25634,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ118">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -25825,7 +25837,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.09</v>
@@ -26031,7 +26043,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ120">
         <v>2.45</v>
@@ -26365,7 +26377,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26571,7 +26583,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27395,7 +27407,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27473,10 +27485,10 @@
         <v>2.57</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ127">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR127">
         <v>1.3</v>
@@ -27807,7 +27819,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28013,7 +28025,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28091,7 +28103,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ130">
         <v>1.73</v>
@@ -28300,7 +28312,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ131">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -28425,7 +28437,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28631,7 +28643,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29124,7 +29136,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR135">
         <v>1.64</v>
@@ -29455,7 +29467,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29661,7 +29673,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29867,7 +29879,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29945,7 +29957,7 @@
         <v>1.57</v>
       </c>
       <c r="AP139">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ139">
         <v>1.09</v>
@@ -30073,7 +30085,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30151,7 +30163,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>0.92</v>
@@ -31309,7 +31321,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31390,7 +31402,7 @@
         <v>1</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -31593,7 +31605,7 @@
         <v>1.63</v>
       </c>
       <c r="AP147">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ147">
         <v>1.55</v>
@@ -31721,7 +31733,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31927,7 +31939,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32133,7 +32145,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32214,7 +32226,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ150">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR150">
         <v>1.57</v>
@@ -32339,7 +32351,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32545,7 +32557,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32626,7 +32638,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR152">
         <v>1.44</v>
@@ -32751,7 +32763,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33163,7 +33175,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33244,7 +33256,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR155">
         <v>1.44</v>
@@ -33447,7 +33459,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
         <v>1.33</v>
@@ -33575,7 +33587,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33781,7 +33793,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34271,7 +34283,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ160">
         <v>0.92</v>
@@ -34811,7 +34823,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35095,7 +35107,7 @@
         <v>0.11</v>
       </c>
       <c r="AP164">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ164">
         <v>0.17</v>
@@ -35223,7 +35235,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35635,7 +35647,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35841,7 +35853,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36253,7 +36265,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36540,7 +36552,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR171">
         <v>1.64</v>
@@ -36746,7 +36758,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ172">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR172">
         <v>1.58</v>
@@ -36871,7 +36883,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37077,7 +37089,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37283,7 +37295,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37567,7 +37579,7 @@
         <v>0.2</v>
       </c>
       <c r="AP176">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ176">
         <v>0.17</v>
@@ -37695,7 +37707,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38313,7 +38325,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38519,7 +38531,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38725,7 +38737,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39012,7 +39024,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ183">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR183">
         <v>2.35</v>
@@ -39343,7 +39355,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39421,7 +39433,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39549,7 +39561,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39627,7 +39639,7 @@
         <v>0.11</v>
       </c>
       <c r="AP186">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ186">
         <v>0.4</v>
@@ -39961,7 +39973,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40039,7 +40051,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ188">
         <v>1.2</v>
@@ -40373,7 +40385,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40454,7 +40466,7 @@
         <v>1</v>
       </c>
       <c r="AQ190">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40579,7 +40591,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40785,7 +40797,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41197,7 +41209,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41403,7 +41415,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41609,7 +41621,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q196">
         <v>5.5</v>
@@ -41815,7 +41827,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q197">
         <v>2.3</v>
@@ -42102,7 +42114,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ198">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR198">
         <v>1.26</v>
@@ -42227,7 +42239,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42590,6 +42602,624 @@
       </c>
       <c r="BP200">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7468555</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>81</v>
+      </c>
+      <c r="H201" t="s">
+        <v>73</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>3</v>
+      </c>
+      <c r="L201">
+        <v>2</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>3</v>
+      </c>
+      <c r="O201" t="s">
+        <v>230</v>
+      </c>
+      <c r="P201" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q201">
+        <v>2.75</v>
+      </c>
+      <c r="R201">
+        <v>2.3</v>
+      </c>
+      <c r="S201">
+        <v>3.6</v>
+      </c>
+      <c r="T201">
+        <v>1.33</v>
+      </c>
+      <c r="U201">
+        <v>3.25</v>
+      </c>
+      <c r="V201">
+        <v>2.5</v>
+      </c>
+      <c r="W201">
+        <v>1.5</v>
+      </c>
+      <c r="X201">
+        <v>6.5</v>
+      </c>
+      <c r="Y201">
+        <v>1.11</v>
+      </c>
+      <c r="Z201">
+        <v>2.24</v>
+      </c>
+      <c r="AA201">
+        <v>3.64</v>
+      </c>
+      <c r="AB201">
+        <v>3.19</v>
+      </c>
+      <c r="AC201">
+        <v>1.03</v>
+      </c>
+      <c r="AD201">
+        <v>15</v>
+      </c>
+      <c r="AE201">
+        <v>1.22</v>
+      </c>
+      <c r="AF201">
+        <v>4.33</v>
+      </c>
+      <c r="AG201">
+        <v>1.73</v>
+      </c>
+      <c r="AH201">
+        <v>2</v>
+      </c>
+      <c r="AI201">
+        <v>1.57</v>
+      </c>
+      <c r="AJ201">
+        <v>2.25</v>
+      </c>
+      <c r="AK201">
+        <v>1.35</v>
+      </c>
+      <c r="AL201">
+        <v>1.27</v>
+      </c>
+      <c r="AM201">
+        <v>1.68</v>
+      </c>
+      <c r="AN201">
+        <v>1.91</v>
+      </c>
+      <c r="AO201">
+        <v>1.4</v>
+      </c>
+      <c r="AP201">
+        <v>2</v>
+      </c>
+      <c r="AQ201">
+        <v>1.27</v>
+      </c>
+      <c r="AR201">
+        <v>1.63</v>
+      </c>
+      <c r="AS201">
+        <v>1.62</v>
+      </c>
+      <c r="AT201">
+        <v>3.25</v>
+      </c>
+      <c r="AU201">
+        <v>6</v>
+      </c>
+      <c r="AV201">
+        <v>4</v>
+      </c>
+      <c r="AW201">
+        <v>3</v>
+      </c>
+      <c r="AX201">
+        <v>8</v>
+      </c>
+      <c r="AY201">
+        <v>12</v>
+      </c>
+      <c r="AZ201">
+        <v>16</v>
+      </c>
+      <c r="BA201">
+        <v>1</v>
+      </c>
+      <c r="BB201">
+        <v>6</v>
+      </c>
+      <c r="BC201">
+        <v>7</v>
+      </c>
+      <c r="BD201">
+        <v>1.74</v>
+      </c>
+      <c r="BE201">
+        <v>6.25</v>
+      </c>
+      <c r="BF201">
+        <v>2.4</v>
+      </c>
+      <c r="BG201">
+        <v>1.35</v>
+      </c>
+      <c r="BH201">
+        <v>2.9</v>
+      </c>
+      <c r="BI201">
+        <v>1.6</v>
+      </c>
+      <c r="BJ201">
+        <v>2.17</v>
+      </c>
+      <c r="BK201">
+        <v>1.98</v>
+      </c>
+      <c r="BL201">
+        <v>1.72</v>
+      </c>
+      <c r="BM201">
+        <v>2.5</v>
+      </c>
+      <c r="BN201">
+        <v>1.46</v>
+      </c>
+      <c r="BO201">
+        <v>3.3</v>
+      </c>
+      <c r="BP201">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7468558</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45710.625</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>82</v>
+      </c>
+      <c r="H202" t="s">
+        <v>77</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>2</v>
+      </c>
+      <c r="K202">
+        <v>3</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>3</v>
+      </c>
+      <c r="N202">
+        <v>6</v>
+      </c>
+      <c r="O202" t="s">
+        <v>231</v>
+      </c>
+      <c r="P202" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q202">
+        <v>3.1</v>
+      </c>
+      <c r="R202">
+        <v>2.1</v>
+      </c>
+      <c r="S202">
+        <v>3.6</v>
+      </c>
+      <c r="T202">
+        <v>1.44</v>
+      </c>
+      <c r="U202">
+        <v>2.63</v>
+      </c>
+      <c r="V202">
+        <v>3.25</v>
+      </c>
+      <c r="W202">
+        <v>1.33</v>
+      </c>
+      <c r="X202">
+        <v>9</v>
+      </c>
+      <c r="Y202">
+        <v>1.07</v>
+      </c>
+      <c r="Z202">
+        <v>2.5</v>
+      </c>
+      <c r="AA202">
+        <v>3.31</v>
+      </c>
+      <c r="AB202">
+        <v>3</v>
+      </c>
+      <c r="AC202">
+        <v>1.07</v>
+      </c>
+      <c r="AD202">
+        <v>9.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.33</v>
+      </c>
+      <c r="AF202">
+        <v>3.3</v>
+      </c>
+      <c r="AG202">
+        <v>1.93</v>
+      </c>
+      <c r="AH202">
+        <v>1.88</v>
+      </c>
+      <c r="AI202">
+        <v>1.8</v>
+      </c>
+      <c r="AJ202">
+        <v>1.95</v>
+      </c>
+      <c r="AK202">
+        <v>1.39</v>
+      </c>
+      <c r="AL202">
+        <v>1.31</v>
+      </c>
+      <c r="AM202">
+        <v>1.55</v>
+      </c>
+      <c r="AN202">
+        <v>1.6</v>
+      </c>
+      <c r="AO202">
+        <v>1.36</v>
+      </c>
+      <c r="AP202">
+        <v>1.55</v>
+      </c>
+      <c r="AQ202">
+        <v>1.33</v>
+      </c>
+      <c r="AR202">
+        <v>1.29</v>
+      </c>
+      <c r="AS202">
+        <v>1.08</v>
+      </c>
+      <c r="AT202">
+        <v>2.37</v>
+      </c>
+      <c r="AU202">
+        <v>9</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>11</v>
+      </c>
+      <c r="AX202">
+        <v>8</v>
+      </c>
+      <c r="AY202">
+        <v>25</v>
+      </c>
+      <c r="AZ202">
+        <v>13</v>
+      </c>
+      <c r="BA202">
+        <v>4</v>
+      </c>
+      <c r="BB202">
+        <v>3</v>
+      </c>
+      <c r="BC202">
+        <v>7</v>
+      </c>
+      <c r="BD202">
+        <v>1.81</v>
+      </c>
+      <c r="BE202">
+        <v>6.4</v>
+      </c>
+      <c r="BF202">
+        <v>2.2</v>
+      </c>
+      <c r="BG202">
+        <v>1.4</v>
+      </c>
+      <c r="BH202">
+        <v>2.7</v>
+      </c>
+      <c r="BI202">
+        <v>1.66</v>
+      </c>
+      <c r="BJ202">
+        <v>2.06</v>
+      </c>
+      <c r="BK202">
+        <v>2.07</v>
+      </c>
+      <c r="BL202">
+        <v>1.66</v>
+      </c>
+      <c r="BM202">
+        <v>2.65</v>
+      </c>
+      <c r="BN202">
+        <v>1.41</v>
+      </c>
+      <c r="BO202">
+        <v>3.55</v>
+      </c>
+      <c r="BP202">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7468559</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45710.71180555555</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>74</v>
+      </c>
+      <c r="H203" t="s">
+        <v>87</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>3</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>3</v>
+      </c>
+      <c r="O203" t="s">
+        <v>232</v>
+      </c>
+      <c r="P203" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q203">
+        <v>5</v>
+      </c>
+      <c r="R203">
+        <v>2.4</v>
+      </c>
+      <c r="S203">
+        <v>2.1</v>
+      </c>
+      <c r="T203">
+        <v>1.3</v>
+      </c>
+      <c r="U203">
+        <v>3.4</v>
+      </c>
+      <c r="V203">
+        <v>2.38</v>
+      </c>
+      <c r="W203">
+        <v>1.53</v>
+      </c>
+      <c r="X203">
+        <v>6</v>
+      </c>
+      <c r="Y203">
+        <v>1.13</v>
+      </c>
+      <c r="Z203">
+        <v>5</v>
+      </c>
+      <c r="AA203">
+        <v>4.1</v>
+      </c>
+      <c r="AB203">
+        <v>1.7</v>
+      </c>
+      <c r="AC203">
+        <v>1.03</v>
+      </c>
+      <c r="AD203">
+        <v>17</v>
+      </c>
+      <c r="AE203">
+        <v>1.2</v>
+      </c>
+      <c r="AF203">
+        <v>4.5</v>
+      </c>
+      <c r="AG203">
+        <v>1.73</v>
+      </c>
+      <c r="AH203">
+        <v>2</v>
+      </c>
+      <c r="AI203">
+        <v>1.67</v>
+      </c>
+      <c r="AJ203">
+        <v>2.1</v>
+      </c>
+      <c r="AK203">
+        <v>2.25</v>
+      </c>
+      <c r="AL203">
+        <v>1.22</v>
+      </c>
+      <c r="AM203">
+        <v>1.17</v>
+      </c>
+      <c r="AN203">
+        <v>1.82</v>
+      </c>
+      <c r="AO203">
+        <v>2.45</v>
+      </c>
+      <c r="AP203">
+        <v>1.92</v>
+      </c>
+      <c r="AQ203">
+        <v>2.25</v>
+      </c>
+      <c r="AR203">
+        <v>1.31</v>
+      </c>
+      <c r="AS203">
+        <v>1.5</v>
+      </c>
+      <c r="AT203">
+        <v>2.81</v>
+      </c>
+      <c r="AU203">
+        <v>7</v>
+      </c>
+      <c r="AV203">
+        <v>4</v>
+      </c>
+      <c r="AW203">
+        <v>4</v>
+      </c>
+      <c r="AX203">
+        <v>5</v>
+      </c>
+      <c r="AY203">
+        <v>12</v>
+      </c>
+      <c r="AZ203">
+        <v>10</v>
+      </c>
+      <c r="BA203">
+        <v>2</v>
+      </c>
+      <c r="BB203">
+        <v>5</v>
+      </c>
+      <c r="BC203">
+        <v>7</v>
+      </c>
+      <c r="BD203">
+        <v>3.15</v>
+      </c>
+      <c r="BE203">
+        <v>6.75</v>
+      </c>
+      <c r="BF203">
+        <v>1.45</v>
+      </c>
+      <c r="BG203">
+        <v>1.38</v>
+      </c>
+      <c r="BH203">
+        <v>2.7</v>
+      </c>
+      <c r="BI203">
+        <v>1.65</v>
+      </c>
+      <c r="BJ203">
+        <v>2.08</v>
+      </c>
+      <c r="BK203">
+        <v>2.05</v>
+      </c>
+      <c r="BL203">
+        <v>1.67</v>
+      </c>
+      <c r="BM203">
+        <v>2.63</v>
+      </c>
+      <c r="BN203">
+        <v>1.41</v>
+      </c>
+      <c r="BO203">
+        <v>3.4</v>
+      </c>
+      <c r="BP203">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="347">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,13 +706,22 @@
     <t>['10']</t>
   </si>
   <si>
-    <t>['22', '42']</t>
+    <t>['22', '43']</t>
   </si>
   <si>
     <t>['36', '52', '73']</t>
   </si>
   <si>
     <t>['34', '77', '90+1']</t>
+  </si>
+  <si>
+    <t>['36', '60', '90+5']</t>
+  </si>
+  <si>
+    <t>['30', '65']</t>
+  </si>
+  <si>
+    <t>['83', '90+2']</t>
   </si>
   <si>
     <t>['3', '84', '86', '90']</t>
@@ -1040,6 +1049,12 @@
   </si>
   <si>
     <t>['7', '17', '90+4']</t>
+  </si>
+  <si>
+    <t>['9', '56', '63', '78']</t>
+  </si>
+  <si>
+    <t>['53', '59', '85']</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1657,7 +1672,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1735,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1863,7 +1878,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2069,7 +2084,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2481,7 +2496,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2687,7 +2702,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3180,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3592,7 +3607,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ11">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3717,7 +3732,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3795,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>1.27</v>
@@ -4129,7 +4144,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4416,7 +4431,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4541,7 +4556,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4619,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.4</v>
@@ -4825,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ17">
         <v>0.45</v>
@@ -5031,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ18">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5159,7 +5174,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5365,7 +5380,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5443,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5777,7 +5792,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5983,7 +5998,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6189,7 +6204,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6270,7 +6285,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ24">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -6395,7 +6410,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6679,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ26">
         <v>0.45</v>
@@ -6807,7 +6822,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7013,7 +7028,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7094,7 +7109,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7631,7 +7646,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7918,7 +7933,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>2.81</v>
@@ -8124,7 +8139,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ33">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR33">
         <v>2.21</v>
@@ -8249,7 +8264,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8327,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8455,7 +8470,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8533,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
         <v>1.09</v>
@@ -9151,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ38">
         <v>0.17</v>
@@ -9279,7 +9294,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9485,7 +9500,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9566,7 +9581,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ40">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9772,7 +9787,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -10184,7 +10199,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10309,7 +10324,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10515,7 +10530,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10721,7 +10736,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10799,7 +10814,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46">
         <v>2.25</v>
@@ -11008,7 +11023,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR47">
         <v>1.61</v>
@@ -11133,7 +11148,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11545,7 +11560,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11623,7 +11638,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ50">
         <v>1.55</v>
@@ -11751,7 +11766,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11832,7 +11847,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ51">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11957,7 +11972,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12163,7 +12178,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12241,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ53">
         <v>0.17</v>
@@ -12369,7 +12384,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12653,7 +12668,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>2.25</v>
@@ -12987,7 +13002,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13274,7 +13289,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13399,7 +13414,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13683,7 +13698,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ60">
         <v>0.92</v>
@@ -14017,7 +14032,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14095,10 +14110,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14223,7 +14238,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14304,7 +14319,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ63">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR63">
         <v>0.8100000000000001</v>
@@ -14429,7 +14444,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14507,10 +14522,10 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -15047,7 +15062,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15128,7 +15143,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ67">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -15253,7 +15268,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15459,7 +15474,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15537,7 +15552,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ69">
         <v>1.33</v>
@@ -15665,7 +15680,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15871,7 +15886,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15949,7 +15964,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ71">
         <v>1.33</v>
@@ -16077,7 +16092,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16283,7 +16298,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16695,7 +16710,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16901,7 +16916,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16982,7 +16997,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ76">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR76">
         <v>1.01</v>
@@ -17107,7 +17122,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17313,7 +17328,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17391,7 +17406,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ78">
         <v>0.45</v>
@@ -17519,7 +17534,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17600,7 +17615,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -17725,7 +17740,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17803,7 +17818,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>0.92</v>
@@ -18009,7 +18024,7 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ81">
         <v>1.27</v>
@@ -18137,7 +18152,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18218,7 +18233,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ82">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18836,7 +18851,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ85">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -18961,7 +18976,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19863,10 +19878,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ90">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR90">
         <v>1.17</v>
@@ -19991,7 +20006,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20069,7 +20084,7 @@
         <v>2.4</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ91">
         <v>2.25</v>
@@ -20197,7 +20212,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20403,7 +20418,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20481,7 +20496,7 @@
         <v>2.25</v>
       </c>
       <c r="AP93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>1.27</v>
@@ -20609,7 +20624,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20815,7 +20830,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20896,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -21021,7 +21036,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21099,7 +21114,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ96">
         <v>1.55</v>
@@ -21227,7 +21242,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21308,7 +21323,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ97">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21433,7 +21448,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21514,7 +21529,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR98">
         <v>1.3</v>
@@ -21639,7 +21654,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21717,7 +21732,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ99">
         <v>1.09</v>
@@ -21923,7 +21938,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
         <v>0.17</v>
@@ -22051,7 +22066,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22132,7 +22147,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ101">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -22338,7 +22353,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ102">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22463,7 +22478,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22750,7 +22765,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ104">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23493,7 +23508,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23571,7 +23586,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23699,7 +23714,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23777,7 +23792,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23905,7 +23920,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23986,7 +24001,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ110">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24729,7 +24744,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24935,7 +24950,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25013,7 +25028,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25347,7 +25362,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25425,7 +25440,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ117">
         <v>1.33</v>
@@ -25553,7 +25568,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25840,7 +25855,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR119">
         <v>1.36</v>
@@ -26046,7 +26061,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ120">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26252,7 +26267,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ121">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26377,7 +26392,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26455,7 +26470,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26583,7 +26598,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26870,7 +26885,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ124">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR124">
         <v>1.73</v>
@@ -27073,7 +27088,7 @@
         <v>1.67</v>
       </c>
       <c r="AP125">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1.09</v>
@@ -27279,7 +27294,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126">
         <v>0.4</v>
@@ -27407,7 +27422,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27819,7 +27834,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28025,7 +28040,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28106,7 +28121,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ130">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28437,7 +28452,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28643,7 +28658,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28721,7 +28736,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29467,7 +29482,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29548,7 +29563,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ137">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29673,7 +29688,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29751,7 +29766,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ138">
         <v>0.4</v>
@@ -29879,7 +29894,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30085,7 +30100,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30369,10 +30384,10 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ141">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -30578,7 +30593,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -30781,7 +30796,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>0.45</v>
@@ -30990,7 +31005,7 @@
         <v>1</v>
       </c>
       <c r="AQ144">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR144">
         <v>1.26</v>
@@ -31321,7 +31336,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31399,7 +31414,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ146">
         <v>1.27</v>
@@ -31733,7 +31748,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31939,7 +31954,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32145,7 +32160,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32351,7 +32366,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32429,10 +32444,10 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ151">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR151">
         <v>1.15</v>
@@ -32557,7 +32572,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32763,7 +32778,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33175,7 +33190,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33587,7 +33602,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33668,7 +33683,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ157">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR157">
         <v>1.67</v>
@@ -33793,7 +33808,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33874,7 +33889,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ158">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.48</v>
@@ -34077,10 +34092,10 @@
         <v>1.25</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ159">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34823,7 +34838,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35235,7 +35250,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35519,7 +35534,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>1.55</v>
@@ -35647,7 +35662,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35853,7 +35868,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35931,10 +35946,10 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ168">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR168">
         <v>1.13</v>
@@ -36137,7 +36152,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ169">
         <v>1.33</v>
@@ -36265,7 +36280,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36346,7 +36361,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ170">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR170">
         <v>1.48</v>
@@ -36755,7 +36770,7 @@
         <v>2.67</v>
       </c>
       <c r="AP172">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ172">
         <v>2.25</v>
@@ -36883,7 +36898,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -36964,7 +36979,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37089,7 +37104,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37170,7 +37185,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR174">
         <v>1.46</v>
@@ -37295,7 +37310,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37707,7 +37722,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38325,7 +38340,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38531,7 +38546,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38737,7 +38752,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38815,10 +38830,10 @@
         <v>0.9</v>
       </c>
       <c r="AP182">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ182">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39227,10 +39242,10 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ184">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR184">
         <v>1.58</v>
@@ -39355,7 +39370,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39561,7 +39576,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39845,7 +39860,7 @@
         <v>1.33</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ187">
         <v>1.09</v>
@@ -39973,7 +39988,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40054,7 +40069,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ188">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR188">
         <v>1.32</v>
@@ -40257,10 +40272,10 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ189">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR189">
         <v>1.26</v>
@@ -40385,7 +40400,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40591,7 +40606,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40797,7 +40812,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41209,7 +41224,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41290,7 +41305,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ194">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41415,7 +41430,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41621,7 +41636,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q196">
         <v>5.5</v>
@@ -41699,7 +41714,7 @@
         <v>1.18</v>
       </c>
       <c r="AP196">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ196">
         <v>1.33</v>
@@ -41827,7 +41842,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q197">
         <v>2.3</v>
@@ -42239,7 +42254,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42857,7 +42872,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43220,6 +43235,1036 @@
       </c>
       <c r="BP203">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7468557</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>85</v>
+      </c>
+      <c r="H204" t="s">
+        <v>83</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>3</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>4</v>
+      </c>
+      <c r="O204" t="s">
+        <v>233</v>
+      </c>
+      <c r="P204" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q204">
+        <v>4</v>
+      </c>
+      <c r="R204">
+        <v>2.1</v>
+      </c>
+      <c r="S204">
+        <v>2.75</v>
+      </c>
+      <c r="T204">
+        <v>1.44</v>
+      </c>
+      <c r="U204">
+        <v>2.63</v>
+      </c>
+      <c r="V204">
+        <v>3</v>
+      </c>
+      <c r="W204">
+        <v>1.36</v>
+      </c>
+      <c r="X204">
+        <v>9</v>
+      </c>
+      <c r="Y204">
+        <v>1.07</v>
+      </c>
+      <c r="Z204">
+        <v>3.67</v>
+      </c>
+      <c r="AA204">
+        <v>3.41</v>
+      </c>
+      <c r="AB204">
+        <v>2.13</v>
+      </c>
+      <c r="AC204">
+        <v>1.07</v>
+      </c>
+      <c r="AD204">
+        <v>10</v>
+      </c>
+      <c r="AE204">
+        <v>1.33</v>
+      </c>
+      <c r="AF204">
+        <v>3.3</v>
+      </c>
+      <c r="AG204">
+        <v>2.03</v>
+      </c>
+      <c r="AH204">
+        <v>1.79</v>
+      </c>
+      <c r="AI204">
+        <v>1.8</v>
+      </c>
+      <c r="AJ204">
+        <v>1.95</v>
+      </c>
+      <c r="AK204">
+        <v>1.68</v>
+      </c>
+      <c r="AL204">
+        <v>1.31</v>
+      </c>
+      <c r="AM204">
+        <v>1.3</v>
+      </c>
+      <c r="AN204">
+        <v>1</v>
+      </c>
+      <c r="AO204">
+        <v>1.73</v>
+      </c>
+      <c r="AP204">
+        <v>1.18</v>
+      </c>
+      <c r="AQ204">
+        <v>1.58</v>
+      </c>
+      <c r="AR204">
+        <v>1.42</v>
+      </c>
+      <c r="AS204">
+        <v>1.47</v>
+      </c>
+      <c r="AT204">
+        <v>2.89</v>
+      </c>
+      <c r="AU204">
+        <v>7</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>8</v>
+      </c>
+      <c r="AX204">
+        <v>10</v>
+      </c>
+      <c r="AY204">
+        <v>16</v>
+      </c>
+      <c r="AZ204">
+        <v>21</v>
+      </c>
+      <c r="BA204">
+        <v>2</v>
+      </c>
+      <c r="BB204">
+        <v>11</v>
+      </c>
+      <c r="BC204">
+        <v>13</v>
+      </c>
+      <c r="BD204">
+        <v>2.25</v>
+      </c>
+      <c r="BE204">
+        <v>6.4</v>
+      </c>
+      <c r="BF204">
+        <v>1.77</v>
+      </c>
+      <c r="BG204">
+        <v>1.32</v>
+      </c>
+      <c r="BH204">
+        <v>3.05</v>
+      </c>
+      <c r="BI204">
+        <v>1.55</v>
+      </c>
+      <c r="BJ204">
+        <v>2.28</v>
+      </c>
+      <c r="BK204">
+        <v>1.9</v>
+      </c>
+      <c r="BL204">
+        <v>1.79</v>
+      </c>
+      <c r="BM204">
+        <v>2.4</v>
+      </c>
+      <c r="BN204">
+        <v>1.5</v>
+      </c>
+      <c r="BO204">
+        <v>3.05</v>
+      </c>
+      <c r="BP204">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7468556</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45711.55208333334</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>84</v>
+      </c>
+      <c r="H205" t="s">
+        <v>71</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>90</v>
+      </c>
+      <c r="P205" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q205">
+        <v>2.63</v>
+      </c>
+      <c r="R205">
+        <v>2.25</v>
+      </c>
+      <c r="S205">
+        <v>4</v>
+      </c>
+      <c r="T205">
+        <v>1.36</v>
+      </c>
+      <c r="U205">
+        <v>3</v>
+      </c>
+      <c r="V205">
+        <v>2.63</v>
+      </c>
+      <c r="W205">
+        <v>1.44</v>
+      </c>
+      <c r="X205">
+        <v>7</v>
+      </c>
+      <c r="Y205">
+        <v>1.1</v>
+      </c>
+      <c r="Z205">
+        <v>2.23</v>
+      </c>
+      <c r="AA205">
+        <v>3.45</v>
+      </c>
+      <c r="AB205">
+        <v>3.4</v>
+      </c>
+      <c r="AC205">
+        <v>1.04</v>
+      </c>
+      <c r="AD205">
+        <v>13</v>
+      </c>
+      <c r="AE205">
+        <v>1.26</v>
+      </c>
+      <c r="AF205">
+        <v>4</v>
+      </c>
+      <c r="AG205">
+        <v>1.9</v>
+      </c>
+      <c r="AH205">
+        <v>1.8</v>
+      </c>
+      <c r="AI205">
+        <v>1.67</v>
+      </c>
+      <c r="AJ205">
+        <v>2.1</v>
+      </c>
+      <c r="AK205">
+        <v>1.3</v>
+      </c>
+      <c r="AL205">
+        <v>1.29</v>
+      </c>
+      <c r="AM205">
+        <v>1.73</v>
+      </c>
+      <c r="AN205">
+        <v>2.1</v>
+      </c>
+      <c r="AO205">
+        <v>1.09</v>
+      </c>
+      <c r="AP205">
+        <v>2</v>
+      </c>
+      <c r="AQ205">
+        <v>1.08</v>
+      </c>
+      <c r="AR205">
+        <v>1.37</v>
+      </c>
+      <c r="AS205">
+        <v>1.4</v>
+      </c>
+      <c r="AT205">
+        <v>2.77</v>
+      </c>
+      <c r="AU205">
+        <v>4</v>
+      </c>
+      <c r="AV205">
+        <v>3</v>
+      </c>
+      <c r="AW205">
+        <v>3</v>
+      </c>
+      <c r="AX205">
+        <v>10</v>
+      </c>
+      <c r="AY205">
+        <v>7</v>
+      </c>
+      <c r="AZ205">
+        <v>15</v>
+      </c>
+      <c r="BA205">
+        <v>1</v>
+      </c>
+      <c r="BB205">
+        <v>8</v>
+      </c>
+      <c r="BC205">
+        <v>9</v>
+      </c>
+      <c r="BD205">
+        <v>1.79</v>
+      </c>
+      <c r="BE205">
+        <v>6.1</v>
+      </c>
+      <c r="BF205">
+        <v>2.28</v>
+      </c>
+      <c r="BG205">
+        <v>1.46</v>
+      </c>
+      <c r="BH205">
+        <v>2.5</v>
+      </c>
+      <c r="BI205">
+        <v>1.76</v>
+      </c>
+      <c r="BJ205">
+        <v>1.94</v>
+      </c>
+      <c r="BK205">
+        <v>2.23</v>
+      </c>
+      <c r="BL205">
+        <v>1.57</v>
+      </c>
+      <c r="BM205">
+        <v>2.9</v>
+      </c>
+      <c r="BN205">
+        <v>1.34</v>
+      </c>
+      <c r="BO205">
+        <v>3.9</v>
+      </c>
+      <c r="BP205">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7468560</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.55208333334</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>86</v>
+      </c>
+      <c r="H206" t="s">
+        <v>75</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>234</v>
+      </c>
+      <c r="P206" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q206">
+        <v>1.83</v>
+      </c>
+      <c r="R206">
+        <v>2.63</v>
+      </c>
+      <c r="S206">
+        <v>6.5</v>
+      </c>
+      <c r="T206">
+        <v>1.25</v>
+      </c>
+      <c r="U206">
+        <v>3.75</v>
+      </c>
+      <c r="V206">
+        <v>2.2</v>
+      </c>
+      <c r="W206">
+        <v>1.62</v>
+      </c>
+      <c r="X206">
+        <v>5</v>
+      </c>
+      <c r="Y206">
+        <v>1.17</v>
+      </c>
+      <c r="Z206">
+        <v>1.48</v>
+      </c>
+      <c r="AA206">
+        <v>4.8</v>
+      </c>
+      <c r="AB206">
+        <v>6.5</v>
+      </c>
+      <c r="AC206">
+        <v>1.01</v>
+      </c>
+      <c r="AD206">
+        <v>23</v>
+      </c>
+      <c r="AE206">
+        <v>1.15</v>
+      </c>
+      <c r="AF206">
+        <v>5.5</v>
+      </c>
+      <c r="AG206">
+        <v>1.57</v>
+      </c>
+      <c r="AH206">
+        <v>2.25</v>
+      </c>
+      <c r="AI206">
+        <v>1.7</v>
+      </c>
+      <c r="AJ206">
+        <v>2.05</v>
+      </c>
+      <c r="AK206">
+        <v>1.1</v>
+      </c>
+      <c r="AL206">
+        <v>1.17</v>
+      </c>
+      <c r="AM206">
+        <v>2.95</v>
+      </c>
+      <c r="AN206">
+        <v>2.4</v>
+      </c>
+      <c r="AO206">
+        <v>0.3</v>
+      </c>
+      <c r="AP206">
+        <v>2.45</v>
+      </c>
+      <c r="AQ206">
+        <v>0.27</v>
+      </c>
+      <c r="AR206">
+        <v>1.64</v>
+      </c>
+      <c r="AS206">
+        <v>1.19</v>
+      </c>
+      <c r="AT206">
+        <v>2.83</v>
+      </c>
+      <c r="AU206">
+        <v>7</v>
+      </c>
+      <c r="AV206">
+        <v>4</v>
+      </c>
+      <c r="AW206">
+        <v>10</v>
+      </c>
+      <c r="AX206">
+        <v>11</v>
+      </c>
+      <c r="AY206">
+        <v>18</v>
+      </c>
+      <c r="AZ206">
+        <v>17</v>
+      </c>
+      <c r="BA206">
+        <v>8</v>
+      </c>
+      <c r="BB206">
+        <v>5</v>
+      </c>
+      <c r="BC206">
+        <v>13</v>
+      </c>
+      <c r="BD206">
+        <v>1.33</v>
+      </c>
+      <c r="BE206">
+        <v>7</v>
+      </c>
+      <c r="BF206">
+        <v>3.65</v>
+      </c>
+      <c r="BG206">
+        <v>1.26</v>
+      </c>
+      <c r="BH206">
+        <v>3.4</v>
+      </c>
+      <c r="BI206">
+        <v>1.48</v>
+      </c>
+      <c r="BJ206">
+        <v>2.43</v>
+      </c>
+      <c r="BK206">
+        <v>1.77</v>
+      </c>
+      <c r="BL206">
+        <v>1.92</v>
+      </c>
+      <c r="BM206">
+        <v>2.2</v>
+      </c>
+      <c r="BN206">
+        <v>1.58</v>
+      </c>
+      <c r="BO206">
+        <v>2.8</v>
+      </c>
+      <c r="BP206">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7468554</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.55208333334</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>70</v>
+      </c>
+      <c r="H207" t="s">
+        <v>76</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>4</v>
+      </c>
+      <c r="N207">
+        <v>5</v>
+      </c>
+      <c r="O207" t="s">
+        <v>130</v>
+      </c>
+      <c r="P207" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q207">
+        <v>4.5</v>
+      </c>
+      <c r="R207">
+        <v>2.1</v>
+      </c>
+      <c r="S207">
+        <v>2.63</v>
+      </c>
+      <c r="T207">
+        <v>1.44</v>
+      </c>
+      <c r="U207">
+        <v>2.63</v>
+      </c>
+      <c r="V207">
+        <v>3.25</v>
+      </c>
+      <c r="W207">
+        <v>1.33</v>
+      </c>
+      <c r="X207">
+        <v>9</v>
+      </c>
+      <c r="Y207">
+        <v>1.07</v>
+      </c>
+      <c r="Z207">
+        <v>3.91</v>
+      </c>
+      <c r="AA207">
+        <v>3.47</v>
+      </c>
+      <c r="AB207">
+        <v>2.03</v>
+      </c>
+      <c r="AC207">
+        <v>1.06</v>
+      </c>
+      <c r="AD207">
+        <v>10</v>
+      </c>
+      <c r="AE207">
+        <v>1.33</v>
+      </c>
+      <c r="AF207">
+        <v>3.3</v>
+      </c>
+      <c r="AG207">
+        <v>2.03</v>
+      </c>
+      <c r="AH207">
+        <v>1.79</v>
+      </c>
+      <c r="AI207">
+        <v>1.91</v>
+      </c>
+      <c r="AJ207">
+        <v>1.91</v>
+      </c>
+      <c r="AK207">
+        <v>1.8</v>
+      </c>
+      <c r="AL207">
+        <v>1.3</v>
+      </c>
+      <c r="AM207">
+        <v>1.25</v>
+      </c>
+      <c r="AN207">
+        <v>0.55</v>
+      </c>
+      <c r="AO207">
+        <v>1.2</v>
+      </c>
+      <c r="AP207">
+        <v>0.5</v>
+      </c>
+      <c r="AQ207">
+        <v>1.36</v>
+      </c>
+      <c r="AR207">
+        <v>1.17</v>
+      </c>
+      <c r="AS207">
+        <v>1.2</v>
+      </c>
+      <c r="AT207">
+        <v>2.37</v>
+      </c>
+      <c r="AU207">
+        <v>4</v>
+      </c>
+      <c r="AV207">
+        <v>7</v>
+      </c>
+      <c r="AW207">
+        <v>8</v>
+      </c>
+      <c r="AX207">
+        <v>6</v>
+      </c>
+      <c r="AY207">
+        <v>13</v>
+      </c>
+      <c r="AZ207">
+        <v>16</v>
+      </c>
+      <c r="BA207">
+        <v>5</v>
+      </c>
+      <c r="BB207">
+        <v>3</v>
+      </c>
+      <c r="BC207">
+        <v>8</v>
+      </c>
+      <c r="BD207">
+        <v>2.43</v>
+      </c>
+      <c r="BE207">
+        <v>6.4</v>
+      </c>
+      <c r="BF207">
+        <v>1.68</v>
+      </c>
+      <c r="BG207">
+        <v>1.41</v>
+      </c>
+      <c r="BH207">
+        <v>2.65</v>
+      </c>
+      <c r="BI207">
+        <v>1.68</v>
+      </c>
+      <c r="BJ207">
+        <v>2.02</v>
+      </c>
+      <c r="BK207">
+        <v>2.1</v>
+      </c>
+      <c r="BL207">
+        <v>1.64</v>
+      </c>
+      <c r="BM207">
+        <v>2.7</v>
+      </c>
+      <c r="BN207">
+        <v>1.38</v>
+      </c>
+      <c r="BO207">
+        <v>3.65</v>
+      </c>
+      <c r="BP207">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7468561</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45711.69791666666</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>80</v>
+      </c>
+      <c r="H208" t="s">
+        <v>79</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>2</v>
+      </c>
+      <c r="M208">
+        <v>3</v>
+      </c>
+      <c r="N208">
+        <v>5</v>
+      </c>
+      <c r="O208" t="s">
+        <v>235</v>
+      </c>
+      <c r="P208" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q208">
+        <v>4</v>
+      </c>
+      <c r="R208">
+        <v>2.5</v>
+      </c>
+      <c r="S208">
+        <v>2.3</v>
+      </c>
+      <c r="T208">
+        <v>1.22</v>
+      </c>
+      <c r="U208">
+        <v>4</v>
+      </c>
+      <c r="V208">
+        <v>2.1</v>
+      </c>
+      <c r="W208">
+        <v>1.67</v>
+      </c>
+      <c r="X208">
+        <v>4.5</v>
+      </c>
+      <c r="Y208">
+        <v>1.18</v>
+      </c>
+      <c r="Z208">
+        <v>4.2</v>
+      </c>
+      <c r="AA208">
+        <v>4.2</v>
+      </c>
+      <c r="AB208">
+        <v>1.78</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>23</v>
+      </c>
+      <c r="AE208">
+        <v>1.13</v>
+      </c>
+      <c r="AF208">
+        <v>6</v>
+      </c>
+      <c r="AG208">
+        <v>1.36</v>
+      </c>
+      <c r="AH208">
+        <v>2.99</v>
+      </c>
+      <c r="AI208">
+        <v>1.44</v>
+      </c>
+      <c r="AJ208">
+        <v>2.63</v>
+      </c>
+      <c r="AK208">
+        <v>2</v>
+      </c>
+      <c r="AL208">
+        <v>1.22</v>
+      </c>
+      <c r="AM208">
+        <v>1.25</v>
+      </c>
+      <c r="AN208">
+        <v>2</v>
+      </c>
+      <c r="AO208">
+        <v>2.45</v>
+      </c>
+      <c r="AP208">
+        <v>1.82</v>
+      </c>
+      <c r="AQ208">
+        <v>2.5</v>
+      </c>
+      <c r="AR208">
+        <v>1.74</v>
+      </c>
+      <c r="AS208">
+        <v>2.16</v>
+      </c>
+      <c r="AT208">
+        <v>3.9</v>
+      </c>
+      <c r="AU208">
+        <v>8</v>
+      </c>
+      <c r="AV208">
+        <v>9</v>
+      </c>
+      <c r="AW208">
+        <v>7</v>
+      </c>
+      <c r="AX208">
+        <v>7</v>
+      </c>
+      <c r="AY208">
+        <v>18</v>
+      </c>
+      <c r="AZ208">
+        <v>21</v>
+      </c>
+      <c r="BA208">
+        <v>5</v>
+      </c>
+      <c r="BB208">
+        <v>4</v>
+      </c>
+      <c r="BC208">
+        <v>9</v>
+      </c>
+      <c r="BD208">
+        <v>2.9</v>
+      </c>
+      <c r="BE208">
+        <v>6.75</v>
+      </c>
+      <c r="BF208">
+        <v>1.49</v>
+      </c>
+      <c r="BG208">
+        <v>1.3</v>
+      </c>
+      <c r="BH208">
+        <v>3.15</v>
+      </c>
+      <c r="BI208">
+        <v>1.5</v>
+      </c>
+      <c r="BJ208">
+        <v>2.35</v>
+      </c>
+      <c r="BK208">
+        <v>1.83</v>
+      </c>
+      <c r="BL208">
+        <v>1.85</v>
+      </c>
+      <c r="BM208">
+        <v>2.3</v>
+      </c>
+      <c r="BN208">
+        <v>1.54</v>
+      </c>
+      <c r="BO208">
+        <v>2.95</v>
+      </c>
+      <c r="BP208">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,9 @@
     <t>['83', '90+2']</t>
   </si>
   <si>
+    <t>['34', '39', '51']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1416,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1672,7 +1675,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1878,7 +1881,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2084,7 +2087,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2368,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ5">
         <v>0.17</v>
@@ -2496,7 +2499,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2702,7 +2705,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3732,7 +3735,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4144,7 +4147,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4556,7 +4559,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5174,7 +5177,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5255,7 +5258,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ19">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5380,7 +5383,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5792,7 +5795,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5998,7 +6001,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6204,7 +6207,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6282,7 +6285,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ24">
         <v>1.58</v>
@@ -6410,7 +6413,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6822,7 +6825,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7028,7 +7031,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7646,7 +7649,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8264,7 +8267,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8470,7 +8473,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8551,7 +8554,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.39</v>
@@ -9294,7 +9297,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9500,7 +9503,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9990,7 +9993,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10324,7 +10327,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10530,7 +10533,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10736,7 +10739,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11148,7 +11151,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11560,7 +11563,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11766,7 +11769,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11844,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ51">
         <v>0.27</v>
@@ -11972,7 +11975,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12178,7 +12181,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12384,7 +12387,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12465,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.25</v>
@@ -13002,7 +13005,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13414,7 +13417,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -14032,7 +14035,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14238,7 +14241,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14444,7 +14447,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14728,7 +14731,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ65">
         <v>1.55</v>
@@ -15062,7 +15065,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15268,7 +15271,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15474,7 +15477,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15680,7 +15683,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15886,7 +15889,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16092,7 +16095,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16173,7 +16176,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ72">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16298,7 +16301,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16710,7 +16713,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16916,7 +16919,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17122,7 +17125,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17328,7 +17331,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17534,7 +17537,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17740,7 +17743,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18152,7 +18155,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18436,7 +18439,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ83">
         <v>1.33</v>
@@ -18976,7 +18979,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19469,7 +19472,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.33</v>
@@ -20006,7 +20009,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20212,7 +20215,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20418,7 +20421,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20624,7 +20627,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20830,7 +20833,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21036,7 +21039,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21242,7 +21245,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21448,7 +21451,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21654,7 +21657,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21735,7 +21738,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ99">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.18</v>
@@ -22066,7 +22069,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22144,7 +22147,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ101">
         <v>1.08</v>
@@ -22478,7 +22481,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23508,7 +23511,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23714,7 +23717,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23920,7 +23923,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24744,7 +24747,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24950,7 +24953,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25362,7 +25365,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25568,7 +25571,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26264,7 +26267,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ121">
         <v>1.36</v>
@@ -26392,7 +26395,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26598,7 +26601,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27091,7 +27094,7 @@
         <v>2</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27422,7 +27425,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27834,7 +27837,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28040,7 +28043,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28452,7 +28455,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28658,7 +28661,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29482,7 +29485,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29560,7 +29563,7 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ137">
         <v>2.5</v>
@@ -29688,7 +29691,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29894,7 +29897,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29975,7 +29978,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ139">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.2</v>
@@ -30100,7 +30103,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -31336,7 +31339,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31748,7 +31751,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31954,7 +31957,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32160,7 +32163,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32366,7 +32369,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32572,7 +32575,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32778,7 +32781,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33190,7 +33193,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33602,7 +33605,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33808,7 +33811,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34838,7 +34841,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35250,7 +35253,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35328,7 +35331,7 @@
         <v>0.13</v>
       </c>
       <c r="AP165">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ165">
         <v>0.4</v>
@@ -35662,7 +35665,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35743,7 +35746,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ167">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR167">
         <v>2.34</v>
@@ -35868,7 +35871,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36280,7 +36283,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36898,7 +36901,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37104,7 +37107,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37310,7 +37313,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37388,7 +37391,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ175">
         <v>0.45</v>
@@ -37722,7 +37725,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38340,7 +38343,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38546,7 +38549,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38752,7 +38755,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39370,7 +39373,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39576,7 +39579,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39863,7 +39866,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ187">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.71</v>
@@ -39988,7 +39991,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40400,7 +40403,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40606,7 +40609,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40812,7 +40815,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41096,7 +41099,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ193">
         <v>0.92</v>
@@ -41224,7 +41227,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41430,7 +41433,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41636,7 +41639,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q196">
         <v>5.5</v>
@@ -41842,7 +41845,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q197">
         <v>2.3</v>
@@ -42254,7 +42257,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42541,7 +42544,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ200">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.51</v>
@@ -42872,7 +42875,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43902,7 +43905,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44108,7 +44111,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44265,6 +44268,212 @@
       </c>
       <c r="BP208">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7468569</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>73</v>
+      </c>
+      <c r="H209" t="s">
+        <v>72</v>
+      </c>
+      <c r="I209">
+        <v>2</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>3</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>236</v>
+      </c>
+      <c r="P209" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q209">
+        <v>1.83</v>
+      </c>
+      <c r="R209">
+        <v>2.63</v>
+      </c>
+      <c r="S209">
+        <v>6</v>
+      </c>
+      <c r="T209">
+        <v>1.25</v>
+      </c>
+      <c r="U209">
+        <v>3.75</v>
+      </c>
+      <c r="V209">
+        <v>2.1</v>
+      </c>
+      <c r="W209">
+        <v>1.67</v>
+      </c>
+      <c r="X209">
+        <v>5</v>
+      </c>
+      <c r="Y209">
+        <v>1.17</v>
+      </c>
+      <c r="Z209">
+        <v>1.48</v>
+      </c>
+      <c r="AA209">
+        <v>5</v>
+      </c>
+      <c r="AB209">
+        <v>6.3</v>
+      </c>
+      <c r="AC209">
+        <v>1.01</v>
+      </c>
+      <c r="AD209">
+        <v>23</v>
+      </c>
+      <c r="AE209">
+        <v>1.13</v>
+      </c>
+      <c r="AF209">
+        <v>6</v>
+      </c>
+      <c r="AG209">
+        <v>1.44</v>
+      </c>
+      <c r="AH209">
+        <v>2.67</v>
+      </c>
+      <c r="AI209">
+        <v>1.67</v>
+      </c>
+      <c r="AJ209">
+        <v>2.1</v>
+      </c>
+      <c r="AK209">
+        <v>1.11</v>
+      </c>
+      <c r="AL209">
+        <v>1.17</v>
+      </c>
+      <c r="AM209">
+        <v>2.8</v>
+      </c>
+      <c r="AN209">
+        <v>2.17</v>
+      </c>
+      <c r="AO209">
+        <v>1.09</v>
+      </c>
+      <c r="AP209">
+        <v>2.23</v>
+      </c>
+      <c r="AQ209">
+        <v>1</v>
+      </c>
+      <c r="AR209">
+        <v>1.71</v>
+      </c>
+      <c r="AS209">
+        <v>1.19</v>
+      </c>
+      <c r="AT209">
+        <v>2.9</v>
+      </c>
+      <c r="AU209">
+        <v>10</v>
+      </c>
+      <c r="AV209">
+        <v>8</v>
+      </c>
+      <c r="AW209">
+        <v>14</v>
+      </c>
+      <c r="AX209">
+        <v>3</v>
+      </c>
+      <c r="AY209">
+        <v>27</v>
+      </c>
+      <c r="AZ209">
+        <v>12</v>
+      </c>
+      <c r="BA209">
+        <v>7</v>
+      </c>
+      <c r="BB209">
+        <v>2</v>
+      </c>
+      <c r="BC209">
+        <v>9</v>
+      </c>
+      <c r="BD209">
+        <v>1.35</v>
+      </c>
+      <c r="BE209">
+        <v>7</v>
+      </c>
+      <c r="BF209">
+        <v>3.55</v>
+      </c>
+      <c r="BG209">
+        <v>1.3</v>
+      </c>
+      <c r="BH209">
+        <v>3.05</v>
+      </c>
+      <c r="BI209">
+        <v>1.54</v>
+      </c>
+      <c r="BJ209">
+        <v>2.3</v>
+      </c>
+      <c r="BK209">
+        <v>1.89</v>
+      </c>
+      <c r="BL209">
+        <v>1.8</v>
+      </c>
+      <c r="BM209">
+        <v>2.38</v>
+      </c>
+      <c r="BN209">
+        <v>1.5</v>
+      </c>
+      <c r="BO209">
+        <v>3.05</v>
+      </c>
+      <c r="BP209">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,15 @@
     <t>['34', '39', '51']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['3', '19', '48']</t>
+  </si>
+  <si>
+    <t>['6', '22', '28', '37']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -979,9 +988,6 @@
     <t>['14', '26']</t>
   </si>
   <si>
-    <t>['32']</t>
-  </si>
-  <si>
     <t>['59', '86']</t>
   </si>
   <si>
@@ -1042,10 +1048,10 @@
     <t>['3', '50', '53', '73']</t>
   </si>
   <si>
-    <t>['16', '18', '90+4']</t>
+    <t>['81', '90+6']</t>
   </si>
   <si>
-    <t>['81', '90+6']</t>
+    <t>['16', '18', '90+4']</t>
   </si>
   <si>
     <t>['80', '86']</t>
@@ -1058,6 +1064,12 @@
   </si>
   <si>
     <t>['53', '59', '85']</t>
+  </si>
+  <si>
+    <t>['10', '52', '69']</t>
+  </si>
+  <si>
+    <t>['28', '33', '62', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1675,7 +1687,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1881,7 +1893,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2087,7 +2099,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2168,7 +2180,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ4">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2499,7 +2511,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2580,7 +2592,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2705,7 +2717,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3607,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ11">
         <v>0.27</v>
@@ -3735,7 +3747,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4147,7 +4159,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4225,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4431,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -4559,7 +4571,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5177,7 +5189,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5383,7 +5395,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5795,7 +5807,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6001,7 +6013,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6207,7 +6219,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6413,7 +6425,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6494,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6825,7 +6837,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7031,7 +7043,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7315,10 +7327,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR29">
         <v>1.65</v>
@@ -7524,7 +7536,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -7649,7 +7661,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7933,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -8267,7 +8279,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8473,7 +8485,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8760,7 +8772,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -8963,7 +8975,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9297,7 +9309,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9503,7 +9515,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9996,7 +10008,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10327,7 +10339,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10533,7 +10545,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10739,7 +10751,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11151,7 +11163,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11229,7 +11241,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ48">
         <v>0.4</v>
@@ -11435,10 +11447,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11563,7 +11575,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11644,7 +11656,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ50">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR50">
         <v>1.41</v>
@@ -11769,7 +11781,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11975,7 +11987,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12181,7 +12193,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12387,7 +12399,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -13005,7 +13017,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13083,7 +13095,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
         <v>0.45</v>
@@ -13417,7 +13429,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13910,7 +13922,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -14035,7 +14047,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14241,7 +14253,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14447,7 +14459,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14734,7 +14746,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ65">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR65">
         <v>1.54</v>
@@ -15065,7 +15077,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15143,7 +15155,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67">
         <v>1.58</v>
@@ -15271,7 +15283,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15349,7 +15361,7 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15477,7 +15489,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15683,7 +15695,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15889,7 +15901,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15970,7 +15982,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -16095,7 +16107,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16301,7 +16313,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16588,7 +16600,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16713,7 +16725,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16919,7 +16931,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17125,7 +17137,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17203,10 +17215,10 @@
         <v>1.75</v>
       </c>
       <c r="AP77">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR77">
         <v>1.98</v>
@@ -17331,7 +17343,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17537,7 +17549,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17743,7 +17755,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18155,7 +18167,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18851,7 +18863,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ85">
         <v>1.58</v>
@@ -18979,7 +18991,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19060,7 +19072,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19263,7 +19275,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -20009,7 +20021,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20215,7 +20227,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20421,7 +20433,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20627,7 +20639,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20705,7 +20717,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ94">
         <v>0.92</v>
@@ -20833,7 +20845,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21039,7 +21051,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21120,7 +21132,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ96">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR96">
         <v>1.64</v>
@@ -21245,7 +21257,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21451,7 +21463,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21657,7 +21669,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22069,7 +22081,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22353,7 +22365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP102">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ102">
         <v>1.36</v>
@@ -22481,7 +22493,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22559,7 +22571,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103">
         <v>2.25</v>
@@ -22765,7 +22777,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>0.27</v>
@@ -23511,7 +23523,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23592,7 +23604,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23717,7 +23729,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23923,7 +23935,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24619,7 +24631,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ113">
         <v>0.92</v>
@@ -24747,7 +24759,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24828,7 +24840,7 @@
         <v>1</v>
       </c>
       <c r="AQ114">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR114">
         <v>1.36</v>
@@ -24953,7 +24965,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25365,7 +25377,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25446,7 +25458,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -25571,7 +25583,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26395,7 +26407,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26476,7 +26488,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26601,7 +26613,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26885,7 +26897,7 @@
         <v>0</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ124">
         <v>0.27</v>
@@ -27425,7 +27437,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27503,7 +27515,7 @@
         <v>2.57</v>
       </c>
       <c r="AP127">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
         <v>2.25</v>
@@ -27837,7 +27849,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27918,7 +27930,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR129">
         <v>1.4</v>
@@ -28043,7 +28055,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28455,7 +28467,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28536,7 +28548,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28661,7 +28673,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29357,7 +29369,7 @@
         <v>1.71</v>
       </c>
       <c r="AP136">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ136">
         <v>1.33</v>
@@ -29485,7 +29497,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29691,7 +29703,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29897,7 +29909,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29975,7 +29987,7 @@
         <v>1.57</v>
       </c>
       <c r="AP139">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30103,7 +30115,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30593,7 +30605,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ142">
         <v>1.36</v>
@@ -31214,7 +31226,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ145">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31339,7 +31351,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31626,7 +31638,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ147">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR147">
         <v>1.33</v>
@@ -31751,7 +31763,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31957,7 +31969,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32038,7 +32050,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ149">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32163,7 +32175,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32369,7 +32381,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32575,7 +32587,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32781,7 +32793,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33065,7 +33077,7 @@
         <v>0.13</v>
       </c>
       <c r="AP154">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ154">
         <v>0.17</v>
@@ -33193,7 +33205,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>237</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33480,7 +33492,7 @@
         <v>2</v>
       </c>
       <c r="AQ156">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33605,7 +33617,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33683,7 +33695,7 @@
         <v>2.25</v>
       </c>
       <c r="AP157">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ157">
         <v>2.5</v>
@@ -33811,7 +33823,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34301,7 +34313,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ160">
         <v>0.92</v>
@@ -34716,7 +34728,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ162">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -34841,7 +34853,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35253,7 +35265,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35540,7 +35552,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR166">
         <v>1.19</v>
@@ -35665,7 +35677,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35743,7 +35755,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35871,7 +35883,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36283,7 +36295,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36567,7 +36579,7 @@
         <v>1.33</v>
       </c>
       <c r="AP171">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ171">
         <v>1.33</v>
@@ -36901,7 +36913,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37107,7 +37119,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37313,7 +37325,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37725,7 +37737,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37806,7 +37818,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ177">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR177">
         <v>1.51</v>
@@ -38218,7 +38230,7 @@
         <v>1</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR179">
         <v>1.27</v>
@@ -38343,7 +38355,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38549,7 +38561,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38755,7 +38767,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39039,7 +39051,7 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ183">
         <v>1.27</v>
@@ -39373,7 +39385,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39454,7 +39466,7 @@
         <v>2</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR185">
         <v>1.58</v>
@@ -39579,7 +39591,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39657,7 +39669,7 @@
         <v>0.11</v>
       </c>
       <c r="AP186">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ186">
         <v>0.4</v>
@@ -39991,7 +40003,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40403,7 +40415,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40609,7 +40621,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40815,7 +40827,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41227,7 +41239,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41433,7 +41445,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41597,7 +41609,7 @@
         <v>195</v>
       </c>
       <c r="B196">
-        <v>7468551</v>
+        <v>7468547</v>
       </c>
       <c r="C196" t="s">
         <v>68</v>
@@ -41612,49 +41624,49 @@
         <v>22</v>
       </c>
       <c r="G196" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H196" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K196">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N196">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O196" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q196">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="R196">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S196">
-        <v>2.2</v>
+        <v>4.75</v>
       </c>
       <c r="T196">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U196">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V196">
         <v>2.63</v>
@@ -41663,139 +41675,139 @@
         <v>1.44</v>
       </c>
       <c r="X196">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y196">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z196">
-        <v>5.4</v>
+        <v>1.75</v>
       </c>
       <c r="AA196">
         <v>4.1</v>
       </c>
       <c r="AB196">
-        <v>1.65</v>
+        <v>4.6</v>
       </c>
       <c r="AC196">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD196">
+        <v>11</v>
+      </c>
+      <c r="AE196">
+        <v>1.24</v>
+      </c>
+      <c r="AF196">
+        <v>3.8</v>
+      </c>
+      <c r="AG196">
+        <v>1.73</v>
+      </c>
+      <c r="AH196">
+        <v>2</v>
+      </c>
+      <c r="AI196">
+        <v>1.67</v>
+      </c>
+      <c r="AJ196">
+        <v>2.1</v>
+      </c>
+      <c r="AK196">
+        <v>1.21</v>
+      </c>
+      <c r="AL196">
+        <v>1.25</v>
+      </c>
+      <c r="AM196">
+        <v>2.05</v>
+      </c>
+      <c r="AN196">
+        <v>1.4</v>
+      </c>
+      <c r="AO196">
+        <v>0.82</v>
+      </c>
+      <c r="AP196">
+        <v>1.17</v>
+      </c>
+      <c r="AQ196">
+        <v>1</v>
+      </c>
+      <c r="AR196">
+        <v>1.69</v>
+      </c>
+      <c r="AS196">
+        <v>1.23</v>
+      </c>
+      <c r="AT196">
+        <v>2.92</v>
+      </c>
+      <c r="AU196">
+        <v>0</v>
+      </c>
+      <c r="AV196">
+        <v>5</v>
+      </c>
+      <c r="AW196">
+        <v>8</v>
+      </c>
+      <c r="AX196">
+        <v>9</v>
+      </c>
+      <c r="AY196">
         <v>10</v>
       </c>
-      <c r="AE196">
-        <v>1.27</v>
-      </c>
-      <c r="AF196">
-        <v>3.94</v>
-      </c>
-      <c r="AG196">
-        <v>1.86</v>
-      </c>
-      <c r="AH196">
-        <v>1.95</v>
-      </c>
-      <c r="AI196">
-        <v>1.8</v>
-      </c>
-      <c r="AJ196">
-        <v>1.95</v>
-      </c>
-      <c r="AK196">
-        <v>2.2</v>
-      </c>
-      <c r="AL196">
-        <v>1.24</v>
-      </c>
-      <c r="AM196">
+      <c r="AZ196">
+        <v>17</v>
+      </c>
+      <c r="BA196">
+        <v>7</v>
+      </c>
+      <c r="BB196">
+        <v>3</v>
+      </c>
+      <c r="BC196">
+        <v>10</v>
+      </c>
+      <c r="BD196">
+        <v>1.32</v>
+      </c>
+      <c r="BE196">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF196">
+        <v>4.4</v>
+      </c>
+      <c r="BG196">
+        <v>1.39</v>
+      </c>
+      <c r="BH196">
+        <v>2.67</v>
+      </c>
+      <c r="BI196">
+        <v>1.73</v>
+      </c>
+      <c r="BJ196">
+        <v>1.99</v>
+      </c>
+      <c r="BK196">
+        <v>2.19</v>
+      </c>
+      <c r="BL196">
+        <v>1.57</v>
+      </c>
+      <c r="BM196">
+        <v>2.92</v>
+      </c>
+      <c r="BN196">
+        <v>1.31</v>
+      </c>
+      <c r="BO196">
+        <v>4.2</v>
+      </c>
+      <c r="BP196">
         <v>1.16</v>
-      </c>
-      <c r="AN196">
-        <v>0.6</v>
-      </c>
-      <c r="AO196">
-        <v>1.18</v>
-      </c>
-      <c r="AP196">
-        <v>0.5</v>
-      </c>
-      <c r="AQ196">
-        <v>1.33</v>
-      </c>
-      <c r="AR196">
-        <v>1.12</v>
-      </c>
-      <c r="AS196">
-        <v>1.47</v>
-      </c>
-      <c r="AT196">
-        <v>2.59</v>
-      </c>
-      <c r="AU196">
-        <v>5</v>
-      </c>
-      <c r="AV196">
-        <v>6</v>
-      </c>
-      <c r="AW196">
-        <v>11</v>
-      </c>
-      <c r="AX196">
-        <v>4</v>
-      </c>
-      <c r="AY196">
-        <v>16</v>
-      </c>
-      <c r="AZ196">
-        <v>11</v>
-      </c>
-      <c r="BA196">
-        <v>6</v>
-      </c>
-      <c r="BB196">
-        <v>2</v>
-      </c>
-      <c r="BC196">
-        <v>8</v>
-      </c>
-      <c r="BD196">
-        <v>3.22</v>
-      </c>
-      <c r="BE196">
-        <v>9.1</v>
-      </c>
-      <c r="BF196">
-        <v>1.5</v>
-      </c>
-      <c r="BG196">
-        <v>1.24</v>
-      </c>
-      <c r="BH196">
-        <v>3.34</v>
-      </c>
-      <c r="BI196">
-        <v>1.48</v>
-      </c>
-      <c r="BJ196">
-        <v>2.4</v>
-      </c>
-      <c r="BK196">
-        <v>1.85</v>
-      </c>
-      <c r="BL196">
-        <v>1.85</v>
-      </c>
-      <c r="BM196">
-        <v>2.38</v>
-      </c>
-      <c r="BN196">
-        <v>1.49</v>
-      </c>
-      <c r="BO196">
-        <v>3.14</v>
-      </c>
-      <c r="BP196">
-        <v>1.27</v>
       </c>
     </row>
     <row r="197" spans="1:68">
@@ -41803,7 +41815,7 @@
         <v>196</v>
       </c>
       <c r="B197">
-        <v>7468547</v>
+        <v>7468550</v>
       </c>
       <c r="C197" t="s">
         <v>68</v>
@@ -41818,190 +41830,190 @@
         <v>22</v>
       </c>
       <c r="G197" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H197" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I197">
         <v>0</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197">
         <v>0</v>
       </c>
       <c r="M197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O197" t="s">
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>343</v>
+        <v>218</v>
       </c>
       <c r="Q197">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="R197">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S197">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="T197">
+        <v>1.4</v>
+      </c>
+      <c r="U197">
+        <v>2.75</v>
+      </c>
+      <c r="V197">
+        <v>3</v>
+      </c>
+      <c r="W197">
+        <v>1.36</v>
+      </c>
+      <c r="X197">
+        <v>8</v>
+      </c>
+      <c r="Y197">
+        <v>1.08</v>
+      </c>
+      <c r="Z197">
+        <v>1.99</v>
+      </c>
+      <c r="AA197">
+        <v>3.5</v>
+      </c>
+      <c r="AB197">
+        <v>4.1</v>
+      </c>
+      <c r="AC197">
+        <v>1.06</v>
+      </c>
+      <c r="AD197">
+        <v>9</v>
+      </c>
+      <c r="AE197">
+        <v>1.32</v>
+      </c>
+      <c r="AF197">
+        <v>3.56</v>
+      </c>
+      <c r="AG197">
+        <v>1.98</v>
+      </c>
+      <c r="AH197">
+        <v>1.84</v>
+      </c>
+      <c r="AI197">
+        <v>1.8</v>
+      </c>
+      <c r="AJ197">
+        <v>1.95</v>
+      </c>
+      <c r="AK197">
+        <v>1.25</v>
+      </c>
+      <c r="AL197">
+        <v>1.29</v>
+      </c>
+      <c r="AM197">
+        <v>1.82</v>
+      </c>
+      <c r="AN197">
+        <v>0.91</v>
+      </c>
+      <c r="AO197">
+        <v>1.2</v>
+      </c>
+      <c r="AP197">
+        <v>0.83</v>
+      </c>
+      <c r="AQ197">
         <v>1.33</v>
       </c>
-      <c r="U197">
-        <v>3.25</v>
-      </c>
-      <c r="V197">
-        <v>2.63</v>
-      </c>
-      <c r="W197">
-        <v>1.44</v>
-      </c>
-      <c r="X197">
-        <v>6.5</v>
-      </c>
-      <c r="Y197">
-        <v>1.11</v>
-      </c>
-      <c r="Z197">
-        <v>1.75</v>
-      </c>
-      <c r="AA197">
-        <v>4.1</v>
-      </c>
-      <c r="AB197">
-        <v>4.6</v>
-      </c>
-      <c r="AC197">
-        <v>1.04</v>
-      </c>
-      <c r="AD197">
-        <v>11</v>
-      </c>
-      <c r="AE197">
-        <v>1.24</v>
-      </c>
-      <c r="AF197">
-        <v>3.8</v>
-      </c>
-      <c r="AG197">
-        <v>1.73</v>
-      </c>
-      <c r="AH197">
-        <v>2</v>
-      </c>
-      <c r="AI197">
-        <v>1.67</v>
-      </c>
-      <c r="AJ197">
-        <v>2.1</v>
-      </c>
-      <c r="AK197">
-        <v>1.21</v>
-      </c>
-      <c r="AL197">
-        <v>1.25</v>
-      </c>
-      <c r="AM197">
-        <v>2.05</v>
-      </c>
-      <c r="AN197">
-        <v>1.4</v>
-      </c>
-      <c r="AO197">
-        <v>0.82</v>
-      </c>
-      <c r="AP197">
-        <v>1.27</v>
-      </c>
-      <c r="AQ197">
-        <v>1</v>
-      </c>
       <c r="AR197">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="AS197">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AT197">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="AU197">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV197">
+        <v>3</v>
+      </c>
+      <c r="AW197">
+        <v>10</v>
+      </c>
+      <c r="AX197">
+        <v>6</v>
+      </c>
+      <c r="AY197">
+        <v>19</v>
+      </c>
+      <c r="AZ197">
+        <v>10</v>
+      </c>
+      <c r="BA197">
+        <v>1</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
         <v>5</v>
       </c>
-      <c r="AW197">
-        <v>8</v>
-      </c>
-      <c r="AX197">
-        <v>9</v>
-      </c>
-      <c r="AY197">
-        <v>10</v>
-      </c>
-      <c r="AZ197">
-        <v>17</v>
-      </c>
-      <c r="BA197">
-        <v>7</v>
-      </c>
-      <c r="BB197">
-        <v>3</v>
-      </c>
-      <c r="BC197">
-        <v>10</v>
-      </c>
       <c r="BD197">
+        <v>1.46</v>
+      </c>
+      <c r="BE197">
+        <v>8.9</v>
+      </c>
+      <c r="BF197">
+        <v>3.44</v>
+      </c>
+      <c r="BG197">
         <v>1.32</v>
       </c>
-      <c r="BE197">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BF197">
-        <v>4.4</v>
-      </c>
-      <c r="BG197">
-        <v>1.39</v>
-      </c>
       <c r="BH197">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="BI197">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BJ197">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="BK197">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="BL197">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="BM197">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="BN197">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="BO197">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="BP197">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="198" spans="1:68">
@@ -42009,7 +42021,7 @@
         <v>197</v>
       </c>
       <c r="B198">
-        <v>7468550</v>
+        <v>7468551</v>
       </c>
       <c r="C198" t="s">
         <v>68</v>
@@ -42024,88 +42036,88 @@
         <v>22</v>
       </c>
       <c r="G198" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H198" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O198" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>218</v>
+        <v>345</v>
       </c>
       <c r="Q198">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R198">
+        <v>2.25</v>
+      </c>
+      <c r="S198">
         <v>2.2</v>
       </c>
-      <c r="S198">
-        <v>4.33</v>
-      </c>
       <c r="T198">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U198">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V198">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W198">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X198">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y198">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z198">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="AA198">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB198">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC198">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD198">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE198">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF198">
-        <v>3.56</v>
+        <v>3.94</v>
       </c>
       <c r="AG198">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AH198">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AI198">
         <v>1.8</v>
@@ -42114,100 +42126,100 @@
         <v>1.95</v>
       </c>
       <c r="AK198">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL198">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AM198">
-        <v>1.82</v>
+        <v>1.16</v>
       </c>
       <c r="AN198">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="AO198">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AP198">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AQ198">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR198">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AS198">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="AT198">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AU198">
         <v>5</v>
       </c>
       <c r="AV198">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW198">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX198">
+        <v>4</v>
+      </c>
+      <c r="AY198">
+        <v>16</v>
+      </c>
+      <c r="AZ198">
+        <v>11</v>
+      </c>
+      <c r="BA198">
         <v>6</v>
       </c>
-      <c r="AY198">
-        <v>19</v>
-      </c>
-      <c r="AZ198">
-        <v>10</v>
-      </c>
-      <c r="BA198">
-        <v>1</v>
-      </c>
       <c r="BB198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC198">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD198">
-        <v>1.46</v>
+        <v>3.22</v>
       </c>
       <c r="BE198">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="BF198">
-        <v>3.44</v>
+        <v>1.5</v>
       </c>
       <c r="BG198">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="BH198">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="BI198">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="BJ198">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="BK198">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BL198">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="BM198">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="BN198">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="BO198">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="BP198">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="199" spans="1:68">
@@ -42257,7 +42269,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42338,7 +42350,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ199">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR199">
         <v>1.59</v>
@@ -42875,7 +42887,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -42953,7 +42965,7 @@
         <v>1.36</v>
       </c>
       <c r="AP202">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ202">
         <v>1.33</v>
@@ -43451,7 +43463,7 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>7468556</v>
+        <v>7468560</v>
       </c>
       <c r="C205" t="s">
         <v>68</v>
@@ -43466,190 +43478,190 @@
         <v>23</v>
       </c>
       <c r="G205" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H205" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205">
         <v>0</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M205">
         <v>0</v>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O205" t="s">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="P205" t="s">
         <v>90</v>
       </c>
       <c r="Q205">
+        <v>1.83</v>
+      </c>
+      <c r="R205">
         <v>2.63</v>
       </c>
-      <c r="R205">
+      <c r="S205">
+        <v>6.5</v>
+      </c>
+      <c r="T205">
+        <v>1.25</v>
+      </c>
+      <c r="U205">
+        <v>3.75</v>
+      </c>
+      <c r="V205">
+        <v>2.2</v>
+      </c>
+      <c r="W205">
+        <v>1.62</v>
+      </c>
+      <c r="X205">
+        <v>5</v>
+      </c>
+      <c r="Y205">
+        <v>1.17</v>
+      </c>
+      <c r="Z205">
+        <v>1.48</v>
+      </c>
+      <c r="AA205">
+        <v>4.8</v>
+      </c>
+      <c r="AB205">
+        <v>6.5</v>
+      </c>
+      <c r="AC205">
+        <v>1.01</v>
+      </c>
+      <c r="AD205">
+        <v>23</v>
+      </c>
+      <c r="AE205">
+        <v>1.15</v>
+      </c>
+      <c r="AF205">
+        <v>5.5</v>
+      </c>
+      <c r="AG205">
+        <v>1.57</v>
+      </c>
+      <c r="AH205">
         <v>2.25</v>
       </c>
-      <c r="S205">
+      <c r="AI205">
+        <v>1.7</v>
+      </c>
+      <c r="AJ205">
+        <v>2.05</v>
+      </c>
+      <c r="AK205">
+        <v>1.1</v>
+      </c>
+      <c r="AL205">
+        <v>1.17</v>
+      </c>
+      <c r="AM205">
+        <v>2.95</v>
+      </c>
+      <c r="AN205">
+        <v>2.4</v>
+      </c>
+      <c r="AO205">
+        <v>0.3</v>
+      </c>
+      <c r="AP205">
+        <v>2.45</v>
+      </c>
+      <c r="AQ205">
+        <v>0.27</v>
+      </c>
+      <c r="AR205">
+        <v>1.64</v>
+      </c>
+      <c r="AS205">
+        <v>1.19</v>
+      </c>
+      <c r="AT205">
+        <v>2.83</v>
+      </c>
+      <c r="AU205">
+        <v>7</v>
+      </c>
+      <c r="AV205">
         <v>4</v>
       </c>
-      <c r="T205">
+      <c r="AW205">
+        <v>10</v>
+      </c>
+      <c r="AX205">
+        <v>11</v>
+      </c>
+      <c r="AY205">
+        <v>18</v>
+      </c>
+      <c r="AZ205">
+        <v>17</v>
+      </c>
+      <c r="BA205">
+        <v>8</v>
+      </c>
+      <c r="BB205">
+        <v>5</v>
+      </c>
+      <c r="BC205">
+        <v>13</v>
+      </c>
+      <c r="BD205">
+        <v>1.33</v>
+      </c>
+      <c r="BE205">
+        <v>7</v>
+      </c>
+      <c r="BF205">
+        <v>3.65</v>
+      </c>
+      <c r="BG205">
+        <v>1.26</v>
+      </c>
+      <c r="BH205">
+        <v>3.4</v>
+      </c>
+      <c r="BI205">
+        <v>1.48</v>
+      </c>
+      <c r="BJ205">
+        <v>2.43</v>
+      </c>
+      <c r="BK205">
+        <v>1.77</v>
+      </c>
+      <c r="BL205">
+        <v>1.92</v>
+      </c>
+      <c r="BM205">
+        <v>2.2</v>
+      </c>
+      <c r="BN205">
+        <v>1.58</v>
+      </c>
+      <c r="BO205">
+        <v>2.8</v>
+      </c>
+      <c r="BP205">
         <v>1.36</v>
-      </c>
-      <c r="U205">
-        <v>3</v>
-      </c>
-      <c r="V205">
-        <v>2.63</v>
-      </c>
-      <c r="W205">
-        <v>1.44</v>
-      </c>
-      <c r="X205">
-        <v>7</v>
-      </c>
-      <c r="Y205">
-        <v>1.1</v>
-      </c>
-      <c r="Z205">
-        <v>2.23</v>
-      </c>
-      <c r="AA205">
-        <v>3.45</v>
-      </c>
-      <c r="AB205">
-        <v>3.4</v>
-      </c>
-      <c r="AC205">
-        <v>1.04</v>
-      </c>
-      <c r="AD205">
-        <v>13</v>
-      </c>
-      <c r="AE205">
-        <v>1.26</v>
-      </c>
-      <c r="AF205">
-        <v>4</v>
-      </c>
-      <c r="AG205">
-        <v>1.9</v>
-      </c>
-      <c r="AH205">
-        <v>1.8</v>
-      </c>
-      <c r="AI205">
-        <v>1.67</v>
-      </c>
-      <c r="AJ205">
-        <v>2.1</v>
-      </c>
-      <c r="AK205">
-        <v>1.3</v>
-      </c>
-      <c r="AL205">
-        <v>1.29</v>
-      </c>
-      <c r="AM205">
-        <v>1.73</v>
-      </c>
-      <c r="AN205">
-        <v>2.1</v>
-      </c>
-      <c r="AO205">
-        <v>1.09</v>
-      </c>
-      <c r="AP205">
-        <v>2</v>
-      </c>
-      <c r="AQ205">
-        <v>1.08</v>
-      </c>
-      <c r="AR205">
-        <v>1.37</v>
-      </c>
-      <c r="AS205">
-        <v>1.4</v>
-      </c>
-      <c r="AT205">
-        <v>2.77</v>
-      </c>
-      <c r="AU205">
-        <v>4</v>
-      </c>
-      <c r="AV205">
-        <v>3</v>
-      </c>
-      <c r="AW205">
-        <v>3</v>
-      </c>
-      <c r="AX205">
-        <v>10</v>
-      </c>
-      <c r="AY205">
-        <v>7</v>
-      </c>
-      <c r="AZ205">
-        <v>15</v>
-      </c>
-      <c r="BA205">
-        <v>1</v>
-      </c>
-      <c r="BB205">
-        <v>8</v>
-      </c>
-      <c r="BC205">
-        <v>9</v>
-      </c>
-      <c r="BD205">
-        <v>1.79</v>
-      </c>
-      <c r="BE205">
-        <v>6.1</v>
-      </c>
-      <c r="BF205">
-        <v>2.28</v>
-      </c>
-      <c r="BG205">
-        <v>1.46</v>
-      </c>
-      <c r="BH205">
-        <v>2.5</v>
-      </c>
-      <c r="BI205">
-        <v>1.76</v>
-      </c>
-      <c r="BJ205">
-        <v>1.94</v>
-      </c>
-      <c r="BK205">
-        <v>2.23</v>
-      </c>
-      <c r="BL205">
-        <v>1.57</v>
-      </c>
-      <c r="BM205">
-        <v>2.9</v>
-      </c>
-      <c r="BN205">
-        <v>1.34</v>
-      </c>
-      <c r="BO205">
-        <v>3.9</v>
-      </c>
-      <c r="BP205">
-        <v>1.2</v>
       </c>
     </row>
     <row r="206" spans="1:68">
@@ -43657,7 +43669,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>7468560</v>
+        <v>7468556</v>
       </c>
       <c r="C206" t="s">
         <v>68</v>
@@ -43672,190 +43684,190 @@
         <v>23</v>
       </c>
       <c r="G206" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H206" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206">
         <v>0</v>
       </c>
       <c r="K206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L206">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M206">
         <v>0</v>
       </c>
       <c r="N206">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O206" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="P206" t="s">
         <v>90</v>
       </c>
       <c r="Q206">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="R206">
+        <v>2.25</v>
+      </c>
+      <c r="S206">
+        <v>4</v>
+      </c>
+      <c r="T206">
+        <v>1.36</v>
+      </c>
+      <c r="U206">
+        <v>3</v>
+      </c>
+      <c r="V206">
         <v>2.63</v>
       </c>
-      <c r="S206">
-        <v>6.5</v>
-      </c>
-      <c r="T206">
-        <v>1.25</v>
-      </c>
-      <c r="U206">
-        <v>3.75</v>
-      </c>
-      <c r="V206">
-        <v>2.2</v>
-      </c>
       <c r="W206">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="X206">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y206">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z206">
-        <v>1.48</v>
+        <v>2.23</v>
       </c>
       <c r="AA206">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AB206">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC206">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD206">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE206">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF206">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AG206">
+        <v>1.9</v>
+      </c>
+      <c r="AH206">
+        <v>1.8</v>
+      </c>
+      <c r="AI206">
+        <v>1.67</v>
+      </c>
+      <c r="AJ206">
+        <v>2.1</v>
+      </c>
+      <c r="AK206">
+        <v>1.3</v>
+      </c>
+      <c r="AL206">
+        <v>1.29</v>
+      </c>
+      <c r="AM206">
+        <v>1.73</v>
+      </c>
+      <c r="AN206">
+        <v>2.1</v>
+      </c>
+      <c r="AO206">
+        <v>1.09</v>
+      </c>
+      <c r="AP206">
+        <v>2</v>
+      </c>
+      <c r="AQ206">
+        <v>1.08</v>
+      </c>
+      <c r="AR206">
+        <v>1.37</v>
+      </c>
+      <c r="AS206">
+        <v>1.4</v>
+      </c>
+      <c r="AT206">
+        <v>2.77</v>
+      </c>
+      <c r="AU206">
+        <v>4</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>3</v>
+      </c>
+      <c r="AX206">
+        <v>10</v>
+      </c>
+      <c r="AY206">
+        <v>7</v>
+      </c>
+      <c r="AZ206">
+        <v>15</v>
+      </c>
+      <c r="BA206">
+        <v>1</v>
+      </c>
+      <c r="BB206">
+        <v>8</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>1.79</v>
+      </c>
+      <c r="BE206">
+        <v>6.1</v>
+      </c>
+      <c r="BF206">
+        <v>2.28</v>
+      </c>
+      <c r="BG206">
+        <v>1.46</v>
+      </c>
+      <c r="BH206">
+        <v>2.5</v>
+      </c>
+      <c r="BI206">
+        <v>1.76</v>
+      </c>
+      <c r="BJ206">
+        <v>1.94</v>
+      </c>
+      <c r="BK206">
+        <v>2.23</v>
+      </c>
+      <c r="BL206">
         <v>1.57</v>
       </c>
-      <c r="AH206">
-        <v>2.25</v>
-      </c>
-      <c r="AI206">
-        <v>1.7</v>
-      </c>
-      <c r="AJ206">
-        <v>2.05</v>
-      </c>
-      <c r="AK206">
-        <v>1.1</v>
-      </c>
-      <c r="AL206">
-        <v>1.17</v>
-      </c>
-      <c r="AM206">
-        <v>2.95</v>
-      </c>
-      <c r="AN206">
-        <v>2.4</v>
-      </c>
-      <c r="AO206">
-        <v>0.3</v>
-      </c>
-      <c r="AP206">
-        <v>2.45</v>
-      </c>
-      <c r="AQ206">
-        <v>0.27</v>
-      </c>
-      <c r="AR206">
-        <v>1.64</v>
-      </c>
-      <c r="AS206">
-        <v>1.19</v>
-      </c>
-      <c r="AT206">
-        <v>2.83</v>
-      </c>
-      <c r="AU206">
-        <v>7</v>
-      </c>
-      <c r="AV206">
-        <v>4</v>
-      </c>
-      <c r="AW206">
-        <v>10</v>
-      </c>
-      <c r="AX206">
-        <v>11</v>
-      </c>
-      <c r="AY206">
-        <v>18</v>
-      </c>
-      <c r="AZ206">
-        <v>17</v>
-      </c>
-      <c r="BA206">
-        <v>8</v>
-      </c>
-      <c r="BB206">
-        <v>5</v>
-      </c>
-      <c r="BC206">
-        <v>13</v>
-      </c>
-      <c r="BD206">
-        <v>1.33</v>
-      </c>
-      <c r="BE206">
-        <v>7</v>
-      </c>
-      <c r="BF206">
-        <v>3.65</v>
-      </c>
-      <c r="BG206">
-        <v>1.26</v>
-      </c>
-      <c r="BH206">
-        <v>3.4</v>
-      </c>
-      <c r="BI206">
-        <v>1.48</v>
-      </c>
-      <c r="BJ206">
-        <v>2.43</v>
-      </c>
-      <c r="BK206">
-        <v>1.77</v>
-      </c>
-      <c r="BL206">
-        <v>1.92</v>
-      </c>
       <c r="BM206">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="BN206">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="BO206">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP206">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="207" spans="1:68">
@@ -43905,7 +43917,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44111,7 +44123,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44474,6 +44486,624 @@
       </c>
       <c r="BP209">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7468566</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45717.54166666666</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>82</v>
+      </c>
+      <c r="H210" t="s">
+        <v>86</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>2</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>3</v>
+      </c>
+      <c r="N210">
+        <v>4</v>
+      </c>
+      <c r="O210" t="s">
+        <v>237</v>
+      </c>
+      <c r="P210" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q210">
+        <v>4.75</v>
+      </c>
+      <c r="R210">
+        <v>2.38</v>
+      </c>
+      <c r="S210">
+        <v>2.25</v>
+      </c>
+      <c r="T210">
+        <v>1.3</v>
+      </c>
+      <c r="U210">
+        <v>3.4</v>
+      </c>
+      <c r="V210">
+        <v>2.5</v>
+      </c>
+      <c r="W210">
+        <v>1.5</v>
+      </c>
+      <c r="X210">
+        <v>6</v>
+      </c>
+      <c r="Y210">
+        <v>1.13</v>
+      </c>
+      <c r="Z210">
+        <v>4.5</v>
+      </c>
+      <c r="AA210">
+        <v>4</v>
+      </c>
+      <c r="AB210">
+        <v>1.78</v>
+      </c>
+      <c r="AC210">
+        <v>1.03</v>
+      </c>
+      <c r="AD210">
+        <v>12</v>
+      </c>
+      <c r="AE210">
+        <v>1.2</v>
+      </c>
+      <c r="AF210">
+        <v>4.2</v>
+      </c>
+      <c r="AG210">
+        <v>1.67</v>
+      </c>
+      <c r="AH210">
+        <v>2.1</v>
+      </c>
+      <c r="AI210">
+        <v>1.62</v>
+      </c>
+      <c r="AJ210">
+        <v>2.2</v>
+      </c>
+      <c r="AK210">
+        <v>2.15</v>
+      </c>
+      <c r="AL210">
+        <v>1.23</v>
+      </c>
+      <c r="AM210">
+        <v>1.19</v>
+      </c>
+      <c r="AN210">
+        <v>1.55</v>
+      </c>
+      <c r="AO210">
+        <v>1.33</v>
+      </c>
+      <c r="AP210">
+        <v>1.42</v>
+      </c>
+      <c r="AQ210">
+        <v>1.46</v>
+      </c>
+      <c r="AR210">
+        <v>1.39</v>
+      </c>
+      <c r="AS210">
+        <v>1.46</v>
+      </c>
+      <c r="AT210">
+        <v>2.85</v>
+      </c>
+      <c r="AU210">
+        <v>5</v>
+      </c>
+      <c r="AV210">
+        <v>9</v>
+      </c>
+      <c r="AW210">
+        <v>8</v>
+      </c>
+      <c r="AX210">
+        <v>11</v>
+      </c>
+      <c r="AY210">
+        <v>15</v>
+      </c>
+      <c r="AZ210">
+        <v>21</v>
+      </c>
+      <c r="BA210">
+        <v>3</v>
+      </c>
+      <c r="BB210">
+        <v>4</v>
+      </c>
+      <c r="BC210">
+        <v>7</v>
+      </c>
+      <c r="BD210">
+        <v>2.9</v>
+      </c>
+      <c r="BE210">
+        <v>6.5</v>
+      </c>
+      <c r="BF210">
+        <v>1.49</v>
+      </c>
+      <c r="BG210">
+        <v>1.3</v>
+      </c>
+      <c r="BH210">
+        <v>3.15</v>
+      </c>
+      <c r="BI210">
+        <v>1.5</v>
+      </c>
+      <c r="BJ210">
+        <v>2.35</v>
+      </c>
+      <c r="BK210">
+        <v>1.83</v>
+      </c>
+      <c r="BL210">
+        <v>1.85</v>
+      </c>
+      <c r="BM210">
+        <v>2.32</v>
+      </c>
+      <c r="BN210">
+        <v>1.53</v>
+      </c>
+      <c r="BO210">
+        <v>3</v>
+      </c>
+      <c r="BP210">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7468567</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.625</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>83</v>
+      </c>
+      <c r="H211" t="s">
+        <v>70</v>
+      </c>
+      <c r="I211">
+        <v>2</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211">
+        <v>4</v>
+      </c>
+      <c r="L211">
+        <v>3</v>
+      </c>
+      <c r="M211">
+        <v>4</v>
+      </c>
+      <c r="N211">
+        <v>7</v>
+      </c>
+      <c r="O211" t="s">
+        <v>238</v>
+      </c>
+      <c r="P211" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q211">
+        <v>1.83</v>
+      </c>
+      <c r="R211">
+        <v>2.5</v>
+      </c>
+      <c r="S211">
+        <v>7</v>
+      </c>
+      <c r="T211">
+        <v>1.33</v>
+      </c>
+      <c r="U211">
+        <v>3.25</v>
+      </c>
+      <c r="V211">
+        <v>2.5</v>
+      </c>
+      <c r="W211">
+        <v>1.5</v>
+      </c>
+      <c r="X211">
+        <v>6</v>
+      </c>
+      <c r="Y211">
+        <v>1.13</v>
+      </c>
+      <c r="Z211">
+        <v>1.37</v>
+      </c>
+      <c r="AA211">
+        <v>5.1</v>
+      </c>
+      <c r="AB211">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC211">
+        <v>1.03</v>
+      </c>
+      <c r="AD211">
+        <v>11.5</v>
+      </c>
+      <c r="AE211">
+        <v>1.27</v>
+      </c>
+      <c r="AF211">
+        <v>3.74</v>
+      </c>
+      <c r="AG211">
+        <v>1.7</v>
+      </c>
+      <c r="AH211">
+        <v>2.05</v>
+      </c>
+      <c r="AI211">
+        <v>2</v>
+      </c>
+      <c r="AJ211">
+        <v>1.75</v>
+      </c>
+      <c r="AK211">
+        <v>1.08</v>
+      </c>
+      <c r="AL211">
+        <v>1.17</v>
+      </c>
+      <c r="AM211">
+        <v>3</v>
+      </c>
+      <c r="AN211">
+        <v>1.27</v>
+      </c>
+      <c r="AO211">
+        <v>1</v>
+      </c>
+      <c r="AP211">
+        <v>1.17</v>
+      </c>
+      <c r="AQ211">
+        <v>1.17</v>
+      </c>
+      <c r="AR211">
+        <v>1.62</v>
+      </c>
+      <c r="AS211">
+        <v>1.02</v>
+      </c>
+      <c r="AT211">
+        <v>2.64</v>
+      </c>
+      <c r="AU211">
+        <v>9</v>
+      </c>
+      <c r="AV211">
+        <v>5</v>
+      </c>
+      <c r="AW211">
+        <v>12</v>
+      </c>
+      <c r="AX211">
+        <v>4</v>
+      </c>
+      <c r="AY211">
+        <v>24</v>
+      </c>
+      <c r="AZ211">
+        <v>11</v>
+      </c>
+      <c r="BA211">
+        <v>9</v>
+      </c>
+      <c r="BB211">
+        <v>2</v>
+      </c>
+      <c r="BC211">
+        <v>11</v>
+      </c>
+      <c r="BD211">
+        <v>1.23</v>
+      </c>
+      <c r="BE211">
+        <v>8</v>
+      </c>
+      <c r="BF211">
+        <v>4.6</v>
+      </c>
+      <c r="BG211">
+        <v>1.33</v>
+      </c>
+      <c r="BH211">
+        <v>2.95</v>
+      </c>
+      <c r="BI211">
+        <v>1.56</v>
+      </c>
+      <c r="BJ211">
+        <v>2.23</v>
+      </c>
+      <c r="BK211">
+        <v>1.91</v>
+      </c>
+      <c r="BL211">
+        <v>1.78</v>
+      </c>
+      <c r="BM211">
+        <v>2.4</v>
+      </c>
+      <c r="BN211">
+        <v>1.49</v>
+      </c>
+      <c r="BO211">
+        <v>3.15</v>
+      </c>
+      <c r="BP211">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7468562</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45717.71180555555</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>79</v>
+      </c>
+      <c r="H212" t="s">
+        <v>81</v>
+      </c>
+      <c r="I212">
+        <v>4</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>4</v>
+      </c>
+      <c r="L212">
+        <v>4</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>5</v>
+      </c>
+      <c r="O212" t="s">
+        <v>239</v>
+      </c>
+      <c r="P212" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q212">
+        <v>1.91</v>
+      </c>
+      <c r="R212">
+        <v>2.63</v>
+      </c>
+      <c r="S212">
+        <v>5.5</v>
+      </c>
+      <c r="T212">
+        <v>1.25</v>
+      </c>
+      <c r="U212">
+        <v>3.75</v>
+      </c>
+      <c r="V212">
+        <v>2.1</v>
+      </c>
+      <c r="W212">
+        <v>1.67</v>
+      </c>
+      <c r="X212">
+        <v>5</v>
+      </c>
+      <c r="Y212">
+        <v>1.17</v>
+      </c>
+      <c r="Z212">
+        <v>1.49</v>
+      </c>
+      <c r="AA212">
+        <v>5.1</v>
+      </c>
+      <c r="AB212">
+        <v>5.9</v>
+      </c>
+      <c r="AC212">
+        <v>1.01</v>
+      </c>
+      <c r="AD212">
+        <v>17</v>
+      </c>
+      <c r="AE212">
+        <v>1.14</v>
+      </c>
+      <c r="AF212">
+        <v>5.5</v>
+      </c>
+      <c r="AG212">
+        <v>1.44</v>
+      </c>
+      <c r="AH212">
+        <v>2.67</v>
+      </c>
+      <c r="AI212">
+        <v>1.62</v>
+      </c>
+      <c r="AJ212">
+        <v>2.2</v>
+      </c>
+      <c r="AK212">
+        <v>1.13</v>
+      </c>
+      <c r="AL212">
+        <v>1.17</v>
+      </c>
+      <c r="AM212">
+        <v>2.65</v>
+      </c>
+      <c r="AN212">
+        <v>2.64</v>
+      </c>
+      <c r="AO212">
+        <v>1.55</v>
+      </c>
+      <c r="AP212">
+        <v>2.67</v>
+      </c>
+      <c r="AQ212">
+        <v>1.42</v>
+      </c>
+      <c r="AR212">
+        <v>2.34</v>
+      </c>
+      <c r="AS212">
+        <v>1.56</v>
+      </c>
+      <c r="AT212">
+        <v>3.9</v>
+      </c>
+      <c r="AU212">
+        <v>12</v>
+      </c>
+      <c r="AV212">
+        <v>3</v>
+      </c>
+      <c r="AW212">
+        <v>15</v>
+      </c>
+      <c r="AX212">
+        <v>4</v>
+      </c>
+      <c r="AY212">
+        <v>34</v>
+      </c>
+      <c r="AZ212">
+        <v>7</v>
+      </c>
+      <c r="BA212">
+        <v>9</v>
+      </c>
+      <c r="BB212">
+        <v>3</v>
+      </c>
+      <c r="BC212">
+        <v>12</v>
+      </c>
+      <c r="BD212">
+        <v>1.27</v>
+      </c>
+      <c r="BE212">
+        <v>7.5</v>
+      </c>
+      <c r="BF212">
+        <v>4.3</v>
+      </c>
+      <c r="BG212">
+        <v>1.34</v>
+      </c>
+      <c r="BH212">
+        <v>2.9</v>
+      </c>
+      <c r="BI212">
+        <v>1.57</v>
+      </c>
+      <c r="BJ212">
+        <v>2.23</v>
+      </c>
+      <c r="BK212">
+        <v>1.91</v>
+      </c>
+      <c r="BL212">
+        <v>1.77</v>
+      </c>
+      <c r="BM212">
+        <v>2.4</v>
+      </c>
+      <c r="BN212">
+        <v>1.49</v>
+      </c>
+      <c r="BO212">
+        <v>3.1</v>
+      </c>
+      <c r="BP212">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['6', '22', '28', '37']</t>
   </si>
   <si>
+    <t>['24', '82']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1070,6 +1073,15 @@
   </si>
   <si>
     <t>['28', '33', '62', '90+1']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['51', '57', '71', '90+4']</t>
+  </si>
+  <si>
+    <t>['28', '56', '69', '87']</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1687,7 +1699,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1893,7 +1905,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2099,7 +2111,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2511,7 +2523,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2589,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>1.46</v>
@@ -2717,7 +2729,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2795,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3207,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ9">
         <v>1.58</v>
@@ -3747,7 +3759,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3825,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>1.27</v>
@@ -4159,7 +4171,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4446,7 +4458,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ15">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4571,7 +4583,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4652,7 +4664,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5064,7 +5076,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ18">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5189,7 +5201,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5395,7 +5407,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5473,10 +5485,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5807,7 +5819,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5885,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ22">
         <v>0.92</v>
@@ -6013,7 +6025,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6219,7 +6231,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6425,7 +6437,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6503,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ25">
         <v>1.46</v>
@@ -6837,7 +6849,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6918,7 +6930,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ27">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR27">
         <v>0.32</v>
@@ -7043,7 +7055,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7661,7 +7673,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7739,7 +7751,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ31">
         <v>1.27</v>
@@ -7948,7 +7960,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>2.81</v>
@@ -8279,7 +8291,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8485,7 +8497,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9309,7 +9321,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9390,7 +9402,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9515,7 +9527,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10214,7 +10226,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10339,7 +10351,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10417,7 +10429,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ44">
         <v>0.92</v>
@@ -10545,7 +10557,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10623,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ45">
         <v>0.45</v>
@@ -10751,7 +10763,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10829,7 +10841,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ46">
         <v>2.25</v>
@@ -11035,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.61</v>
@@ -11163,7 +11175,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11244,7 +11256,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ48">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR48">
         <v>2.56</v>
@@ -11575,7 +11587,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11781,7 +11793,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11987,7 +11999,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12193,7 +12205,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12399,7 +12411,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12477,7 +12489,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -13017,7 +13029,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13304,7 +13316,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13429,7 +13441,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13713,7 +13725,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ60">
         <v>0.92</v>
@@ -14047,7 +14059,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14253,7 +14265,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14459,7 +14471,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14952,7 +14964,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ66">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15077,7 +15089,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15283,7 +15295,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15364,7 +15376,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15489,7 +15501,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15695,7 +15707,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15901,7 +15913,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16107,7 +16119,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16185,7 +16197,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -16313,7 +16325,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16391,7 +16403,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ73">
         <v>2.25</v>
@@ -16725,7 +16737,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16803,7 +16815,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75">
         <v>0.17</v>
@@ -16931,7 +16943,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17012,7 +17024,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.01</v>
@@ -17137,7 +17149,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17343,7 +17355,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17421,7 +17433,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ78">
         <v>0.45</v>
@@ -17549,7 +17561,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17627,10 +17639,10 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ79">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -17755,7 +17767,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18167,7 +18179,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18991,7 +19003,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19278,7 +19290,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19687,10 +19699,10 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ89">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR89">
         <v>1.39</v>
@@ -20021,7 +20033,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20227,7 +20239,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20433,7 +20445,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20639,7 +20651,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20845,7 +20857,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20923,7 +20935,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ95">
         <v>2.5</v>
@@ -21051,7 +21063,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21257,7 +21269,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21338,7 +21350,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ97">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21463,7 +21475,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21541,10 +21553,10 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ98">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.3</v>
@@ -21669,7 +21681,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21953,7 +21965,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>0.17</v>
@@ -22081,7 +22093,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22162,7 +22174,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ101">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -22368,7 +22380,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ102">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22493,7 +22505,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23192,7 +23204,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR106">
         <v>1.43</v>
@@ -23395,7 +23407,7 @@
         <v>1.2</v>
       </c>
       <c r="AP107">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ107">
         <v>1.33</v>
@@ -23523,7 +23535,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23729,7 +23741,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23810,7 +23822,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23935,7 +23947,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24428,7 +24440,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24759,7 +24771,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24837,7 +24849,7 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ114">
         <v>1.42</v>
@@ -24965,7 +24977,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25377,7 +25389,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25455,7 +25467,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ117">
         <v>1.46</v>
@@ -25583,7 +25595,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25870,7 +25882,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.36</v>
@@ -26073,7 +26085,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120">
         <v>2.5</v>
@@ -26282,7 +26294,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ121">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26407,7 +26419,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26613,7 +26625,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26691,7 +26703,7 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -27312,7 +27324,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ126">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR126">
         <v>1.51</v>
@@ -27437,7 +27449,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27849,7 +27861,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28055,7 +28067,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28133,7 +28145,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ130">
         <v>1.58</v>
@@ -28467,7 +28479,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28545,7 +28557,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132">
         <v>1.46</v>
@@ -28673,7 +28685,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28754,7 +28766,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -29497,7 +29509,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29703,7 +29715,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29784,7 +29796,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ138">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR138">
         <v>1.63</v>
@@ -29909,7 +29921,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30115,7 +30127,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30399,7 +30411,7 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ141">
         <v>0.27</v>
@@ -30608,7 +30620,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -31017,10 +31029,10 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ144">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.26</v>
@@ -31351,7 +31363,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31635,7 +31647,7 @@
         <v>1.63</v>
       </c>
       <c r="AP147">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ147">
         <v>1.42</v>
@@ -31763,7 +31775,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31969,7 +31981,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32175,7 +32187,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32381,7 +32393,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32587,7 +32599,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32665,7 +32677,7 @@
         <v>1.13</v>
       </c>
       <c r="AP152">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ152">
         <v>1.33</v>
@@ -32793,7 +32805,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32874,7 +32886,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33283,7 +33295,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ155">
         <v>1.27</v>
@@ -33617,7 +33629,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33823,7 +33835,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33904,7 +33916,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.48</v>
@@ -34107,10 +34119,10 @@
         <v>1.25</v>
       </c>
       <c r="AP159">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34519,7 +34531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ161">
         <v>0.45</v>
@@ -34853,7 +34865,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34934,7 +34946,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR163">
         <v>1.45</v>
@@ -35137,7 +35149,7 @@
         <v>0.11</v>
       </c>
       <c r="AP164">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ164">
         <v>0.17</v>
@@ -35265,7 +35277,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35346,7 +35358,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ165">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR165">
         <v>1.5</v>
@@ -35677,7 +35689,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35883,7 +35895,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35964,7 +35976,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ168">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR168">
         <v>1.13</v>
@@ -36295,7 +36307,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36913,7 +36925,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -36991,7 +37003,7 @@
         <v>1.78</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ173">
         <v>1.58</v>
@@ -37119,7 +37131,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37325,7 +37337,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37737,7 +37749,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38024,7 +38036,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR178">
         <v>1.61</v>
@@ -38227,7 +38239,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ179">
         <v>1.17</v>
@@ -38355,7 +38367,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38561,7 +38573,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38767,7 +38779,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38848,7 +38860,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ182">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39385,7 +39397,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39591,7 +39603,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39672,7 +39684,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ186">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR186">
         <v>1.27</v>
@@ -39875,7 +39887,7 @@
         <v>1.33</v>
       </c>
       <c r="AP187">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -40003,7 +40015,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40081,10 +40093,10 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ188">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.32</v>
@@ -40415,7 +40427,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40493,7 +40505,7 @@
         <v>2.4</v>
       </c>
       <c r="AP190">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ190">
         <v>2.25</v>
@@ -40621,7 +40633,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40827,7 +40839,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41239,7 +41251,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41445,7 +41457,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41523,7 +41535,7 @@
         <v>1.18</v>
       </c>
       <c r="AP195">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ195">
         <v>1.33</v>
@@ -41651,7 +41663,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41732,7 +41744,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR196">
         <v>1.69</v>
@@ -42063,7 +42075,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42269,7 +42281,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42887,7 +42899,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43171,7 +43183,7 @@
         <v>2.45</v>
       </c>
       <c r="AP203">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ203">
         <v>2.25</v>
@@ -43792,7 +43804,7 @@
         <v>2</v>
       </c>
       <c r="AQ206">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR206">
         <v>1.37</v>
@@ -43917,7 +43929,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -43998,7 +44010,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ207">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR207">
         <v>1.17</v>
@@ -44123,7 +44135,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44201,7 +44213,7 @@
         <v>2.45</v>
       </c>
       <c r="AP208">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ208">
         <v>2.5</v>
@@ -44535,7 +44547,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44741,7 +44753,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45104,6 +45116,830 @@
       </c>
       <c r="BP212">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7468564</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>80</v>
+      </c>
+      <c r="H213" t="s">
+        <v>71</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>2</v>
+      </c>
+      <c r="L213">
+        <v>2</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213" t="s">
+        <v>240</v>
+      </c>
+      <c r="P213" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q213">
+        <v>2.2</v>
+      </c>
+      <c r="R213">
+        <v>2.38</v>
+      </c>
+      <c r="S213">
+        <v>5</v>
+      </c>
+      <c r="T213">
+        <v>1.33</v>
+      </c>
+      <c r="U213">
+        <v>3.25</v>
+      </c>
+      <c r="V213">
+        <v>2.5</v>
+      </c>
+      <c r="W213">
+        <v>1.5</v>
+      </c>
+      <c r="X213">
+        <v>6.5</v>
+      </c>
+      <c r="Y213">
+        <v>1.11</v>
+      </c>
+      <c r="Z213">
+        <v>1.69</v>
+      </c>
+      <c r="AA213">
+        <v>4.4</v>
+      </c>
+      <c r="AB213">
+        <v>4.7</v>
+      </c>
+      <c r="AC213">
+        <v>1.01</v>
+      </c>
+      <c r="AD213">
+        <v>16</v>
+      </c>
+      <c r="AE213">
+        <v>1.17</v>
+      </c>
+      <c r="AF213">
+        <v>4.25</v>
+      </c>
+      <c r="AG213">
+        <v>1.57</v>
+      </c>
+      <c r="AH213">
+        <v>2.25</v>
+      </c>
+      <c r="AI213">
+        <v>1.7</v>
+      </c>
+      <c r="AJ213">
+        <v>2.05</v>
+      </c>
+      <c r="AK213">
+        <v>1.18</v>
+      </c>
+      <c r="AL213">
+        <v>1.23</v>
+      </c>
+      <c r="AM213">
+        <v>2.2</v>
+      </c>
+      <c r="AN213">
+        <v>1.82</v>
+      </c>
+      <c r="AO213">
+        <v>1.08</v>
+      </c>
+      <c r="AP213">
+        <v>1.92</v>
+      </c>
+      <c r="AQ213">
+        <v>1</v>
+      </c>
+      <c r="AR213">
+        <v>1.74</v>
+      </c>
+      <c r="AS213">
+        <v>1.4</v>
+      </c>
+      <c r="AT213">
+        <v>3.14</v>
+      </c>
+      <c r="AU213">
+        <v>5</v>
+      </c>
+      <c r="AV213">
+        <v>6</v>
+      </c>
+      <c r="AW213">
+        <v>6</v>
+      </c>
+      <c r="AX213">
+        <v>12</v>
+      </c>
+      <c r="AY213">
+        <v>11</v>
+      </c>
+      <c r="AZ213">
+        <v>18</v>
+      </c>
+      <c r="BA213">
+        <v>2</v>
+      </c>
+      <c r="BB213">
+        <v>5</v>
+      </c>
+      <c r="BC213">
+        <v>7</v>
+      </c>
+      <c r="BD213">
+        <v>1.53</v>
+      </c>
+      <c r="BE213">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF213">
+        <v>3.12</v>
+      </c>
+      <c r="BG213">
+        <v>1.24</v>
+      </c>
+      <c r="BH213">
+        <v>3.34</v>
+      </c>
+      <c r="BI213">
+        <v>1.48</v>
+      </c>
+      <c r="BJ213">
+        <v>2.4</v>
+      </c>
+      <c r="BK213">
+        <v>1.85</v>
+      </c>
+      <c r="BL213">
+        <v>1.85</v>
+      </c>
+      <c r="BM213">
+        <v>2.38</v>
+      </c>
+      <c r="BN213">
+        <v>1.49</v>
+      </c>
+      <c r="BO213">
+        <v>3.14</v>
+      </c>
+      <c r="BP213">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7468570</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45718.55208333334</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>77</v>
+      </c>
+      <c r="H214" t="s">
+        <v>76</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>4</v>
+      </c>
+      <c r="N214">
+        <v>4</v>
+      </c>
+      <c r="O214" t="s">
+        <v>90</v>
+      </c>
+      <c r="P214" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q214">
+        <v>4</v>
+      </c>
+      <c r="R214">
+        <v>2</v>
+      </c>
+      <c r="S214">
+        <v>3.1</v>
+      </c>
+      <c r="T214">
+        <v>1.5</v>
+      </c>
+      <c r="U214">
+        <v>2.5</v>
+      </c>
+      <c r="V214">
+        <v>3.5</v>
+      </c>
+      <c r="W214">
+        <v>1.29</v>
+      </c>
+      <c r="X214">
+        <v>11</v>
+      </c>
+      <c r="Y214">
+        <v>1.05</v>
+      </c>
+      <c r="Z214">
+        <v>2.88</v>
+      </c>
+      <c r="AA214">
+        <v>3.41</v>
+      </c>
+      <c r="AB214">
+        <v>2.53</v>
+      </c>
+      <c r="AC214">
+        <v>1.08</v>
+      </c>
+      <c r="AD214">
+        <v>9</v>
+      </c>
+      <c r="AE214">
+        <v>1.42</v>
+      </c>
+      <c r="AF214">
+        <v>2.9</v>
+      </c>
+      <c r="AG214">
+        <v>2</v>
+      </c>
+      <c r="AH214">
+        <v>1.75</v>
+      </c>
+      <c r="AI214">
+        <v>1.95</v>
+      </c>
+      <c r="AJ214">
+        <v>1.8</v>
+      </c>
+      <c r="AK214">
+        <v>1.58</v>
+      </c>
+      <c r="AL214">
+        <v>1.33</v>
+      </c>
+      <c r="AM214">
+        <v>1.35</v>
+      </c>
+      <c r="AN214">
+        <v>1</v>
+      </c>
+      <c r="AO214">
+        <v>1.36</v>
+      </c>
+      <c r="AP214">
+        <v>0.92</v>
+      </c>
+      <c r="AQ214">
+        <v>1.5</v>
+      </c>
+      <c r="AR214">
+        <v>1.25</v>
+      </c>
+      <c r="AS214">
+        <v>1.23</v>
+      </c>
+      <c r="AT214">
+        <v>2.48</v>
+      </c>
+      <c r="AU214">
+        <v>2</v>
+      </c>
+      <c r="AV214">
+        <v>14</v>
+      </c>
+      <c r="AW214">
+        <v>5</v>
+      </c>
+      <c r="AX214">
+        <v>7</v>
+      </c>
+      <c r="AY214">
+        <v>9</v>
+      </c>
+      <c r="AZ214">
+        <v>21</v>
+      </c>
+      <c r="BA214">
+        <v>4</v>
+      </c>
+      <c r="BB214">
+        <v>9</v>
+      </c>
+      <c r="BC214">
+        <v>13</v>
+      </c>
+      <c r="BD214">
+        <v>2.41</v>
+      </c>
+      <c r="BE214">
+        <v>6.15</v>
+      </c>
+      <c r="BF214">
+        <v>1.96</v>
+      </c>
+      <c r="BG214">
+        <v>1.49</v>
+      </c>
+      <c r="BH214">
+        <v>2.38</v>
+      </c>
+      <c r="BI214">
+        <v>1.9</v>
+      </c>
+      <c r="BJ214">
+        <v>1.8</v>
+      </c>
+      <c r="BK214">
+        <v>2.51</v>
+      </c>
+      <c r="BL214">
+        <v>1.44</v>
+      </c>
+      <c r="BM214">
+        <v>3.42</v>
+      </c>
+      <c r="BN214">
+        <v>1.23</v>
+      </c>
+      <c r="BO214">
+        <v>4.95</v>
+      </c>
+      <c r="BP214">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7468565</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45718.55208333334</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>75</v>
+      </c>
+      <c r="H215" t="s">
+        <v>78</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>4</v>
+      </c>
+      <c r="N215">
+        <v>4</v>
+      </c>
+      <c r="O215" t="s">
+        <v>90</v>
+      </c>
+      <c r="P215" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q215">
+        <v>4</v>
+      </c>
+      <c r="R215">
+        <v>2.2</v>
+      </c>
+      <c r="S215">
+        <v>2.63</v>
+      </c>
+      <c r="T215">
+        <v>1.36</v>
+      </c>
+      <c r="U215">
+        <v>3</v>
+      </c>
+      <c r="V215">
+        <v>2.75</v>
+      </c>
+      <c r="W215">
+        <v>1.4</v>
+      </c>
+      <c r="X215">
+        <v>7</v>
+      </c>
+      <c r="Y215">
+        <v>1.1</v>
+      </c>
+      <c r="Z215">
+        <v>3.5</v>
+      </c>
+      <c r="AA215">
+        <v>3.61</v>
+      </c>
+      <c r="AB215">
+        <v>2.12</v>
+      </c>
+      <c r="AC215">
+        <v>1.05</v>
+      </c>
+      <c r="AD215">
+        <v>12</v>
+      </c>
+      <c r="AE215">
+        <v>1.28</v>
+      </c>
+      <c r="AF215">
+        <v>3.75</v>
+      </c>
+      <c r="AG215">
+        <v>1.81</v>
+      </c>
+      <c r="AH215">
+        <v>2.01</v>
+      </c>
+      <c r="AI215">
+        <v>1.7</v>
+      </c>
+      <c r="AJ215">
+        <v>2.05</v>
+      </c>
+      <c r="AK215">
+        <v>1.71</v>
+      </c>
+      <c r="AL215">
+        <v>1.29</v>
+      </c>
+      <c r="AM215">
+        <v>1.31</v>
+      </c>
+      <c r="AN215">
+        <v>1</v>
+      </c>
+      <c r="AO215">
+        <v>0.4</v>
+      </c>
+      <c r="AP215">
+        <v>0.92</v>
+      </c>
+      <c r="AQ215">
+        <v>0.64</v>
+      </c>
+      <c r="AR215">
+        <v>1.47</v>
+      </c>
+      <c r="AS215">
+        <v>1.3</v>
+      </c>
+      <c r="AT215">
+        <v>2.77</v>
+      </c>
+      <c r="AU215">
+        <v>8</v>
+      </c>
+      <c r="AV215">
+        <v>8</v>
+      </c>
+      <c r="AW215">
+        <v>12</v>
+      </c>
+      <c r="AX215">
+        <v>5</v>
+      </c>
+      <c r="AY215">
+        <v>23</v>
+      </c>
+      <c r="AZ215">
+        <v>14</v>
+      </c>
+      <c r="BA215">
+        <v>6</v>
+      </c>
+      <c r="BB215">
+        <v>5</v>
+      </c>
+      <c r="BC215">
+        <v>11</v>
+      </c>
+      <c r="BD215">
+        <v>2.45</v>
+      </c>
+      <c r="BE215">
+        <v>8.5</v>
+      </c>
+      <c r="BF215">
+        <v>1.78</v>
+      </c>
+      <c r="BG215">
+        <v>1.28</v>
+      </c>
+      <c r="BH215">
+        <v>3.08</v>
+      </c>
+      <c r="BI215">
+        <v>1.54</v>
+      </c>
+      <c r="BJ215">
+        <v>2.25</v>
+      </c>
+      <c r="BK215">
+        <v>1.95</v>
+      </c>
+      <c r="BL215">
+        <v>1.76</v>
+      </c>
+      <c r="BM215">
+        <v>2.54</v>
+      </c>
+      <c r="BN215">
+        <v>1.43</v>
+      </c>
+      <c r="BO215">
+        <v>3.42</v>
+      </c>
+      <c r="BP215">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7468568</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45718.55208333334</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>74</v>
+      </c>
+      <c r="H216" t="s">
+        <v>84</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>90</v>
+      </c>
+      <c r="P216" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q216">
+        <v>3.4</v>
+      </c>
+      <c r="R216">
+        <v>2.2</v>
+      </c>
+      <c r="S216">
+        <v>3.1</v>
+      </c>
+      <c r="T216">
+        <v>1.36</v>
+      </c>
+      <c r="U216">
+        <v>3</v>
+      </c>
+      <c r="V216">
+        <v>2.75</v>
+      </c>
+      <c r="W216">
+        <v>1.4</v>
+      </c>
+      <c r="X216">
+        <v>7</v>
+      </c>
+      <c r="Y216">
+        <v>1.1</v>
+      </c>
+      <c r="Z216">
+        <v>2.92</v>
+      </c>
+      <c r="AA216">
+        <v>3.37</v>
+      </c>
+      <c r="AB216">
+        <v>2.52</v>
+      </c>
+      <c r="AC216">
+        <v>1.05</v>
+      </c>
+      <c r="AD216">
+        <v>11</v>
+      </c>
+      <c r="AE216">
+        <v>1.28</v>
+      </c>
+      <c r="AF216">
+        <v>3.75</v>
+      </c>
+      <c r="AG216">
+        <v>1.82</v>
+      </c>
+      <c r="AH216">
+        <v>2</v>
+      </c>
+      <c r="AI216">
+        <v>1.67</v>
+      </c>
+      <c r="AJ216">
+        <v>2.1</v>
+      </c>
+      <c r="AK216">
+        <v>1.52</v>
+      </c>
+      <c r="AL216">
+        <v>1.3</v>
+      </c>
+      <c r="AM216">
+        <v>1.43</v>
+      </c>
+      <c r="AN216">
+        <v>1.92</v>
+      </c>
+      <c r="AO216">
+        <v>1</v>
+      </c>
+      <c r="AP216">
+        <v>1.77</v>
+      </c>
+      <c r="AQ216">
+        <v>1.15</v>
+      </c>
+      <c r="AR216">
+        <v>1.31</v>
+      </c>
+      <c r="AS216">
+        <v>1.25</v>
+      </c>
+      <c r="AT216">
+        <v>2.56</v>
+      </c>
+      <c r="AU216">
+        <v>6</v>
+      </c>
+      <c r="AV216">
+        <v>3</v>
+      </c>
+      <c r="AW216">
+        <v>9</v>
+      </c>
+      <c r="AX216">
+        <v>3</v>
+      </c>
+      <c r="AY216">
+        <v>20</v>
+      </c>
+      <c r="AZ216">
+        <v>8</v>
+      </c>
+      <c r="BA216">
+        <v>5</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>8</v>
+      </c>
+      <c r="BD216">
+        <v>1.96</v>
+      </c>
+      <c r="BE216">
+        <v>6.4</v>
+      </c>
+      <c r="BF216">
+        <v>2.38</v>
+      </c>
+      <c r="BG216">
+        <v>1.36</v>
+      </c>
+      <c r="BH216">
+        <v>2.78</v>
+      </c>
+      <c r="BI216">
+        <v>1.68</v>
+      </c>
+      <c r="BJ216">
+        <v>2.06</v>
+      </c>
+      <c r="BK216">
+        <v>2.14</v>
+      </c>
+      <c r="BL216">
+        <v>1.6</v>
+      </c>
+      <c r="BM216">
+        <v>2.83</v>
+      </c>
+      <c r="BN216">
+        <v>1.33</v>
+      </c>
+      <c r="BO216">
+        <v>4</v>
+      </c>
+      <c r="BP216">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -739,6 +739,9 @@
     <t>['24', '82']</t>
   </si>
   <si>
+    <t>['73', '77']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1443,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1699,7 +1702,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1905,7 +1908,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2111,7 +2114,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2523,7 +2526,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2729,7 +2732,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3016,7 +3019,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3759,7 +3762,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4171,7 +4174,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4583,7 +4586,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5201,7 +5204,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5279,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5407,7 +5410,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5819,7 +5822,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5900,7 +5903,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ22">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -6025,7 +6028,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6231,7 +6234,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6437,7 +6440,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6849,7 +6852,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7055,7 +7058,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7545,7 +7548,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ30">
         <v>1.46</v>
@@ -7673,7 +7676,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8291,7 +8294,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8497,7 +8500,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9321,7 +9324,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9527,7 +9530,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10351,7 +10354,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10432,7 +10435,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10557,7 +10560,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10763,7 +10766,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11175,7 +11178,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11587,7 +11590,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11793,7 +11796,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11999,7 +12002,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12205,7 +12208,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12411,7 +12414,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12901,7 +12904,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ56">
         <v>1.33</v>
@@ -13029,7 +13032,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13441,7 +13444,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13728,7 +13731,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ60">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -14059,7 +14062,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14265,7 +14268,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14471,7 +14474,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15089,7 +15092,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15295,7 +15298,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15501,7 +15504,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15707,7 +15710,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15913,7 +15916,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16119,7 +16122,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16325,7 +16328,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16737,7 +16740,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16943,7 +16946,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17149,7 +17152,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17355,7 +17358,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17561,7 +17564,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17767,7 +17770,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17848,7 +17851,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -18179,7 +18182,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18257,7 +18260,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ82">
         <v>2.5</v>
@@ -19003,7 +19006,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -20033,7 +20036,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20239,7 +20242,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20317,7 +20320,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ92">
         <v>0.45</v>
@@ -20445,7 +20448,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20651,7 +20654,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20732,7 +20735,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ94">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -20857,7 +20860,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21063,7 +21066,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21269,7 +21272,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21475,7 +21478,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21681,7 +21684,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22093,7 +22096,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22505,7 +22508,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23535,7 +23538,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23741,7 +23744,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23947,7 +23950,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24646,7 +24649,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ113">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24771,7 +24774,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24977,7 +24980,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25389,7 +25392,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25595,7 +25598,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25673,7 +25676,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ118">
         <v>1.27</v>
@@ -26419,7 +26422,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26625,7 +26628,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27449,7 +27452,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27861,7 +27864,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27939,7 +27942,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ129">
         <v>1.42</v>
@@ -28067,7 +28070,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28479,7 +28482,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28685,7 +28688,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28972,7 +28975,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ134">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29509,7 +29512,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29715,7 +29718,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29921,7 +29924,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30127,7 +30130,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30208,7 +30211,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -31235,7 +31238,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ145">
         <v>1.17</v>
@@ -31363,7 +31366,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31775,7 +31778,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31981,7 +31984,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32187,7 +32190,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32393,7 +32396,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32599,7 +32602,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32805,7 +32808,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33629,7 +33632,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33835,7 +33838,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34328,7 +34331,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ160">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34865,7 +34868,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34943,7 +34946,7 @@
         <v>0.89</v>
       </c>
       <c r="AP163">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ163">
         <v>1.15</v>
@@ -35277,7 +35280,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35689,7 +35692,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35895,7 +35898,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36307,7 +36310,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36925,7 +36928,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37131,7 +37134,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37337,7 +37340,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37749,7 +37752,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38367,7 +38370,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38448,7 +38451,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ180">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR180">
         <v>1.22</v>
@@ -38573,7 +38576,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38651,7 +38654,7 @@
         <v>1.3</v>
       </c>
       <c r="AP181">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ181">
         <v>1.33</v>
@@ -38779,7 +38782,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39397,7 +39400,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39603,7 +39606,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -40015,7 +40018,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40427,7 +40430,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40633,7 +40636,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40839,7 +40842,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -40917,7 +40920,7 @@
         <v>0.18</v>
       </c>
       <c r="AP192">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ192">
         <v>0.17</v>
@@ -41126,7 +41129,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ193">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -41251,7 +41254,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41457,7 +41460,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41663,7 +41666,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42075,7 +42078,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42281,7 +42284,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42899,7 +42902,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43929,7 +43932,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44135,7 +44138,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44547,7 +44550,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44753,7 +44756,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45165,7 +45168,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45371,7 +45374,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45577,7 +45580,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45940,6 +45943,212 @@
       </c>
       <c r="BP216">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7468563</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45718.69791666666</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>87</v>
+      </c>
+      <c r="H217" t="s">
+        <v>85</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>241</v>
+      </c>
+      <c r="P217" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q217">
+        <v>1.91</v>
+      </c>
+      <c r="R217">
+        <v>2.5</v>
+      </c>
+      <c r="S217">
+        <v>6.5</v>
+      </c>
+      <c r="T217">
+        <v>1.3</v>
+      </c>
+      <c r="U217">
+        <v>3.4</v>
+      </c>
+      <c r="V217">
+        <v>2.38</v>
+      </c>
+      <c r="W217">
+        <v>1.53</v>
+      </c>
+      <c r="X217">
+        <v>6</v>
+      </c>
+      <c r="Y217">
+        <v>1.13</v>
+      </c>
+      <c r="Z217">
+        <v>1.36</v>
+      </c>
+      <c r="AA217">
+        <v>5.6</v>
+      </c>
+      <c r="AB217">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC217">
+        <v>1.02</v>
+      </c>
+      <c r="AD217">
+        <v>13.5</v>
+      </c>
+      <c r="AE217">
+        <v>1.19</v>
+      </c>
+      <c r="AF217">
+        <v>4.4</v>
+      </c>
+      <c r="AG217">
+        <v>1.6</v>
+      </c>
+      <c r="AH217">
+        <v>2.2</v>
+      </c>
+      <c r="AI217">
+        <v>1.8</v>
+      </c>
+      <c r="AJ217">
+        <v>1.95</v>
+      </c>
+      <c r="AK217">
+        <v>1.11</v>
+      </c>
+      <c r="AL217">
+        <v>1.17</v>
+      </c>
+      <c r="AM217">
+        <v>2.8</v>
+      </c>
+      <c r="AN217">
+        <v>1.73</v>
+      </c>
+      <c r="AO217">
+        <v>0.92</v>
+      </c>
+      <c r="AP217">
+        <v>1.83</v>
+      </c>
+      <c r="AQ217">
+        <v>0.85</v>
+      </c>
+      <c r="AR217">
+        <v>1.76</v>
+      </c>
+      <c r="AS217">
+        <v>1.14</v>
+      </c>
+      <c r="AT217">
+        <v>2.9</v>
+      </c>
+      <c r="AU217">
+        <v>8</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>15</v>
+      </c>
+      <c r="AX217">
+        <v>6</v>
+      </c>
+      <c r="AY217">
+        <v>26</v>
+      </c>
+      <c r="AZ217">
+        <v>10</v>
+      </c>
+      <c r="BA217">
+        <v>3</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>5</v>
+      </c>
+      <c r="BD217">
+        <v>1.18</v>
+      </c>
+      <c r="BE217">
+        <v>12</v>
+      </c>
+      <c r="BF217">
+        <v>6.3</v>
+      </c>
+      <c r="BG217">
+        <v>1.22</v>
+      </c>
+      <c r="BH217">
+        <v>3.5</v>
+      </c>
+      <c r="BI217">
+        <v>1.44</v>
+      </c>
+      <c r="BJ217">
+        <v>2.51</v>
+      </c>
+      <c r="BK217">
+        <v>1.78</v>
+      </c>
+      <c r="BL217">
+        <v>1.93</v>
+      </c>
+      <c r="BM217">
+        <v>2.23</v>
+      </c>
+      <c r="BN217">
+        <v>1.55</v>
+      </c>
+      <c r="BO217">
+        <v>2.92</v>
+      </c>
+      <c r="BP217">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="358">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,9 @@
     <t>['73', '77']</t>
   </si>
   <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -908,9 +911,6 @@
   </si>
   <si>
     <t>['14', '23']</t>
-  </si>
-  <si>
-    <t>['50']</t>
   </si>
   <si>
     <t>['15', '21', '57']</t>
@@ -1085,6 +1085,9 @@
   </si>
   <si>
     <t>['28', '56', '69', '87']</t>
+  </si>
+  <si>
+    <t>['27', '50', '90+1', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1702,7 +1705,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1783,7 +1786,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1908,7 +1911,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2114,7 +2117,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2526,7 +2529,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2732,7 +2735,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3016,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ8">
         <v>0.85</v>
@@ -3225,7 +3228,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3428,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3637,7 +3640,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ11">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3762,7 +3765,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3843,7 +3846,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4046,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -4174,7 +4177,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4586,7 +4589,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5204,7 +5207,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5282,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5410,7 +5413,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5822,7 +5825,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6028,7 +6031,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6106,7 +6109,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ23">
         <v>2.25</v>
@@ -6234,7 +6237,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6315,7 +6318,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ24">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -6440,7 +6443,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6852,7 +6855,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7058,7 +7061,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7136,10 +7139,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7548,7 +7551,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ30">
         <v>1.46</v>
@@ -7676,7 +7679,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7757,7 +7760,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -8166,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ33">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR33">
         <v>2.21</v>
@@ -8294,7 +8297,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8500,7 +8503,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8784,7 +8787,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ36">
         <v>1.17</v>
@@ -9324,7 +9327,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9402,7 +9405,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ39">
         <v>1.15</v>
@@ -9530,7 +9533,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9608,10 +9611,10 @@
         <v>2</v>
       </c>
       <c r="AP40">
+        <v>1.57</v>
+      </c>
+      <c r="AQ40">
         <v>1.69</v>
-      </c>
-      <c r="AQ40">
-        <v>1.58</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9817,7 +9820,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ41">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -10354,7 +10357,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10560,7 +10563,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10766,7 +10769,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11178,7 +11181,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11590,7 +11593,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11796,7 +11799,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11877,7 +11880,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ51">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -12002,7 +12005,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12080,7 +12083,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -12208,7 +12211,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12414,7 +12417,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12904,7 +12907,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ56">
         <v>1.33</v>
@@ -13032,7 +13035,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13316,7 +13319,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ58">
         <v>1.5</v>
@@ -13444,7 +13447,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13522,10 +13525,10 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -14062,7 +14065,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14143,7 +14146,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14268,7 +14271,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14349,7 +14352,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ63">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR63">
         <v>0.8100000000000001</v>
@@ -14474,7 +14477,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14555,7 +14558,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -15092,7 +15095,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15173,7 +15176,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ67">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -15298,7 +15301,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15504,7 +15507,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15710,7 +15713,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15788,7 +15791,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -15916,7 +15919,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16122,7 +16125,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16328,7 +16331,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16612,7 +16615,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ74">
         <v>1.17</v>
@@ -16740,7 +16743,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16946,7 +16949,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17152,7 +17155,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17358,7 +17361,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17564,7 +17567,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17770,7 +17773,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18057,7 +18060,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ81">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18182,7 +18185,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18260,10 +18263,10 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ82">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18672,7 +18675,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18881,7 +18884,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ85">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -19006,7 +19009,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19496,7 +19499,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19911,7 +19914,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ90">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR90">
         <v>1.17</v>
@@ -20036,7 +20039,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20242,7 +20245,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20320,7 +20323,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ92">
         <v>0.45</v>
@@ -20448,7 +20451,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20529,7 +20532,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20654,7 +20657,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20860,7 +20863,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20941,7 +20944,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ95">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -21066,7 +21069,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21272,7 +21275,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21350,7 +21353,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ97">
         <v>1.5</v>
@@ -21478,7 +21481,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -22795,7 +22798,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23204,7 +23207,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106">
         <v>0.64</v>
@@ -24031,7 +24034,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ110">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24234,7 +24237,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ111">
         <v>0.17</v>
@@ -25264,7 +25267,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ116">
         <v>0.45</v>
@@ -25676,10 +25679,10 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ118">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -25882,7 +25885,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26091,7 +26094,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26915,7 +26918,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ124">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR124">
         <v>1.73</v>
@@ -27736,7 +27739,7 @@
         <v>0.14</v>
       </c>
       <c r="AP128">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ128">
         <v>0.17</v>
@@ -27942,7 +27945,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ129">
         <v>1.42</v>
@@ -28151,7 +28154,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ130">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28357,7 +28360,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ131">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -29178,7 +29181,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135">
         <v>1.33</v>
@@ -29593,7 +29596,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ137">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29924,7 +29927,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30208,7 +30211,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ140">
         <v>0.85</v>
@@ -30417,7 +30420,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ141">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -31238,7 +31241,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145">
         <v>1.17</v>
@@ -31447,7 +31450,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ146">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -32268,7 +32271,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ150">
         <v>2.25</v>
@@ -32477,7 +32480,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ151">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR151">
         <v>1.15</v>
@@ -32886,7 +32889,7 @@
         <v>0.63</v>
       </c>
       <c r="AP153">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ153">
         <v>1.15</v>
@@ -33301,7 +33304,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ155">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR155">
         <v>1.44</v>
@@ -33504,7 +33507,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ156">
         <v>1.46</v>
@@ -33713,7 +33716,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ157">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR157">
         <v>1.67</v>
@@ -33916,7 +33919,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34946,7 +34949,7 @@
         <v>0.89</v>
       </c>
       <c r="AP163">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ163">
         <v>1.15</v>
@@ -36388,10 +36391,10 @@
         <v>0</v>
       </c>
       <c r="AP170">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ170">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR170">
         <v>1.48</v>
@@ -37009,7 +37012,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ173">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37215,7 +37218,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR174">
         <v>1.46</v>
@@ -37624,7 +37627,7 @@
         <v>0.2</v>
       </c>
       <c r="AP176">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ176">
         <v>0.17</v>
@@ -37752,7 +37755,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37830,7 +37833,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ177">
         <v>1.46</v>
@@ -38036,7 +38039,7 @@
         <v>0.9</v>
       </c>
       <c r="AP178">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ178">
         <v>1.15</v>
@@ -38654,7 +38657,7 @@
         <v>1.3</v>
       </c>
       <c r="AP181">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ181">
         <v>1.33</v>
@@ -39069,7 +39072,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ183">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR183">
         <v>2.35</v>
@@ -39275,7 +39278,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ184">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR184">
         <v>1.58</v>
@@ -39478,7 +39481,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ185">
         <v>1.17</v>
@@ -40305,7 +40308,7 @@
         <v>2</v>
       </c>
       <c r="AQ189">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR189">
         <v>1.26</v>
@@ -40920,7 +40923,7 @@
         <v>0.18</v>
       </c>
       <c r="AP192">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ192">
         <v>0.17</v>
@@ -41254,7 +41257,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41332,10 +41335,10 @@
         <v>2.4</v>
       </c>
       <c r="AP194">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ194">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -42362,7 +42365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ199">
         <v>1.42</v>
@@ -42568,7 +42571,7 @@
         <v>1.2</v>
       </c>
       <c r="AP200">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42774,10 +42777,10 @@
         <v>1.4</v>
       </c>
       <c r="AP201">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ201">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR201">
         <v>1.63</v>
@@ -43395,7 +43398,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ204">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR204">
         <v>1.42</v>
@@ -43601,7 +43604,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ205">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR205">
         <v>1.64</v>
@@ -44219,7 +44222,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ208">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR208">
         <v>1.74</v>
@@ -46070,7 +46073,7 @@
         <v>0.92</v>
       </c>
       <c r="AP217">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ217">
         <v>0.85</v>
@@ -46149,6 +46152,830 @@
       </c>
       <c r="BP217">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7468574</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s">
+        <v>73</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>2</v>
+      </c>
+      <c r="O218" t="s">
+        <v>188</v>
+      </c>
+      <c r="P218" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q218">
+        <v>3.6</v>
+      </c>
+      <c r="R218">
+        <v>2.25</v>
+      </c>
+      <c r="S218">
+        <v>2.75</v>
+      </c>
+      <c r="T218">
+        <v>1.33</v>
+      </c>
+      <c r="U218">
+        <v>3.25</v>
+      </c>
+      <c r="V218">
+        <v>2.63</v>
+      </c>
+      <c r="W218">
+        <v>1.44</v>
+      </c>
+      <c r="X218">
+        <v>6.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.11</v>
+      </c>
+      <c r="Z218">
+        <v>3.31</v>
+      </c>
+      <c r="AA218">
+        <v>3.62</v>
+      </c>
+      <c r="AB218">
+        <v>2.19</v>
+      </c>
+      <c r="AC218">
+        <v>1.03</v>
+      </c>
+      <c r="AD218">
+        <v>13</v>
+      </c>
+      <c r="AE218">
+        <v>1.22</v>
+      </c>
+      <c r="AF218">
+        <v>4.33</v>
+      </c>
+      <c r="AG218">
+        <v>1.65</v>
+      </c>
+      <c r="AH218">
+        <v>2.15</v>
+      </c>
+      <c r="AI218">
+        <v>1.62</v>
+      </c>
+      <c r="AJ218">
+        <v>2.2</v>
+      </c>
+      <c r="AK218">
+        <v>1.73</v>
+      </c>
+      <c r="AL218">
+        <v>1.27</v>
+      </c>
+      <c r="AM218">
+        <v>1.33</v>
+      </c>
+      <c r="AN218">
+        <v>1.25</v>
+      </c>
+      <c r="AO218">
+        <v>1.27</v>
+      </c>
+      <c r="AP218">
+        <v>1.23</v>
+      </c>
+      <c r="AQ218">
+        <v>1.25</v>
+      </c>
+      <c r="AR218">
+        <v>1.52</v>
+      </c>
+      <c r="AS218">
+        <v>1.61</v>
+      </c>
+      <c r="AT218">
+        <v>3.13</v>
+      </c>
+      <c r="AU218">
+        <v>4</v>
+      </c>
+      <c r="AV218">
+        <v>5</v>
+      </c>
+      <c r="AW218">
+        <v>6</v>
+      </c>
+      <c r="AX218">
+        <v>9</v>
+      </c>
+      <c r="AY218">
+        <v>11</v>
+      </c>
+      <c r="AZ218">
+        <v>15</v>
+      </c>
+      <c r="BA218">
+        <v>3</v>
+      </c>
+      <c r="BB218">
+        <v>5</v>
+      </c>
+      <c r="BC218">
+        <v>8</v>
+      </c>
+      <c r="BD218">
+        <v>2.05</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>1.95</v>
+      </c>
+      <c r="BG218">
+        <v>1.35</v>
+      </c>
+      <c r="BH218">
+        <v>2.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.6</v>
+      </c>
+      <c r="BJ218">
+        <v>2.17</v>
+      </c>
+      <c r="BK218">
+        <v>1.98</v>
+      </c>
+      <c r="BL218">
+        <v>1.73</v>
+      </c>
+      <c r="BM218">
+        <v>2.5</v>
+      </c>
+      <c r="BN218">
+        <v>1.46</v>
+      </c>
+      <c r="BO218">
+        <v>3.3</v>
+      </c>
+      <c r="BP218">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7468578</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45724.54166666666</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>78</v>
+      </c>
+      <c r="H219" t="s">
+        <v>79</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>4</v>
+      </c>
+      <c r="N219">
+        <v>5</v>
+      </c>
+      <c r="O219" t="s">
+        <v>100</v>
+      </c>
+      <c r="P219" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q219">
+        <v>5.5</v>
+      </c>
+      <c r="R219">
+        <v>2.5</v>
+      </c>
+      <c r="S219">
+        <v>2.05</v>
+      </c>
+      <c r="T219">
+        <v>1.29</v>
+      </c>
+      <c r="U219">
+        <v>3.5</v>
+      </c>
+      <c r="V219">
+        <v>2.25</v>
+      </c>
+      <c r="W219">
+        <v>1.57</v>
+      </c>
+      <c r="X219">
+        <v>5.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.14</v>
+      </c>
+      <c r="Z219">
+        <v>5.6</v>
+      </c>
+      <c r="AA219">
+        <v>4.7</v>
+      </c>
+      <c r="AB219">
+        <v>1.55</v>
+      </c>
+      <c r="AC219">
+        <v>1.02</v>
+      </c>
+      <c r="AD219">
+        <v>19</v>
+      </c>
+      <c r="AE219">
+        <v>1.17</v>
+      </c>
+      <c r="AF219">
+        <v>5</v>
+      </c>
+      <c r="AG219">
+        <v>1.55</v>
+      </c>
+      <c r="AH219">
+        <v>2.36</v>
+      </c>
+      <c r="AI219">
+        <v>1.67</v>
+      </c>
+      <c r="AJ219">
+        <v>2.1</v>
+      </c>
+      <c r="AK219">
+        <v>2.4</v>
+      </c>
+      <c r="AL219">
+        <v>1.21</v>
+      </c>
+      <c r="AM219">
+        <v>1.15</v>
+      </c>
+      <c r="AN219">
+        <v>1.69</v>
+      </c>
+      <c r="AO219">
+        <v>2.5</v>
+      </c>
+      <c r="AP219">
+        <v>1.57</v>
+      </c>
+      <c r="AQ219">
+        <v>2.54</v>
+      </c>
+      <c r="AR219">
+        <v>1.62</v>
+      </c>
+      <c r="AS219">
+        <v>2.15</v>
+      </c>
+      <c r="AT219">
+        <v>3.77</v>
+      </c>
+      <c r="AU219">
+        <v>4</v>
+      </c>
+      <c r="AV219">
+        <v>10</v>
+      </c>
+      <c r="AW219">
+        <v>9</v>
+      </c>
+      <c r="AX219">
+        <v>10</v>
+      </c>
+      <c r="AY219">
+        <v>14</v>
+      </c>
+      <c r="AZ219">
+        <v>23</v>
+      </c>
+      <c r="BA219">
+        <v>3</v>
+      </c>
+      <c r="BB219">
+        <v>2</v>
+      </c>
+      <c r="BC219">
+        <v>5</v>
+      </c>
+      <c r="BD219">
+        <v>3.15</v>
+      </c>
+      <c r="BE219">
+        <v>6.75</v>
+      </c>
+      <c r="BF219">
+        <v>1.45</v>
+      </c>
+      <c r="BG219">
+        <v>1.34</v>
+      </c>
+      <c r="BH219">
+        <v>2.9</v>
+      </c>
+      <c r="BI219">
+        <v>1.58</v>
+      </c>
+      <c r="BJ219">
+        <v>2.18</v>
+      </c>
+      <c r="BK219">
+        <v>1.96</v>
+      </c>
+      <c r="BL219">
+        <v>1.73</v>
+      </c>
+      <c r="BM219">
+        <v>2.5</v>
+      </c>
+      <c r="BN219">
+        <v>1.46</v>
+      </c>
+      <c r="BO219">
+        <v>3.3</v>
+      </c>
+      <c r="BP219">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7468577</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.625</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>81</v>
+      </c>
+      <c r="H220" t="s">
+        <v>75</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>242</v>
+      </c>
+      <c r="P220" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q220">
+        <v>1.91</v>
+      </c>
+      <c r="R220">
+        <v>2.5</v>
+      </c>
+      <c r="S220">
+        <v>6.5</v>
+      </c>
+      <c r="T220">
+        <v>1.3</v>
+      </c>
+      <c r="U220">
+        <v>3.4</v>
+      </c>
+      <c r="V220">
+        <v>2.38</v>
+      </c>
+      <c r="W220">
+        <v>1.53</v>
+      </c>
+      <c r="X220">
+        <v>6</v>
+      </c>
+      <c r="Y220">
+        <v>1.13</v>
+      </c>
+      <c r="Z220">
+        <v>1.4</v>
+      </c>
+      <c r="AA220">
+        <v>5.3</v>
+      </c>
+      <c r="AB220">
+        <v>7.5</v>
+      </c>
+      <c r="AC220">
+        <v>1.02</v>
+      </c>
+      <c r="AD220">
+        <v>19</v>
+      </c>
+      <c r="AE220">
+        <v>1.18</v>
+      </c>
+      <c r="AF220">
+        <v>5</v>
+      </c>
+      <c r="AG220">
+        <v>1.55</v>
+      </c>
+      <c r="AH220">
+        <v>2.3</v>
+      </c>
+      <c r="AI220">
+        <v>1.8</v>
+      </c>
+      <c r="AJ220">
+        <v>1.95</v>
+      </c>
+      <c r="AK220">
+        <v>1.1</v>
+      </c>
+      <c r="AL220">
+        <v>1.18</v>
+      </c>
+      <c r="AM220">
+        <v>2.87</v>
+      </c>
+      <c r="AN220">
+        <v>2</v>
+      </c>
+      <c r="AO220">
+        <v>0.27</v>
+      </c>
+      <c r="AP220">
+        <v>2.08</v>
+      </c>
+      <c r="AQ220">
+        <v>0.25</v>
+      </c>
+      <c r="AR220">
+        <v>1.6</v>
+      </c>
+      <c r="AS220">
+        <v>1.22</v>
+      </c>
+      <c r="AT220">
+        <v>2.82</v>
+      </c>
+      <c r="AU220">
+        <v>8</v>
+      </c>
+      <c r="AV220">
+        <v>3</v>
+      </c>
+      <c r="AW220">
+        <v>11</v>
+      </c>
+      <c r="AX220">
+        <v>7</v>
+      </c>
+      <c r="AY220">
+        <v>24</v>
+      </c>
+      <c r="AZ220">
+        <v>10</v>
+      </c>
+      <c r="BA220">
+        <v>7</v>
+      </c>
+      <c r="BB220">
+        <v>1</v>
+      </c>
+      <c r="BC220">
+        <v>8</v>
+      </c>
+      <c r="BD220">
+        <v>1.34</v>
+      </c>
+      <c r="BE220">
+        <v>7</v>
+      </c>
+      <c r="BF220">
+        <v>3.65</v>
+      </c>
+      <c r="BG220">
+        <v>1.34</v>
+      </c>
+      <c r="BH220">
+        <v>2.9</v>
+      </c>
+      <c r="BI220">
+        <v>1.57</v>
+      </c>
+      <c r="BJ220">
+        <v>2.23</v>
+      </c>
+      <c r="BK220">
+        <v>1.93</v>
+      </c>
+      <c r="BL220">
+        <v>1.76</v>
+      </c>
+      <c r="BM220">
+        <v>2.4</v>
+      </c>
+      <c r="BN220">
+        <v>1.49</v>
+      </c>
+      <c r="BO220">
+        <v>3.15</v>
+      </c>
+      <c r="BP220">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7468579</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45724.71180555555</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>87</v>
+      </c>
+      <c r="H221" t="s">
+        <v>83</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>1</v>
+      </c>
+      <c r="O221" t="s">
+        <v>90</v>
+      </c>
+      <c r="P221" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q221">
+        <v>2.1</v>
+      </c>
+      <c r="R221">
+        <v>2.4</v>
+      </c>
+      <c r="S221">
+        <v>5.5</v>
+      </c>
+      <c r="T221">
+        <v>1.3</v>
+      </c>
+      <c r="U221">
+        <v>3.4</v>
+      </c>
+      <c r="V221">
+        <v>2.38</v>
+      </c>
+      <c r="W221">
+        <v>1.53</v>
+      </c>
+      <c r="X221">
+        <v>6</v>
+      </c>
+      <c r="Y221">
+        <v>1.13</v>
+      </c>
+      <c r="Z221">
+        <v>1.64</v>
+      </c>
+      <c r="AA221">
+        <v>4.3</v>
+      </c>
+      <c r="AB221">
+        <v>5.2</v>
+      </c>
+      <c r="AC221">
+        <v>1.03</v>
+      </c>
+      <c r="AD221">
+        <v>15</v>
+      </c>
+      <c r="AE221">
+        <v>1.22</v>
+      </c>
+      <c r="AF221">
+        <v>4.33</v>
+      </c>
+      <c r="AG221">
+        <v>1.67</v>
+      </c>
+      <c r="AH221">
+        <v>2.1</v>
+      </c>
+      <c r="AI221">
+        <v>1.67</v>
+      </c>
+      <c r="AJ221">
+        <v>2.1</v>
+      </c>
+      <c r="AK221">
+        <v>1.16</v>
+      </c>
+      <c r="AL221">
+        <v>1.21</v>
+      </c>
+      <c r="AM221">
+        <v>2.35</v>
+      </c>
+      <c r="AN221">
+        <v>1.83</v>
+      </c>
+      <c r="AO221">
+        <v>1.58</v>
+      </c>
+      <c r="AP221">
+        <v>1.69</v>
+      </c>
+      <c r="AQ221">
+        <v>1.69</v>
+      </c>
+      <c r="AR221">
+        <v>1.82</v>
+      </c>
+      <c r="AS221">
+        <v>1.48</v>
+      </c>
+      <c r="AT221">
+        <v>3.3</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>2</v>
+      </c>
+      <c r="AW221">
+        <v>11</v>
+      </c>
+      <c r="AX221">
+        <v>2</v>
+      </c>
+      <c r="AY221">
+        <v>19</v>
+      </c>
+      <c r="AZ221">
+        <v>5</v>
+      </c>
+      <c r="BA221">
+        <v>7</v>
+      </c>
+      <c r="BB221">
+        <v>0</v>
+      </c>
+      <c r="BC221">
+        <v>7</v>
+      </c>
+      <c r="BD221">
+        <v>1.49</v>
+      </c>
+      <c r="BE221">
+        <v>6.4</v>
+      </c>
+      <c r="BF221">
+        <v>2.95</v>
+      </c>
+      <c r="BG221">
+        <v>1.46</v>
+      </c>
+      <c r="BH221">
+        <v>2.48</v>
+      </c>
+      <c r="BI221">
+        <v>1.79</v>
+      </c>
+      <c r="BJ221">
+        <v>1.9</v>
+      </c>
+      <c r="BK221">
+        <v>2.25</v>
+      </c>
+      <c r="BL221">
+        <v>1.55</v>
+      </c>
+      <c r="BM221">
+        <v>2.9</v>
+      </c>
+      <c r="BN221">
+        <v>1.34</v>
+      </c>
+      <c r="BO221">
+        <v>3.9</v>
+      </c>
+      <c r="BP221">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="361">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -745,6 +745,9 @@
     <t>['50']</t>
   </si>
   <si>
+    <t>['19', '60']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1088,6 +1091,12 @@
   </si>
   <si>
     <t>['27', '50', '90+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['15', '24']</t>
+  </si>
+  <si>
+    <t>['78', '83']</t>
   </si>
 </sst>
 </file>
@@ -1449,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1705,7 +1714,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1783,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ2">
         <v>2.54</v>
@@ -1911,7 +1920,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1989,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ3">
         <v>2.25</v>
@@ -2117,7 +2126,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2195,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ4">
         <v>1.42</v>
@@ -2404,7 +2413,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ5">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2529,7 +2538,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2735,7 +2744,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2816,7 +2825,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3434,7 +3443,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3765,7 +3774,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4052,7 +4061,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4177,7 +4186,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4589,7 +4598,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4873,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ17">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5079,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ18">
         <v>1.5</v>
@@ -5207,7 +5216,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5413,7 +5422,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5494,7 +5503,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ20">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5697,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5825,7 +5834,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6031,7 +6040,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6237,7 +6246,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6443,7 +6452,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6727,10 +6736,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ26">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6855,7 +6864,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6933,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ27">
         <v>0.64</v>
@@ -7061,7 +7070,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7679,7 +7688,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8297,7 +8306,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8378,7 +8387,7 @@
         <v>2</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8503,7 +8512,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8581,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8996,7 +9005,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -9199,10 +9208,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9327,7 +9336,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9408,7 +9417,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ39">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9533,7 +9542,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9817,7 +9826,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ41">
         <v>2.54</v>
@@ -10229,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -10357,7 +10366,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10563,7 +10572,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10644,7 +10653,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ45">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10769,7 +10778,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11181,7 +11190,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11593,7 +11602,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11671,7 +11680,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ50">
         <v>1.42</v>
@@ -11799,7 +11808,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12005,7 +12014,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12086,7 +12095,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR52">
         <v>1.24</v>
@@ -12211,7 +12220,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12289,10 +12298,10 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12417,7 +12426,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12910,7 +12919,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -13035,7 +13044,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13116,7 +13125,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13447,7 +13456,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13937,7 +13946,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ61">
         <v>1.17</v>
@@ -14065,7 +14074,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14271,7 +14280,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14349,7 +14358,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ63">
         <v>0.25</v>
@@ -14477,7 +14486,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14555,7 +14564,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ64">
         <v>2.54</v>
@@ -14967,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -15095,7 +15104,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15301,7 +15310,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15382,7 +15391,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ68">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15507,7 +15516,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15585,10 +15594,10 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ69">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR69">
         <v>1.32</v>
@@ -15713,7 +15722,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15794,7 +15803,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR70">
         <v>1.25</v>
@@ -15919,7 +15928,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15997,7 +16006,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ71">
         <v>1.46</v>
@@ -16125,7 +16134,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16331,7 +16340,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16743,7 +16752,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16824,7 +16833,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16949,7 +16958,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17027,7 +17036,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17155,7 +17164,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17361,7 +17370,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17442,7 +17451,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ78">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17567,7 +17576,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17773,7 +17782,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18057,7 +18066,7 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ81">
         <v>1.25</v>
@@ -18185,7 +18194,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18472,7 +18481,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR83">
         <v>1.55</v>
@@ -18678,7 +18687,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -19009,7 +19018,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19087,7 +19096,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ86">
         <v>1.46</v>
@@ -19296,7 +19305,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ87">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19911,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ90">
         <v>0.25</v>
@@ -20039,7 +20048,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20117,7 +20126,7 @@
         <v>2.4</v>
       </c>
       <c r="AP91">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ91">
         <v>2.25</v>
@@ -20245,7 +20254,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20326,7 +20335,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ92">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20451,7 +20460,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20657,7 +20666,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20863,7 +20872,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21069,7 +21078,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21147,7 +21156,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ96">
         <v>1.42</v>
@@ -21275,7 +21284,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21687,7 +21696,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21765,7 +21774,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -21974,7 +21983,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22099,7 +22108,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22511,7 +22520,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23001,10 +23010,10 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ105">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR105">
         <v>1.09</v>
@@ -23416,7 +23425,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ107">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR107">
         <v>1.49</v>
@@ -23541,7 +23550,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23619,7 +23628,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>1.17</v>
@@ -23747,7 +23756,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23825,10 +23834,10 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23953,7 +23962,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24031,7 +24040,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ110">
         <v>1.69</v>
@@ -24240,7 +24249,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ111">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24443,10 +24452,10 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24777,7 +24786,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24983,7 +24992,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25061,10 +25070,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25270,7 +25279,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ116">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25395,7 +25404,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25601,7 +25610,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26425,7 +26434,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26503,7 +26512,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ122">
         <v>1.17</v>
@@ -26631,7 +26640,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26712,7 +26721,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ123">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27327,7 +27336,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ126">
         <v>0.64</v>
@@ -27455,7 +27464,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27742,7 +27751,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27867,7 +27876,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28073,7 +28082,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28357,7 +28366,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ131">
         <v>1.25</v>
@@ -28485,7 +28494,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28691,7 +28700,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28769,10 +28778,10 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ133">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -28975,7 +28984,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
         <v>0.85</v>
@@ -29184,7 +29193,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR135">
         <v>1.64</v>
@@ -29390,7 +29399,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ136">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR136">
         <v>2.35</v>
@@ -29515,7 +29524,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29721,7 +29730,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29799,7 +29808,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ138">
         <v>0.64</v>
@@ -29927,7 +29936,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30133,7 +30142,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30832,7 +30841,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -31369,7 +31378,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31447,7 +31456,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ146">
         <v>1.25</v>
@@ -31781,7 +31790,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31859,10 +31868,10 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR148">
         <v>1.48</v>
@@ -31987,7 +31996,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32065,7 +32074,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ149">
         <v>1.46</v>
@@ -32193,7 +32202,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32399,7 +32408,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32477,7 +32486,7 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ151">
         <v>1.69</v>
@@ -32605,7 +32614,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32686,7 +32695,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ152">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR152">
         <v>1.44</v>
@@ -32811,7 +32820,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32892,7 +32901,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ153">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33098,7 +33107,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ154">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR154">
         <v>2.26</v>
@@ -33635,7 +33644,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33841,7 +33850,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34540,7 +34549,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ161">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR161">
         <v>1.21</v>
@@ -34743,7 +34752,7 @@
         <v>0.75</v>
       </c>
       <c r="AP162">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ162">
         <v>1.17</v>
@@ -34871,7 +34880,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34952,7 +34961,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ163">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR163">
         <v>1.45</v>
@@ -35158,7 +35167,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ164">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35283,7 +35292,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35695,7 +35704,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35901,7 +35910,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35979,7 +35988,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ168">
         <v>1</v>
@@ -36185,10 +36194,10 @@
         <v>1.33</v>
       </c>
       <c r="AP169">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ169">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR169">
         <v>1.4</v>
@@ -36313,7 +36322,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36600,7 +36609,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ171">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR171">
         <v>1.64</v>
@@ -36803,7 +36812,7 @@
         <v>2.67</v>
       </c>
       <c r="AP172">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ172">
         <v>2.25</v>
@@ -36931,7 +36940,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37137,7 +37146,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37215,7 +37224,7 @@
         <v>2.33</v>
       </c>
       <c r="AP174">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
         <v>2.54</v>
@@ -37343,7 +37352,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37424,7 +37433,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ175">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR175">
         <v>1.59</v>
@@ -37630,7 +37639,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ176">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR176">
         <v>1.38</v>
@@ -37755,7 +37764,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38042,7 +38051,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ178">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR178">
         <v>1.61</v>
@@ -38373,7 +38382,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38451,7 +38460,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ180">
         <v>0.85</v>
@@ -38579,7 +38588,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38660,7 +38669,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ181">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR181">
         <v>1.5</v>
@@ -38785,7 +38794,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38863,7 +38872,7 @@
         <v>0.9</v>
       </c>
       <c r="AP182">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -39275,7 +39284,7 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ184">
         <v>1.69</v>
@@ -39403,7 +39412,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39609,7 +39618,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -40021,7 +40030,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40433,7 +40442,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40639,7 +40648,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40717,10 +40726,10 @@
         <v>0.4</v>
       </c>
       <c r="AP191">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ191">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR191">
         <v>1.49</v>
@@ -40845,7 +40854,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -40926,7 +40935,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ192">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AR192">
         <v>1.6</v>
@@ -41257,7 +41266,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41463,7 +41472,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41544,7 +41553,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ195">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR195">
         <v>1.46</v>
@@ -41669,7 +41678,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41750,7 +41759,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ196">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR196">
         <v>1.69</v>
@@ -41953,10 +41962,10 @@
         <v>1.2</v>
       </c>
       <c r="AP197">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ197">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR197">
         <v>1.26</v>
@@ -42081,7 +42090,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42159,7 +42168,7 @@
         <v>1.18</v>
       </c>
       <c r="AP198">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ198">
         <v>1.46</v>
@@ -42287,7 +42296,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42905,7 +42914,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -42986,7 +42995,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ202">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR202">
         <v>1.29</v>
@@ -43395,7 +43404,7 @@
         <v>1.73</v>
       </c>
       <c r="AP204">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ204">
         <v>1.69</v>
@@ -43601,7 +43610,7 @@
         <v>0.3</v>
       </c>
       <c r="AP205">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AQ205">
         <v>0.25</v>
@@ -43935,7 +43944,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44013,7 +44022,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ207">
         <v>1.5</v>
@@ -44141,7 +44150,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44553,7 +44562,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44759,7 +44768,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45171,7 +45180,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45377,7 +45386,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45583,7 +45592,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45870,7 +45879,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ216">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR216">
         <v>1.31</v>
@@ -46407,7 +46416,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46819,7 +46828,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -46976,6 +46985,1036 @@
       </c>
       <c r="BP221">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7468576</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>71</v>
+      </c>
+      <c r="H222" t="s">
+        <v>77</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>2</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>2</v>
+      </c>
+      <c r="O222" t="s">
+        <v>243</v>
+      </c>
+      <c r="P222" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q222">
+        <v>2.38</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>5</v>
+      </c>
+      <c r="T222">
+        <v>1.4</v>
+      </c>
+      <c r="U222">
+        <v>2.75</v>
+      </c>
+      <c r="V222">
+        <v>3</v>
+      </c>
+      <c r="W222">
+        <v>1.36</v>
+      </c>
+      <c r="X222">
+        <v>8</v>
+      </c>
+      <c r="Y222">
+        <v>1.08</v>
+      </c>
+      <c r="Z222">
+        <v>1.86</v>
+      </c>
+      <c r="AA222">
+        <v>3.66</v>
+      </c>
+      <c r="AB222">
+        <v>4.5</v>
+      </c>
+      <c r="AC222">
+        <v>1.06</v>
+      </c>
+      <c r="AD222">
+        <v>10</v>
+      </c>
+      <c r="AE222">
+        <v>1.35</v>
+      </c>
+      <c r="AF222">
+        <v>3.25</v>
+      </c>
+      <c r="AG222">
+        <v>2.03</v>
+      </c>
+      <c r="AH222">
+        <v>1.79</v>
+      </c>
+      <c r="AI222">
+        <v>1.91</v>
+      </c>
+      <c r="AJ222">
+        <v>1.91</v>
+      </c>
+      <c r="AK222">
+        <v>1.21</v>
+      </c>
+      <c r="AL222">
+        <v>1.28</v>
+      </c>
+      <c r="AM222">
+        <v>1.95</v>
+      </c>
+      <c r="AN222">
+        <v>1.82</v>
+      </c>
+      <c r="AO222">
+        <v>1.33</v>
+      </c>
+      <c r="AP222">
+        <v>1.92</v>
+      </c>
+      <c r="AQ222">
+        <v>1.23</v>
+      </c>
+      <c r="AR222">
+        <v>1.57</v>
+      </c>
+      <c r="AS222">
+        <v>1.1</v>
+      </c>
+      <c r="AT222">
+        <v>2.67</v>
+      </c>
+      <c r="AU222">
+        <v>9</v>
+      </c>
+      <c r="AV222">
+        <v>3</v>
+      </c>
+      <c r="AW222">
+        <v>11</v>
+      </c>
+      <c r="AX222">
+        <v>6</v>
+      </c>
+      <c r="AY222">
+        <v>23</v>
+      </c>
+      <c r="AZ222">
+        <v>10</v>
+      </c>
+      <c r="BA222">
+        <v>6</v>
+      </c>
+      <c r="BB222">
+        <v>6</v>
+      </c>
+      <c r="BC222">
+        <v>12</v>
+      </c>
+      <c r="BD222">
+        <v>1.46</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
+        <v>3.05</v>
+      </c>
+      <c r="BG222">
+        <v>1.47</v>
+      </c>
+      <c r="BH222">
+        <v>2.48</v>
+      </c>
+      <c r="BI222">
+        <v>1.77</v>
+      </c>
+      <c r="BJ222">
+        <v>1.92</v>
+      </c>
+      <c r="BK222">
+        <v>2.23</v>
+      </c>
+      <c r="BL222">
+        <v>1.56</v>
+      </c>
+      <c r="BM222">
+        <v>2.9</v>
+      </c>
+      <c r="BN222">
+        <v>1.34</v>
+      </c>
+      <c r="BO222">
+        <v>3.9</v>
+      </c>
+      <c r="BP222">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7468573</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45725.55208333334</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>85</v>
+      </c>
+      <c r="H223" t="s">
+        <v>84</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>90</v>
+      </c>
+      <c r="P223" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q223">
+        <v>3.25</v>
+      </c>
+      <c r="R223">
+        <v>2.1</v>
+      </c>
+      <c r="S223">
+        <v>3.4</v>
+      </c>
+      <c r="T223">
+        <v>1.44</v>
+      </c>
+      <c r="U223">
+        <v>2.63</v>
+      </c>
+      <c r="V223">
+        <v>3</v>
+      </c>
+      <c r="W223">
+        <v>1.36</v>
+      </c>
+      <c r="X223">
+        <v>9</v>
+      </c>
+      <c r="Y223">
+        <v>1.07</v>
+      </c>
+      <c r="Z223">
+        <v>2.58</v>
+      </c>
+      <c r="AA223">
+        <v>3.34</v>
+      </c>
+      <c r="AB223">
+        <v>2.87</v>
+      </c>
+      <c r="AC223">
+        <v>1.07</v>
+      </c>
+      <c r="AD223">
+        <v>9.5</v>
+      </c>
+      <c r="AE223">
+        <v>1.33</v>
+      </c>
+      <c r="AF223">
+        <v>3.3</v>
+      </c>
+      <c r="AG223">
+        <v>2.01</v>
+      </c>
+      <c r="AH223">
+        <v>1.81</v>
+      </c>
+      <c r="AI223">
+        <v>1.75</v>
+      </c>
+      <c r="AJ223">
+        <v>2</v>
+      </c>
+      <c r="AK223">
+        <v>1.42</v>
+      </c>
+      <c r="AL223">
+        <v>1.32</v>
+      </c>
+      <c r="AM223">
+        <v>1.51</v>
+      </c>
+      <c r="AN223">
+        <v>1.18</v>
+      </c>
+      <c r="AO223">
+        <v>1.15</v>
+      </c>
+      <c r="AP223">
+        <v>1.08</v>
+      </c>
+      <c r="AQ223">
+        <v>1.29</v>
+      </c>
+      <c r="AR223">
+        <v>1.45</v>
+      </c>
+      <c r="AS223">
+        <v>1.22</v>
+      </c>
+      <c r="AT223">
+        <v>2.67</v>
+      </c>
+      <c r="AU223">
+        <v>3</v>
+      </c>
+      <c r="AV223">
+        <v>3</v>
+      </c>
+      <c r="AW223">
+        <v>9</v>
+      </c>
+      <c r="AX223">
+        <v>7</v>
+      </c>
+      <c r="AY223">
+        <v>15</v>
+      </c>
+      <c r="AZ223">
+        <v>13</v>
+      </c>
+      <c r="BA223">
+        <v>3</v>
+      </c>
+      <c r="BB223">
+        <v>9</v>
+      </c>
+      <c r="BC223">
+        <v>12</v>
+      </c>
+      <c r="BD223">
+        <v>1.73</v>
+      </c>
+      <c r="BE223">
+        <v>6.4</v>
+      </c>
+      <c r="BF223">
+        <v>2.38</v>
+      </c>
+      <c r="BG223">
+        <v>1.36</v>
+      </c>
+      <c r="BH223">
+        <v>2.8</v>
+      </c>
+      <c r="BI223">
+        <v>1.63</v>
+      </c>
+      <c r="BJ223">
+        <v>2.12</v>
+      </c>
+      <c r="BK223">
+        <v>2</v>
+      </c>
+      <c r="BL223">
+        <v>1.71</v>
+      </c>
+      <c r="BM223">
+        <v>2.55</v>
+      </c>
+      <c r="BN223">
+        <v>1.44</v>
+      </c>
+      <c r="BO223">
+        <v>3.4</v>
+      </c>
+      <c r="BP223">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7468572</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45725.55208333334</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>72</v>
+      </c>
+      <c r="H224" t="s">
+        <v>74</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>2</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>90</v>
+      </c>
+      <c r="P224" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q224">
+        <v>3.1</v>
+      </c>
+      <c r="R224">
+        <v>2.1</v>
+      </c>
+      <c r="S224">
+        <v>3.4</v>
+      </c>
+      <c r="T224">
+        <v>1.4</v>
+      </c>
+      <c r="U224">
+        <v>2.75</v>
+      </c>
+      <c r="V224">
+        <v>3</v>
+      </c>
+      <c r="W224">
+        <v>1.36</v>
+      </c>
+      <c r="X224">
+        <v>8</v>
+      </c>
+      <c r="Y224">
+        <v>1.08</v>
+      </c>
+      <c r="Z224">
+        <v>2.19</v>
+      </c>
+      <c r="AA224">
+        <v>3.31</v>
+      </c>
+      <c r="AB224">
+        <v>3.63</v>
+      </c>
+      <c r="AC224">
+        <v>1.07</v>
+      </c>
+      <c r="AD224">
+        <v>9.5</v>
+      </c>
+      <c r="AE224">
+        <v>1.33</v>
+      </c>
+      <c r="AF224">
+        <v>3.4</v>
+      </c>
+      <c r="AG224">
+        <v>1.93</v>
+      </c>
+      <c r="AH224">
+        <v>1.77</v>
+      </c>
+      <c r="AI224">
+        <v>1.75</v>
+      </c>
+      <c r="AJ224">
+        <v>2</v>
+      </c>
+      <c r="AK224">
+        <v>1.39</v>
+      </c>
+      <c r="AL224">
+        <v>1.31</v>
+      </c>
+      <c r="AM224">
+        <v>1.55</v>
+      </c>
+      <c r="AN224">
+        <v>0.83</v>
+      </c>
+      <c r="AO224">
+        <v>0.45</v>
+      </c>
+      <c r="AP224">
+        <v>0.77</v>
+      </c>
+      <c r="AQ224">
+        <v>0.67</v>
+      </c>
+      <c r="AR224">
+        <v>1.31</v>
+      </c>
+      <c r="AS224">
+        <v>1.26</v>
+      </c>
+      <c r="AT224">
+        <v>2.57</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>9</v>
+      </c>
+      <c r="AW224">
+        <v>13</v>
+      </c>
+      <c r="AX224">
+        <v>4</v>
+      </c>
+      <c r="AY224">
+        <v>26</v>
+      </c>
+      <c r="AZ224">
+        <v>14</v>
+      </c>
+      <c r="BA224">
+        <v>6</v>
+      </c>
+      <c r="BB224">
+        <v>12</v>
+      </c>
+      <c r="BC224">
+        <v>18</v>
+      </c>
+      <c r="BD224">
+        <v>1.7</v>
+      </c>
+      <c r="BE224">
+        <v>6.4</v>
+      </c>
+      <c r="BF224">
+        <v>2.4</v>
+      </c>
+      <c r="BG224">
+        <v>1.42</v>
+      </c>
+      <c r="BH224">
+        <v>2.63</v>
+      </c>
+      <c r="BI224">
+        <v>1.71</v>
+      </c>
+      <c r="BJ224">
+        <v>2</v>
+      </c>
+      <c r="BK224">
+        <v>2.15</v>
+      </c>
+      <c r="BL224">
+        <v>1.61</v>
+      </c>
+      <c r="BM224">
+        <v>2.8</v>
+      </c>
+      <c r="BN224">
+        <v>1.37</v>
+      </c>
+      <c r="BO224">
+        <v>3.65</v>
+      </c>
+      <c r="BP224">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7468571</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45725.55208333334</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>70</v>
+      </c>
+      <c r="H225" t="s">
+        <v>82</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>2</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>2</v>
+      </c>
+      <c r="O225" t="s">
+        <v>218</v>
+      </c>
+      <c r="P225" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q225">
+        <v>3</v>
+      </c>
+      <c r="R225">
+        <v>2.2</v>
+      </c>
+      <c r="S225">
+        <v>3.5</v>
+      </c>
+      <c r="T225">
+        <v>1.36</v>
+      </c>
+      <c r="U225">
+        <v>3</v>
+      </c>
+      <c r="V225">
+        <v>2.75</v>
+      </c>
+      <c r="W225">
+        <v>1.4</v>
+      </c>
+      <c r="X225">
+        <v>8</v>
+      </c>
+      <c r="Y225">
+        <v>1.08</v>
+      </c>
+      <c r="Z225">
+        <v>2.39</v>
+      </c>
+      <c r="AA225">
+        <v>3.45</v>
+      </c>
+      <c r="AB225">
+        <v>3.05</v>
+      </c>
+      <c r="AC225">
+        <v>1.05</v>
+      </c>
+      <c r="AD225">
+        <v>11</v>
+      </c>
+      <c r="AE225">
+        <v>1.3</v>
+      </c>
+      <c r="AF225">
+        <v>3.6</v>
+      </c>
+      <c r="AG225">
+        <v>1.86</v>
+      </c>
+      <c r="AH225">
+        <v>1.95</v>
+      </c>
+      <c r="AI225">
+        <v>1.67</v>
+      </c>
+      <c r="AJ225">
+        <v>2.1</v>
+      </c>
+      <c r="AK225">
+        <v>1.41</v>
+      </c>
+      <c r="AL225">
+        <v>1.29</v>
+      </c>
+      <c r="AM225">
+        <v>1.55</v>
+      </c>
+      <c r="AN225">
+        <v>0.5</v>
+      </c>
+      <c r="AO225">
+        <v>0.17</v>
+      </c>
+      <c r="AP225">
+        <v>0.54</v>
+      </c>
+      <c r="AQ225">
+        <v>0.23</v>
+      </c>
+      <c r="AR225">
+        <v>1.19</v>
+      </c>
+      <c r="AS225">
+        <v>0.99</v>
+      </c>
+      <c r="AT225">
+        <v>2.18</v>
+      </c>
+      <c r="AU225">
+        <v>6</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>7</v>
+      </c>
+      <c r="AX225">
+        <v>9</v>
+      </c>
+      <c r="AY225">
+        <v>14</v>
+      </c>
+      <c r="AZ225">
+        <v>19</v>
+      </c>
+      <c r="BA225">
+        <v>5</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>11</v>
+      </c>
+      <c r="BD225">
+        <v>1.74</v>
+      </c>
+      <c r="BE225">
+        <v>6.25</v>
+      </c>
+      <c r="BF225">
+        <v>2.33</v>
+      </c>
+      <c r="BG225">
+        <v>1.41</v>
+      </c>
+      <c r="BH225">
+        <v>2.65</v>
+      </c>
+      <c r="BI225">
+        <v>1.68</v>
+      </c>
+      <c r="BJ225">
+        <v>2.04</v>
+      </c>
+      <c r="BK225">
+        <v>2.08</v>
+      </c>
+      <c r="BL225">
+        <v>1.65</v>
+      </c>
+      <c r="BM225">
+        <v>2.65</v>
+      </c>
+      <c r="BN225">
+        <v>1.4</v>
+      </c>
+      <c r="BO225">
+        <v>3.55</v>
+      </c>
+      <c r="BP225">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7468575</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45725.69791666666</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>86</v>
+      </c>
+      <c r="H226" t="s">
+        <v>80</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>2</v>
+      </c>
+      <c r="N226">
+        <v>2</v>
+      </c>
+      <c r="O226" t="s">
+        <v>90</v>
+      </c>
+      <c r="P226" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q226">
+        <v>2.6</v>
+      </c>
+      <c r="R226">
+        <v>2.38</v>
+      </c>
+      <c r="S226">
+        <v>3.75</v>
+      </c>
+      <c r="T226">
+        <v>1.3</v>
+      </c>
+      <c r="U226">
+        <v>3.4</v>
+      </c>
+      <c r="V226">
+        <v>2.38</v>
+      </c>
+      <c r="W226">
+        <v>1.53</v>
+      </c>
+      <c r="X226">
+        <v>6</v>
+      </c>
+      <c r="Y226">
+        <v>1.13</v>
+      </c>
+      <c r="Z226">
+        <v>2.32</v>
+      </c>
+      <c r="AA226">
+        <v>3.63</v>
+      </c>
+      <c r="AB226">
+        <v>3.05</v>
+      </c>
+      <c r="AC226">
+        <v>1.03</v>
+      </c>
+      <c r="AD226">
+        <v>13</v>
+      </c>
+      <c r="AE226">
+        <v>1.2</v>
+      </c>
+      <c r="AF226">
+        <v>4.5</v>
+      </c>
+      <c r="AG226">
+        <v>1.61</v>
+      </c>
+      <c r="AH226">
+        <v>2.15</v>
+      </c>
+      <c r="AI226">
+        <v>1.53</v>
+      </c>
+      <c r="AJ226">
+        <v>2.38</v>
+      </c>
+      <c r="AK226">
+        <v>1.33</v>
+      </c>
+      <c r="AL226">
+        <v>1.27</v>
+      </c>
+      <c r="AM226">
+        <v>1.72</v>
+      </c>
+      <c r="AN226">
+        <v>2.45</v>
+      </c>
+      <c r="AO226">
+        <v>1.33</v>
+      </c>
+      <c r="AP226">
+        <v>2.25</v>
+      </c>
+      <c r="AQ226">
+        <v>1.46</v>
+      </c>
+      <c r="AR226">
+        <v>1.66</v>
+      </c>
+      <c r="AS226">
+        <v>1.29</v>
+      </c>
+      <c r="AT226">
+        <v>2.95</v>
+      </c>
+      <c r="AU226">
+        <v>6</v>
+      </c>
+      <c r="AV226">
+        <v>6</v>
+      </c>
+      <c r="AW226">
+        <v>16</v>
+      </c>
+      <c r="AX226">
+        <v>3</v>
+      </c>
+      <c r="AY226">
+        <v>25</v>
+      </c>
+      <c r="AZ226">
+        <v>11</v>
+      </c>
+      <c r="BA226">
+        <v>9</v>
+      </c>
+      <c r="BB226">
+        <v>2</v>
+      </c>
+      <c r="BC226">
+        <v>11</v>
+      </c>
+      <c r="BD226">
+        <v>1.71</v>
+      </c>
+      <c r="BE226">
+        <v>6.5</v>
+      </c>
+      <c r="BF226">
+        <v>2.38</v>
+      </c>
+      <c r="BG226">
+        <v>1.27</v>
+      </c>
+      <c r="BH226">
+        <v>3.3</v>
+      </c>
+      <c r="BI226">
+        <v>1.48</v>
+      </c>
+      <c r="BJ226">
+        <v>2.45</v>
+      </c>
+      <c r="BK226">
+        <v>1.77</v>
+      </c>
+      <c r="BL226">
+        <v>1.92</v>
+      </c>
+      <c r="BM226">
+        <v>2.18</v>
+      </c>
+      <c r="BN226">
+        <v>1.58</v>
+      </c>
+      <c r="BO226">
+        <v>2.8</v>
+      </c>
+      <c r="BP226">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="363">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,12 @@
     <t>['19', '60']</t>
   </si>
   <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -884,9 +890,6 @@
   </si>
   <si>
     <t>['5', '8', '27']</t>
-  </si>
-  <si>
-    <t>['83']</t>
   </si>
   <si>
     <t>['7', '29', '40']</t>
@@ -1097,6 +1100,9 @@
   </si>
   <si>
     <t>['78', '83']</t>
+  </si>
+  <si>
+    <t>['77', '88']</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1714,7 +1720,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1920,7 +1926,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2126,7 +2132,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2207,7 +2213,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2538,7 +2544,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2744,7 +2750,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3234,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ9">
         <v>1.69</v>
@@ -3774,7 +3780,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3855,7 +3861,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4186,7 +4192,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4470,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4598,7 +4604,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4679,7 +4685,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4882,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ17">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5088,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ18">
         <v>1.5</v>
@@ -5216,7 +5222,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5422,7 +5428,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5834,7 +5840,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6040,7 +6046,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6246,7 +6252,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6452,7 +6458,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6530,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ25">
         <v>1.46</v>
@@ -6739,7 +6745,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ26">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6864,7 +6870,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6945,7 +6951,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ27">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR27">
         <v>0.32</v>
@@ -7070,7 +7076,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7357,7 +7363,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ29">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR29">
         <v>1.65</v>
@@ -7688,7 +7694,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7769,7 +7775,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ31">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -8306,7 +8312,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8512,7 +8518,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8590,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -9002,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ37">
         <v>1.46</v>
@@ -9208,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ38">
         <v>0.23</v>
@@ -9336,7 +9342,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9542,7 +9548,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10366,7 +10372,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10444,7 +10450,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ44">
         <v>0.85</v>
@@ -10572,7 +10578,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10653,7 +10659,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ45">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10778,7 +10784,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11190,7 +11196,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11271,7 +11277,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ48">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR48">
         <v>2.56</v>
@@ -11474,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ49">
         <v>1.46</v>
@@ -11602,7 +11608,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11683,7 +11689,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ50">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR50">
         <v>1.41</v>
@@ -11808,7 +11814,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12014,7 +12020,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12220,7 +12226,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12298,7 +12304,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53">
         <v>0.23</v>
@@ -12426,7 +12432,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12504,7 +12510,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -13044,7 +13050,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13125,7 +13131,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13456,7 +13462,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13537,7 +13543,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -14074,7 +14080,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14280,7 +14286,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14486,7 +14492,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14564,7 +14570,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ64">
         <v>2.54</v>
@@ -14773,7 +14779,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ65">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR65">
         <v>1.54</v>
@@ -14979,7 +14985,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15104,7 +15110,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15310,7 +15316,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15516,7 +15522,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15722,7 +15728,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15928,7 +15934,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16006,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ71">
         <v>1.46</v>
@@ -16134,7 +16140,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16340,7 +16346,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16752,7 +16758,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16830,7 +16836,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ75">
         <v>0.23</v>
@@ -16958,7 +16964,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17164,7 +17170,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17242,10 +17248,10 @@
         <v>1.75</v>
       </c>
       <c r="AP77">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ77">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR77">
         <v>1.98</v>
@@ -17370,7 +17376,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17451,7 +17457,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ78">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17576,7 +17582,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17782,7 +17788,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18066,10 +18072,10 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ81">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18194,7 +18200,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -19018,7 +19024,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19717,7 +19723,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ89">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR89">
         <v>1.39</v>
@@ -20048,7 +20054,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20126,7 +20132,7 @@
         <v>2.4</v>
       </c>
       <c r="AP91">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ91">
         <v>2.25</v>
@@ -20254,7 +20260,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20335,7 +20341,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ92">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20460,7 +20466,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20541,7 +20547,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20666,7 +20672,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20744,7 +20750,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ94">
         <v>0.85</v>
@@ -20872,7 +20878,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20950,7 +20956,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ95">
         <v>2.54</v>
@@ -21078,7 +21084,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21156,10 +21162,10 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ96">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR96">
         <v>1.64</v>
@@ -21284,7 +21290,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21696,7 +21702,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22108,7 +22114,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22520,7 +22526,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22598,7 +22604,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ103">
         <v>2.25</v>
@@ -23219,7 +23225,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ106">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR106">
         <v>1.43</v>
@@ -23550,7 +23556,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23628,7 +23634,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
         <v>1.17</v>
@@ -23756,7 +23762,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23834,7 +23840,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ109">
         <v>1.29</v>
@@ -23962,7 +23968,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24786,7 +24792,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24867,7 +24873,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ114">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR114">
         <v>1.36</v>
@@ -24992,7 +24998,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25279,7 +25285,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ116">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25404,7 +25410,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25610,7 +25616,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25691,7 +25697,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ118">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -26434,7 +26440,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26512,7 +26518,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ122">
         <v>1.17</v>
@@ -26640,7 +26646,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26718,7 +26724,7 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ123">
         <v>1.46</v>
@@ -26924,7 +26930,7 @@
         <v>0</v>
       </c>
       <c r="AP124">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ124">
         <v>0.25</v>
@@ -27336,10 +27342,10 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ126">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR126">
         <v>1.51</v>
@@ -27464,7 +27470,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27876,7 +27882,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27957,7 +27963,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ129">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR129">
         <v>1.4</v>
@@ -28082,7 +28088,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28369,7 +28375,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ131">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -28494,7 +28500,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28700,7 +28706,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29524,7 +29530,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29730,7 +29736,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29808,10 +29814,10 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ138">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR138">
         <v>1.63</v>
@@ -29936,7 +29942,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30142,7 +30148,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30632,7 +30638,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ142">
         <v>1.5</v>
@@ -30841,7 +30847,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -31044,7 +31050,7 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31378,7 +31384,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31456,10 +31462,10 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ146">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -31665,7 +31671,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ147">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR147">
         <v>1.33</v>
@@ -31790,7 +31796,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31996,7 +32002,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32202,7 +32208,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32408,7 +32414,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32614,7 +32620,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32820,7 +32826,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33313,7 +33319,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ155">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR155">
         <v>1.44</v>
@@ -33644,7 +33650,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33722,7 +33728,7 @@
         <v>2.25</v>
       </c>
       <c r="AP157">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157">
         <v>2.54</v>
@@ -33850,7 +33856,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34546,10 +34552,10 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ161">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR161">
         <v>1.21</v>
@@ -34880,7 +34886,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35292,7 +35298,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35373,7 +35379,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ165">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR165">
         <v>1.5</v>
@@ -35579,7 +35585,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR166">
         <v>1.19</v>
@@ -35704,7 +35710,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35910,7 +35916,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36194,7 +36200,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ169">
         <v>1.46</v>
@@ -36322,7 +36328,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36606,7 +36612,7 @@
         <v>1.33</v>
       </c>
       <c r="AP171">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ171">
         <v>1.23</v>
@@ -36812,7 +36818,7 @@
         <v>2.67</v>
       </c>
       <c r="AP172">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ172">
         <v>2.25</v>
@@ -36940,7 +36946,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37146,7 +37152,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37352,7 +37358,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37433,7 +37439,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ175">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175">
         <v>1.59</v>
@@ -37764,7 +37770,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38254,7 +38260,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ179">
         <v>1.17</v>
@@ -38382,7 +38388,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38588,7 +38594,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38794,7 +38800,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38872,7 +38878,7 @@
         <v>0.9</v>
       </c>
       <c r="AP182">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -39081,7 +39087,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ183">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR183">
         <v>2.35</v>
@@ -39284,7 +39290,7 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ184">
         <v>1.69</v>
@@ -39412,7 +39418,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39618,7 +39624,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39699,7 +39705,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ186">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR186">
         <v>1.27</v>
@@ -40030,7 +40036,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40442,7 +40448,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40520,7 +40526,7 @@
         <v>2.4</v>
       </c>
       <c r="AP190">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ190">
         <v>2.25</v>
@@ -40648,7 +40654,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40729,7 +40735,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ191">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR191">
         <v>1.49</v>
@@ -40854,7 +40860,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41266,7 +41272,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41472,7 +41478,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41678,7 +41684,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41756,7 +41762,7 @@
         <v>0.82</v>
       </c>
       <c r="AP196">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ196">
         <v>1.29</v>
@@ -42090,7 +42096,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42296,7 +42302,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42377,7 +42383,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ199">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR199">
         <v>1.59</v>
@@ -42789,7 +42795,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ201">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR201">
         <v>1.63</v>
@@ -42914,7 +42920,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43404,7 +43410,7 @@
         <v>1.73</v>
       </c>
       <c r="AP204">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ204">
         <v>1.69</v>
@@ -43610,7 +43616,7 @@
         <v>0.3</v>
       </c>
       <c r="AP205">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ205">
         <v>0.25</v>
@@ -43944,7 +43950,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44150,7 +44156,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44562,7 +44568,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44768,7 +44774,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -44846,7 +44852,7 @@
         <v>1</v>
       </c>
       <c r="AP211">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ211">
         <v>1.17</v>
@@ -45055,7 +45061,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ212">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR212">
         <v>2.34</v>
@@ -45180,7 +45186,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45386,7 +45392,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45464,7 +45470,7 @@
         <v>1.36</v>
       </c>
       <c r="AP214">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ214">
         <v>1.5</v>
@@ -45592,7 +45598,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45673,7 +45679,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ215">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR215">
         <v>1.47</v>
@@ -46291,7 +46297,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ218">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR218">
         <v>1.52</v>
@@ -46416,7 +46422,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46828,7 +46834,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47240,7 +47246,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47318,7 +47324,7 @@
         <v>1.15</v>
       </c>
       <c r="AP223">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ223">
         <v>1.29</v>
@@ -47446,7 +47452,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47527,7 +47533,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ224">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR224">
         <v>1.31</v>
@@ -47858,7 +47864,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -47936,7 +47942,7 @@
         <v>1.33</v>
       </c>
       <c r="AP226">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ226">
         <v>1.46</v>
@@ -48015,6 +48021,830 @@
       </c>
       <c r="BP226">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7468581</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>86</v>
+      </c>
+      <c r="H227" t="s">
+        <v>74</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>244</v>
+      </c>
+      <c r="P227" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q227">
+        <v>2.1</v>
+      </c>
+      <c r="R227">
+        <v>2.38</v>
+      </c>
+      <c r="S227">
+        <v>5.5</v>
+      </c>
+      <c r="T227">
+        <v>1.33</v>
+      </c>
+      <c r="U227">
+        <v>3.25</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>6.5</v>
+      </c>
+      <c r="Y227">
+        <v>1.11</v>
+      </c>
+      <c r="Z227">
+        <v>1.53</v>
+      </c>
+      <c r="AA227">
+        <v>4.5</v>
+      </c>
+      <c r="AB227">
+        <v>6.3</v>
+      </c>
+      <c r="AC227">
+        <v>1.04</v>
+      </c>
+      <c r="AD227">
+        <v>10</v>
+      </c>
+      <c r="AE227">
+        <v>1.22</v>
+      </c>
+      <c r="AF227">
+        <v>4.2</v>
+      </c>
+      <c r="AG227">
+        <v>1.6</v>
+      </c>
+      <c r="AH227">
+        <v>2.25</v>
+      </c>
+      <c r="AI227">
+        <v>1.75</v>
+      </c>
+      <c r="AJ227">
+        <v>2</v>
+      </c>
+      <c r="AK227">
+        <v>1.14</v>
+      </c>
+      <c r="AL227">
+        <v>1.22</v>
+      </c>
+      <c r="AM227">
+        <v>2.37</v>
+      </c>
+      <c r="AN227">
+        <v>2.25</v>
+      </c>
+      <c r="AO227">
+        <v>0.67</v>
+      </c>
+      <c r="AP227">
+        <v>2.15</v>
+      </c>
+      <c r="AQ227">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR227">
+        <v>1.7</v>
+      </c>
+      <c r="AS227">
+        <v>1.3</v>
+      </c>
+      <c r="AT227">
+        <v>3</v>
+      </c>
+      <c r="AU227">
+        <v>6</v>
+      </c>
+      <c r="AV227">
+        <v>6</v>
+      </c>
+      <c r="AW227">
+        <v>15</v>
+      </c>
+      <c r="AX227">
+        <v>5</v>
+      </c>
+      <c r="AY227">
+        <v>24</v>
+      </c>
+      <c r="AZ227">
+        <v>14</v>
+      </c>
+      <c r="BA227">
+        <v>7</v>
+      </c>
+      <c r="BB227">
+        <v>3</v>
+      </c>
+      <c r="BC227">
+        <v>10</v>
+      </c>
+      <c r="BD227">
+        <v>1.36</v>
+      </c>
+      <c r="BE227">
+        <v>7.5</v>
+      </c>
+      <c r="BF227">
+        <v>3.45</v>
+      </c>
+      <c r="BG227">
+        <v>1.27</v>
+      </c>
+      <c r="BH227">
+        <v>3.3</v>
+      </c>
+      <c r="BI227">
+        <v>1.49</v>
+      </c>
+      <c r="BJ227">
+        <v>2.4</v>
+      </c>
+      <c r="BK227">
+        <v>1.78</v>
+      </c>
+      <c r="BL227">
+        <v>1.91</v>
+      </c>
+      <c r="BM227">
+        <v>2.25</v>
+      </c>
+      <c r="BN227">
+        <v>1.55</v>
+      </c>
+      <c r="BO227">
+        <v>2.9</v>
+      </c>
+      <c r="BP227">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7468587</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45731.54166666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>85</v>
+      </c>
+      <c r="H228" t="s">
+        <v>81</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>245</v>
+      </c>
+      <c r="P228" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q228">
+        <v>4</v>
+      </c>
+      <c r="R228">
+        <v>2.1</v>
+      </c>
+      <c r="S228">
+        <v>2.75</v>
+      </c>
+      <c r="T228">
+        <v>1.44</v>
+      </c>
+      <c r="U228">
+        <v>2.63</v>
+      </c>
+      <c r="V228">
+        <v>3</v>
+      </c>
+      <c r="W228">
+        <v>1.36</v>
+      </c>
+      <c r="X228">
+        <v>9</v>
+      </c>
+      <c r="Y228">
+        <v>1.07</v>
+      </c>
+      <c r="Z228">
+        <v>3.57</v>
+      </c>
+      <c r="AA228">
+        <v>3.47</v>
+      </c>
+      <c r="AB228">
+        <v>2.14</v>
+      </c>
+      <c r="AC228">
+        <v>1.06</v>
+      </c>
+      <c r="AD228">
+        <v>8.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.33</v>
+      </c>
+      <c r="AF228">
+        <v>3.25</v>
+      </c>
+      <c r="AG228">
+        <v>1.97</v>
+      </c>
+      <c r="AH228">
+        <v>1.84</v>
+      </c>
+      <c r="AI228">
+        <v>1.8</v>
+      </c>
+      <c r="AJ228">
+        <v>1.95</v>
+      </c>
+      <c r="AK228">
+        <v>1.7</v>
+      </c>
+      <c r="AL228">
+        <v>1.3</v>
+      </c>
+      <c r="AM228">
+        <v>1.31</v>
+      </c>
+      <c r="AN228">
+        <v>1.08</v>
+      </c>
+      <c r="AO228">
+        <v>1.42</v>
+      </c>
+      <c r="AP228">
+        <v>1.23</v>
+      </c>
+      <c r="AQ228">
+        <v>1.31</v>
+      </c>
+      <c r="AR228">
+        <v>1.43</v>
+      </c>
+      <c r="AS228">
+        <v>1.5</v>
+      </c>
+      <c r="AT228">
+        <v>2.93</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>4</v>
+      </c>
+      <c r="AW228">
+        <v>6</v>
+      </c>
+      <c r="AX228">
+        <v>5</v>
+      </c>
+      <c r="AY228">
+        <v>10</v>
+      </c>
+      <c r="AZ228">
+        <v>10</v>
+      </c>
+      <c r="BA228">
+        <v>3</v>
+      </c>
+      <c r="BB228">
+        <v>5</v>
+      </c>
+      <c r="BC228">
+        <v>8</v>
+      </c>
+      <c r="BD228">
+        <v>2.93</v>
+      </c>
+      <c r="BE228">
+        <v>6.85</v>
+      </c>
+      <c r="BF228">
+        <v>1.67</v>
+      </c>
+      <c r="BG228">
+        <v>1.24</v>
+      </c>
+      <c r="BH228">
+        <v>3.34</v>
+      </c>
+      <c r="BI228">
+        <v>1.47</v>
+      </c>
+      <c r="BJ228">
+        <v>2.42</v>
+      </c>
+      <c r="BK228">
+        <v>1.83</v>
+      </c>
+      <c r="BL228">
+        <v>1.87</v>
+      </c>
+      <c r="BM228">
+        <v>2.34</v>
+      </c>
+      <c r="BN228">
+        <v>1.5</v>
+      </c>
+      <c r="BO228">
+        <v>3.08</v>
+      </c>
+      <c r="BP228">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7468588</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.625</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>77</v>
+      </c>
+      <c r="H229" t="s">
+        <v>73</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>2</v>
+      </c>
+      <c r="N229">
+        <v>2</v>
+      </c>
+      <c r="O229" t="s">
+        <v>90</v>
+      </c>
+      <c r="P229" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q229">
+        <v>6</v>
+      </c>
+      <c r="R229">
+        <v>2.5</v>
+      </c>
+      <c r="S229">
+        <v>1.91</v>
+      </c>
+      <c r="T229">
+        <v>1.29</v>
+      </c>
+      <c r="U229">
+        <v>3.5</v>
+      </c>
+      <c r="V229">
+        <v>2.25</v>
+      </c>
+      <c r="W229">
+        <v>1.57</v>
+      </c>
+      <c r="X229">
+        <v>5.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.14</v>
+      </c>
+      <c r="Z229">
+        <v>5.7</v>
+      </c>
+      <c r="AA229">
+        <v>4.5</v>
+      </c>
+      <c r="AB229">
+        <v>1.56</v>
+      </c>
+      <c r="AC229">
+        <v>1.03</v>
+      </c>
+      <c r="AD229">
+        <v>11</v>
+      </c>
+      <c r="AE229">
+        <v>1.17</v>
+      </c>
+      <c r="AF229">
+        <v>5</v>
+      </c>
+      <c r="AG229">
+        <v>1.57</v>
+      </c>
+      <c r="AH229">
+        <v>2.25</v>
+      </c>
+      <c r="AI229">
+        <v>1.7</v>
+      </c>
+      <c r="AJ229">
+        <v>2.05</v>
+      </c>
+      <c r="AK229">
+        <v>2.55</v>
+      </c>
+      <c r="AL229">
+        <v>1.2</v>
+      </c>
+      <c r="AM229">
+        <v>1.13</v>
+      </c>
+      <c r="AN229">
+        <v>0.92</v>
+      </c>
+      <c r="AO229">
+        <v>1.25</v>
+      </c>
+      <c r="AP229">
+        <v>0.85</v>
+      </c>
+      <c r="AQ229">
+        <v>1.38</v>
+      </c>
+      <c r="AR229">
+        <v>1.22</v>
+      </c>
+      <c r="AS229">
+        <v>1.6</v>
+      </c>
+      <c r="AT229">
+        <v>2.82</v>
+      </c>
+      <c r="AU229">
+        <v>4</v>
+      </c>
+      <c r="AV229">
+        <v>9</v>
+      </c>
+      <c r="AW229">
+        <v>3</v>
+      </c>
+      <c r="AX229">
+        <v>8</v>
+      </c>
+      <c r="AY229">
+        <v>7</v>
+      </c>
+      <c r="AZ229">
+        <v>20</v>
+      </c>
+      <c r="BA229">
+        <v>0</v>
+      </c>
+      <c r="BB229">
+        <v>9</v>
+      </c>
+      <c r="BC229">
+        <v>9</v>
+      </c>
+      <c r="BD229">
+        <v>3.8</v>
+      </c>
+      <c r="BE229">
+        <v>9.1</v>
+      </c>
+      <c r="BF229">
+        <v>1.4</v>
+      </c>
+      <c r="BG229">
+        <v>1.39</v>
+      </c>
+      <c r="BH229">
+        <v>2.67</v>
+      </c>
+      <c r="BI229">
+        <v>1.73</v>
+      </c>
+      <c r="BJ229">
+        <v>1.99</v>
+      </c>
+      <c r="BK229">
+        <v>2.19</v>
+      </c>
+      <c r="BL229">
+        <v>1.57</v>
+      </c>
+      <c r="BM229">
+        <v>2.92</v>
+      </c>
+      <c r="BN229">
+        <v>1.31</v>
+      </c>
+      <c r="BO229">
+        <v>4.15</v>
+      </c>
+      <c r="BP229">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7468585</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45731.71180555555</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>83</v>
+      </c>
+      <c r="H230" t="s">
+        <v>78</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>162</v>
+      </c>
+      <c r="P230" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q230">
+        <v>2.75</v>
+      </c>
+      <c r="R230">
+        <v>2.2</v>
+      </c>
+      <c r="S230">
+        <v>4</v>
+      </c>
+      <c r="T230">
+        <v>1.4</v>
+      </c>
+      <c r="U230">
+        <v>2.75</v>
+      </c>
+      <c r="V230">
+        <v>2.75</v>
+      </c>
+      <c r="W230">
+        <v>1.4</v>
+      </c>
+      <c r="X230">
+        <v>8</v>
+      </c>
+      <c r="Y230">
+        <v>1.08</v>
+      </c>
+      <c r="Z230">
+        <v>2.01</v>
+      </c>
+      <c r="AA230">
+        <v>3.61</v>
+      </c>
+      <c r="AB230">
+        <v>3.85</v>
+      </c>
+      <c r="AC230">
+        <v>1.06</v>
+      </c>
+      <c r="AD230">
+        <v>8.5</v>
+      </c>
+      <c r="AE230">
+        <v>1.3</v>
+      </c>
+      <c r="AF230">
+        <v>3.45</v>
+      </c>
+      <c r="AG230">
+        <v>1.92</v>
+      </c>
+      <c r="AH230">
+        <v>1.89</v>
+      </c>
+      <c r="AI230">
+        <v>1.75</v>
+      </c>
+      <c r="AJ230">
+        <v>2</v>
+      </c>
+      <c r="AK230">
+        <v>1.3</v>
+      </c>
+      <c r="AL230">
+        <v>1.3</v>
+      </c>
+      <c r="AM230">
+        <v>1.71</v>
+      </c>
+      <c r="AN230">
+        <v>1.17</v>
+      </c>
+      <c r="AO230">
+        <v>0.64</v>
+      </c>
+      <c r="AP230">
+        <v>1.31</v>
+      </c>
+      <c r="AQ230">
+        <v>0.58</v>
+      </c>
+      <c r="AR230">
+        <v>1.69</v>
+      </c>
+      <c r="AS230">
+        <v>1.33</v>
+      </c>
+      <c r="AT230">
+        <v>3.02</v>
+      </c>
+      <c r="AU230">
+        <v>6</v>
+      </c>
+      <c r="AV230">
+        <v>6</v>
+      </c>
+      <c r="AW230">
+        <v>4</v>
+      </c>
+      <c r="AX230">
+        <v>7</v>
+      </c>
+      <c r="AY230">
+        <v>13</v>
+      </c>
+      <c r="AZ230">
+        <v>16</v>
+      </c>
+      <c r="BA230">
+        <v>5</v>
+      </c>
+      <c r="BB230">
+        <v>4</v>
+      </c>
+      <c r="BC230">
+        <v>9</v>
+      </c>
+      <c r="BD230">
+        <v>1.64</v>
+      </c>
+      <c r="BE230">
+        <v>6.7</v>
+      </c>
+      <c r="BF230">
+        <v>3.04</v>
+      </c>
+      <c r="BG230">
+        <v>1.31</v>
+      </c>
+      <c r="BH230">
+        <v>2.92</v>
+      </c>
+      <c r="BI230">
+        <v>1.59</v>
+      </c>
+      <c r="BJ230">
+        <v>2.16</v>
+      </c>
+      <c r="BK230">
+        <v>2.03</v>
+      </c>
+      <c r="BL230">
+        <v>1.7</v>
+      </c>
+      <c r="BM230">
+        <v>2.64</v>
+      </c>
+      <c r="BN230">
+        <v>1.4</v>
+      </c>
+      <c r="BO230">
+        <v>3.58</v>
+      </c>
+      <c r="BP230">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,12 @@
     <t>['83']</t>
   </si>
   <si>
+    <t>['22', '78', '82', '90+6']</t>
+  </si>
+  <si>
+    <t>['17', '42', '76']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1103,6 +1109,9 @@
   </si>
   <si>
     <t>['77', '88']</t>
+  </si>
+  <si>
+    <t>['31', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1720,7 +1729,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1926,7 +1935,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2004,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ3">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2132,7 +2141,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2544,7 +2553,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2750,7 +2759,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3652,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ11">
         <v>0.25</v>
@@ -3780,7 +3789,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3858,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.38</v>
@@ -4192,7 +4201,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4273,7 +4282,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4604,7 +4613,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5222,7 +5231,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5428,7 +5437,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5506,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>1.29</v>
@@ -5712,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ21">
         <v>0.23</v>
@@ -5840,7 +5849,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6046,7 +6055,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6127,7 +6136,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ23">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR23">
         <v>1.52</v>
@@ -6252,7 +6261,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6458,7 +6467,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6870,7 +6879,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7076,7 +7085,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7694,7 +7703,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7978,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8312,7 +8321,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8518,7 +8527,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8805,7 +8814,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ36">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -9342,7 +9351,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9548,7 +9557,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10041,7 +10050,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10244,7 +10253,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -10372,7 +10381,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10578,7 +10587,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10784,7 +10793,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10862,10 +10871,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR46">
         <v>1.4</v>
@@ -11196,7 +11205,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11274,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ48">
         <v>0.58</v>
@@ -11608,7 +11617,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11814,7 +11823,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12020,7 +12029,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12226,7 +12235,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12432,7 +12441,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12719,7 +12728,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR55">
         <v>1.26</v>
@@ -13050,7 +13059,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13462,7 +13471,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13746,7 +13755,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.85</v>
@@ -13952,10 +13961,10 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ61">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -14080,7 +14089,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14286,7 +14295,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14492,7 +14501,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14982,7 +14991,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ66">
         <v>0.58</v>
@@ -15110,7 +15119,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15316,7 +15325,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15394,7 +15403,7 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ68">
         <v>1.29</v>
@@ -15522,7 +15531,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15728,7 +15737,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15934,7 +15943,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16140,7 +16149,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16346,7 +16355,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16427,7 +16436,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ73">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16633,7 +16642,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ74">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16758,7 +16767,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16964,7 +16973,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17170,7 +17179,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17376,7 +17385,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17454,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.6899999999999999</v>
@@ -17582,7 +17591,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -18200,7 +18209,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18896,7 +18905,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ85">
         <v>1.69</v>
@@ -19024,7 +19033,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19102,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ86">
         <v>1.46</v>
@@ -20054,7 +20063,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20135,7 +20144,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ91">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -20260,7 +20269,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20466,7 +20475,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20672,7 +20681,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20878,7 +20887,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21084,7 +21093,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21290,7 +21299,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21702,7 +21711,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21986,7 +21995,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.23</v>
@@ -22114,7 +22123,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22398,7 +22407,7 @@
         <v>1.4</v>
       </c>
       <c r="AP102">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -22526,7 +22535,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22607,7 +22616,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ103">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR103">
         <v>1.68</v>
@@ -23556,7 +23565,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23637,7 +23646,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23762,7 +23771,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23968,7 +23977,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24458,7 +24467,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ112">
         <v>1.29</v>
@@ -24664,7 +24673,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ113">
         <v>0.85</v>
@@ -24792,7 +24801,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24998,7 +25007,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25410,7 +25419,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25488,7 +25497,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.46</v>
@@ -25616,7 +25625,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26440,7 +26449,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26521,7 +26530,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ122">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26646,7 +26655,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27470,7 +27479,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27551,7 +27560,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR127">
         <v>1.3</v>
@@ -27882,7 +27891,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28088,7 +28097,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28500,7 +28509,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28706,7 +28715,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28990,7 +28999,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ134">
         <v>0.85</v>
@@ -29402,7 +29411,7 @@
         <v>1.71</v>
       </c>
       <c r="AP136">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ136">
         <v>1.46</v>
@@ -29530,7 +29539,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29736,7 +29745,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29942,7 +29951,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30148,7 +30157,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30432,7 +30441,7 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
         <v>0.25</v>
@@ -31259,7 +31268,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31384,7 +31393,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31796,7 +31805,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31874,7 +31883,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ148">
         <v>1.46</v>
@@ -32002,7 +32011,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32208,7 +32217,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32289,7 +32298,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ150">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR150">
         <v>1.57</v>
@@ -32414,7 +32423,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32620,7 +32629,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32826,7 +32835,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33110,7 +33119,7 @@
         <v>0.13</v>
       </c>
       <c r="AP154">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ154">
         <v>0.23</v>
@@ -33650,7 +33659,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33856,7 +33865,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34140,7 +34149,7 @@
         <v>1.25</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
         <v>1.5</v>
@@ -34761,7 +34770,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ162">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -34886,7 +34895,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35298,7 +35307,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35710,7 +35719,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35788,7 +35797,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35916,7 +35925,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36328,7 +36337,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36821,7 +36830,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ172">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR172">
         <v>1.58</v>
@@ -36946,7 +36955,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37152,7 +37161,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37230,7 +37239,7 @@
         <v>2.33</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ174">
         <v>2.54</v>
@@ -37358,7 +37367,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37770,7 +37779,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38263,7 +38272,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ179">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR179">
         <v>1.27</v>
@@ -38388,7 +38397,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38594,7 +38603,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38800,7 +38809,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39084,7 +39093,7 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ183">
         <v>1.38</v>
@@ -39418,7 +39427,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39499,7 +39508,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ185">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR185">
         <v>1.58</v>
@@ -39624,7 +39633,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39908,7 +39917,7 @@
         <v>1.33</v>
       </c>
       <c r="AP187">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -40036,7 +40045,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40448,7 +40457,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40529,7 +40538,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ190">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40654,7 +40663,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40732,7 +40741,7 @@
         <v>0.4</v>
       </c>
       <c r="AP191">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ191">
         <v>0.6899999999999999</v>
@@ -40860,7 +40869,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41272,7 +41281,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41478,7 +41487,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41684,7 +41693,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42096,7 +42105,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42302,7 +42311,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42920,7 +42929,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43207,7 +43216,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ203">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR203">
         <v>1.31</v>
@@ -43950,7 +43959,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44156,7 +44165,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44234,7 +44243,7 @@
         <v>2.45</v>
       </c>
       <c r="AP208">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ208">
         <v>2.54</v>
@@ -44568,7 +44577,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44774,7 +44783,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -44855,7 +44864,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ211">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR211">
         <v>1.62</v>
@@ -45058,7 +45067,7 @@
         <v>1.55</v>
       </c>
       <c r="AP212">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ212">
         <v>1.31</v>
@@ -45186,7 +45195,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45264,7 +45273,7 @@
         <v>1.08</v>
       </c>
       <c r="AP213">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ213">
         <v>1</v>
@@ -45392,7 +45401,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45598,7 +45607,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -46422,7 +46431,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46834,7 +46843,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47118,7 +47127,7 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ222">
         <v>1.23</v>
@@ -47246,7 +47255,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47452,7 +47461,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47864,7 +47873,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48070,7 +48079,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48482,7 +48491,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48845,6 +48854,624 @@
       </c>
       <c r="BP230">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7468584</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>80</v>
+      </c>
+      <c r="H231" t="s">
+        <v>70</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>2</v>
+      </c>
+      <c r="K231">
+        <v>3</v>
+      </c>
+      <c r="L231">
+        <v>4</v>
+      </c>
+      <c r="M231">
+        <v>2</v>
+      </c>
+      <c r="N231">
+        <v>6</v>
+      </c>
+      <c r="O231" t="s">
+        <v>246</v>
+      </c>
+      <c r="P231" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q231">
+        <v>1.83</v>
+      </c>
+      <c r="R231">
+        <v>2.6</v>
+      </c>
+      <c r="S231">
+        <v>7</v>
+      </c>
+      <c r="T231">
+        <v>1.25</v>
+      </c>
+      <c r="U231">
+        <v>3.75</v>
+      </c>
+      <c r="V231">
+        <v>2.25</v>
+      </c>
+      <c r="W231">
+        <v>1.57</v>
+      </c>
+      <c r="X231">
+        <v>5.5</v>
+      </c>
+      <c r="Y231">
+        <v>1.14</v>
+      </c>
+      <c r="Z231">
+        <v>1.37</v>
+      </c>
+      <c r="AA231">
+        <v>5.6</v>
+      </c>
+      <c r="AB231">
+        <v>8</v>
+      </c>
+      <c r="AC231">
+        <v>1.01</v>
+      </c>
+      <c r="AD231">
+        <v>17</v>
+      </c>
+      <c r="AE231">
+        <v>1.15</v>
+      </c>
+      <c r="AF231">
+        <v>5.25</v>
+      </c>
+      <c r="AG231">
+        <v>1.49</v>
+      </c>
+      <c r="AH231">
+        <v>2.51</v>
+      </c>
+      <c r="AI231">
+        <v>1.8</v>
+      </c>
+      <c r="AJ231">
+        <v>1.95</v>
+      </c>
+      <c r="AK231">
+        <v>1.08</v>
+      </c>
+      <c r="AL231">
+        <v>1.16</v>
+      </c>
+      <c r="AM231">
+        <v>3.1</v>
+      </c>
+      <c r="AN231">
+        <v>1.92</v>
+      </c>
+      <c r="AO231">
+        <v>1.17</v>
+      </c>
+      <c r="AP231">
+        <v>2</v>
+      </c>
+      <c r="AQ231">
+        <v>1.08</v>
+      </c>
+      <c r="AR231">
+        <v>1.71</v>
+      </c>
+      <c r="AS231">
+        <v>1.02</v>
+      </c>
+      <c r="AT231">
+        <v>2.73</v>
+      </c>
+      <c r="AU231">
+        <v>9</v>
+      </c>
+      <c r="AV231">
+        <v>6</v>
+      </c>
+      <c r="AW231">
+        <v>6</v>
+      </c>
+      <c r="AX231">
+        <v>7</v>
+      </c>
+      <c r="AY231">
+        <v>16</v>
+      </c>
+      <c r="AZ231">
+        <v>16</v>
+      </c>
+      <c r="BA231">
+        <v>4</v>
+      </c>
+      <c r="BB231">
+        <v>1</v>
+      </c>
+      <c r="BC231">
+        <v>5</v>
+      </c>
+      <c r="BD231">
+        <v>1.27</v>
+      </c>
+      <c r="BE231">
+        <v>10.75</v>
+      </c>
+      <c r="BF231">
+        <v>4.85</v>
+      </c>
+      <c r="BG231">
+        <v>1.24</v>
+      </c>
+      <c r="BH231">
+        <v>3.34</v>
+      </c>
+      <c r="BI231">
+        <v>1.47</v>
+      </c>
+      <c r="BJ231">
+        <v>2.42</v>
+      </c>
+      <c r="BK231">
+        <v>1.9</v>
+      </c>
+      <c r="BL231">
+        <v>1.8</v>
+      </c>
+      <c r="BM231">
+        <v>2.32</v>
+      </c>
+      <c r="BN231">
+        <v>1.51</v>
+      </c>
+      <c r="BO231">
+        <v>3.08</v>
+      </c>
+      <c r="BP231">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7468583</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45732.55208333334</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>71</v>
+      </c>
+      <c r="H232" t="s">
+        <v>72</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232" t="s">
+        <v>90</v>
+      </c>
+      <c r="P232" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q232">
+        <v>2.3</v>
+      </c>
+      <c r="R232">
+        <v>2.25</v>
+      </c>
+      <c r="S232">
+        <v>5</v>
+      </c>
+      <c r="T232">
+        <v>1.36</v>
+      </c>
+      <c r="U232">
+        <v>3</v>
+      </c>
+      <c r="V232">
+        <v>2.75</v>
+      </c>
+      <c r="W232">
+        <v>1.4</v>
+      </c>
+      <c r="X232">
+        <v>7</v>
+      </c>
+      <c r="Y232">
+        <v>1.1</v>
+      </c>
+      <c r="Z232">
+        <v>1.82</v>
+      </c>
+      <c r="AA232">
+        <v>3.79</v>
+      </c>
+      <c r="AB232">
+        <v>4.5</v>
+      </c>
+      <c r="AC232">
+        <v>1.05</v>
+      </c>
+      <c r="AD232">
+        <v>9.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.28</v>
+      </c>
+      <c r="AF232">
+        <v>3.6</v>
+      </c>
+      <c r="AG232">
+        <v>1.9</v>
+      </c>
+      <c r="AH232">
+        <v>1.9</v>
+      </c>
+      <c r="AI232">
+        <v>1.8</v>
+      </c>
+      <c r="AJ232">
+        <v>1.95</v>
+      </c>
+      <c r="AK232">
+        <v>1.19</v>
+      </c>
+      <c r="AL232">
+        <v>1.26</v>
+      </c>
+      <c r="AM232">
+        <v>2.05</v>
+      </c>
+      <c r="AN232">
+        <v>1.92</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
+        <v>1.85</v>
+      </c>
+      <c r="AQ232">
+        <v>1</v>
+      </c>
+      <c r="AR232">
+        <v>1.63</v>
+      </c>
+      <c r="AS232">
+        <v>1.22</v>
+      </c>
+      <c r="AT232">
+        <v>2.85</v>
+      </c>
+      <c r="AU232">
+        <v>0</v>
+      </c>
+      <c r="AV232">
+        <v>3</v>
+      </c>
+      <c r="AW232">
+        <v>8</v>
+      </c>
+      <c r="AX232">
+        <v>8</v>
+      </c>
+      <c r="AY232">
+        <v>11</v>
+      </c>
+      <c r="AZ232">
+        <v>15</v>
+      </c>
+      <c r="BA232">
+        <v>4</v>
+      </c>
+      <c r="BB232">
+        <v>4</v>
+      </c>
+      <c r="BC232">
+        <v>8</v>
+      </c>
+      <c r="BD232">
+        <v>1.56</v>
+      </c>
+      <c r="BE232">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF232">
+        <v>3</v>
+      </c>
+      <c r="BG232">
+        <v>1.26</v>
+      </c>
+      <c r="BH232">
+        <v>3.22</v>
+      </c>
+      <c r="BI232">
+        <v>1.51</v>
+      </c>
+      <c r="BJ232">
+        <v>2.32</v>
+      </c>
+      <c r="BK232">
+        <v>1.85</v>
+      </c>
+      <c r="BL232">
+        <v>1.85</v>
+      </c>
+      <c r="BM232">
+        <v>2.45</v>
+      </c>
+      <c r="BN232">
+        <v>1.46</v>
+      </c>
+      <c r="BO232">
+        <v>3.28</v>
+      </c>
+      <c r="BP232">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7468580</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.69791666666</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>79</v>
+      </c>
+      <c r="H233" t="s">
+        <v>87</v>
+      </c>
+      <c r="I233">
+        <v>2</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>2</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>247</v>
+      </c>
+      <c r="P233" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q233">
+        <v>1.91</v>
+      </c>
+      <c r="R233">
+        <v>2.63</v>
+      </c>
+      <c r="S233">
+        <v>5.5</v>
+      </c>
+      <c r="T233">
+        <v>1.22</v>
+      </c>
+      <c r="U233">
+        <v>4</v>
+      </c>
+      <c r="V233">
+        <v>2.1</v>
+      </c>
+      <c r="W233">
+        <v>1.67</v>
+      </c>
+      <c r="X233">
+        <v>4.5</v>
+      </c>
+      <c r="Y233">
+        <v>1.18</v>
+      </c>
+      <c r="Z233">
+        <v>1.47</v>
+      </c>
+      <c r="AA233">
+        <v>5.3</v>
+      </c>
+      <c r="AB233">
+        <v>6</v>
+      </c>
+      <c r="AC233">
+        <v>1.02</v>
+      </c>
+      <c r="AD233">
+        <v>21</v>
+      </c>
+      <c r="AE233">
+        <v>1.11</v>
+      </c>
+      <c r="AF233">
+        <v>6.25</v>
+      </c>
+      <c r="AG233">
+        <v>1.37</v>
+      </c>
+      <c r="AH233">
+        <v>2.94</v>
+      </c>
+      <c r="AI233">
+        <v>1.57</v>
+      </c>
+      <c r="AJ233">
+        <v>2.25</v>
+      </c>
+      <c r="AK233">
+        <v>1.13</v>
+      </c>
+      <c r="AL233">
+        <v>1.17</v>
+      </c>
+      <c r="AM233">
+        <v>2.65</v>
+      </c>
+      <c r="AN233">
+        <v>2.67</v>
+      </c>
+      <c r="AO233">
+        <v>2.25</v>
+      </c>
+      <c r="AP233">
+        <v>2.69</v>
+      </c>
+      <c r="AQ233">
+        <v>2.08</v>
+      </c>
+      <c r="AR233">
+        <v>2.39</v>
+      </c>
+      <c r="AS233">
+        <v>1.48</v>
+      </c>
+      <c r="AT233">
+        <v>3.87</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>11</v>
+      </c>
+      <c r="AX233">
+        <v>9</v>
+      </c>
+      <c r="AY233">
+        <v>21</v>
+      </c>
+      <c r="AZ233">
+        <v>18</v>
+      </c>
+      <c r="BA233">
+        <v>5</v>
+      </c>
+      <c r="BB233">
+        <v>5</v>
+      </c>
+      <c r="BC233">
+        <v>10</v>
+      </c>
+      <c r="BD233">
+        <v>1.4</v>
+      </c>
+      <c r="BE233">
+        <v>9.5</v>
+      </c>
+      <c r="BF233">
+        <v>3.25</v>
+      </c>
+      <c r="BG233">
+        <v>1.28</v>
+      </c>
+      <c r="BH233">
+        <v>3.08</v>
+      </c>
+      <c r="BI233">
+        <v>1.54</v>
+      </c>
+      <c r="BJ233">
+        <v>2.25</v>
+      </c>
+      <c r="BK233">
+        <v>1.85</v>
+      </c>
+      <c r="BL233">
+        <v>1.85</v>
+      </c>
+      <c r="BM233">
+        <v>2.54</v>
+      </c>
+      <c r="BN233">
+        <v>1.43</v>
+      </c>
+      <c r="BO233">
+        <v>3.42</v>
+      </c>
+      <c r="BP233">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="368">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,9 @@
     <t>['22', '78', '82', '90+6']</t>
   </si>
   <si>
+    <t>['47', '54']</t>
+  </si>
+  <si>
     <t>['17', '42', '76']</t>
   </si>
   <si>
@@ -1112,6 +1115,9 @@
   </si>
   <si>
     <t>['31', '45+1']</t>
+  </si>
+  <si>
+    <t>['3']</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1729,7 +1735,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1935,7 +1941,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2141,7 +2147,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2553,7 +2559,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2759,7 +2765,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3789,7 +3795,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4201,7 +4207,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4613,7 +4619,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4691,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
         <v>0.58</v>
@@ -5106,7 +5112,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ18">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5231,7 +5237,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5437,7 +5443,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5849,7 +5855,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6055,7 +6061,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6261,7 +6267,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6467,7 +6473,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6879,7 +6885,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7085,7 +7091,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7703,7 +7709,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8321,7 +8327,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8399,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ34">
         <v>1.23</v>
@@ -8527,7 +8533,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9351,7 +9357,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9557,7 +9563,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10256,7 +10262,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10381,7 +10387,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10587,7 +10593,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10793,7 +10799,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11205,7 +11211,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11617,7 +11623,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11823,7 +11829,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12029,7 +12035,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12235,7 +12241,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12441,7 +12447,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12725,7 +12731,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ55">
         <v>2.08</v>
@@ -13059,7 +13065,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13346,7 +13352,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13471,7 +13477,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -14089,7 +14095,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14167,7 +14173,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62">
         <v>1.69</v>
@@ -14295,7 +14301,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14501,7 +14507,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15119,7 +15125,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15325,7 +15331,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15531,7 +15537,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15737,7 +15743,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15943,7 +15949,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16149,7 +16155,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16355,7 +16361,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16767,7 +16773,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16973,7 +16979,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17179,7 +17185,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17385,7 +17391,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17591,7 +17597,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17672,7 +17678,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -17875,7 +17881,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ80">
         <v>0.85</v>
@@ -18209,7 +18215,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -19033,7 +19039,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -20063,7 +20069,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20269,7 +20275,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20475,7 +20481,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20553,7 +20559,7 @@
         <v>2.25</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ93">
         <v>1.38</v>
@@ -20681,7 +20687,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20887,7 +20893,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21093,7 +21099,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21299,7 +21305,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21380,7 +21386,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21711,7 +21717,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22123,7 +22129,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22410,7 +22416,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22535,7 +22541,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23565,7 +23571,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23771,7 +23777,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23977,7 +23983,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24801,7 +24807,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25007,7 +25013,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25419,7 +25425,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25625,7 +25631,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26324,7 +26330,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ121">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26449,7 +26455,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26655,7 +26661,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27145,7 +27151,7 @@
         <v>1.67</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27479,7 +27485,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27891,7 +27897,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28097,7 +28103,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28509,7 +28515,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28715,7 +28721,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29539,7 +29545,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29745,7 +29751,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29951,7 +29957,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30157,7 +30163,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30650,7 +30656,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -30853,7 +30859,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143">
         <v>0.6899999999999999</v>
@@ -31393,7 +31399,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31805,7 +31811,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -32011,7 +32017,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32217,7 +32223,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32423,7 +32429,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32629,7 +32635,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32835,7 +32841,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33659,7 +33665,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33865,7 +33871,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34152,7 +34158,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34895,7 +34901,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35307,7 +35313,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35591,7 +35597,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ166">
         <v>1.31</v>
@@ -35719,7 +35725,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35925,7 +35931,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36337,7 +36343,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36955,7 +36961,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37161,7 +37167,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37367,7 +37373,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37779,7 +37785,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38397,7 +38403,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38603,7 +38609,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38809,7 +38815,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39427,7 +39433,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39633,7 +39639,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -40045,7 +40051,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40126,7 +40132,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR188">
         <v>1.32</v>
@@ -40329,7 +40335,7 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ189">
         <v>0.25</v>
@@ -40457,7 +40463,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40663,7 +40669,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40869,7 +40875,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41281,7 +41287,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41487,7 +41493,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41693,7 +41699,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42105,7 +42111,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42311,7 +42317,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42929,7 +42935,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43831,7 +43837,7 @@
         <v>1.09</v>
       </c>
       <c r="AP206">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -43959,7 +43965,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44040,7 +44046,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ207">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR207">
         <v>1.17</v>
@@ -44165,7 +44171,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44577,7 +44583,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44783,7 +44789,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45195,7 +45201,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45401,7 +45407,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45482,7 +45488,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ214">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR214">
         <v>1.25</v>
@@ -45607,7 +45613,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -46431,7 +46437,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46843,7 +46849,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47255,7 +47261,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47461,7 +47467,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47873,7 +47879,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48079,7 +48085,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48491,7 +48497,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48903,7 +48909,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49273,7 +49279,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>7468580</v>
+        <v>7468586</v>
       </c>
       <c r="C233" t="s">
         <v>68</v>
@@ -49282,195 +49288,401 @@
         <v>69</v>
       </c>
       <c r="E233" s="2">
-        <v>45732.69791666666</v>
+        <v>45732.55208333334</v>
       </c>
       <c r="F233">
         <v>26</v>
       </c>
       <c r="G233" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H233" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I233">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L233">
+        <v>2</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
         <v>3</v>
-      </c>
-      <c r="M233">
-        <v>1</v>
-      </c>
-      <c r="N233">
-        <v>4</v>
       </c>
       <c r="O233" t="s">
         <v>247</v>
       </c>
       <c r="P233" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q233">
+        <v>3</v>
+      </c>
+      <c r="R233">
+        <v>2.1</v>
+      </c>
+      <c r="S233">
+        <v>3.75</v>
+      </c>
+      <c r="T233">
+        <v>1.44</v>
+      </c>
+      <c r="U233">
+        <v>2.63</v>
+      </c>
+      <c r="V233">
+        <v>3.25</v>
+      </c>
+      <c r="W233">
+        <v>1.33</v>
+      </c>
+      <c r="X233">
+        <v>9</v>
+      </c>
+      <c r="Y233">
+        <v>1.07</v>
+      </c>
+      <c r="Z233">
+        <v>2.24</v>
+      </c>
+      <c r="AA233">
+        <v>3.57</v>
+      </c>
+      <c r="AB233">
+        <v>3.25</v>
+      </c>
+      <c r="AC233">
+        <v>1.06</v>
+      </c>
+      <c r="AD233">
+        <v>8.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.33</v>
+      </c>
+      <c r="AF233">
+        <v>3.2</v>
+      </c>
+      <c r="AG233">
+        <v>1.94</v>
+      </c>
+      <c r="AH233">
+        <v>1.87</v>
+      </c>
+      <c r="AI233">
+        <v>1.8</v>
+      </c>
+      <c r="AJ233">
+        <v>1.95</v>
+      </c>
+      <c r="AK233">
+        <v>1.36</v>
+      </c>
+      <c r="AL233">
+        <v>1.31</v>
+      </c>
+      <c r="AM233">
+        <v>1.6</v>
+      </c>
+      <c r="AN233">
+        <v>2</v>
+      </c>
+      <c r="AO233">
+        <v>1.5</v>
+      </c>
+      <c r="AP233">
+        <v>2.08</v>
+      </c>
+      <c r="AQ233">
+        <v>1.38</v>
+      </c>
+      <c r="AR233">
+        <v>1.34</v>
+      </c>
+      <c r="AS233">
+        <v>1.35</v>
+      </c>
+      <c r="AT233">
+        <v>2.69</v>
+      </c>
+      <c r="AU233">
+        <v>5</v>
+      </c>
+      <c r="AV233">
+        <v>7</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>3</v>
+      </c>
+      <c r="AY233">
+        <v>14</v>
+      </c>
+      <c r="AZ233">
+        <v>11</v>
+      </c>
+      <c r="BA233">
+        <v>4</v>
+      </c>
+      <c r="BB233">
+        <v>3</v>
+      </c>
+      <c r="BC233">
+        <v>7</v>
+      </c>
+      <c r="BD233">
+        <v>2.21</v>
+      </c>
+      <c r="BE233">
+        <v>6.3</v>
+      </c>
+      <c r="BF233">
+        <v>2.1</v>
+      </c>
+      <c r="BG233">
+        <v>1.37</v>
+      </c>
+      <c r="BH233">
+        <v>2.75</v>
+      </c>
+      <c r="BI233">
+        <v>1.69</v>
+      </c>
+      <c r="BJ233">
+        <v>2.04</v>
+      </c>
+      <c r="BK233">
+        <v>2.1</v>
+      </c>
+      <c r="BL233">
+        <v>1.67</v>
+      </c>
+      <c r="BM233">
+        <v>2.83</v>
+      </c>
+      <c r="BN233">
+        <v>1.33</v>
+      </c>
+      <c r="BO233">
+        <v>4.05</v>
+      </c>
+      <c r="BP233">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7468580</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45732.69791666666</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>79</v>
+      </c>
+      <c r="H234" t="s">
+        <v>87</v>
+      </c>
+      <c r="I234">
+        <v>2</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>2</v>
+      </c>
+      <c r="L234">
+        <v>3</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>4</v>
+      </c>
+      <c r="O234" t="s">
+        <v>248</v>
+      </c>
+      <c r="P234" t="s">
         <v>130</v>
       </c>
-      <c r="Q233">
+      <c r="Q234">
         <v>1.91</v>
       </c>
-      <c r="R233">
+      <c r="R234">
         <v>2.63</v>
       </c>
-      <c r="S233">
+      <c r="S234">
         <v>5.5</v>
       </c>
-      <c r="T233">
+      <c r="T234">
         <v>1.22</v>
       </c>
-      <c r="U233">
+      <c r="U234">
         <v>4</v>
       </c>
-      <c r="V233">
+      <c r="V234">
         <v>2.1</v>
       </c>
-      <c r="W233">
+      <c r="W234">
         <v>1.67</v>
       </c>
-      <c r="X233">
+      <c r="X234">
         <v>4.5</v>
       </c>
-      <c r="Y233">
+      <c r="Y234">
         <v>1.18</v>
       </c>
-      <c r="Z233">
+      <c r="Z234">
         <v>1.47</v>
       </c>
-      <c r="AA233">
+      <c r="AA234">
         <v>5.3</v>
       </c>
-      <c r="AB233">
+      <c r="AB234">
         <v>6</v>
       </c>
-      <c r="AC233">
+      <c r="AC234">
         <v>1.02</v>
       </c>
-      <c r="AD233">
+      <c r="AD234">
         <v>21</v>
       </c>
-      <c r="AE233">
+      <c r="AE234">
         <v>1.11</v>
       </c>
-      <c r="AF233">
+      <c r="AF234">
         <v>6.25</v>
       </c>
-      <c r="AG233">
+      <c r="AG234">
         <v>1.37</v>
       </c>
-      <c r="AH233">
+      <c r="AH234">
         <v>2.94</v>
       </c>
-      <c r="AI233">
+      <c r="AI234">
         <v>1.57</v>
       </c>
-      <c r="AJ233">
+      <c r="AJ234">
         <v>2.25</v>
       </c>
-      <c r="AK233">
+      <c r="AK234">
         <v>1.13</v>
       </c>
-      <c r="AL233">
+      <c r="AL234">
         <v>1.17</v>
       </c>
-      <c r="AM233">
+      <c r="AM234">
         <v>2.65</v>
       </c>
-      <c r="AN233">
+      <c r="AN234">
         <v>2.67</v>
       </c>
-      <c r="AO233">
+      <c r="AO234">
         <v>2.25</v>
       </c>
-      <c r="AP233">
+      <c r="AP234">
         <v>2.69</v>
       </c>
-      <c r="AQ233">
+      <c r="AQ234">
         <v>2.08</v>
       </c>
-      <c r="AR233">
+      <c r="AR234">
         <v>2.39</v>
       </c>
-      <c r="AS233">
+      <c r="AS234">
         <v>1.48</v>
       </c>
-      <c r="AT233">
+      <c r="AT234">
         <v>3.87</v>
       </c>
-      <c r="AU233">
+      <c r="AU234">
         <v>6</v>
       </c>
-      <c r="AV233">
+      <c r="AV234">
         <v>3</v>
       </c>
-      <c r="AW233">
+      <c r="AW234">
         <v>11</v>
       </c>
-      <c r="AX233">
+      <c r="AX234">
         <v>9</v>
       </c>
-      <c r="AY233">
+      <c r="AY234">
         <v>21</v>
       </c>
-      <c r="AZ233">
+      <c r="AZ234">
         <v>18</v>
       </c>
-      <c r="BA233">
+      <c r="BA234">
         <v>5</v>
       </c>
-      <c r="BB233">
+      <c r="BB234">
         <v>5</v>
       </c>
-      <c r="BC233">
+      <c r="BC234">
         <v>10</v>
       </c>
-      <c r="BD233">
+      <c r="BD234">
         <v>1.4</v>
       </c>
-      <c r="BE233">
+      <c r="BE234">
         <v>9.5</v>
       </c>
-      <c r="BF233">
+      <c r="BF234">
         <v>3.25</v>
       </c>
-      <c r="BG233">
+      <c r="BG234">
         <v>1.28</v>
       </c>
-      <c r="BH233">
+      <c r="BH234">
         <v>3.08</v>
       </c>
-      <c r="BI233">
+      <c r="BI234">
         <v>1.54</v>
       </c>
-      <c r="BJ233">
+      <c r="BJ234">
         <v>2.25</v>
       </c>
-      <c r="BK233">
+      <c r="BK234">
         <v>1.85</v>
       </c>
-      <c r="BL233">
+      <c r="BL234">
         <v>1.85</v>
       </c>
-      <c r="BM233">
+      <c r="BM234">
         <v>2.54</v>
       </c>
-      <c r="BN233">
+      <c r="BN234">
         <v>1.43</v>
       </c>
-      <c r="BO233">
+      <c r="BO234">
         <v>3.42</v>
       </c>
-      <c r="BP233">
+      <c r="BP234">
         <v>1.23</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="370">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -763,6 +763,9 @@
     <t>['17', '42', '76']</t>
   </si>
   <si>
+    <t>['55', '60', '73', '89']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1118,6 +1121,9 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['62', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1735,7 +1741,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1941,7 +1947,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2147,7 +2153,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2559,7 +2565,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2765,7 +2771,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3464,7 +3470,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ10">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3795,7 +3801,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4207,7 +4213,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4619,7 +4625,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4697,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ16">
         <v>0.58</v>
@@ -5237,7 +5243,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5443,7 +5449,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5855,7 +5861,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6061,7 +6067,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6267,7 +6273,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6473,7 +6479,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6885,7 +6891,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7091,7 +7097,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7709,7 +7715,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8327,7 +8333,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8405,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ34">
         <v>1.23</v>
@@ -8533,7 +8539,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9026,7 +9032,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ37">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -9357,7 +9363,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9563,7 +9569,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10387,7 +10393,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10593,7 +10599,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10799,7 +10805,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11211,7 +11217,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11623,7 +11629,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11829,7 +11835,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12035,7 +12041,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12116,7 +12122,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR52">
         <v>1.24</v>
@@ -12241,7 +12247,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12447,7 +12453,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12731,7 +12737,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ55">
         <v>2.08</v>
@@ -13065,7 +13071,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13477,7 +13483,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -14095,7 +14101,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14173,7 +14179,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ62">
         <v>1.69</v>
@@ -14301,7 +14307,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14507,7 +14513,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15125,7 +15131,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15331,7 +15337,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15537,7 +15543,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15618,7 +15624,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ69">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR69">
         <v>1.32</v>
@@ -15743,7 +15749,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15949,7 +15955,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16155,7 +16161,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16361,7 +16367,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16773,7 +16779,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16979,7 +16985,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17185,7 +17191,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17391,7 +17397,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17597,7 +17603,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17881,7 +17887,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ80">
         <v>0.85</v>
@@ -18215,7 +18221,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18708,7 +18714,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ84">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -19039,7 +19045,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -20069,7 +20075,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20275,7 +20281,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20481,7 +20487,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20559,7 +20565,7 @@
         <v>2.25</v>
       </c>
       <c r="AP93">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ93">
         <v>1.38</v>
@@ -20687,7 +20693,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20893,7 +20899,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21099,7 +21105,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21305,7 +21311,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21717,7 +21723,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22129,7 +22135,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22541,7 +22547,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23034,7 +23040,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ105">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR105">
         <v>1.09</v>
@@ -23571,7 +23577,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23777,7 +23783,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23983,7 +23989,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24807,7 +24813,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25013,7 +25019,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25425,7 +25431,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25631,7 +25637,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26455,7 +26461,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26661,7 +26667,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26742,7 +26748,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ123">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27151,7 +27157,7 @@
         <v>1.67</v>
       </c>
       <c r="AP125">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27485,7 +27491,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27897,7 +27903,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28103,7 +28109,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28515,7 +28521,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28721,7 +28727,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29420,7 +29426,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ136">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR136">
         <v>2.35</v>
@@ -29545,7 +29551,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29751,7 +29757,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29957,7 +29963,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30163,7 +30169,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30859,7 +30865,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ143">
         <v>0.6899999999999999</v>
@@ -31399,7 +31405,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31811,7 +31817,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31892,7 +31898,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR148">
         <v>1.48</v>
@@ -32017,7 +32023,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32223,7 +32229,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32429,7 +32435,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32635,7 +32641,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32841,7 +32847,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33665,7 +33671,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33871,7 +33877,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34901,7 +34907,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35313,7 +35319,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35597,7 +35603,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ166">
         <v>1.31</v>
@@ -35725,7 +35731,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35931,7 +35937,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36218,7 +36224,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ169">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR169">
         <v>1.4</v>
@@ -36343,7 +36349,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36961,7 +36967,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37167,7 +37173,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37373,7 +37379,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37785,7 +37791,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38403,7 +38409,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38609,7 +38615,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38690,7 +38696,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ181">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR181">
         <v>1.5</v>
@@ -38815,7 +38821,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39433,7 +39439,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39639,7 +39645,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -40051,7 +40057,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40335,7 +40341,7 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ189">
         <v>0.25</v>
@@ -40463,7 +40469,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40669,7 +40675,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40875,7 +40881,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41287,7 +41293,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41493,7 +41499,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41574,7 +41580,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ195">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR195">
         <v>1.46</v>
@@ -41699,7 +41705,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42111,7 +42117,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42317,7 +42323,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42935,7 +42941,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43837,7 +43843,7 @@
         <v>1.09</v>
       </c>
       <c r="AP206">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -43965,7 +43971,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44171,7 +44177,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44583,7 +44589,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44789,7 +44795,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45201,7 +45207,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45407,7 +45413,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45613,7 +45619,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -46437,7 +46443,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46849,7 +46855,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47261,7 +47267,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47467,7 +47473,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47879,7 +47885,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -47960,7 +47966,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ226">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR226">
         <v>1.66</v>
@@ -48085,7 +48091,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48497,7 +48503,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48909,7 +48915,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49321,7 +49327,7 @@
         <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q233">
         <v>3</v>
@@ -49399,7 +49405,7 @@
         <v>1.5</v>
       </c>
       <c r="AP233">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ233">
         <v>1.38</v>
@@ -49684,6 +49690,212 @@
       </c>
       <c r="BP234">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7468592</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F235">
+        <v>27</v>
+      </c>
+      <c r="G235" t="s">
+        <v>84</v>
+      </c>
+      <c r="H235" t="s">
+        <v>80</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>4</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>6</v>
+      </c>
+      <c r="O235" t="s">
+        <v>249</v>
+      </c>
+      <c r="P235" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q235">
+        <v>3.2</v>
+      </c>
+      <c r="R235">
+        <v>2.3</v>
+      </c>
+      <c r="S235">
+        <v>3</v>
+      </c>
+      <c r="T235">
+        <v>1.33</v>
+      </c>
+      <c r="U235">
+        <v>3.25</v>
+      </c>
+      <c r="V235">
+        <v>2.5</v>
+      </c>
+      <c r="W235">
+        <v>1.5</v>
+      </c>
+      <c r="X235">
+        <v>6.5</v>
+      </c>
+      <c r="Y235">
+        <v>1.11</v>
+      </c>
+      <c r="Z235">
+        <v>2.78</v>
+      </c>
+      <c r="AA235">
+        <v>3.71</v>
+      </c>
+      <c r="AB235">
+        <v>2.46</v>
+      </c>
+      <c r="AC235">
+        <v>1.04</v>
+      </c>
+      <c r="AD235">
+        <v>10</v>
+      </c>
+      <c r="AE235">
+        <v>1.2</v>
+      </c>
+      <c r="AF235">
+        <v>4.33</v>
+      </c>
+      <c r="AG235">
+        <v>1.67</v>
+      </c>
+      <c r="AH235">
+        <v>2.1</v>
+      </c>
+      <c r="AI235">
+        <v>1.57</v>
+      </c>
+      <c r="AJ235">
+        <v>2.25</v>
+      </c>
+      <c r="AK235">
+        <v>1.52</v>
+      </c>
+      <c r="AL235">
+        <v>1.27</v>
+      </c>
+      <c r="AM235">
+        <v>1.46</v>
+      </c>
+      <c r="AN235">
+        <v>2.08</v>
+      </c>
+      <c r="AO235">
+        <v>1.46</v>
+      </c>
+      <c r="AP235">
+        <v>2.15</v>
+      </c>
+      <c r="AQ235">
+        <v>1.36</v>
+      </c>
+      <c r="AR235">
+        <v>1.35</v>
+      </c>
+      <c r="AS235">
+        <v>1.29</v>
+      </c>
+      <c r="AT235">
+        <v>2.64</v>
+      </c>
+      <c r="AU235">
+        <v>9</v>
+      </c>
+      <c r="AV235">
+        <v>13</v>
+      </c>
+      <c r="AW235">
+        <v>6</v>
+      </c>
+      <c r="AX235">
+        <v>4</v>
+      </c>
+      <c r="AY235">
+        <v>16</v>
+      </c>
+      <c r="AZ235">
+        <v>18</v>
+      </c>
+      <c r="BA235">
+        <v>6</v>
+      </c>
+      <c r="BB235">
+        <v>5</v>
+      </c>
+      <c r="BC235">
+        <v>11</v>
+      </c>
+      <c r="BD235">
+        <v>2.3</v>
+      </c>
+      <c r="BE235">
+        <v>6.25</v>
+      </c>
+      <c r="BF235">
+        <v>1.76</v>
+      </c>
+      <c r="BG235">
+        <v>1.35</v>
+      </c>
+      <c r="BH235">
+        <v>2.9</v>
+      </c>
+      <c r="BI235">
+        <v>1.58</v>
+      </c>
+      <c r="BJ235">
+        <v>2.18</v>
+      </c>
+      <c r="BK235">
+        <v>2</v>
+      </c>
+      <c r="BL235">
+        <v>1.73</v>
+      </c>
+      <c r="BM235">
+        <v>2.48</v>
+      </c>
+      <c r="BN235">
+        <v>1.46</v>
+      </c>
+      <c r="BO235">
+        <v>3.2</v>
+      </c>
+      <c r="BP235">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="373">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,12 @@
     <t>['55', '60', '73', '89']</t>
   </si>
   <si>
+    <t>['29', '51', '68']</t>
+  </si>
+  <si>
+    <t>['55', '73']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1124,6 +1130,9 @@
   </si>
   <si>
     <t>['62', '90+6']</t>
+  </si>
+  <si>
+    <t>['43', '50', '53', '62', '66', '90']</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1741,7 +1750,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1822,7 +1831,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ2">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2028,7 +2037,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ3">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2153,7 +2162,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2231,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ4">
         <v>1.31</v>
@@ -2437,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ5">
         <v>0.23</v>
@@ -2565,7 +2574,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2646,7 +2655,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2771,7 +2780,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3801,7 +3810,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4213,7 +4222,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4291,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ14">
         <v>1.08</v>
@@ -4625,7 +4634,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5243,7 +5252,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5449,7 +5458,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5861,7 +5870,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6067,7 +6076,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6148,7 +6157,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ23">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR23">
         <v>1.52</v>
@@ -6273,7 +6282,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6351,7 +6360,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ24">
         <v>1.69</v>
@@ -6479,7 +6488,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6560,7 +6569,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ25">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6891,7 +6900,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6969,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ27">
         <v>0.58</v>
@@ -7097,7 +7106,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7178,7 +7187,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ28">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7381,7 +7390,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ29">
         <v>1.31</v>
@@ -7590,7 +7599,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ30">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -7715,7 +7724,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8333,7 +8342,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8539,7 +8548,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9363,7 +9372,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9569,7 +9578,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9853,10 +9862,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ41">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -10059,7 +10068,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ42">
         <v>1.08</v>
@@ -10393,7 +10402,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10599,7 +10608,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10805,7 +10814,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10886,7 +10895,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR46">
         <v>1.4</v>
@@ -11217,7 +11226,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11504,7 +11513,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ49">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11629,7 +11638,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11835,7 +11844,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11913,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ51">
         <v>0.25</v>
@@ -12041,7 +12050,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12247,7 +12256,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12453,7 +12462,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12740,7 +12749,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ55">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR55">
         <v>1.26</v>
@@ -13071,7 +13080,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13149,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ57">
         <v>0.6899999999999999</v>
@@ -13483,7 +13492,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -14101,7 +14110,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14307,7 +14316,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14385,7 +14394,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ63">
         <v>0.25</v>
@@ -14513,7 +14522,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14594,7 +14603,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ64">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -14797,7 +14806,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ65">
         <v>1.31</v>
@@ -15131,7 +15140,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15209,7 +15218,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ67">
         <v>1.69</v>
@@ -15337,7 +15346,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15543,7 +15552,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15749,7 +15758,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15955,7 +15964,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16036,7 +16045,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ71">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -16161,7 +16170,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16367,7 +16376,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16448,7 +16457,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ73">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16779,7 +16788,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16985,7 +16994,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17063,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17191,7 +17200,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17397,7 +17406,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17603,7 +17612,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -18221,7 +18230,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18302,7 +18311,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ82">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18505,7 +18514,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ83">
         <v>1.23</v>
@@ -19045,7 +19054,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19126,7 +19135,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ86">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19329,7 +19338,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ87">
         <v>1.29</v>
@@ -20075,7 +20084,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20156,7 +20165,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ91">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -20281,7 +20290,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20487,7 +20496,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20693,7 +20702,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20899,7 +20908,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20980,7 +20989,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ95">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -21105,7 +21114,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21311,7 +21320,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21723,7 +21732,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22135,7 +22144,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22213,7 +22222,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22547,7 +22556,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22628,7 +22637,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ103">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR103">
         <v>1.68</v>
@@ -22831,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ104">
         <v>0.25</v>
@@ -23037,7 +23046,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ105">
         <v>1.36</v>
@@ -23577,7 +23586,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23783,7 +23792,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23989,7 +23998,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24067,7 +24076,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ110">
         <v>1.69</v>
@@ -24813,7 +24822,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25019,7 +25028,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25431,7 +25440,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25512,7 +25521,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -25637,7 +25646,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26130,7 +26139,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26333,7 +26342,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ121">
         <v>1.38</v>
@@ -26461,7 +26470,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26667,7 +26676,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27491,7 +27500,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27569,10 +27578,10 @@
         <v>2.57</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ127">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR127">
         <v>1.3</v>
@@ -27903,7 +27912,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28109,7 +28118,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28393,7 +28402,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28521,7 +28530,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28602,7 +28611,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ132">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28727,7 +28736,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29551,7 +29560,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29629,10 +29638,10 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ137">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29757,7 +29766,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29963,7 +29972,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30041,7 +30050,7 @@
         <v>1.57</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30169,7 +30178,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -31405,7 +31414,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31817,7 +31826,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -32023,7 +32032,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32101,10 +32110,10 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ149">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32229,7 +32238,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32310,7 +32319,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ150">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR150">
         <v>1.57</v>
@@ -32435,7 +32444,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32641,7 +32650,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32847,7 +32856,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33546,7 +33555,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ156">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33671,7 +33680,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33752,7 +33761,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ157">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR157">
         <v>1.67</v>
@@ -33877,7 +33886,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34367,7 +34376,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160">
         <v>0.85</v>
@@ -34779,7 +34788,7 @@
         <v>0.75</v>
       </c>
       <c r="AP162">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ162">
         <v>1.08</v>
@@ -34907,7 +34916,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35319,7 +35328,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35397,7 +35406,7 @@
         <v>0.13</v>
       </c>
       <c r="AP165">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ165">
         <v>0.58</v>
@@ -35731,7 +35740,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35937,7 +35946,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36349,7 +36358,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36842,7 +36851,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ172">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR172">
         <v>1.58</v>
@@ -36967,7 +36976,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37173,7 +37182,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37254,7 +37263,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ174">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR174">
         <v>1.46</v>
@@ -37379,7 +37388,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37457,7 +37466,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ175">
         <v>0.6899999999999999</v>
@@ -37791,7 +37800,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37872,7 +37881,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ177">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR177">
         <v>1.51</v>
@@ -38409,7 +38418,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38487,7 +38496,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ180">
         <v>0.85</v>
@@ -38615,7 +38624,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38821,7 +38830,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39439,7 +39448,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39645,7 +39654,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39723,7 +39732,7 @@
         <v>0.11</v>
       </c>
       <c r="AP186">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ186">
         <v>0.58</v>
@@ -40057,7 +40066,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40469,7 +40478,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40550,7 +40559,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ190">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40675,7 +40684,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40881,7 +40890,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41165,7 +41174,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ193">
         <v>0.85</v>
@@ -41293,7 +41302,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41374,7 +41383,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ194">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41499,7 +41508,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41705,7 +41714,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41989,7 +41998,7 @@
         <v>1.2</v>
       </c>
       <c r="AP197">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ197">
         <v>1.23</v>
@@ -42117,7 +42126,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42198,7 +42207,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ198">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR198">
         <v>1.12</v>
@@ -42323,7 +42332,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42941,7 +42950,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43019,7 +43028,7 @@
         <v>1.36</v>
       </c>
       <c r="AP202">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ202">
         <v>1.23</v>
@@ -43228,7 +43237,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ203">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR203">
         <v>1.31</v>
@@ -43971,7 +43980,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44177,7 +44186,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44258,7 +44267,7 @@
         <v>2</v>
       </c>
       <c r="AQ208">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR208">
         <v>1.74</v>
@@ -44461,7 +44470,7 @@
         <v>1.09</v>
       </c>
       <c r="AP209">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ209">
         <v>1</v>
@@ -44589,7 +44598,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44667,10 +44676,10 @@
         <v>1.33</v>
       </c>
       <c r="AP210">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR210">
         <v>1.39</v>
@@ -44795,7 +44804,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45207,7 +45216,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45413,7 +45422,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45619,7 +45628,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -46443,7 +46452,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46524,7 +46533,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ219">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AR219">
         <v>1.62</v>
@@ -46855,7 +46864,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47267,7 +47276,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47473,7 +47482,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47551,7 +47560,7 @@
         <v>0.45</v>
       </c>
       <c r="AP224">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ224">
         <v>0.6899999999999999</v>
@@ -47885,7 +47894,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48091,7 +48100,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48503,7 +48512,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48915,7 +48924,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49327,7 +49336,7 @@
         <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q233">
         <v>3</v>
@@ -49614,7 +49623,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ234">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR234">
         <v>2.39</v>
@@ -49739,7 +49748,7 @@
         <v>249</v>
       </c>
       <c r="P235" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q235">
         <v>3.2</v>
@@ -49896,6 +49905,624 @@
       </c>
       <c r="BP235">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7468595</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45745.54166666666</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>72</v>
+      </c>
+      <c r="H236" t="s">
+        <v>87</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>3</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>4</v>
+      </c>
+      <c r="O236" t="s">
+        <v>250</v>
+      </c>
+      <c r="P236" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q236">
+        <v>5.5</v>
+      </c>
+      <c r="R236">
+        <v>2.38</v>
+      </c>
+      <c r="S236">
+        <v>2.1</v>
+      </c>
+      <c r="T236">
+        <v>1.33</v>
+      </c>
+      <c r="U236">
+        <v>3.25</v>
+      </c>
+      <c r="V236">
+        <v>2.63</v>
+      </c>
+      <c r="W236">
+        <v>1.44</v>
+      </c>
+      <c r="X236">
+        <v>6.5</v>
+      </c>
+      <c r="Y236">
+        <v>1.11</v>
+      </c>
+      <c r="Z236">
+        <v>5.6</v>
+      </c>
+      <c r="AA236">
+        <v>4.1</v>
+      </c>
+      <c r="AB236">
+        <v>1.62</v>
+      </c>
+      <c r="AC236">
+        <v>1.04</v>
+      </c>
+      <c r="AD236">
+        <v>10</v>
+      </c>
+      <c r="AE236">
+        <v>1.22</v>
+      </c>
+      <c r="AF236">
+        <v>4</v>
+      </c>
+      <c r="AG236">
+        <v>1.81</v>
+      </c>
+      <c r="AH236">
+        <v>2.01</v>
+      </c>
+      <c r="AI236">
+        <v>1.75</v>
+      </c>
+      <c r="AJ236">
+        <v>2</v>
+      </c>
+      <c r="AK236">
+        <v>2.25</v>
+      </c>
+      <c r="AL236">
+        <v>1.23</v>
+      </c>
+      <c r="AM236">
+        <v>1.16</v>
+      </c>
+      <c r="AN236">
+        <v>0.77</v>
+      </c>
+      <c r="AO236">
+        <v>2.08</v>
+      </c>
+      <c r="AP236">
+        <v>0.93</v>
+      </c>
+      <c r="AQ236">
+        <v>1.93</v>
+      </c>
+      <c r="AR236">
+        <v>1.35</v>
+      </c>
+      <c r="AS236">
+        <v>1.47</v>
+      </c>
+      <c r="AT236">
+        <v>2.82</v>
+      </c>
+      <c r="AU236">
+        <v>6</v>
+      </c>
+      <c r="AV236">
+        <v>7</v>
+      </c>
+      <c r="AW236">
+        <v>2</v>
+      </c>
+      <c r="AX236">
+        <v>13</v>
+      </c>
+      <c r="AY236">
+        <v>8</v>
+      </c>
+      <c r="AZ236">
+        <v>23</v>
+      </c>
+      <c r="BA236">
+        <v>0</v>
+      </c>
+      <c r="BB236">
+        <v>12</v>
+      </c>
+      <c r="BC236">
+        <v>12</v>
+      </c>
+      <c r="BD236">
+        <v>3.7</v>
+      </c>
+      <c r="BE236">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF236">
+        <v>1.41</v>
+      </c>
+      <c r="BG236">
+        <v>1.28</v>
+      </c>
+      <c r="BH236">
+        <v>3.08</v>
+      </c>
+      <c r="BI236">
+        <v>1.67</v>
+      </c>
+      <c r="BJ236">
+        <v>2.1</v>
+      </c>
+      <c r="BK236">
+        <v>1.95</v>
+      </c>
+      <c r="BL236">
+        <v>1.76</v>
+      </c>
+      <c r="BM236">
+        <v>2.54</v>
+      </c>
+      <c r="BN236">
+        <v>1.43</v>
+      </c>
+      <c r="BO236">
+        <v>3.42</v>
+      </c>
+      <c r="BP236">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7468594</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45745.625</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>82</v>
+      </c>
+      <c r="H237" t="s">
+        <v>79</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>2</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>6</v>
+      </c>
+      <c r="N237">
+        <v>7</v>
+      </c>
+      <c r="O237" t="s">
+        <v>119</v>
+      </c>
+      <c r="P237" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q237">
+        <v>10</v>
+      </c>
+      <c r="R237">
+        <v>3.5</v>
+      </c>
+      <c r="S237">
+        <v>1.44</v>
+      </c>
+      <c r="T237">
+        <v>1.14</v>
+      </c>
+      <c r="U237">
+        <v>5.5</v>
+      </c>
+      <c r="V237">
+        <v>1.73</v>
+      </c>
+      <c r="W237">
+        <v>2</v>
+      </c>
+      <c r="X237">
+        <v>3.25</v>
+      </c>
+      <c r="Y237">
+        <v>1.33</v>
+      </c>
+      <c r="Z237">
+        <v>13</v>
+      </c>
+      <c r="AA237">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AB237">
+        <v>1.18</v>
+      </c>
+      <c r="AC237">
+        <v>1.01</v>
+      </c>
+      <c r="AD237">
+        <v>41</v>
+      </c>
+      <c r="AE237">
+        <v>1.06</v>
+      </c>
+      <c r="AF237">
+        <v>8.5</v>
+      </c>
+      <c r="AG237">
+        <v>1.23</v>
+      </c>
+      <c r="AH237">
+        <v>3.9</v>
+      </c>
+      <c r="AI237">
+        <v>1.7</v>
+      </c>
+      <c r="AJ237">
+        <v>2.05</v>
+      </c>
+      <c r="AK237">
+        <v>5.5</v>
+      </c>
+      <c r="AL237">
+        <v>1.07</v>
+      </c>
+      <c r="AM237">
+        <v>1.03</v>
+      </c>
+      <c r="AN237">
+        <v>1.42</v>
+      </c>
+      <c r="AO237">
+        <v>2.54</v>
+      </c>
+      <c r="AP237">
+        <v>1.31</v>
+      </c>
+      <c r="AQ237">
+        <v>2.57</v>
+      </c>
+      <c r="AR237">
+        <v>1.42</v>
+      </c>
+      <c r="AS237">
+        <v>2.16</v>
+      </c>
+      <c r="AT237">
+        <v>3.58</v>
+      </c>
+      <c r="AU237">
+        <v>3</v>
+      </c>
+      <c r="AV237">
+        <v>11</v>
+      </c>
+      <c r="AW237">
+        <v>9</v>
+      </c>
+      <c r="AX237">
+        <v>12</v>
+      </c>
+      <c r="AY237">
+        <v>17</v>
+      </c>
+      <c r="AZ237">
+        <v>27</v>
+      </c>
+      <c r="BA237">
+        <v>3</v>
+      </c>
+      <c r="BB237">
+        <v>6</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BE237">
+        <v>14.5</v>
+      </c>
+      <c r="BF237">
+        <v>1.1</v>
+      </c>
+      <c r="BG237">
+        <v>1.26</v>
+      </c>
+      <c r="BH237">
+        <v>3.22</v>
+      </c>
+      <c r="BI237">
+        <v>1.5</v>
+      </c>
+      <c r="BJ237">
+        <v>2.35</v>
+      </c>
+      <c r="BK237">
+        <v>1.85</v>
+      </c>
+      <c r="BL237">
+        <v>1.85</v>
+      </c>
+      <c r="BM237">
+        <v>2.4</v>
+      </c>
+      <c r="BN237">
+        <v>1.48</v>
+      </c>
+      <c r="BO237">
+        <v>3.2</v>
+      </c>
+      <c r="BP237">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7468597</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.71180555555</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>73</v>
+      </c>
+      <c r="H238" t="s">
+        <v>86</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>2</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>3</v>
+      </c>
+      <c r="O238" t="s">
+        <v>251</v>
+      </c>
+      <c r="P238" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q238">
+        <v>2.4</v>
+      </c>
+      <c r="R238">
+        <v>2.38</v>
+      </c>
+      <c r="S238">
+        <v>4</v>
+      </c>
+      <c r="T238">
+        <v>1.3</v>
+      </c>
+      <c r="U238">
+        <v>3.4</v>
+      </c>
+      <c r="V238">
+        <v>2.38</v>
+      </c>
+      <c r="W238">
+        <v>1.53</v>
+      </c>
+      <c r="X238">
+        <v>6</v>
+      </c>
+      <c r="Y238">
+        <v>1.13</v>
+      </c>
+      <c r="Z238">
+        <v>1.9</v>
+      </c>
+      <c r="AA238">
+        <v>3.93</v>
+      </c>
+      <c r="AB238">
+        <v>3.93</v>
+      </c>
+      <c r="AC238">
+        <v>1.04</v>
+      </c>
+      <c r="AD238">
+        <v>10</v>
+      </c>
+      <c r="AE238">
+        <v>1.18</v>
+      </c>
+      <c r="AF238">
+        <v>4.75</v>
+      </c>
+      <c r="AG238">
+        <v>1.77</v>
+      </c>
+      <c r="AH238">
+        <v>2.05</v>
+      </c>
+      <c r="AI238">
+        <v>1.57</v>
+      </c>
+      <c r="AJ238">
+        <v>2.25</v>
+      </c>
+      <c r="AK238">
+        <v>1.26</v>
+      </c>
+      <c r="AL238">
+        <v>1.25</v>
+      </c>
+      <c r="AM238">
+        <v>1.9</v>
+      </c>
+      <c r="AN238">
+        <v>2.23</v>
+      </c>
+      <c r="AO238">
+        <v>1.46</v>
+      </c>
+      <c r="AP238">
+        <v>2.29</v>
+      </c>
+      <c r="AQ238">
+        <v>1.36</v>
+      </c>
+      <c r="AR238">
+        <v>1.79</v>
+      </c>
+      <c r="AS238">
+        <v>1.52</v>
+      </c>
+      <c r="AT238">
+        <v>3.31</v>
+      </c>
+      <c r="AU238">
+        <v>8</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>10</v>
+      </c>
+      <c r="AX238">
+        <v>5</v>
+      </c>
+      <c r="AY238">
+        <v>21</v>
+      </c>
+      <c r="AZ238">
+        <v>11</v>
+      </c>
+      <c r="BA238">
+        <v>7</v>
+      </c>
+      <c r="BB238">
+        <v>4</v>
+      </c>
+      <c r="BC238">
+        <v>11</v>
+      </c>
+      <c r="BD238">
+        <v>1.61</v>
+      </c>
+      <c r="BE238">
+        <v>6.5</v>
+      </c>
+      <c r="BF238">
+        <v>2.55</v>
+      </c>
+      <c r="BG238">
+        <v>1.32</v>
+      </c>
+      <c r="BH238">
+        <v>3</v>
+      </c>
+      <c r="BI238">
+        <v>1.56</v>
+      </c>
+      <c r="BJ238">
+        <v>2.23</v>
+      </c>
+      <c r="BK238">
+        <v>1.85</v>
+      </c>
+      <c r="BL238">
+        <v>1.85</v>
+      </c>
+      <c r="BM238">
+        <v>2.43</v>
+      </c>
+      <c r="BN238">
+        <v>1.47</v>
+      </c>
+      <c r="BO238">
+        <v>3.15</v>
+      </c>
+      <c r="BP238">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,18 @@
     <t>['55', '73']</t>
   </si>
   <si>
+    <t>['65', '78']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['13', '27', '88']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -947,9 +959,6 @@
   </si>
   <si>
     <t>['3', '74']</t>
-  </si>
-  <si>
-    <t>['19']</t>
   </si>
   <si>
     <t>['23', '61']</t>
@@ -1133,6 +1142,15 @@
   </si>
   <si>
     <t>['43', '50', '53', '62', '66', '90']</t>
+  </si>
+  <si>
+    <t>['22', '26', '62', '90']</t>
+  </si>
+  <si>
+    <t>['23', '48']</t>
+  </si>
+  <si>
+    <t>['13', '70', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1750,7 +1768,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1828,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ2">
         <v>2.57</v>
@@ -1956,7 +1974,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2162,7 +2180,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2574,7 +2592,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2652,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
         <v>1.36</v>
@@ -2780,7 +2798,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3064,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3270,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3685,7 +3703,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ11">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3810,7 +3828,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4094,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ13">
         <v>1.23</v>
@@ -4222,7 +4240,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4509,7 +4527,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4634,7 +4652,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4715,7 +4733,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ16">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5252,7 +5270,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5458,7 +5476,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5870,7 +5888,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5951,7 +5969,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ22">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -6076,7 +6094,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6154,7 +6172,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23">
         <v>1.93</v>
@@ -6282,7 +6300,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6363,7 +6381,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ24">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -6488,7 +6506,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6566,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ25">
         <v>1.36</v>
@@ -6772,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ26">
         <v>0.6899999999999999</v>
@@ -6900,7 +6918,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6981,7 +6999,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ27">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR27">
         <v>0.32</v>
@@ -7106,7 +7124,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7184,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ28">
         <v>2.57</v>
@@ -7724,7 +7742,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7802,7 +7820,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ31">
         <v>1.38</v>
@@ -8011,7 +8029,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>2.81</v>
@@ -8217,7 +8235,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ33">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR33">
         <v>2.21</v>
@@ -8342,7 +8360,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8548,7 +8566,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8832,7 +8850,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36">
         <v>1.08</v>
@@ -9372,7 +9390,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9450,7 +9468,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ39">
         <v>1.29</v>
@@ -9578,7 +9596,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9659,7 +9677,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ40">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -10402,7 +10420,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10480,10 +10498,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ44">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10608,7 +10626,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10814,7 +10832,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11098,10 +11116,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>1.61</v>
@@ -11226,7 +11244,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11307,7 +11325,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ48">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR48">
         <v>2.56</v>
@@ -11638,7 +11656,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11716,7 +11734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ50">
         <v>1.31</v>
@@ -11844,7 +11862,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11925,7 +11943,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ51">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -12050,7 +12068,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12128,7 +12146,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>1.36</v>
@@ -12256,7 +12274,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12462,7 +12480,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12540,7 +12558,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -13080,7 +13098,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13364,7 +13382,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ58">
         <v>1.38</v>
@@ -13492,7 +13510,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13779,7 +13797,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -14110,7 +14128,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14191,7 +14209,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ62">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14316,7 +14334,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14397,7 +14415,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ63">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR63">
         <v>0.8100000000000001</v>
@@ -14522,7 +14540,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15015,7 +15033,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ66">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15140,7 +15158,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15221,7 +15239,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ67">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -15346,7 +15364,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15552,7 +15570,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15630,7 +15648,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ69">
         <v>1.36</v>
@@ -15758,7 +15776,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15836,7 +15854,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70">
         <v>1.23</v>
@@ -15964,7 +15982,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16170,7 +16188,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16248,7 +16266,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -16376,7 +16394,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16788,7 +16806,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16866,7 +16884,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ75">
         <v>0.23</v>
@@ -16994,7 +17012,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17075,7 +17093,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
         <v>1.01</v>
@@ -17200,7 +17218,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17406,7 +17424,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17612,7 +17630,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17899,7 +17917,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ80">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -18230,7 +18248,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18720,7 +18738,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ84">
         <v>1.36</v>
@@ -18929,7 +18947,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ85">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -19054,7 +19072,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19544,7 +19562,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19750,10 +19768,10 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ89">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR89">
         <v>1.39</v>
@@ -19956,10 +19974,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ90">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR90">
         <v>1.17</v>
@@ -20084,7 +20102,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20290,7 +20308,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20496,7 +20514,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20702,7 +20720,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20783,7 +20801,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ94">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -20908,7 +20926,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20986,7 +21004,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ95">
         <v>2.57</v>
@@ -21114,7 +21132,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21320,7 +21338,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21607,7 +21625,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR98">
         <v>1.3</v>
@@ -21732,7 +21750,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21810,7 +21828,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -22144,7 +22162,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22225,7 +22243,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -22556,7 +22574,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22843,7 +22861,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ104">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23252,10 +23270,10 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ106">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR106">
         <v>1.43</v>
@@ -23458,7 +23476,7 @@
         <v>1.2</v>
       </c>
       <c r="AP107">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ107">
         <v>1.23</v>
@@ -23586,7 +23604,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23792,7 +23810,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23998,7 +24016,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24079,7 +24097,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ110">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24697,7 +24715,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ113">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24822,7 +24840,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25028,7 +25046,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25106,7 +25124,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ115">
         <v>1.23</v>
@@ -25312,7 +25330,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ116">
         <v>0.6899999999999999</v>
@@ -25440,7 +25458,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25646,7 +25664,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25930,10 +25948,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR119">
         <v>1.36</v>
@@ -26136,7 +26154,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ120">
         <v>2.57</v>
@@ -26470,7 +26488,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26676,7 +26694,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26754,7 +26772,7 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ123">
         <v>1.36</v>
@@ -26963,7 +26981,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ124">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR124">
         <v>1.73</v>
@@ -27375,7 +27393,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ126">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR126">
         <v>1.51</v>
@@ -27500,7 +27518,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27784,7 +27802,7 @@
         <v>0.14</v>
       </c>
       <c r="AP128">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ128">
         <v>0.23</v>
@@ -27912,7 +27930,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28118,7 +28136,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28196,10 +28214,10 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ130">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28530,7 +28548,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28736,7 +28754,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28814,7 +28832,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ133">
         <v>1.29</v>
@@ -29023,7 +29041,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ134">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29560,7 +29578,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29766,7 +29784,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29847,7 +29865,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ138">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR138">
         <v>1.63</v>
@@ -29972,7 +29990,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30178,7 +30196,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30256,10 +30274,10 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ140">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -30465,7 +30483,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -31080,10 +31098,10 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR144">
         <v>1.26</v>
@@ -31414,7 +31432,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31698,7 +31716,7 @@
         <v>1.63</v>
       </c>
       <c r="AP147">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ147">
         <v>1.31</v>
@@ -31826,7 +31844,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -32032,7 +32050,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32238,7 +32256,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32444,7 +32462,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32522,10 +32540,10 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ151">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR151">
         <v>1.15</v>
@@ -32650,7 +32668,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32856,7 +32874,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32934,7 +32952,7 @@
         <v>0.63</v>
       </c>
       <c r="AP153">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ153">
         <v>1.29</v>
@@ -33552,7 +33570,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ156">
         <v>1.36</v>
@@ -33680,7 +33698,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33886,7 +33904,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33967,7 +33985,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR158">
         <v>1.48</v>
@@ -34379,7 +34397,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ160">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34582,7 +34600,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ161">
         <v>0.6899999999999999</v>
@@ -34916,7 +34934,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35200,7 +35218,7 @@
         <v>0.11</v>
       </c>
       <c r="AP164">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ164">
         <v>0.23</v>
@@ -35328,7 +35346,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35409,7 +35427,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ165">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR165">
         <v>1.5</v>
@@ -35740,7 +35758,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35946,7 +35964,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36024,10 +36042,10 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR168">
         <v>1.13</v>
@@ -36358,7 +36376,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36436,10 +36454,10 @@
         <v>0</v>
       </c>
       <c r="AP170">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ170">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR170">
         <v>1.48</v>
@@ -36976,7 +36994,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37057,7 +37075,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ173">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37182,7 +37200,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37388,7 +37406,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37672,7 +37690,7 @@
         <v>0.2</v>
       </c>
       <c r="AP176">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ176">
         <v>0.23</v>
@@ -37800,7 +37818,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -37878,7 +37896,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ177">
         <v>1.36</v>
@@ -38290,7 +38308,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ179">
         <v>1.08</v>
@@ -38418,7 +38436,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38499,7 +38517,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ180">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR180">
         <v>1.22</v>
@@ -38624,7 +38642,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38830,7 +38848,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -38911,7 +38929,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39323,7 +39341,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ184">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR184">
         <v>1.58</v>
@@ -39448,7 +39466,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39526,7 +39544,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ185">
         <v>1.08</v>
@@ -39654,7 +39672,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39735,7 +39753,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ186">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR186">
         <v>1.27</v>
@@ -40066,7 +40084,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40144,7 +40162,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40353,7 +40371,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ189">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR189">
         <v>1.26</v>
@@ -40478,7 +40496,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40556,7 +40574,7 @@
         <v>2.4</v>
       </c>
       <c r="AP190">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ190">
         <v>1.93</v>
@@ -40684,7 +40702,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40890,7 +40908,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41177,7 +41195,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ193">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -41302,7 +41320,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41380,7 +41398,7 @@
         <v>2.4</v>
       </c>
       <c r="AP194">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ194">
         <v>2.57</v>
@@ -41508,7 +41526,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41714,7 +41732,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42126,7 +42144,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42204,7 +42222,7 @@
         <v>1.18</v>
       </c>
       <c r="AP198">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ198">
         <v>1.36</v>
@@ -42332,7 +42350,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42822,7 +42840,7 @@
         <v>1.4</v>
       </c>
       <c r="AP201">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ201">
         <v>1.38</v>
@@ -42950,7 +42968,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43234,7 +43252,7 @@
         <v>2.45</v>
       </c>
       <c r="AP203">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ203">
         <v>1.93</v>
@@ -43443,7 +43461,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ204">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR204">
         <v>1.42</v>
@@ -43649,7 +43667,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ205">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR205">
         <v>1.64</v>
@@ -43855,7 +43873,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR206">
         <v>1.37</v>
@@ -43980,7 +43998,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44058,7 +44076,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ207">
         <v>1.38</v>
@@ -44186,7 +44204,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44598,7 +44616,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44804,7 +44822,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45216,7 +45234,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45297,7 +45315,7 @@
         <v>2</v>
       </c>
       <c r="AQ213">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR213">
         <v>1.74</v>
@@ -45422,7 +45440,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45500,7 +45518,7 @@
         <v>1.36</v>
       </c>
       <c r="AP214">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ214">
         <v>1.38</v>
@@ -45628,7 +45646,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45709,7 +45727,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ215">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR215">
         <v>1.47</v>
@@ -45912,7 +45930,7 @@
         <v>1</v>
       </c>
       <c r="AP216">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ216">
         <v>1.29</v>
@@ -46121,7 +46139,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ217">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR217">
         <v>1.76</v>
@@ -46324,7 +46342,7 @@
         <v>1.27</v>
       </c>
       <c r="AP218">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ218">
         <v>1.38</v>
@@ -46452,7 +46470,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46736,10 +46754,10 @@
         <v>0.27</v>
       </c>
       <c r="AP220">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ220">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR220">
         <v>1.6</v>
@@ -46864,7 +46882,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -46945,7 +46963,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ221">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR221">
         <v>1.82</v>
@@ -47276,7 +47294,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47482,7 +47500,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47766,7 +47784,7 @@
         <v>0.17</v>
       </c>
       <c r="AP225">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AQ225">
         <v>0.23</v>
@@ -47894,7 +47912,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48100,7 +48118,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48512,7 +48530,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48590,7 +48608,7 @@
         <v>1.25</v>
       </c>
       <c r="AP229">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ229">
         <v>1.38</v>
@@ -48799,7 +48817,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ230">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR230">
         <v>1.69</v>
@@ -48924,7 +48942,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49336,7 +49354,7 @@
         <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q233">
         <v>3</v>
@@ -49748,7 +49766,7 @@
         <v>249</v>
       </c>
       <c r="P235" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q235">
         <v>3.2</v>
@@ -50068,10 +50086,10 @@
         <v>0</v>
       </c>
       <c r="BB236">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC236">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD236">
         <v>3.7</v>
@@ -50160,7 +50178,7 @@
         <v>119</v>
       </c>
       <c r="P237" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q237">
         <v>10</v>
@@ -50366,7 +50384,7 @@
         <v>251</v>
       </c>
       <c r="P238" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q238">
         <v>2.4</v>
@@ -50523,6 +50541,1036 @@
       </c>
       <c r="BP238">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7468593</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>76</v>
+      </c>
+      <c r="H239" t="s">
+        <v>71</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+      <c r="L239">
+        <v>2</v>
+      </c>
+      <c r="M239">
+        <v>4</v>
+      </c>
+      <c r="N239">
+        <v>6</v>
+      </c>
+      <c r="O239" t="s">
+        <v>252</v>
+      </c>
+      <c r="P239" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q239">
+        <v>2.75</v>
+      </c>
+      <c r="R239">
+        <v>2.05</v>
+      </c>
+      <c r="S239">
+        <v>4.33</v>
+      </c>
+      <c r="T239">
+        <v>1.44</v>
+      </c>
+      <c r="U239">
+        <v>2.63</v>
+      </c>
+      <c r="V239">
+        <v>3.25</v>
+      </c>
+      <c r="W239">
+        <v>1.33</v>
+      </c>
+      <c r="X239">
+        <v>10</v>
+      </c>
+      <c r="Y239">
+        <v>1.06</v>
+      </c>
+      <c r="Z239">
+        <v>2.02</v>
+      </c>
+      <c r="AA239">
+        <v>3.36</v>
+      </c>
+      <c r="AB239">
+        <v>4.1</v>
+      </c>
+      <c r="AC239">
+        <v>1.07</v>
+      </c>
+      <c r="AD239">
+        <v>8</v>
+      </c>
+      <c r="AE239">
+        <v>1.38</v>
+      </c>
+      <c r="AF239">
+        <v>3</v>
+      </c>
+      <c r="AG239">
+        <v>2.05</v>
+      </c>
+      <c r="AH239">
+        <v>1.7</v>
+      </c>
+      <c r="AI239">
+        <v>1.91</v>
+      </c>
+      <c r="AJ239">
+        <v>1.91</v>
+      </c>
+      <c r="AK239">
+        <v>1.27</v>
+      </c>
+      <c r="AL239">
+        <v>1.3</v>
+      </c>
+      <c r="AM239">
+        <v>1.77</v>
+      </c>
+      <c r="AN239">
+        <v>1.23</v>
+      </c>
+      <c r="AO239">
+        <v>1</v>
+      </c>
+      <c r="AP239">
+        <v>1.14</v>
+      </c>
+      <c r="AQ239">
+        <v>1.14</v>
+      </c>
+      <c r="AR239">
+        <v>1.5</v>
+      </c>
+      <c r="AS239">
+        <v>1.44</v>
+      </c>
+      <c r="AT239">
+        <v>2.94</v>
+      </c>
+      <c r="AU239">
+        <v>6</v>
+      </c>
+      <c r="AV239">
+        <v>6</v>
+      </c>
+      <c r="AW239">
+        <v>10</v>
+      </c>
+      <c r="AX239">
+        <v>2</v>
+      </c>
+      <c r="AY239">
+        <v>19</v>
+      </c>
+      <c r="AZ239">
+        <v>8</v>
+      </c>
+      <c r="BA239">
+        <v>10</v>
+      </c>
+      <c r="BB239">
+        <v>3</v>
+      </c>
+      <c r="BC239">
+        <v>13</v>
+      </c>
+      <c r="BD239">
+        <v>1.72</v>
+      </c>
+      <c r="BE239">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF239">
+        <v>2.59</v>
+      </c>
+      <c r="BG239">
+        <v>1.38</v>
+      </c>
+      <c r="BH239">
+        <v>2.71</v>
+      </c>
+      <c r="BI239">
+        <v>1.73</v>
+      </c>
+      <c r="BJ239">
+        <v>2</v>
+      </c>
+      <c r="BK239">
+        <v>2.17</v>
+      </c>
+      <c r="BL239">
+        <v>1.58</v>
+      </c>
+      <c r="BM239">
+        <v>2.88</v>
+      </c>
+      <c r="BN239">
+        <v>1.32</v>
+      </c>
+      <c r="BO239">
+        <v>4.1</v>
+      </c>
+      <c r="BP239">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7468590</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45746.51041666666</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>74</v>
+      </c>
+      <c r="H240" t="s">
+        <v>75</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>1</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>1</v>
+      </c>
+      <c r="O240" t="s">
+        <v>253</v>
+      </c>
+      <c r="P240" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q240">
+        <v>2.38</v>
+      </c>
+      <c r="R240">
+        <v>2.3</v>
+      </c>
+      <c r="S240">
+        <v>4.5</v>
+      </c>
+      <c r="T240">
+        <v>1.33</v>
+      </c>
+      <c r="U240">
+        <v>3.25</v>
+      </c>
+      <c r="V240">
+        <v>2.63</v>
+      </c>
+      <c r="W240">
+        <v>1.44</v>
+      </c>
+      <c r="X240">
+        <v>6.5</v>
+      </c>
+      <c r="Y240">
+        <v>1.11</v>
+      </c>
+      <c r="Z240">
+        <v>1.83</v>
+      </c>
+      <c r="AA240">
+        <v>3.87</v>
+      </c>
+      <c r="AB240">
+        <v>4.33</v>
+      </c>
+      <c r="AC240">
+        <v>1.04</v>
+      </c>
+      <c r="AD240">
+        <v>10</v>
+      </c>
+      <c r="AE240">
+        <v>1.22</v>
+      </c>
+      <c r="AF240">
+        <v>4</v>
+      </c>
+      <c r="AG240">
+        <v>1.73</v>
+      </c>
+      <c r="AH240">
+        <v>2</v>
+      </c>
+      <c r="AI240">
+        <v>1.7</v>
+      </c>
+      <c r="AJ240">
+        <v>2.05</v>
+      </c>
+      <c r="AK240">
+        <v>1.23</v>
+      </c>
+      <c r="AL240">
+        <v>1.26</v>
+      </c>
+      <c r="AM240">
+        <v>1.95</v>
+      </c>
+      <c r="AN240">
+        <v>1.77</v>
+      </c>
+      <c r="AO240">
+        <v>0.25</v>
+      </c>
+      <c r="AP240">
+        <v>1.86</v>
+      </c>
+      <c r="AQ240">
+        <v>0.23</v>
+      </c>
+      <c r="AR240">
+        <v>1.36</v>
+      </c>
+      <c r="AS240">
+        <v>1.2</v>
+      </c>
+      <c r="AT240">
+        <v>2.56</v>
+      </c>
+      <c r="AU240">
+        <v>7</v>
+      </c>
+      <c r="AV240">
+        <v>2</v>
+      </c>
+      <c r="AW240">
+        <v>15</v>
+      </c>
+      <c r="AX240">
+        <v>11</v>
+      </c>
+      <c r="AY240">
+        <v>28</v>
+      </c>
+      <c r="AZ240">
+        <v>17</v>
+      </c>
+      <c r="BA240">
+        <v>10</v>
+      </c>
+      <c r="BB240">
+        <v>6</v>
+      </c>
+      <c r="BC240">
+        <v>16</v>
+      </c>
+      <c r="BD240">
+        <v>1.71</v>
+      </c>
+      <c r="BE240">
+        <v>6.4</v>
+      </c>
+      <c r="BF240">
+        <v>2.4</v>
+      </c>
+      <c r="BG240">
+        <v>1.37</v>
+      </c>
+      <c r="BH240">
+        <v>2.8</v>
+      </c>
+      <c r="BI240">
+        <v>1.64</v>
+      </c>
+      <c r="BJ240">
+        <v>2.1</v>
+      </c>
+      <c r="BK240">
+        <v>1.85</v>
+      </c>
+      <c r="BL240">
+        <v>1.85</v>
+      </c>
+      <c r="BM240">
+        <v>2.55</v>
+      </c>
+      <c r="BN240">
+        <v>1.44</v>
+      </c>
+      <c r="BO240">
+        <v>3.4</v>
+      </c>
+      <c r="BP240">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7468591</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45746.51041666666</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>70</v>
+      </c>
+      <c r="H241" t="s">
+        <v>85</v>
+      </c>
+      <c r="I241">
+        <v>2</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>3</v>
+      </c>
+      <c r="L241">
+        <v>3</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>5</v>
+      </c>
+      <c r="O241" t="s">
+        <v>254</v>
+      </c>
+      <c r="P241" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q241">
+        <v>3.6</v>
+      </c>
+      <c r="R241">
+        <v>2.05</v>
+      </c>
+      <c r="S241">
+        <v>3.1</v>
+      </c>
+      <c r="T241">
+        <v>1.44</v>
+      </c>
+      <c r="U241">
+        <v>2.63</v>
+      </c>
+      <c r="V241">
+        <v>3.25</v>
+      </c>
+      <c r="W241">
+        <v>1.33</v>
+      </c>
+      <c r="X241">
+        <v>10</v>
+      </c>
+      <c r="Y241">
+        <v>1.06</v>
+      </c>
+      <c r="Z241">
+        <v>2.97</v>
+      </c>
+      <c r="AA241">
+        <v>3.33</v>
+      </c>
+      <c r="AB241">
+        <v>2.51</v>
+      </c>
+      <c r="AC241">
+        <v>1.07</v>
+      </c>
+      <c r="AD241">
+        <v>8</v>
+      </c>
+      <c r="AE241">
+        <v>1.38</v>
+      </c>
+      <c r="AF241">
+        <v>3</v>
+      </c>
+      <c r="AG241">
+        <v>2.15</v>
+      </c>
+      <c r="AH241">
+        <v>1.65</v>
+      </c>
+      <c r="AI241">
+        <v>1.8</v>
+      </c>
+      <c r="AJ241">
+        <v>1.95</v>
+      </c>
+      <c r="AK241">
+        <v>1.51</v>
+      </c>
+      <c r="AL241">
+        <v>1.32</v>
+      </c>
+      <c r="AM241">
+        <v>1.41</v>
+      </c>
+      <c r="AN241">
+        <v>0.54</v>
+      </c>
+      <c r="AO241">
+        <v>0.85</v>
+      </c>
+      <c r="AP241">
+        <v>0.71</v>
+      </c>
+      <c r="AQ241">
+        <v>0.79</v>
+      </c>
+      <c r="AR241">
+        <v>1.21</v>
+      </c>
+      <c r="AS241">
+        <v>1.13</v>
+      </c>
+      <c r="AT241">
+        <v>2.34</v>
+      </c>
+      <c r="AU241">
+        <v>5</v>
+      </c>
+      <c r="AV241">
+        <v>3</v>
+      </c>
+      <c r="AW241">
+        <v>10</v>
+      </c>
+      <c r="AX241">
+        <v>5</v>
+      </c>
+      <c r="AY241">
+        <v>19</v>
+      </c>
+      <c r="AZ241">
+        <v>10</v>
+      </c>
+      <c r="BA241">
+        <v>3</v>
+      </c>
+      <c r="BB241">
+        <v>4</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>2</v>
+      </c>
+      <c r="BE241">
+        <v>8.5</v>
+      </c>
+      <c r="BF241">
+        <v>2.13</v>
+      </c>
+      <c r="BG241">
+        <v>1.24</v>
+      </c>
+      <c r="BH241">
+        <v>3.34</v>
+      </c>
+      <c r="BI241">
+        <v>1.67</v>
+      </c>
+      <c r="BJ241">
+        <v>2.1</v>
+      </c>
+      <c r="BK241">
+        <v>1.83</v>
+      </c>
+      <c r="BL241">
+        <v>1.87</v>
+      </c>
+      <c r="BM241">
+        <v>2.34</v>
+      </c>
+      <c r="BN241">
+        <v>1.5</v>
+      </c>
+      <c r="BO241">
+        <v>3.08</v>
+      </c>
+      <c r="BP241">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7468589</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45746.51041666666</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>77</v>
+      </c>
+      <c r="H242" t="s">
+        <v>78</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>3</v>
+      </c>
+      <c r="N242">
+        <v>3</v>
+      </c>
+      <c r="O242" t="s">
+        <v>90</v>
+      </c>
+      <c r="P242" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q242">
+        <v>4.5</v>
+      </c>
+      <c r="R242">
+        <v>2.2</v>
+      </c>
+      <c r="S242">
+        <v>2.5</v>
+      </c>
+      <c r="T242">
+        <v>1.4</v>
+      </c>
+      <c r="U242">
+        <v>2.75</v>
+      </c>
+      <c r="V242">
+        <v>3</v>
+      </c>
+      <c r="W242">
+        <v>1.36</v>
+      </c>
+      <c r="X242">
+        <v>8</v>
+      </c>
+      <c r="Y242">
+        <v>1.08</v>
+      </c>
+      <c r="Z242">
+        <v>4</v>
+      </c>
+      <c r="AA242">
+        <v>3.45</v>
+      </c>
+      <c r="AB242">
+        <v>2.02</v>
+      </c>
+      <c r="AC242">
+        <v>1.06</v>
+      </c>
+      <c r="AD242">
+        <v>8.5</v>
+      </c>
+      <c r="AE242">
+        <v>1.33</v>
+      </c>
+      <c r="AF242">
+        <v>3.3</v>
+      </c>
+      <c r="AG242">
+        <v>1.96</v>
+      </c>
+      <c r="AH242">
+        <v>1.8</v>
+      </c>
+      <c r="AI242">
+        <v>1.8</v>
+      </c>
+      <c r="AJ242">
+        <v>1.95</v>
+      </c>
+      <c r="AK242">
+        <v>1.82</v>
+      </c>
+      <c r="AL242">
+        <v>1.29</v>
+      </c>
+      <c r="AM242">
+        <v>1.25</v>
+      </c>
+      <c r="AN242">
+        <v>0.85</v>
+      </c>
+      <c r="AO242">
+        <v>0.58</v>
+      </c>
+      <c r="AP242">
+        <v>0.79</v>
+      </c>
+      <c r="AQ242">
+        <v>0.77</v>
+      </c>
+      <c r="AR242">
+        <v>1.21</v>
+      </c>
+      <c r="AS242">
+        <v>1.4</v>
+      </c>
+      <c r="AT242">
+        <v>2.61</v>
+      </c>
+      <c r="AU242">
+        <v>5</v>
+      </c>
+      <c r="AV242">
+        <v>9</v>
+      </c>
+      <c r="AW242">
+        <v>6</v>
+      </c>
+      <c r="AX242">
+        <v>7</v>
+      </c>
+      <c r="AY242">
+        <v>12</v>
+      </c>
+      <c r="AZ242">
+        <v>16</v>
+      </c>
+      <c r="BA242">
+        <v>5</v>
+      </c>
+      <c r="BB242">
+        <v>5</v>
+      </c>
+      <c r="BC242">
+        <v>10</v>
+      </c>
+      <c r="BD242">
+        <v>2.72</v>
+      </c>
+      <c r="BE242">
+        <v>8.4</v>
+      </c>
+      <c r="BF242">
+        <v>1.67</v>
+      </c>
+      <c r="BG242">
+        <v>1.4</v>
+      </c>
+      <c r="BH242">
+        <v>2.64</v>
+      </c>
+      <c r="BI242">
+        <v>1.73</v>
+      </c>
+      <c r="BJ242">
+        <v>2</v>
+      </c>
+      <c r="BK242">
+        <v>2.21</v>
+      </c>
+      <c r="BL242">
+        <v>1.56</v>
+      </c>
+      <c r="BM242">
+        <v>2.97</v>
+      </c>
+      <c r="BN242">
+        <v>1.3</v>
+      </c>
+      <c r="BO242">
+        <v>4.2</v>
+      </c>
+      <c r="BP242">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7468596</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45746.65625</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>81</v>
+      </c>
+      <c r="H243" t="s">
+        <v>83</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
+        <v>255</v>
+      </c>
+      <c r="P243" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q243">
+        <v>2.75</v>
+      </c>
+      <c r="R243">
+        <v>2.1</v>
+      </c>
+      <c r="S243">
+        <v>4.33</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3</v>
+      </c>
+      <c r="W243">
+        <v>1.36</v>
+      </c>
+      <c r="X243">
+        <v>9</v>
+      </c>
+      <c r="Y243">
+        <v>1.07</v>
+      </c>
+      <c r="Z243">
+        <v>1.97</v>
+      </c>
+      <c r="AA243">
+        <v>3.6</v>
+      </c>
+      <c r="AB243">
+        <v>4</v>
+      </c>
+      <c r="AC243">
+        <v>1.06</v>
+      </c>
+      <c r="AD243">
+        <v>8.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.33</v>
+      </c>
+      <c r="AF243">
+        <v>3.25</v>
+      </c>
+      <c r="AG243">
+        <v>2</v>
+      </c>
+      <c r="AH243">
+        <v>1.82</v>
+      </c>
+      <c r="AI243">
+        <v>1.8</v>
+      </c>
+      <c r="AJ243">
+        <v>1.95</v>
+      </c>
+      <c r="AK243">
+        <v>1.28</v>
+      </c>
+      <c r="AL243">
+        <v>1.3</v>
+      </c>
+      <c r="AM243">
+        <v>1.75</v>
+      </c>
+      <c r="AN243">
+        <v>2.08</v>
+      </c>
+      <c r="AO243">
+        <v>1.69</v>
+      </c>
+      <c r="AP243">
+        <v>2.14</v>
+      </c>
+      <c r="AQ243">
+        <v>1.57</v>
+      </c>
+      <c r="AR243">
+        <v>1.66</v>
+      </c>
+      <c r="AS243">
+        <v>1.41</v>
+      </c>
+      <c r="AT243">
+        <v>3.07</v>
+      </c>
+      <c r="AU243">
+        <v>6</v>
+      </c>
+      <c r="AV243">
+        <v>2</v>
+      </c>
+      <c r="AW243">
+        <v>6</v>
+      </c>
+      <c r="AX243">
+        <v>4</v>
+      </c>
+      <c r="AY243">
+        <v>14</v>
+      </c>
+      <c r="AZ243">
+        <v>7</v>
+      </c>
+      <c r="BA243">
+        <v>6</v>
+      </c>
+      <c r="BB243">
+        <v>2</v>
+      </c>
+      <c r="BC243">
+        <v>8</v>
+      </c>
+      <c r="BD243">
+        <v>1.71</v>
+      </c>
+      <c r="BE243">
+        <v>6.25</v>
+      </c>
+      <c r="BF243">
+        <v>2.4</v>
+      </c>
+      <c r="BG243">
+        <v>1.47</v>
+      </c>
+      <c r="BH243">
+        <v>2.48</v>
+      </c>
+      <c r="BI243">
+        <v>1.67</v>
+      </c>
+      <c r="BJ243">
+        <v>2.1</v>
+      </c>
+      <c r="BK243">
+        <v>2.23</v>
+      </c>
+      <c r="BL243">
+        <v>1.56</v>
+      </c>
+      <c r="BM243">
+        <v>2.9</v>
+      </c>
+      <c r="BN243">
+        <v>1.34</v>
+      </c>
+      <c r="BO243">
+        <v>3.9</v>
+      </c>
+      <c r="BP243">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -51319,13 +51319,13 @@
         <v>16</v>
       </c>
       <c r="BA242">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB242">
         <v>5</v>
       </c>
       <c r="BC242">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD242">
         <v>2.72</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1152,6 +1152,9 @@
   <si>
     <t>['13', '70', '90+5']</t>
   </si>
+  <si>
+    <t>['11', '38']</t>
+  </si>
 </sst>
 </file>
 
@@ -1512,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3085,7 +3088,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -5142,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>1.38</v>
@@ -5969,7 +5972,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ22">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -9262,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>0.23</v>
@@ -10501,7 +10504,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ44">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -13797,7 +13800,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -14618,7 +14621,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>2.57</v>
@@ -17917,7 +17920,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ80">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -18120,7 +18123,7 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>1.38</v>
@@ -20801,7 +20804,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ94">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -21210,7 +21213,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1.31</v>
@@ -23888,7 +23891,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>1.29</v>
@@ -24715,7 +24718,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ113">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -26566,7 +26569,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>1.08</v>
@@ -29041,7 +29044,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ134">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29862,7 +29865,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
         <v>0.77</v>
@@ -30277,7 +30280,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ140">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -34397,7 +34400,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ160">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -36866,7 +36869,7 @@
         <v>2.67</v>
       </c>
       <c r="AP172">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>1.93</v>
@@ -38517,7 +38520,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ180">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR180">
         <v>1.22</v>
@@ -39338,7 +39341,7 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ184">
         <v>1.57</v>
@@ -41195,7 +41198,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ193">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -43664,7 +43667,7 @@
         <v>0.3</v>
       </c>
       <c r="AP205">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>0.23</v>
@@ -46139,7 +46142,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ217">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR217">
         <v>1.76</v>
@@ -47990,7 +47993,7 @@
         <v>1.33</v>
       </c>
       <c r="AP226">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ226">
         <v>1.36</v>
@@ -48196,7 +48199,7 @@
         <v>0.67</v>
       </c>
       <c r="AP227">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ227">
         <v>0.6899999999999999</v>
@@ -51083,7 +51086,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ241">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR241">
         <v>1.21</v>
@@ -51571,6 +51574,212 @@
       </c>
       <c r="BP243">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7468599</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F244">
+        <v>28</v>
+      </c>
+      <c r="G244" t="s">
+        <v>86</v>
+      </c>
+      <c r="H244" t="s">
+        <v>85</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244">
+        <v>2</v>
+      </c>
+      <c r="K244">
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>2</v>
+      </c>
+      <c r="N244">
+        <v>3</v>
+      </c>
+      <c r="O244" t="s">
+        <v>127</v>
+      </c>
+      <c r="P244" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q244">
+        <v>2.1</v>
+      </c>
+      <c r="R244">
+        <v>2.3</v>
+      </c>
+      <c r="S244">
+        <v>6</v>
+      </c>
+      <c r="T244">
+        <v>1.33</v>
+      </c>
+      <c r="U244">
+        <v>3.25</v>
+      </c>
+      <c r="V244">
+        <v>2.63</v>
+      </c>
+      <c r="W244">
+        <v>1.44</v>
+      </c>
+      <c r="X244">
+        <v>7</v>
+      </c>
+      <c r="Y244">
+        <v>1.1</v>
+      </c>
+      <c r="Z244">
+        <v>1.54</v>
+      </c>
+      <c r="AA244">
+        <v>4.5</v>
+      </c>
+      <c r="AB244">
+        <v>6.2</v>
+      </c>
+      <c r="AC244">
+        <v>1.04</v>
+      </c>
+      <c r="AD244">
+        <v>10</v>
+      </c>
+      <c r="AE244">
+        <v>1.25</v>
+      </c>
+      <c r="AF244">
+        <v>3.9</v>
+      </c>
+      <c r="AG244">
+        <v>1.8</v>
+      </c>
+      <c r="AH244">
+        <v>2.02</v>
+      </c>
+      <c r="AI244">
+        <v>1.91</v>
+      </c>
+      <c r="AJ244">
+        <v>1.91</v>
+      </c>
+      <c r="AK244">
+        <v>1.13</v>
+      </c>
+      <c r="AL244">
+        <v>1.22</v>
+      </c>
+      <c r="AM244">
+        <v>2.45</v>
+      </c>
+      <c r="AN244">
+        <v>2.15</v>
+      </c>
+      <c r="AO244">
+        <v>0.79</v>
+      </c>
+      <c r="AP244">
+        <v>2</v>
+      </c>
+      <c r="AQ244">
+        <v>0.93</v>
+      </c>
+      <c r="AR244">
+        <v>1.74</v>
+      </c>
+      <c r="AS244">
+        <v>1.11</v>
+      </c>
+      <c r="AT244">
+        <v>2.85</v>
+      </c>
+      <c r="AU244">
+        <v>-1</v>
+      </c>
+      <c r="AV244">
+        <v>-1</v>
+      </c>
+      <c r="AW244">
+        <v>-1</v>
+      </c>
+      <c r="AX244">
+        <v>-1</v>
+      </c>
+      <c r="AY244">
+        <v>-1</v>
+      </c>
+      <c r="AZ244">
+        <v>-1</v>
+      </c>
+      <c r="BA244">
+        <v>-1</v>
+      </c>
+      <c r="BB244">
+        <v>-1</v>
+      </c>
+      <c r="BC244">
+        <v>-1</v>
+      </c>
+      <c r="BD244">
+        <v>1.38</v>
+      </c>
+      <c r="BE244">
+        <v>7</v>
+      </c>
+      <c r="BF244">
+        <v>3.4</v>
+      </c>
+      <c r="BG244">
+        <v>1.27</v>
+      </c>
+      <c r="BH244">
+        <v>3.3</v>
+      </c>
+      <c r="BI244">
+        <v>1.48</v>
+      </c>
+      <c r="BJ244">
+        <v>2.45</v>
+      </c>
+      <c r="BK244">
+        <v>1.77</v>
+      </c>
+      <c r="BL244">
+        <v>1.91</v>
+      </c>
+      <c r="BM244">
+        <v>2.2</v>
+      </c>
+      <c r="BN244">
+        <v>1.58</v>
+      </c>
+      <c r="BO244">
+        <v>2.8</v>
+      </c>
+      <c r="BP244">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="383">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,12 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['42', '90+4']</t>
+  </si>
+  <si>
+    <t>['38', '70']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -1155,6 +1161,9 @@
   <si>
     <t>['11', '38']</t>
   </si>
+  <si>
+    <t>['1']</t>
+  </si>
 </sst>
 </file>
 
@@ -1515,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1771,7 +1780,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1977,7 +1986,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2055,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ3">
         <v>1.93</v>
@@ -2183,7 +2192,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2264,7 +2273,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ4">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2595,7 +2604,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2801,7 +2810,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3703,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ11">
         <v>0.23</v>
@@ -3831,7 +3840,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3909,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4118,7 +4127,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ13">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4243,7 +4252,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4655,7 +4664,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5273,7 +5282,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5479,7 +5488,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5557,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ20">
         <v>1.29</v>
@@ -5763,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21">
         <v>0.23</v>
@@ -5891,7 +5900,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -6097,7 +6106,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6303,7 +6312,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6509,7 +6518,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6921,7 +6930,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7127,7 +7136,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7414,7 +7423,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ29">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR29">
         <v>1.65</v>
@@ -7745,7 +7754,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7826,7 +7835,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ31">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -8029,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ32">
         <v>1.14</v>
@@ -8363,7 +8372,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8444,7 +8453,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ34">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8569,7 +8578,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9393,7 +9402,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9599,7 +9608,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10295,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ43">
         <v>1.38</v>
@@ -10423,7 +10432,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10629,7 +10638,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10835,7 +10844,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10913,7 +10922,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ46">
         <v>1.93</v>
@@ -11247,7 +11256,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11325,7 +11334,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ48">
         <v>0.77</v>
@@ -11659,7 +11668,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11740,7 +11749,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ50">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR50">
         <v>1.41</v>
@@ -11865,7 +11874,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12071,7 +12080,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12277,7 +12286,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12483,7 +12492,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12976,7 +12985,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -13101,7 +13110,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13513,7 +13522,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13594,7 +13603,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ59">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -13797,7 +13806,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ60">
         <v>0.93</v>
@@ -14003,7 +14012,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ61">
         <v>1.08</v>
@@ -14131,7 +14140,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14337,7 +14346,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14543,7 +14552,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14830,7 +14839,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ65">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR65">
         <v>1.54</v>
@@ -15033,7 +15042,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ66">
         <v>0.77</v>
@@ -15161,7 +15170,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15367,7 +15376,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15445,7 +15454,7 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ68">
         <v>1.29</v>
@@ -15573,7 +15582,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15779,7 +15788,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15860,7 +15869,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.25</v>
@@ -15985,7 +15994,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16191,7 +16200,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16397,7 +16406,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16809,7 +16818,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -17015,7 +17024,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17221,7 +17230,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17302,7 +17311,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ77">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR77">
         <v>1.98</v>
@@ -17427,7 +17436,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17505,7 +17514,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ78">
         <v>0.6899999999999999</v>
@@ -17633,7 +17642,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -18126,7 +18135,7 @@
         <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18251,7 +18260,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18538,7 +18547,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ83">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR83">
         <v>1.55</v>
@@ -18947,7 +18956,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ85">
         <v>1.57</v>
@@ -19075,7 +19084,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19153,7 +19162,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ86">
         <v>1.36</v>
@@ -20105,7 +20114,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20311,7 +20320,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20517,7 +20526,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20598,7 +20607,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ93">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20723,7 +20732,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20929,7 +20938,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21135,7 +21144,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21216,7 +21225,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR96">
         <v>1.64</v>
@@ -21341,7 +21350,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21753,7 +21762,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22037,7 +22046,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ100">
         <v>0.23</v>
@@ -22165,7 +22174,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22449,7 +22458,7 @@
         <v>1.4</v>
       </c>
       <c r="AP102">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ102">
         <v>1.38</v>
@@ -22577,7 +22586,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23482,7 +23491,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ107">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR107">
         <v>1.49</v>
@@ -23607,7 +23616,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -24019,7 +24028,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24509,7 +24518,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ112">
         <v>1.29</v>
@@ -24715,7 +24724,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ113">
         <v>0.93</v>
@@ -24843,7 +24852,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24924,7 +24933,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ114">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR114">
         <v>1.36</v>
@@ -25049,7 +25058,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25130,7 +25139,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ115">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25461,7 +25470,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25539,7 +25548,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ117">
         <v>1.36</v>
@@ -25667,7 +25676,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25748,7 +25757,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ118">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -26491,7 +26500,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26697,7 +26706,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27521,7 +27530,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27933,7 +27942,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28014,7 +28023,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ129">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.4</v>
@@ -28139,7 +28148,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28426,7 +28435,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -28551,7 +28560,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28757,7 +28766,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29041,7 +29050,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ134">
         <v>0.93</v>
@@ -29250,7 +29259,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR135">
         <v>1.64</v>
@@ -29453,7 +29462,7 @@
         <v>1.71</v>
       </c>
       <c r="AP136">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ136">
         <v>1.36</v>
@@ -29581,7 +29590,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29787,7 +29796,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29993,7 +30002,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30199,7 +30208,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30483,7 +30492,7 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ141">
         <v>0.23</v>
@@ -31435,7 +31444,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31516,7 +31525,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ146">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -31722,7 +31731,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ147">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR147">
         <v>1.33</v>
@@ -31847,7 +31856,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31925,7 +31934,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ148">
         <v>1.36</v>
@@ -32053,7 +32062,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32259,7 +32268,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32465,7 +32474,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32671,7 +32680,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32752,7 +32761,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ152">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR152">
         <v>1.44</v>
@@ -32877,7 +32886,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33161,7 +33170,7 @@
         <v>0.13</v>
       </c>
       <c r="AP154">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ154">
         <v>0.23</v>
@@ -33370,7 +33379,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ155">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR155">
         <v>1.44</v>
@@ -33701,7 +33710,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33907,7 +33916,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34191,7 +34200,7 @@
         <v>1.25</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ159">
         <v>1.38</v>
@@ -34937,7 +34946,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35349,7 +35358,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35636,7 +35645,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ166">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR166">
         <v>1.19</v>
@@ -35761,7 +35770,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35839,7 +35848,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35967,7 +35976,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36379,7 +36388,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36666,7 +36675,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ171">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR171">
         <v>1.64</v>
@@ -36997,7 +37006,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37203,7 +37212,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37281,7 +37290,7 @@
         <v>2.33</v>
       </c>
       <c r="AP174">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ174">
         <v>2.57</v>
@@ -37409,7 +37418,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37821,7 +37830,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38439,7 +38448,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38645,7 +38654,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38851,7 +38860,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39135,10 +39144,10 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ183">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR183">
         <v>2.35</v>
@@ -39469,7 +39478,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39675,7 +39684,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39959,7 +39968,7 @@
         <v>1.33</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -40087,7 +40096,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40499,7 +40508,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40705,7 +40714,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40783,7 +40792,7 @@
         <v>0.4</v>
       </c>
       <c r="AP191">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ191">
         <v>0.6899999999999999</v>
@@ -40911,7 +40920,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -41323,7 +41332,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41529,7 +41538,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41735,7 +41744,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42022,7 +42031,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ197">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR197">
         <v>1.26</v>
@@ -42147,7 +42156,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42353,7 +42362,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42434,7 +42443,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ199">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR199">
         <v>1.59</v>
@@ -42846,7 +42855,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ201">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR201">
         <v>1.63</v>
@@ -42971,7 +42980,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43052,7 +43061,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ202">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR202">
         <v>1.29</v>
@@ -44001,7 +44010,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44207,7 +44216,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44285,7 +44294,7 @@
         <v>2.45</v>
       </c>
       <c r="AP208">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ208">
         <v>2.57</v>
@@ -44619,7 +44628,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44825,7 +44834,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -45109,10 +45118,10 @@
         <v>1.55</v>
       </c>
       <c r="AP212">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ212">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR212">
         <v>2.34</v>
@@ -45237,7 +45246,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45315,7 +45324,7 @@
         <v>1.08</v>
       </c>
       <c r="AP213">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ213">
         <v>1.14</v>
@@ -45443,7 +45452,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45649,7 +45658,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -46348,7 +46357,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ218">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR218">
         <v>1.52</v>
@@ -46473,7 +46482,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46885,7 +46894,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -47169,10 +47178,10 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ222">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR222">
         <v>1.57</v>
@@ -47297,7 +47306,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47503,7 +47512,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47915,7 +47924,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48121,7 +48130,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48408,7 +48417,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ228">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR228">
         <v>1.43</v>
@@ -48533,7 +48542,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48614,7 +48623,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ229">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR229">
         <v>1.22</v>
@@ -48945,7 +48954,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49023,7 +49032,7 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ231">
         <v>1.08</v>
@@ -49229,7 +49238,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -49357,7 +49366,7 @@
         <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q233">
         <v>3</v>
@@ -49641,7 +49650,7 @@
         <v>2.25</v>
       </c>
       <c r="AP234">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ234">
         <v>1.93</v>
@@ -49769,7 +49778,7 @@
         <v>249</v>
       </c>
       <c r="P235" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q235">
         <v>3.2</v>
@@ -50181,7 +50190,7 @@
         <v>119</v>
       </c>
       <c r="P237" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q237">
         <v>10</v>
@@ -50387,7 +50396,7 @@
         <v>251</v>
       </c>
       <c r="P238" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q238">
         <v>2.4</v>
@@ -50593,7 +50602,7 @@
         <v>252</v>
       </c>
       <c r="P239" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q239">
         <v>2.75</v>
@@ -51005,7 +51014,7 @@
         <v>254</v>
       </c>
       <c r="P241" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q241">
         <v>3.6</v>
@@ -51211,7 +51220,7 @@
         <v>90</v>
       </c>
       <c r="P242" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q242">
         <v>4.5</v>
@@ -51623,7 +51632,7 @@
         <v>127</v>
       </c>
       <c r="P244" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51716,31 +51725,31 @@
         <v>2.85</v>
       </c>
       <c r="AU244">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AV244">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW244">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AX244">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY244">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AZ244">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA244">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BB244">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC244">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD244">
         <v>1.38</v>
@@ -51780,6 +51789,624 @@
       </c>
       <c r="BP244">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7468604</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45752.5</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>79</v>
+      </c>
+      <c r="H245" t="s">
+        <v>77</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>1</v>
+      </c>
+      <c r="O245" t="s">
+        <v>163</v>
+      </c>
+      <c r="P245" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q245">
+        <v>1.44</v>
+      </c>
+      <c r="R245">
+        <v>3.4</v>
+      </c>
+      <c r="S245">
+        <v>10</v>
+      </c>
+      <c r="T245">
+        <v>1.17</v>
+      </c>
+      <c r="U245">
+        <v>5</v>
+      </c>
+      <c r="V245">
+        <v>1.8</v>
+      </c>
+      <c r="W245">
+        <v>1.91</v>
+      </c>
+      <c r="X245">
+        <v>3.5</v>
+      </c>
+      <c r="Y245">
+        <v>1.29</v>
+      </c>
+      <c r="Z245">
+        <v>1.2</v>
+      </c>
+      <c r="AA245">
+        <v>8.5</v>
+      </c>
+      <c r="AB245">
+        <v>12</v>
+      </c>
+      <c r="AC245">
+        <v>1.01</v>
+      </c>
+      <c r="AD245">
+        <v>36</v>
+      </c>
+      <c r="AE245">
+        <v>1.07</v>
+      </c>
+      <c r="AF245">
+        <v>8</v>
+      </c>
+      <c r="AG245">
+        <v>1.24</v>
+      </c>
+      <c r="AH245">
+        <v>3.8</v>
+      </c>
+      <c r="AI245">
+        <v>1.8</v>
+      </c>
+      <c r="AJ245">
+        <v>1.95</v>
+      </c>
+      <c r="AK245">
+        <v>1.02</v>
+      </c>
+      <c r="AL245">
+        <v>1.07</v>
+      </c>
+      <c r="AM245">
+        <v>5.75</v>
+      </c>
+      <c r="AN245">
+        <v>2.69</v>
+      </c>
+      <c r="AO245">
+        <v>1.23</v>
+      </c>
+      <c r="AP245">
+        <v>2.71</v>
+      </c>
+      <c r="AQ245">
+        <v>1.14</v>
+      </c>
+      <c r="AR245">
+        <v>2.34</v>
+      </c>
+      <c r="AS245">
+        <v>1.1</v>
+      </c>
+      <c r="AT245">
+        <v>3.44</v>
+      </c>
+      <c r="AU245">
+        <v>7</v>
+      </c>
+      <c r="AV245">
+        <v>0</v>
+      </c>
+      <c r="AW245">
+        <v>14</v>
+      </c>
+      <c r="AX245">
+        <v>6</v>
+      </c>
+      <c r="AY245">
+        <v>24</v>
+      </c>
+      <c r="AZ245">
+        <v>7</v>
+      </c>
+      <c r="BA245">
+        <v>5</v>
+      </c>
+      <c r="BB245">
+        <v>1</v>
+      </c>
+      <c r="BC245">
+        <v>6</v>
+      </c>
+      <c r="BD245">
+        <v>1.1</v>
+      </c>
+      <c r="BE245">
+        <v>11</v>
+      </c>
+      <c r="BF245">
+        <v>9.25</v>
+      </c>
+      <c r="BG245">
+        <v>1.21</v>
+      </c>
+      <c r="BH245">
+        <v>3.75</v>
+      </c>
+      <c r="BI245">
+        <v>1.4</v>
+      </c>
+      <c r="BJ245">
+        <v>2.6</v>
+      </c>
+      <c r="BK245">
+        <v>1.73</v>
+      </c>
+      <c r="BL245">
+        <v>1.93</v>
+      </c>
+      <c r="BM245">
+        <v>2.2</v>
+      </c>
+      <c r="BN245">
+        <v>1.55</v>
+      </c>
+      <c r="BO245">
+        <v>3</v>
+      </c>
+      <c r="BP245">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7468600</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45752.58333333334</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>71</v>
+      </c>
+      <c r="H246" t="s">
+        <v>73</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>2</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>3</v>
+      </c>
+      <c r="O246" t="s">
+        <v>256</v>
+      </c>
+      <c r="P246" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q246">
+        <v>4</v>
+      </c>
+      <c r="R246">
+        <v>2.3</v>
+      </c>
+      <c r="S246">
+        <v>2.5</v>
+      </c>
+      <c r="T246">
+        <v>1.3</v>
+      </c>
+      <c r="U246">
+        <v>3.4</v>
+      </c>
+      <c r="V246">
+        <v>2.5</v>
+      </c>
+      <c r="W246">
+        <v>1.5</v>
+      </c>
+      <c r="X246">
+        <v>6</v>
+      </c>
+      <c r="Y246">
+        <v>1.13</v>
+      </c>
+      <c r="Z246">
+        <v>3.68</v>
+      </c>
+      <c r="AA246">
+        <v>3.81</v>
+      </c>
+      <c r="AB246">
+        <v>2</v>
+      </c>
+      <c r="AC246">
+        <v>1.04</v>
+      </c>
+      <c r="AD246">
+        <v>10</v>
+      </c>
+      <c r="AE246">
+        <v>1.2</v>
+      </c>
+      <c r="AF246">
+        <v>4.33</v>
+      </c>
+      <c r="AG246">
+        <v>1.61</v>
+      </c>
+      <c r="AH246">
+        <v>2.15</v>
+      </c>
+      <c r="AI246">
+        <v>1.57</v>
+      </c>
+      <c r="AJ246">
+        <v>2.25</v>
+      </c>
+      <c r="AK246">
+        <v>1.83</v>
+      </c>
+      <c r="AL246">
+        <v>1.26</v>
+      </c>
+      <c r="AM246">
+        <v>1.28</v>
+      </c>
+      <c r="AN246">
+        <v>1.85</v>
+      </c>
+      <c r="AO246">
+        <v>1.38</v>
+      </c>
+      <c r="AP246">
+        <v>1.93</v>
+      </c>
+      <c r="AQ246">
+        <v>1.29</v>
+      </c>
+      <c r="AR246">
+        <v>1.58</v>
+      </c>
+      <c r="AS246">
+        <v>1.66</v>
+      </c>
+      <c r="AT246">
+        <v>3.24</v>
+      </c>
+      <c r="AU246">
+        <v>-1</v>
+      </c>
+      <c r="AV246">
+        <v>-1</v>
+      </c>
+      <c r="AW246">
+        <v>-1</v>
+      </c>
+      <c r="AX246">
+        <v>-1</v>
+      </c>
+      <c r="AY246">
+        <v>-1</v>
+      </c>
+      <c r="AZ246">
+        <v>-1</v>
+      </c>
+      <c r="BA246">
+        <v>-1</v>
+      </c>
+      <c r="BB246">
+        <v>-1</v>
+      </c>
+      <c r="BC246">
+        <v>-1</v>
+      </c>
+      <c r="BD246">
+        <v>2.25</v>
+      </c>
+      <c r="BE246">
+        <v>6.25</v>
+      </c>
+      <c r="BF246">
+        <v>1.87</v>
+      </c>
+      <c r="BG246">
+        <v>1.31</v>
+      </c>
+      <c r="BH246">
+        <v>3</v>
+      </c>
+      <c r="BI246">
+        <v>1.58</v>
+      </c>
+      <c r="BJ246">
+        <v>2.15</v>
+      </c>
+      <c r="BK246">
+        <v>2</v>
+      </c>
+      <c r="BL246">
+        <v>1.66</v>
+      </c>
+      <c r="BM246">
+        <v>2.7</v>
+      </c>
+      <c r="BN246">
+        <v>1.38</v>
+      </c>
+      <c r="BO246">
+        <v>3.9</v>
+      </c>
+      <c r="BP246">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7468602</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.67013888889</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>80</v>
+      </c>
+      <c r="H247" t="s">
+        <v>81</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247">
+        <v>2</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>3</v>
+      </c>
+      <c r="O247" t="s">
+        <v>257</v>
+      </c>
+      <c r="P247" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q247">
+        <v>2.88</v>
+      </c>
+      <c r="R247">
+        <v>2.25</v>
+      </c>
+      <c r="S247">
+        <v>3.5</v>
+      </c>
+      <c r="T247">
+        <v>1.33</v>
+      </c>
+      <c r="U247">
+        <v>3.25</v>
+      </c>
+      <c r="V247">
+        <v>2.63</v>
+      </c>
+      <c r="W247">
+        <v>1.44</v>
+      </c>
+      <c r="X247">
+        <v>6.5</v>
+      </c>
+      <c r="Y247">
+        <v>1.11</v>
+      </c>
+      <c r="Z247">
+        <v>2.19</v>
+      </c>
+      <c r="AA247">
+        <v>3.73</v>
+      </c>
+      <c r="AB247">
+        <v>3.23</v>
+      </c>
+      <c r="AC247">
+        <v>1.04</v>
+      </c>
+      <c r="AD247">
+        <v>10</v>
+      </c>
+      <c r="AE247">
+        <v>1.22</v>
+      </c>
+      <c r="AF247">
+        <v>4.2</v>
+      </c>
+      <c r="AG247">
+        <v>1.61</v>
+      </c>
+      <c r="AH247">
+        <v>2.15</v>
+      </c>
+      <c r="AI247">
+        <v>1.62</v>
+      </c>
+      <c r="AJ247">
+        <v>2.2</v>
+      </c>
+      <c r="AK247">
+        <v>1.37</v>
+      </c>
+      <c r="AL247">
+        <v>1.28</v>
+      </c>
+      <c r="AM247">
+        <v>1.63</v>
+      </c>
+      <c r="AN247">
+        <v>2</v>
+      </c>
+      <c r="AO247">
+        <v>1.31</v>
+      </c>
+      <c r="AP247">
+        <v>2.07</v>
+      </c>
+      <c r="AQ247">
+        <v>1.21</v>
+      </c>
+      <c r="AR247">
+        <v>1.73</v>
+      </c>
+      <c r="AS247">
+        <v>1.5</v>
+      </c>
+      <c r="AT247">
+        <v>3.23</v>
+      </c>
+      <c r="AU247">
+        <v>-1</v>
+      </c>
+      <c r="AV247">
+        <v>-1</v>
+      </c>
+      <c r="AW247">
+        <v>-1</v>
+      </c>
+      <c r="AX247">
+        <v>-1</v>
+      </c>
+      <c r="AY247">
+        <v>-1</v>
+      </c>
+      <c r="AZ247">
+        <v>-1</v>
+      </c>
+      <c r="BA247">
+        <v>-1</v>
+      </c>
+      <c r="BB247">
+        <v>-1</v>
+      </c>
+      <c r="BC247">
+        <v>-1</v>
+      </c>
+      <c r="BD247">
+        <v>1.75</v>
+      </c>
+      <c r="BE247">
+        <v>6.5</v>
+      </c>
+      <c r="BF247">
+        <v>2.45</v>
+      </c>
+      <c r="BG247">
+        <v>1.3</v>
+      </c>
+      <c r="BH247">
+        <v>3.1</v>
+      </c>
+      <c r="BI247">
+        <v>1.57</v>
+      </c>
+      <c r="BJ247">
+        <v>2.2</v>
+      </c>
+      <c r="BK247">
+        <v>1.98</v>
+      </c>
+      <c r="BL247">
+        <v>1.68</v>
+      </c>
+      <c r="BM247">
+        <v>2.65</v>
+      </c>
+      <c r="BN247">
+        <v>1.39</v>
+      </c>
+      <c r="BO247">
+        <v>3.8</v>
+      </c>
+      <c r="BP247">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="386">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -790,6 +790,12 @@
     <t>['38', '70']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['21', '57', '64']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -860,9 +866,6 @@
   </si>
   <si>
     <t>['69', '82', '90+5']</t>
-  </si>
-  <si>
-    <t>['75']</t>
   </si>
   <si>
     <t>['23', '35', '79']</t>
@@ -1163,6 +1166,12 @@
   </si>
   <si>
     <t>['1']</t>
+  </si>
+  <si>
+    <t>['3', '33']</t>
+  </si>
+  <si>
+    <t>['28', '76']</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP247"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1780,7 +1789,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1986,7 +1995,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -2192,7 +2201,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2270,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ4">
         <v>1.21</v>
@@ -2479,7 +2488,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ5">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2604,7 +2613,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2810,7 +2819,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2888,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ7">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3506,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ10">
         <v>1.36</v>
@@ -3840,7 +3849,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -4252,7 +4261,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4333,7 +4342,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ14">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4536,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ15">
         <v>1.14</v>
@@ -4664,7 +4673,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4951,7 +4960,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ17">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5157,7 +5166,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5282,7 +5291,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5360,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5488,7 +5497,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5569,7 +5578,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ20">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5775,7 +5784,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ21">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5900,7 +5909,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5978,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ22">
         <v>0.93</v>
@@ -6106,7 +6115,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6312,7 +6321,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6518,7 +6527,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6805,7 +6814,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ26">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6930,7 +6939,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7008,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ27">
         <v>0.77</v>
@@ -7136,7 +7145,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7626,7 +7635,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ30">
         <v>1.36</v>
@@ -7754,7 +7763,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8244,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ33">
         <v>0.23</v>
@@ -8372,7 +8381,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8578,7 +8587,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8865,7 +8874,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -9068,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
         <v>1.36</v>
@@ -9277,7 +9286,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9402,7 +9411,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9483,7 +9492,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ39">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9608,7 +9617,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9686,7 +9695,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ40">
         <v>1.57</v>
@@ -9892,7 +9901,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ41">
         <v>2.57</v>
@@ -10101,7 +10110,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ42">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10307,7 +10316,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10432,7 +10441,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10638,7 +10647,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10716,10 +10725,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ45">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10844,7 +10853,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -11256,7 +11265,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11540,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ49">
         <v>1.36</v>
@@ -11668,7 +11677,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11874,7 +11883,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -12080,7 +12089,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12286,7 +12295,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12367,7 +12376,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ53">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12492,7 +12501,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12982,7 +12991,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ56">
         <v>1.14</v>
@@ -13110,7 +13119,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13191,7 +13200,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ57">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13397,7 +13406,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ58">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13522,7 +13531,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13600,7 +13609,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ59">
         <v>1.29</v>
@@ -14015,7 +14024,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ61">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -14140,7 +14149,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14346,7 +14355,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14424,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ63">
         <v>0.23</v>
@@ -14552,7 +14561,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -15170,7 +15179,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15376,7 +15385,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15457,7 +15466,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ68">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15582,7 +15591,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15788,7 +15797,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15994,7 +16003,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -16200,7 +16209,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16406,7 +16415,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16484,7 +16493,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ73">
         <v>1.93</v>
@@ -16690,10 +16699,10 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16818,7 +16827,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16899,7 +16908,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ75">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -17024,7 +17033,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17102,7 +17111,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ76">
         <v>1.14</v>
@@ -17230,7 +17239,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17308,7 +17317,7 @@
         <v>1.75</v>
       </c>
       <c r="AP77">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ77">
         <v>1.21</v>
@@ -17436,7 +17445,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17517,7 +17526,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ78">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17642,7 +17651,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17720,10 +17729,10 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ79">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -18260,7 +18269,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18338,7 +18347,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ82">
         <v>2.57</v>
@@ -19084,7 +19093,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19371,7 +19380,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ87">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -20114,7 +20123,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20320,7 +20329,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20398,10 +20407,10 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ92">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20526,7 +20535,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20732,7 +20741,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20810,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20938,7 +20947,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -21144,7 +21153,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21350,7 +21359,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21428,10 +21437,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ97">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21634,7 +21643,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ98">
         <v>1.14</v>
@@ -21762,7 +21771,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -22049,7 +22058,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ100">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22174,7 +22183,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22461,7 +22470,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ102">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22586,7 +22595,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22664,7 +22673,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ103">
         <v>1.93</v>
@@ -23076,7 +23085,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ105">
         <v>1.36</v>
@@ -23616,7 +23625,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23697,7 +23706,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23903,7 +23912,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24028,7 +24037,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24106,7 +24115,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ110">
         <v>1.57</v>
@@ -24312,10 +24321,10 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ111">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24521,7 +24530,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ112">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24852,7 +24861,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24930,7 +24939,7 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ114">
         <v>1.21</v>
@@ -25058,7 +25067,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25345,7 +25354,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ116">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25470,7 +25479,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25676,7 +25685,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25754,7 +25763,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ118">
         <v>1.29</v>
@@ -26375,7 +26384,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ121">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26500,7 +26509,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26581,7 +26590,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26706,7 +26715,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26990,7 +26999,7 @@
         <v>0</v>
       </c>
       <c r="AP124">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ124">
         <v>0.23</v>
@@ -27530,7 +27539,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27817,7 +27826,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ128">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27942,7 +27951,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28020,7 +28029,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ129">
         <v>1.21</v>
@@ -28148,7 +28157,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28432,7 +28441,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ131">
         <v>1.29</v>
@@ -28560,7 +28569,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28638,7 +28647,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ132">
         <v>1.36</v>
@@ -28766,7 +28775,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28847,7 +28856,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ133">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -29256,7 +29265,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ135">
         <v>1.14</v>
@@ -29590,7 +29599,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29796,7 +29805,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -30002,7 +30011,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -30208,7 +30217,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30698,10 +30707,10 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ142">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -30907,7 +30916,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ143">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -31316,10 +31325,10 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ145">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31444,7 +31453,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31856,7 +31865,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -32062,7 +32071,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32140,7 +32149,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ149">
         <v>1.36</v>
@@ -32268,7 +32277,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32346,7 +32355,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ150">
         <v>1.93</v>
@@ -32474,7 +32483,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32680,7 +32689,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32758,7 +32767,7 @@
         <v>1.13</v>
       </c>
       <c r="AP152">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ152">
         <v>1.14</v>
@@ -32886,7 +32895,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32967,7 +32976,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ153">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33173,7 +33182,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ154">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR154">
         <v>2.26</v>
@@ -33376,7 +33385,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ155">
         <v>1.29</v>
@@ -33710,7 +33719,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33788,7 +33797,7 @@
         <v>2.25</v>
       </c>
       <c r="AP157">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>2.57</v>
@@ -33916,7 +33925,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -33994,7 +34003,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ158">
         <v>1.14</v>
@@ -34203,7 +34212,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ159">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34615,7 +34624,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ161">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR161">
         <v>1.21</v>
@@ -34818,10 +34827,10 @@
         <v>0.75</v>
       </c>
       <c r="AP162">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ162">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -34946,7 +34955,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -35024,10 +35033,10 @@
         <v>0.89</v>
       </c>
       <c r="AP163">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ163">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR163">
         <v>1.45</v>
@@ -35233,7 +35242,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ164">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35358,7 +35367,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q165">
         <v>2.25</v>
@@ -35770,7 +35779,7 @@
         <v>162</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q167">
         <v>1.62</v>
@@ -35976,7 +35985,7 @@
         <v>90</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36388,7 +36397,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36672,7 +36681,7 @@
         <v>1.33</v>
       </c>
       <c r="AP171">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ171">
         <v>1.14</v>
@@ -37006,7 +37015,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q173">
         <v>4.33</v>
@@ -37084,7 +37093,7 @@
         <v>1.78</v>
       </c>
       <c r="AP173">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ173">
         <v>1.57</v>
@@ -37212,7 +37221,7 @@
         <v>214</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q174">
         <v>5.25</v>
@@ -37418,7 +37427,7 @@
         <v>215</v>
       </c>
       <c r="P175" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q175">
         <v>1.73</v>
@@ -37499,7 +37508,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ175">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR175">
         <v>1.59</v>
@@ -37705,7 +37714,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ176">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR176">
         <v>1.38</v>
@@ -37830,7 +37839,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q177">
         <v>3.1</v>
@@ -38114,10 +38123,10 @@
         <v>0.9</v>
       </c>
       <c r="AP178">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ178">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR178">
         <v>1.61</v>
@@ -38323,7 +38332,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ179">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR179">
         <v>1.27</v>
@@ -38448,7 +38457,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38526,7 +38535,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ180">
         <v>0.93</v>
@@ -38654,7 +38663,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38732,7 +38741,7 @@
         <v>1.3</v>
       </c>
       <c r="AP181">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ181">
         <v>1.36</v>
@@ -38860,7 +38869,7 @@
         <v>90</v>
       </c>
       <c r="P182" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q182">
         <v>3.3</v>
@@ -39478,7 +39487,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q185">
         <v>1.83</v>
@@ -39559,7 +39568,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ185">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR185">
         <v>1.58</v>
@@ -39684,7 +39693,7 @@
         <v>90</v>
       </c>
       <c r="P186" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -40096,7 +40105,7 @@
         <v>224</v>
       </c>
       <c r="P188" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q188">
         <v>3.6</v>
@@ -40177,7 +40186,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ188">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR188">
         <v>1.32</v>
@@ -40508,7 +40517,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q190">
         <v>5.5</v>
@@ -40714,7 +40723,7 @@
         <v>226</v>
       </c>
       <c r="P191" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40795,7 +40804,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ191">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR191">
         <v>1.49</v>
@@ -40920,7 +40929,7 @@
         <v>227</v>
       </c>
       <c r="P192" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q192">
         <v>1.67</v>
@@ -40998,10 +41007,10 @@
         <v>0.18</v>
       </c>
       <c r="AP192">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ192">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR192">
         <v>1.6</v>
@@ -41332,7 +41341,7 @@
         <v>90</v>
       </c>
       <c r="P194" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41538,7 +41547,7 @@
         <v>138</v>
       </c>
       <c r="P195" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -41616,7 +41625,7 @@
         <v>1.18</v>
       </c>
       <c r="AP195">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ195">
         <v>1.36</v>
@@ -41744,7 +41753,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41822,10 +41831,10 @@
         <v>0.82</v>
       </c>
       <c r="AP196">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ196">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR196">
         <v>1.69</v>
@@ -42028,7 +42037,7 @@
         <v>1.2</v>
       </c>
       <c r="AP197">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ197">
         <v>1.14</v>
@@ -42156,7 +42165,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q198">
         <v>5.5</v>
@@ -42362,7 +42371,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q199">
         <v>3.2</v>
@@ -42440,7 +42449,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ199">
         <v>1.21</v>
@@ -42646,7 +42655,7 @@
         <v>1.2</v>
       </c>
       <c r="AP200">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42980,7 +42989,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -44010,7 +44019,7 @@
         <v>130</v>
       </c>
       <c r="P207" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q207">
         <v>4.5</v>
@@ -44091,7 +44100,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ207">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR207">
         <v>1.17</v>
@@ -44216,7 +44225,7 @@
         <v>235</v>
       </c>
       <c r="P208" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44628,7 +44637,7 @@
         <v>237</v>
       </c>
       <c r="P210" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q210">
         <v>4.75</v>
@@ -44834,7 +44843,7 @@
         <v>238</v>
       </c>
       <c r="P211" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q211">
         <v>1.83</v>
@@ -44912,10 +44921,10 @@
         <v>1</v>
       </c>
       <c r="AP211">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ211">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR211">
         <v>1.62</v>
@@ -45246,7 +45255,7 @@
         <v>240</v>
       </c>
       <c r="P213" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -45452,7 +45461,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45533,7 +45542,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ214">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR214">
         <v>1.25</v>
@@ -45658,7 +45667,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45736,7 +45745,7 @@
         <v>0.4</v>
       </c>
       <c r="AP215">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ215">
         <v>0.77</v>
@@ -45945,7 +45954,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ216">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR216">
         <v>1.31</v>
@@ -46148,7 +46157,7 @@
         <v>0.92</v>
       </c>
       <c r="AP217">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ217">
         <v>0.93</v>
@@ -46482,7 +46491,7 @@
         <v>100</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q219">
         <v>5.5</v>
@@ -46560,7 +46569,7 @@
         <v>2.5</v>
       </c>
       <c r="AP219">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ219">
         <v>2.57</v>
@@ -46894,7 +46903,7 @@
         <v>90</v>
       </c>
       <c r="P221" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q221">
         <v>2.1</v>
@@ -46972,7 +46981,7 @@
         <v>1.58</v>
       </c>
       <c r="AP221">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221">
         <v>1.57</v>
@@ -47306,7 +47315,7 @@
         <v>90</v>
       </c>
       <c r="P223" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q223">
         <v>3.25</v>
@@ -47387,7 +47396,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ223">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR223">
         <v>1.45</v>
@@ -47512,7 +47521,7 @@
         <v>90</v>
       </c>
       <c r="P224" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q224">
         <v>3.1</v>
@@ -47590,10 +47599,10 @@
         <v>0.45</v>
       </c>
       <c r="AP224">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ224">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR224">
         <v>1.31</v>
@@ -47799,7 +47808,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ225">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR225">
         <v>1.19</v>
@@ -47924,7 +47933,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q226">
         <v>2.6</v>
@@ -48130,7 +48139,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q227">
         <v>2.1</v>
@@ -48211,7 +48220,7 @@
         <v>2</v>
       </c>
       <c r="AQ227">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR227">
         <v>1.7</v>
@@ -48542,7 +48551,7 @@
         <v>90</v>
       </c>
       <c r="P229" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q229">
         <v>6</v>
@@ -48826,7 +48835,7 @@
         <v>0.64</v>
       </c>
       <c r="AP230">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ230">
         <v>0.77</v>
@@ -48954,7 +48963,7 @@
         <v>246</v>
       </c>
       <c r="P231" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q231">
         <v>1.83</v>
@@ -49035,7 +49044,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ231">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49366,7 +49375,7 @@
         <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q233">
         <v>3</v>
@@ -49447,7 +49456,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ233">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR233">
         <v>1.34</v>
@@ -49778,7 +49787,7 @@
         <v>249</v>
       </c>
       <c r="P235" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q235">
         <v>3.2</v>
@@ -50062,7 +50071,7 @@
         <v>2.08</v>
       </c>
       <c r="AP236">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ236">
         <v>1.93</v>
@@ -50190,7 +50199,7 @@
         <v>119</v>
       </c>
       <c r="P237" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q237">
         <v>10</v>
@@ -50396,7 +50405,7 @@
         <v>251</v>
       </c>
       <c r="P238" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q238">
         <v>2.4</v>
@@ -50602,7 +50611,7 @@
         <v>252</v>
       </c>
       <c r="P239" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q239">
         <v>2.75</v>
@@ -51014,7 +51023,7 @@
         <v>254</v>
       </c>
       <c r="P241" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q241">
         <v>3.6</v>
@@ -51220,7 +51229,7 @@
         <v>90</v>
       </c>
       <c r="P242" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q242">
         <v>4.5</v>
@@ -51632,7 +51641,7 @@
         <v>127</v>
       </c>
       <c r="P244" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52044,7 +52053,7 @@
         <v>256</v>
       </c>
       <c r="P246" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q246">
         <v>4</v>
@@ -52137,31 +52146,31 @@
         <v>3.24</v>
       </c>
       <c r="AU246">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV246">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW246">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AX246">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY246">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ246">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA246">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB246">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BC246">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD246">
         <v>2.25</v>
@@ -52250,7 +52259,7 @@
         <v>257</v>
       </c>
       <c r="P247" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q247">
         <v>2.88</v>
@@ -52343,31 +52352,31 @@
         <v>3.23</v>
       </c>
       <c r="AU247">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV247">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW247">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX247">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY247">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ247">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA247">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB247">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC247">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD247">
         <v>1.75</v>
@@ -52407,6 +52416,1036 @@
       </c>
       <c r="BP247">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7468603</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>83</v>
+      </c>
+      <c r="H248" t="s">
+        <v>82</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
+        <v>258</v>
+      </c>
+      <c r="P248" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q248">
+        <v>2.1</v>
+      </c>
+      <c r="R248">
+        <v>2.5</v>
+      </c>
+      <c r="S248">
+        <v>5</v>
+      </c>
+      <c r="T248">
+        <v>1.29</v>
+      </c>
+      <c r="U248">
+        <v>3.5</v>
+      </c>
+      <c r="V248">
+        <v>2.38</v>
+      </c>
+      <c r="W248">
+        <v>1.53</v>
+      </c>
+      <c r="X248">
+        <v>5.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.14</v>
+      </c>
+      <c r="Z248">
+        <v>1.6</v>
+      </c>
+      <c r="AA248">
+        <v>4.6</v>
+      </c>
+      <c r="AB248">
+        <v>5.1</v>
+      </c>
+      <c r="AC248">
+        <v>1.03</v>
+      </c>
+      <c r="AD248">
+        <v>11</v>
+      </c>
+      <c r="AE248">
+        <v>1.18</v>
+      </c>
+      <c r="AF248">
+        <v>4.75</v>
+      </c>
+      <c r="AG248">
+        <v>1.87</v>
+      </c>
+      <c r="AH248">
+        <v>1.93</v>
+      </c>
+      <c r="AI248">
+        <v>1.67</v>
+      </c>
+      <c r="AJ248">
+        <v>2.1</v>
+      </c>
+      <c r="AK248">
+        <v>1.16</v>
+      </c>
+      <c r="AL248">
+        <v>1.21</v>
+      </c>
+      <c r="AM248">
+        <v>2.35</v>
+      </c>
+      <c r="AN248">
+        <v>1.31</v>
+      </c>
+      <c r="AO248">
+        <v>0.23</v>
+      </c>
+      <c r="AP248">
+        <v>1.43</v>
+      </c>
+      <c r="AQ248">
+        <v>0.21</v>
+      </c>
+      <c r="AR248">
+        <v>1.7</v>
+      </c>
+      <c r="AS248">
+        <v>1.04</v>
+      </c>
+      <c r="AT248">
+        <v>2.74</v>
+      </c>
+      <c r="AU248">
+        <v>6</v>
+      </c>
+      <c r="AV248">
+        <v>3</v>
+      </c>
+      <c r="AW248">
+        <v>16</v>
+      </c>
+      <c r="AX248">
+        <v>6</v>
+      </c>
+      <c r="AY248">
+        <v>22</v>
+      </c>
+      <c r="AZ248">
+        <v>10</v>
+      </c>
+      <c r="BA248">
+        <v>6</v>
+      </c>
+      <c r="BB248">
+        <v>3</v>
+      </c>
+      <c r="BC248">
+        <v>9</v>
+      </c>
+      <c r="BD248">
+        <v>1.32</v>
+      </c>
+      <c r="BE248">
+        <v>7</v>
+      </c>
+      <c r="BF248">
+        <v>3.8</v>
+      </c>
+      <c r="BG248">
+        <v>1.32</v>
+      </c>
+      <c r="BH248">
+        <v>3.05</v>
+      </c>
+      <c r="BI248">
+        <v>1.55</v>
+      </c>
+      <c r="BJ248">
+        <v>2.25</v>
+      </c>
+      <c r="BK248">
+        <v>1.91</v>
+      </c>
+      <c r="BL248">
+        <v>1.77</v>
+      </c>
+      <c r="BM248">
+        <v>2.4</v>
+      </c>
+      <c r="BN248">
+        <v>1.49</v>
+      </c>
+      <c r="BO248">
+        <v>3.1</v>
+      </c>
+      <c r="BP248">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7468605</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45753.51041666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>72</v>
+      </c>
+      <c r="H249" t="s">
+        <v>84</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>90</v>
+      </c>
+      <c r="P249" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q249">
+        <v>3.75</v>
+      </c>
+      <c r="R249">
+        <v>2.1</v>
+      </c>
+      <c r="S249">
+        <v>2.88</v>
+      </c>
+      <c r="T249">
+        <v>1.4</v>
+      </c>
+      <c r="U249">
+        <v>2.75</v>
+      </c>
+      <c r="V249">
+        <v>3</v>
+      </c>
+      <c r="W249">
+        <v>1.36</v>
+      </c>
+      <c r="X249">
+        <v>8</v>
+      </c>
+      <c r="Y249">
+        <v>1.08</v>
+      </c>
+      <c r="Z249">
+        <v>3.25</v>
+      </c>
+      <c r="AA249">
+        <v>3.5</v>
+      </c>
+      <c r="AB249">
+        <v>2.27</v>
+      </c>
+      <c r="AC249">
+        <v>1.05</v>
+      </c>
+      <c r="AD249">
+        <v>9</v>
+      </c>
+      <c r="AE249">
+        <v>1.3</v>
+      </c>
+      <c r="AF249">
+        <v>3.4</v>
+      </c>
+      <c r="AG249">
+        <v>1.94</v>
+      </c>
+      <c r="AH249">
+        <v>1.87</v>
+      </c>
+      <c r="AI249">
+        <v>1.75</v>
+      </c>
+      <c r="AJ249">
+        <v>2</v>
+      </c>
+      <c r="AK249">
+        <v>1.66</v>
+      </c>
+      <c r="AL249">
+        <v>1.29</v>
+      </c>
+      <c r="AM249">
+        <v>1.33</v>
+      </c>
+      <c r="AN249">
+        <v>0.93</v>
+      </c>
+      <c r="AO249">
+        <v>1.29</v>
+      </c>
+      <c r="AP249">
+        <v>0.87</v>
+      </c>
+      <c r="AQ249">
+        <v>1.4</v>
+      </c>
+      <c r="AR249">
+        <v>1.32</v>
+      </c>
+      <c r="AS249">
+        <v>1.23</v>
+      </c>
+      <c r="AT249">
+        <v>2.55</v>
+      </c>
+      <c r="AU249">
+        <v>6</v>
+      </c>
+      <c r="AV249">
+        <v>6</v>
+      </c>
+      <c r="AW249">
+        <v>10</v>
+      </c>
+      <c r="AX249">
+        <v>7</v>
+      </c>
+      <c r="AY249">
+        <v>17</v>
+      </c>
+      <c r="AZ249">
+        <v>16</v>
+      </c>
+      <c r="BA249">
+        <v>4</v>
+      </c>
+      <c r="BB249">
+        <v>7</v>
+      </c>
+      <c r="BC249">
+        <v>11</v>
+      </c>
+      <c r="BD249">
+        <v>1.97</v>
+      </c>
+      <c r="BE249">
+        <v>6.25</v>
+      </c>
+      <c r="BF249">
+        <v>2.05</v>
+      </c>
+      <c r="BG249">
+        <v>1.41</v>
+      </c>
+      <c r="BH249">
+        <v>2.65</v>
+      </c>
+      <c r="BI249">
+        <v>1.68</v>
+      </c>
+      <c r="BJ249">
+        <v>2.04</v>
+      </c>
+      <c r="BK249">
+        <v>2.08</v>
+      </c>
+      <c r="BL249">
+        <v>1.65</v>
+      </c>
+      <c r="BM249">
+        <v>2.7</v>
+      </c>
+      <c r="BN249">
+        <v>1.4</v>
+      </c>
+      <c r="BO249">
+        <v>3.65</v>
+      </c>
+      <c r="BP249">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7468606</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45753.51041666666</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H250" t="s">
+        <v>74</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>1</v>
+      </c>
+      <c r="O250" t="s">
+        <v>90</v>
+      </c>
+      <c r="P250" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q250">
+        <v>2.5</v>
+      </c>
+      <c r="R250">
+        <v>2.2</v>
+      </c>
+      <c r="S250">
+        <v>4.5</v>
+      </c>
+      <c r="T250">
+        <v>1.36</v>
+      </c>
+      <c r="U250">
+        <v>3</v>
+      </c>
+      <c r="V250">
+        <v>2.75</v>
+      </c>
+      <c r="W250">
+        <v>1.4</v>
+      </c>
+      <c r="X250">
+        <v>8</v>
+      </c>
+      <c r="Y250">
+        <v>1.08</v>
+      </c>
+      <c r="Z250">
+        <v>1.84</v>
+      </c>
+      <c r="AA250">
+        <v>3.81</v>
+      </c>
+      <c r="AB250">
+        <v>4.33</v>
+      </c>
+      <c r="AC250">
+        <v>1.05</v>
+      </c>
+      <c r="AD250">
+        <v>9.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.28</v>
+      </c>
+      <c r="AF250">
+        <v>3.65</v>
+      </c>
+      <c r="AG250">
+        <v>1.84</v>
+      </c>
+      <c r="AH250">
+        <v>1.97</v>
+      </c>
+      <c r="AI250">
+        <v>1.75</v>
+      </c>
+      <c r="AJ250">
+        <v>2</v>
+      </c>
+      <c r="AK250">
+        <v>1.23</v>
+      </c>
+      <c r="AL250">
+        <v>1.26</v>
+      </c>
+      <c r="AM250">
+        <v>1.93</v>
+      </c>
+      <c r="AN250">
+        <v>1.57</v>
+      </c>
+      <c r="AO250">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP250">
+        <v>1.47</v>
+      </c>
+      <c r="AQ250">
+        <v>0.86</v>
+      </c>
+      <c r="AR250">
+        <v>1.6</v>
+      </c>
+      <c r="AS250">
+        <v>1.31</v>
+      </c>
+      <c r="AT250">
+        <v>2.91</v>
+      </c>
+      <c r="AU250">
+        <v>7</v>
+      </c>
+      <c r="AV250">
+        <v>6</v>
+      </c>
+      <c r="AW250">
+        <v>13</v>
+      </c>
+      <c r="AX250">
+        <v>9</v>
+      </c>
+      <c r="AY250">
+        <v>23</v>
+      </c>
+      <c r="AZ250">
+        <v>19</v>
+      </c>
+      <c r="BA250">
+        <v>8</v>
+      </c>
+      <c r="BB250">
+        <v>5</v>
+      </c>
+      <c r="BC250">
+        <v>13</v>
+      </c>
+      <c r="BD250">
+        <v>1.44</v>
+      </c>
+      <c r="BE250">
+        <v>6.75</v>
+      </c>
+      <c r="BF250">
+        <v>3.15</v>
+      </c>
+      <c r="BG250">
+        <v>1.41</v>
+      </c>
+      <c r="BH250">
+        <v>2.65</v>
+      </c>
+      <c r="BI250">
+        <v>1.7</v>
+      </c>
+      <c r="BJ250">
+        <v>2</v>
+      </c>
+      <c r="BK250">
+        <v>2.1</v>
+      </c>
+      <c r="BL250">
+        <v>1.64</v>
+      </c>
+      <c r="BM250">
+        <v>2.7</v>
+      </c>
+      <c r="BN250">
+        <v>1.4</v>
+      </c>
+      <c r="BO250">
+        <v>3.55</v>
+      </c>
+      <c r="BP250">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7468601</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45753.51041666666</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>75</v>
+      </c>
+      <c r="H251" t="s">
+        <v>70</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>2</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>90</v>
+      </c>
+      <c r="P251" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q251">
+        <v>3</v>
+      </c>
+      <c r="R251">
+        <v>2.2</v>
+      </c>
+      <c r="S251">
+        <v>3.4</v>
+      </c>
+      <c r="T251">
+        <v>1.36</v>
+      </c>
+      <c r="U251">
+        <v>3</v>
+      </c>
+      <c r="V251">
+        <v>2.75</v>
+      </c>
+      <c r="W251">
+        <v>1.4</v>
+      </c>
+      <c r="X251">
+        <v>8</v>
+      </c>
+      <c r="Y251">
+        <v>1.08</v>
+      </c>
+      <c r="Z251">
+        <v>2.38</v>
+      </c>
+      <c r="AA251">
+        <v>3.55</v>
+      </c>
+      <c r="AB251">
+        <v>3</v>
+      </c>
+      <c r="AC251">
+        <v>1.05</v>
+      </c>
+      <c r="AD251">
+        <v>9.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.28</v>
+      </c>
+      <c r="AF251">
+        <v>3.55</v>
+      </c>
+      <c r="AG251">
+        <v>1.87</v>
+      </c>
+      <c r="AH251">
+        <v>1.94</v>
+      </c>
+      <c r="AI251">
+        <v>1.67</v>
+      </c>
+      <c r="AJ251">
+        <v>2.1</v>
+      </c>
+      <c r="AK251">
+        <v>1.39</v>
+      </c>
+      <c r="AL251">
+        <v>1.29</v>
+      </c>
+      <c r="AM251">
+        <v>1.58</v>
+      </c>
+      <c r="AN251">
+        <v>0.92</v>
+      </c>
+      <c r="AO251">
+        <v>1.08</v>
+      </c>
+      <c r="AP251">
+        <v>0.86</v>
+      </c>
+      <c r="AQ251">
+        <v>1.21</v>
+      </c>
+      <c r="AR251">
+        <v>1.53</v>
+      </c>
+      <c r="AS251">
+        <v>1.06</v>
+      </c>
+      <c r="AT251">
+        <v>2.59</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>6</v>
+      </c>
+      <c r="AX251">
+        <v>10</v>
+      </c>
+      <c r="AY251">
+        <v>16</v>
+      </c>
+      <c r="AZ251">
+        <v>18</v>
+      </c>
+      <c r="BA251">
+        <v>5</v>
+      </c>
+      <c r="BB251">
+        <v>2</v>
+      </c>
+      <c r="BC251">
+        <v>7</v>
+      </c>
+      <c r="BD251">
+        <v>1.71</v>
+      </c>
+      <c r="BE251">
+        <v>6.4</v>
+      </c>
+      <c r="BF251">
+        <v>2.4</v>
+      </c>
+      <c r="BG251">
+        <v>1.4</v>
+      </c>
+      <c r="BH251">
+        <v>2.7</v>
+      </c>
+      <c r="BI251">
+        <v>1.66</v>
+      </c>
+      <c r="BJ251">
+        <v>2.07</v>
+      </c>
+      <c r="BK251">
+        <v>2.07</v>
+      </c>
+      <c r="BL251">
+        <v>1.66</v>
+      </c>
+      <c r="BM251">
+        <v>2.65</v>
+      </c>
+      <c r="BN251">
+        <v>1.41</v>
+      </c>
+      <c r="BO251">
+        <v>3.55</v>
+      </c>
+      <c r="BP251">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7468598</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45753.65625</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>87</v>
+      </c>
+      <c r="H252" t="s">
+        <v>76</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>2</v>
+      </c>
+      <c r="L252">
+        <v>3</v>
+      </c>
+      <c r="M252">
+        <v>2</v>
+      </c>
+      <c r="N252">
+        <v>5</v>
+      </c>
+      <c r="O252" t="s">
+        <v>259</v>
+      </c>
+      <c r="P252" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q252">
+        <v>2.38</v>
+      </c>
+      <c r="R252">
+        <v>2.25</v>
+      </c>
+      <c r="S252">
+        <v>4.75</v>
+      </c>
+      <c r="T252">
+        <v>1.36</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.75</v>
+      </c>
+      <c r="W252">
+        <v>1.4</v>
+      </c>
+      <c r="X252">
+        <v>7</v>
+      </c>
+      <c r="Y252">
+        <v>1.1</v>
+      </c>
+      <c r="Z252">
+        <v>1.65</v>
+      </c>
+      <c r="AA252">
+        <v>4.1</v>
+      </c>
+      <c r="AB252">
+        <v>5.4</v>
+      </c>
+      <c r="AC252">
+        <v>1.05</v>
+      </c>
+      <c r="AD252">
+        <v>9.5</v>
+      </c>
+      <c r="AE252">
+        <v>1.25</v>
+      </c>
+      <c r="AF252">
+        <v>3.7</v>
+      </c>
+      <c r="AG252">
+        <v>1.83</v>
+      </c>
+      <c r="AH252">
+        <v>1.98</v>
+      </c>
+      <c r="AI252">
+        <v>1.8</v>
+      </c>
+      <c r="AJ252">
+        <v>1.95</v>
+      </c>
+      <c r="AK252">
+        <v>1.21</v>
+      </c>
+      <c r="AL252">
+        <v>1.25</v>
+      </c>
+      <c r="AM252">
+        <v>2</v>
+      </c>
+      <c r="AN252">
+        <v>1.69</v>
+      </c>
+      <c r="AO252">
+        <v>1.38</v>
+      </c>
+      <c r="AP252">
+        <v>1.79</v>
+      </c>
+      <c r="AQ252">
+        <v>1.29</v>
+      </c>
+      <c r="AR252">
+        <v>1.84</v>
+      </c>
+      <c r="AS252">
+        <v>1.36</v>
+      </c>
+      <c r="AT252">
+        <v>3.2</v>
+      </c>
+      <c r="AU252">
+        <v>8</v>
+      </c>
+      <c r="AV252">
+        <v>5</v>
+      </c>
+      <c r="AW252">
+        <v>5</v>
+      </c>
+      <c r="AX252">
+        <v>5</v>
+      </c>
+      <c r="AY252">
+        <v>14</v>
+      </c>
+      <c r="AZ252">
+        <v>10</v>
+      </c>
+      <c r="BA252">
+        <v>5</v>
+      </c>
+      <c r="BB252">
+        <v>1</v>
+      </c>
+      <c r="BC252">
+        <v>6</v>
+      </c>
+      <c r="BD252">
+        <v>1.44</v>
+      </c>
+      <c r="BE252">
+        <v>6.75</v>
+      </c>
+      <c r="BF252">
+        <v>3.15</v>
+      </c>
+      <c r="BG252">
+        <v>1.41</v>
+      </c>
+      <c r="BH252">
+        <v>2.65</v>
+      </c>
+      <c r="BI252">
+        <v>1.71</v>
+      </c>
+      <c r="BJ252">
+        <v>2</v>
+      </c>
+      <c r="BK252">
+        <v>2.14</v>
+      </c>
+      <c r="BL252">
+        <v>1.62</v>
+      </c>
+      <c r="BM252">
+        <v>2.75</v>
+      </c>
+      <c r="BN252">
+        <v>1.38</v>
+      </c>
+      <c r="BO252">
+        <v>3.65</v>
+      </c>
+      <c r="BP252">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 1_20242025.xlsx
@@ -2053,10 +2053,10 @@
         <v>3</v>
       </c>
       <c r="AY2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2">
         <v>2</v>
@@ -2259,10 +2259,10 @@
         <v>1</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2465,10 +2465,10 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BA4">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>5</v>
       </c>
       <c r="AY5">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2877,10 +2877,10 @@
         <v>4</v>
       </c>
       <c r="AY6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA6">
         <v>3</v>
@@ -3083,10 +3083,10 @@
         <v>6</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA7">
         <v>6</v>
@@ -3289,10 +3289,10 @@
         <v>5</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA8">
         <v>10</v>
@@ -3495,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ9">
         <v>11</v>
@@ -3701,10 +3701,10 @@
         <v>8</v>
       </c>
       <c r="AY10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA10">
         <v>7</v>
@@ -3907,10 +3907,10 @@
         <v>3</v>
       </c>
       <c r="AY11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AZ11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA11">
         <v>10</v>
@@ -4116,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA12">
         <v>0</v>
@@ -4319,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="AY13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA13">
         <v>3</v>
@@ -4525,10 +4525,10 @@
         <v>7</v>
       </c>
       <c r="AY14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA14">
         <v>2</v>
@@ -4731,7 +4731,7 @@
         <v>9</v>
       </c>
       <c r="AY15">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ15">
         <v>12</v>
@@ -4937,10 +4937,10 @@
         <v>6</v>
       </c>
       <c r="AY16">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA16">
         <v>2</v>
@@ -5143,10 +5143,10 @@
         <v>4</v>
       </c>
       <c r="AY17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA17">
         <v>3</v>
@@ -5349,10 +5349,10 @@
         <v>7</v>
       </c>
       <c r="AY18">
+        <v>9</v>
+      </c>
+      <c r="AZ18">
         <v>11</v>
-      </c>
-      <c r="AZ18">
-        <v>17</v>
       </c>
       <c r="BA18">
         <v>4</v>
@@ -5555,10 +5555,10 @@
         <v>5</v>
       </c>
       <c r="AY19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA19">
         <v>2</v>
@@ -5761,10 +5761,10 @@
         <v>2</v>
       </c>
       <c r="AY20">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ20">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA20">
         <v>9</v>
@@ -5967,10 +5967,10 @@
         <v>5</v>
       </c>
       <c r="AY21">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA21">
         <v>7</v>
@@ -6173,10 +6173,10 @@
         <v>4</v>
       </c>
       <c r="AY22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA22">
         <v>8</v>
@@ -6382,7 +6382,7 @@
         <v>4</v>
       </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA23">
         <v>2</v>
@@ -6585,10 +6585,10 @@
         <v>6</v>
       </c>
       <c r="AY24">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA24">
         <v>7</v>
@@ -6791,19 +6791,19 @@
         <v>2</v>
       </c>
       <c r="AY25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA25">
         <v>4</v>
       </c>
       <c r="BB25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD25">
         <v>2.43</v>
@@ -6997,10 +6997,10 @@
         <v>1</v>
       </c>
       <c r="AY26">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA26">
         <v>2</v>
@@ -7203,10 +7203,10 @@
         <v>3</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA27">
         <v>3</v>
@@ -7412,7 +7412,7 @@
         <v>9</v>
       </c>
       <c r="AZ28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -7618,7 +7618,7 @@
         <v>11</v>
       </c>
       <c r="AZ29">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA29">
         <v>2</v>
@@ -7821,10 +7821,10 @@
         <v>4</v>
       </c>
       <c r="AY30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA30">
         <v>1</v>
@@ -8027,10 +8027,10 @@
         <v>4</v>
       </c>
       <c r="AY31">
+        <v>9</v>
+      </c>
+      <c r="AZ31">
         <v>14</v>
-      </c>
-      <c r="AZ31">
-        <v>20</v>
       </c>
       <c r="BA31">
         <v>1</v>
@@ -8233,10 +8233,10 @@
         <v>0</v>
       </c>
       <c r="AY32">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA32">
         <v>9</v>
@@ -8442,7 +8442,7 @@
         <v>12</v>
       </c>
       <c r="AZ33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA33">
         <v>3</v>
@@ -8645,10 +8645,10 @@
         <v>5</v>
       </c>
       <c r="AY34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA34">
         <v>6</v>
@@ -8851,10 +8851,10 @@
         <v>5</v>
       </c>
       <c r="AY35">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ35">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA35">
         <v>6</v>
@@ -9057,10 +9057,10 @@
         <v>1</v>
       </c>
       <c r="AY36">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9263,10 +9263,10 @@
         <v>1</v>
       </c>
       <c r="AY37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA37">
         <v>5</v>
@@ -9469,10 +9469,10 @@
         <v>4</v>
       </c>
       <c r="AY38">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA38">
         <v>3</v>
@@ -9675,10 +9675,10 @@
         <v>1</v>
       </c>
       <c r="AY39">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ39">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA39">
         <v>9</v>
@@ -9881,10 +9881,10 @@
         <v>3</v>
       </c>
       <c r="AY40">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ40">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA40">
         <v>4</v>
@@ -10087,10 +10087,10 @@
         <v>5</v>
       </c>
       <c r="AY41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ41">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA41">
         <v>3</v>
@@ -10293,10 +10293,10 @@
         <v>3</v>
       </c>
       <c r="AY42">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA42">
         <v>6</v>
@@ -10499,10 +10499,10 @@
         <v>9</v>
       </c>
       <c r="AY43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA43">
         <v>4</v>
@@ -10705,10 +10705,10 @@
         <v>2</v>
       </c>
       <c r="AY44">
+        <v>5</v>
+      </c>
+      <c r="AZ44">
         <v>6</v>
-      </c>
-      <c r="AZ44">
-        <v>10</v>
       </c>
       <c r="BA44">
         <v>3</v>
@@ -10911,10 +10911,10 @@
         <v>3</v>
       </c>
       <c r="AY45">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ45">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA45">
         <v>11</v>
@@ -11117,10 +11117,10 @@
         <v>2</v>
       </c>
       <c r="AY46">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA46">
         <v>10</v>
@@ -11323,7 +11323,7 @@
         <v>4</v>
       </c>
       <c r="AY47">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ47">
         <v>9</v>
@@ -11529,10 +11529,10 @@
         <v>3</v>
       </c>
       <c r="AY48">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ48">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA48">
         <v>6</v>
@@ -11735,10 +11735,10 @@
         <v>3</v>
       </c>
       <c r="AY49">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ49">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA49">
         <v>11</v>
@@ -11944,7 +11944,7 @@
         <v>8</v>
       </c>
       <c r="AZ50">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA50">
         <v>1</v>
@@ -12147,10 +12147,10 @@
         <v>3</v>
       </c>
       <c r="AY51">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA51">
         <v>6</v>
@@ -12353,10 +12353,10 @@
         <v>1</v>
       </c>
       <c r="AY52">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA52">
         <v>3</v>
@@ -12559,10 +12559,10 @@
         <v>2</v>
       </c>
       <c r="AY53">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA53">
         <v>8</v>
@@ -12765,10 +12765,10 @@
         <v>9</v>
       </c>
       <c r="AY54">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ54">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA54">
         <v>5</v>
@@ -12971,10 +12971,10 @@
         <v>5</v>
       </c>
       <c r="AY55">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ55">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA55">
         <v>8</v>
@@ -13177,10 +13177,10 @@
         <v>4</v>
       </c>
       <c r="AY56">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ56">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA56">
         <v>9</v>
@@ -13383,10 +13383,10 @@
         <v>5</v>
       </c>
       <c r="AY57">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ57">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA57">
         <v>5</v>
@@ -13589,10 +13589,10 @@
         <v>5</v>
       </c>
       <c r="AY58">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ58">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA58">
         <v>4</v>
@@ -13795,10 +13795,10 @@
         <v>2</v>
       </c>
       <c r="AY59">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA59">
         <v>10</v>
@@ -14001,10 +14001,10 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ60">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA60">
         <v>6</v>
@@ -14207,10 +14207,10 @@
         <v>10</v>
       </c>
       <c r="AY61">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ61">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA61">
         <v>1</v>
@@ -14413,10 +14413,10 @@
         <v>3</v>
       </c>
       <c r="AY62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ62">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA62">
         <v>3</v>
@@ -14619,10 +14619,10 @@
         <v>4</v>
       </c>
       <c r="AY63">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ63">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA63">
         <v>4</v>
@@ -14825,10 +14825,10 @@
         <v>5</v>
       </c>
       <c r="AY64">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ64">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA64">
         <v>5</v>
@@ -15237,7 +15237,7 @@
         <v>2</v>
       </c>
       <c r="AY66">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ66">
         <v>7</v>
@@ -15443,10 +15443,10 @@
         <v>7</v>
       </c>
       <c r="AY67">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ67">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA67">
         <v>2</v>
@@ -15649,10 +15649,10 @@
         <v>1</v>
       </c>
       <c r="AY68">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ68">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BA68">
         <v>5</v>
@@ -17091,10 +17091,10 @@
         <v>6</v>
       </c>
       <c r="AY75">
+        <v>13</v>
+      </c>
+      <c r="AZ75">
         <v>14</v>
-      </c>
-      <c r="AZ75">
-        <v>21</v>
       </c>
       <c r="BA75">
         <v>2</v>
@@ -17297,10 +17297,10 @@
         <v>4</v>
       </c>
       <c r="AY76">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ76">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA76">
         <v>7</v>
@@ -17503,10 +17503,10 @@
         <v>1</v>
       </c>
       <c r="AY77">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ77">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BA77">
         <v>8</v>
@@ -17709,10 +17709,10 @@
         <v>7</v>
       </c>
       <c r="AY78">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ78">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA78">
         <v>5</v>
@@ -17915,10 +17915,10 @@
         <v>5</v>
       </c>
       <c r="AY79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ79">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA79">
         <v>1</v>
@@ -18121,10 +18121,10 @@
         <v>1</v>
       </c>
       <c r="AY80">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ80">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA80">
         <v>5</v>
@@ -18327,10 +18327,10 @@
         <v>1</v>
       </c>
       <c r="AY81">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ81">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA81">
         <v>6</v>
@@ -18533,10 +18533,10 @@
         <v>9</v>
       </c>
       <c r="AY82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ82">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA82">
         <v>1</v>
@@ -18739,10 +18739,10 @@
         <v>3</v>
       </c>
       <c r="AY83">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ83">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA83">
         <v>4</v>
@@ -18945,10 +18945,10 @@
         <v>6</v>
       </c>
       <c r="AY84">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ84">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA84">
         <v>4</v>
@@ -19151,10 +19151,10 @@
         <v>6</v>
       </c>
       <c r="AY85">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ85">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA85">
         <v>7</v>
@@ -19357,10 +19357,10 @@
         <v>8</v>
       </c>
       <c r="AY86">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ86">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA86">
         <v>6</v>
@@ -19563,10 +19563,10 @@
         <v>4</v>
       </c>
       <c r="AY87">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ87">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA87">
         <v>2</v>
@@ -19769,10 +19769,10 @@
         <v>4</v>
       </c>
       <c r="AY88">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ88">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA88">
         <v>6</v>
@@ -19975,10 +19975,10 @@
         <v>1</v>
       </c>
       <c r="AY89">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA89">
         <v>3</v>
@@ -20181,10 +20181,10 @@
         <v>8</v>
       </c>
       <c r="AY90">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ90">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA90">
         <v>2</v>
@@ -20387,10 +20387,10 @@
         <v>3</v>
       </c>
       <c r="AY91">
+        <v>7</v>
+      </c>
+      <c r="AZ91">
         <v>8</v>
-      </c>
-      <c r="AZ91">
-        <v>11</v>
       </c>
       <c r="BA91">
         <v>2</v>
@@ -20593,19 +20593,19 @@
         <v>2</v>
       </c>
       <c r="AY92">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ92">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB92">
         <v>3</v>
       </c>
       <c r="BC92">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD92">
         <v>1.33</v>
@@ -20802,7 +20802,7 @@
         <v>6</v>
       </c>
       <c r="AZ93">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA93">
         <v>1</v>
@@ -21005,10 +21005,10 @@
         <v>5</v>
       </c>
       <c r="AY94">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ94">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA94">
         <v>6</v>
@@ -21211,10 +21211,10 @@
         <v>9</v>
       </c>
       <c r="AY95">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ95">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA95">
         <v>6</v>
@@ -21417,10 +21417,10 @@
         <v>5</v>
       </c>
       <c r="AY96">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ96">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA96">
         <v>6</v>
@@ -21623,10 +21623,10 @@
         <v>6</v>
       </c>
       <c r="AY97">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA97">
         <v>5</v>
@@ -21829,10 +21829,10 @@
         <v>12</v>
       </c>
       <c r="AY98">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ98">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA98">
         <v>3</v>
@@ -22035,10 +22035,10 @@
         <v>6</v>
       </c>
       <c r="AY99">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ99">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA99">
         <v>8</v>
@@ -22241,10 +22241,10 @@
         <v>2</v>
       </c>
       <c r="AY100">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ100">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA100">
         <v>7</v>
@@ -24301,10 +24301,10 @@
         <v>4</v>
       </c>
       <c r="AY110">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ110">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA110">
         <v>3</v>
@@ -24507,10 +24507,10 @@
         <v>2</v>
       </c>
       <c r="AY111">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -24713,10 +24713,10 @@
         <v>5</v>
       </c>
       <c r="AY112">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ112">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA112">
         <v>4</v>
@@ -24919,10 +24919,10 @@
         <v>2</v>
       </c>
       <c r="AY113">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ113">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA113">
         <v>9</v>
@@ -25125,10 +25125,10 @@
         <v>7</v>
       </c>
       <c r="AY114">
+        <v>11</v>
+      </c>
+      <c r="AZ114">
         <v>12</v>
-      </c>
-      <c r="AZ114">
-        <v>14</v>
       </c>
       <c r="BA114">
         <v>7</v>
@@ -25331,10 +25331,10 @@
         <v>5</v>
       </c>
       <c r="AY115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ115">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA115">
         <v>2</v>
@@ -25537,10 +25537,10 @@
         <v>2</v>
       </c>
       <c r="AY116">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ116">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BA116">
         <v>6</v>
@@ -25743,10 +25743,10 @@
         <v>3</v>
       </c>
       <c r="AY117">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ117">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA117">
         <v>5</v>
@@ -25949,10 +25949,10 @@
         <v>1</v>
       </c>
       <c r="AY118">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ118">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA118">
         <v>5</v>
@@ -26155,7 +26155,7 @@
         <v>4</v>
       </c>
       <c r="AY119">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ119">
         <v>8</v>
@@ -26361,10 +26361,10 @@
         <v>9</v>
       </c>
       <c r="AY120">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ120">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA120">
         <v>3</v>
@@ -26567,10 +26567,10 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ121">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA121">
         <v>2</v>
@@ -26773,10 +26773,10 @@
         <v>5</v>
       </c>
       <c r="AY122">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ122">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA122">
         <v>5</v>
@@ -26979,10 +26979,10 @@
         <v>1</v>
       </c>
       <c r="AY123">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ123">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA123">
         <v>2</v>
@@ -27185,10 +27185,10 @@
         <v>4</v>
       </c>
       <c r="AY124">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ124">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA124">
         <v>6</v>
@@ -27391,10 +27391,10 @@
         <v>4</v>
       </c>
       <c r="AY125">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ125">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA125">
         <v>3</v>
@@ -27597,7 +27597,7 @@
         <v>2</v>
       </c>
       <c r="AY126">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ126">
         <v>7</v>
@@ -27803,10 +27803,10 @@
         <v>4</v>
       </c>
       <c r="AY127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ127">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA127">
         <v>0</v>
@@ -28009,7 +28009,7 @@
         <v>1</v>
       </c>
       <c r="AY128">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ128">
         <v>4</v>
@@ -28215,10 +28215,10 @@
         <v>4</v>
       </c>
       <c r="AY129">
+        <v>7</v>
+      </c>
+      <c r="AZ129">
         <v>10</v>
-      </c>
-      <c r="AZ129">
-        <v>11</v>
       </c>
       <c r="BA129">
         <v>3</v>
@@ -28421,10 +28421,10 @@
         <v>5</v>
       </c>
       <c r="AY130">
+        <v>8</v>
+      </c>
+      <c r="AZ130">
         <v>11</v>
-      </c>
-      <c r="AZ130">
-        <v>17</v>
       </c>
       <c r="BA130">
         <v>3</v>
@@ -28627,10 +28627,10 @@
         <v>7</v>
       </c>
       <c r="AY131">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ131">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA131">
         <v>1</v>
@@ -28833,10 +28833,10 @@
         <v>7</v>
       </c>
       <c r="AY132">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ132">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA132">
         <v>9</v>
@@ -29039,10 +29039,10 @@
         <v>3</v>
       </c>
       <c r="AY133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ133">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA133">
         <v>3</v>
@@ -29245,10 +29245,10 @@
         <v>3</v>
       </c>
       <c r="AY134">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ134">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA134">
         <v>0</v>
@@ -29451,10 +29451,10 @@
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA135">
         <v>2</v>
@@ -29657,10 +29657,10 @@
         <v>2</v>
       </c>
       <c r="AY136">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ136">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA136">
         <v>4</v>
@@ -29863,10 +29863,10 @@
         <v>3</v>
       </c>
       <c r="AY137">
+        <v>11</v>
+      </c>
+      <c r="AZ137">
         <v>16</v>
-      </c>
-      <c r="AZ137">
-        <v>18</v>
       </c>
       <c r="BA137">
         <v>1</v>
@@ -30069,10 +30069,10 @@
         <v>3</v>
       </c>
       <c r="AY138">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ138">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA138">
         <v>3</v>
@@ -30275,10 +30275,10 @@
         <v>6</v>
       </c>
       <c r="AY139">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ139">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA139">
         <v>6</v>
@@ -30481,10 +30481,10 @@
         <v>3</v>
       </c>
       <c r="AY140">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA140">
         <v>2</v>
@@ -30687,10 +30687,10 @@
         <v>8</v>
       </c>
       <c r="AY141">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ141">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA141">
         <v>3</v>
@@ -30893,10 +30893,10 @@
         <v>1</v>
       </c>
       <c r="AY142">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ142">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA142">
         <v>7</v>
@@ -31099,10 +31099,10 @@
         <v>6</v>
       </c>
       <c r="AY143">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ143">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA143">
         <v>4</v>
@@ -31305,10 +31305,10 @@
         <v>6</v>
       </c>
       <c r="AY144">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ144">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA144">
         <v>2</v>
@@ -31511,10 +31511,10 @@
         <v>2</v>
       </c>
       <c r="AY145">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA145">
         <v>4</v>
@@ -31717,10 +31717,10 @@
         <v>5</v>
       </c>
       <c r="AY146">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ146">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31923,10 +31923,10 @@
         <v>1</v>
       </c>
       <c r="AY147">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ147">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA147">
         <v>6</v>
@@ -32129,10 +32129,10 @@
         <v>4</v>
       </c>
       <c r="AY148">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ148">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA148">
         <v>4</v>
@@ -32335,10 +32335,10 @@
         <v>3</v>
       </c>
       <c r="AY149">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ149">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA149">
         <v>6</v>
@@ -32541,10 +32541,10 @@
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ150">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA150">
         <v>2</v>
@@ -32747,10 +32747,10 @@
         <v>10</v>
       </c>
       <c r="AY151">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ151">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BA151">
         <v>3</v>
@@ -32953,10 +32953,10 @@
         <v>13</v>
       </c>
       <c r="AY152">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ152">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BA152">
         <v>3</v>
@@ -33159,10 +33159,10 @@
         <v>5</v>
       </c>
       <c r="AY153">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ153">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA153">
         <v>3</v>
@@ -33365,10 +33365,10 @@
         <v>4</v>
       </c>
       <c r="AY154">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ154">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA154">
         <v>7</v>
@@ -33571,10 +33571,10 @@
         <v>18</v>
       </c>
       <c r="AY155">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ155">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="BA155">
         <v>4</v>
@@ -33777,10 +33777,10 @@
         <v>8</v>
       </c>
       <c r="AY156">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ156">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA156">
         <v>7</v>
@@ -33983,10 +33983,10 @@
         <v>2</v>
       </c>
       <c r="AY157">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ157">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA157">
         <v>6</v>
@@ -34189,7 +34189,7 @@
         <v>6</v>
       </c>
       <c r="AY158">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ158">
         <v>10</v>
@@ -34395,10 +34395,10 @@
         <v>7</v>
       </c>
       <c r="AY159">
+        <v>11</v>
+      </c>
+      <c r="AZ159">
         <v>13</v>
-      </c>
-      <c r="AZ159">
-        <v>15</v>
       </c>
       <c r="BA159">
         <v>8</v>
@@ -34601,10 +34601,10 @@
         <v>4</v>
       </c>
       <c r="AY160">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ160">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA160">
         <v>7</v>
@@ -34807,7 +34807,7 @@
         <v>6</v>
       </c>
       <c r="AY161">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ161">
         <v>11</v>
@@ -35013,7 +35013,7 @@
         <v>3</v>
       </c>
       <c r="AY162">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ162">
         <v>6</v>
@@ -35219,10 +35219,10 @@
         <v>5</v>
       </c>
       <c r="AY163">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ163">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA163">
         <v>9</v>
@@ -35425,10 +35425,10 @@
         <v>6</v>
       </c>
       <c r="AY164">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ164">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA164">
         <v>3</v>
@@ -35631,7 +35631,7 @@
         <v>7</v>
       </c>
       <c r="AY165">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ165">
         <v>13</v>
@@ -35840,7 +35840,7 @@
         <v>14</v>
       </c>
       <c r="AZ166">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA166">
         <v>6</v>
@@ -36043,10 +36043,10 @@
         <v>3</v>
       </c>
       <c r="AY167">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ167">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA167">
         <v>8</v>
@@ -36249,10 +36249,10 @@
         <v>11</v>
       </c>
       <c r="AY168">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ168">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA168">
         <v>6</v>
@@ -36455,10 +36455,10 @@
         <v>7</v>
       </c>
       <c r="AY169">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ169">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA169">
         <v>4</v>
@@ -36661,7 +36661,7 @@
         <v>2</v>
       </c>
       <c r="AY170">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ170">
         <v>7</v>
@@ -36867,10 +36867,10 @@
         <v>2</v>
       </c>
       <c r="AY171">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ171">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA171">
         <v>4</v>
@@ -37076,7 +37076,7 @@
         <v>15</v>
       </c>
       <c r="AZ172">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA172">
         <v>6</v>
@@ -37279,10 +37279,10 @@
         <v>12</v>
       </c>
       <c r="AY173">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ173">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BA173">
         <v>4</v>
@@ -37485,10 +37485,10 @@
         <v>7</v>
       </c>
       <c r="AY174">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ174">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA174">
         <v>4</v>
@@ -37691,7 +37691,7 @@
         <v>6</v>
       </c>
       <c r="AY175">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ175">
         <v>14</v>
@@ -37897,10 +37897,10 @@
         <v>7</v>
       </c>
       <c r="AY176">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AZ176">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA176">
         <v>7</v>
@@ -38103,10 +38103,10 @@
         <v>10</v>
       </c>
       <c r="AY177">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ177">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA177">
         <v>7</v>
@@ -38309,10 +38309,10 @@
         <v>3</v>
       </c>
       <c r="AY178">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ178">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA178">
         <v>6</v>
@@ -38518,7 +38518,7 @@
         <v>16</v>
       </c>
       <c r="AZ179">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA179">
         <v>4</v>
@@ -38721,10 +38721,10 @@
         <v>4</v>
       </c>
       <c r="AY180">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ180">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA180">
         <v>9</v>
@@ -38930,7 +38930,7 @@
         <v>20</v>
       </c>
       <c r="AZ181">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA181">
         <v>6</v>
@@ -39133,10 +39133,10 @@
         <v>5</v>
       </c>
       <c r="AY182">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ182">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA182">
         <v>12</v>
@@ -39339,10 +39339,10 @@
         <v>6</v>
       </c>
       <c r="AY183">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ183">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA183">
         <v>1</v>
@@ -39545,10 +39545,10 @@
         <v>8</v>
       </c>
       <c r="AY184">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ184">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA184">
         <v>7</v>
@@ -39957,10 +39957,10 @@
         <v>11</v>
       </c>
       <c r="AY186">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ186">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA186">
         <v>2</v>
@@ -40163,10 +40163,10 @@
         <v>6</v>
       </c>
       <c r="AY187">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ187">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA187">
         <v>6</v>
@@ -40369,10 +40369,10 @@
         <v>4</v>
       </c>
       <c r="AY188">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ188">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA188">
         <v>3</v>
@@ -40575,10 +40575,10 @@
         <v>10</v>
       </c>
       <c r="AY189">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ189">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA189">
         <v>6</v>
@@ -40781,10 +40781,10 @@
         <v>8</v>
       </c>
       <c r="AY190">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ190">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA190">
         <v>1</v>
@@ -40987,10 +40987,10 @@
         <v>6</v>
       </c>
       <c r="AY191">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ191">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA191">
         <v>6</v>
@@ -41193,10 +41193,10 @@
         <v>6</v>
       </c>
       <c r="AY192">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AZ192">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA192">
         <v>14</v>
@@ -41399,10 +41399,10 @@
         <v>4</v>
       </c>
       <c r="AY193">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ193">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA193">
         <v>9</v>
@@ -41605,10 +41605,10 @@
         <v>14</v>
       </c>
       <c r="AY194">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ194">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BA194">
         <v>5</v>
@@ -41811,10 +41811,10 @@
         <v>4</v>
       </c>
       <c r="AY195">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ195">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA195">
         <v>7</v>
@@ -42017,10 +42017,10 @@
         <v>9</v>
       </c>
       <c r="AY196">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ196">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA196">
         <v>7</v>
@@ -42223,10 +42223,10 @@
         <v>6</v>
       </c>
       <c r="AY197">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ197">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA197">
         <v>1</v>
@@ -42432,7 +42432,7 @@
         <v>16</v>
       </c>
       <c r="AZ198">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA198">
         <v>6</v>
@@ -42635,10 +42635,10 @@
         <v>12</v>
       </c>
       <c r="AY199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ199">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA199">
         <v>4</v>
@@ -42841,10 +42841,10 @@
         <v>4</v>
       </c>
       <c r="AY200">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AZ200">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA200">
         <v>9</v>
@@ -43047,10 +43047,10 @@
         <v>8</v>
       </c>
       <c r="AY201">
+        <v>9</v>
+      </c>
+      <c r="AZ201">
         <v>12</v>
-      </c>
-      <c r="AZ201">
-        <v>16</v>
       </c>
       <c r="BA201">
         <v>1</v>
@@ -43253,7 +43253,7 @@
         <v>8</v>
       </c>
       <c r="AY202">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ202">
         <v>13</v>
@@ -43459,10 +43459,10 @@
         <v>5</v>
       </c>
       <c r="AY203">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ203">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA203">
         <v>2</v>
@@ -43665,10 +43665,10 @@
         <v>10</v>
       </c>
       <c r="AY204">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ204">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA204">
         <v>2</v>
@@ -43871,10 +43871,10 @@
         <v>11</v>
       </c>
       <c r="AY205">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ205">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA205">
         <v>8</v>
@@ -44080,7 +44080,7 @@
         <v>7</v>
       </c>
       <c r="AZ206">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA206">
         <v>1</v>
@@ -44283,10 +44283,10 @@
         <v>6</v>
       </c>
       <c r="AY207">
+        <v>12</v>
+      </c>
+      <c r="AZ207">
         <v>13</v>
-      </c>
-      <c r="AZ207">
-        <v>16</v>
       </c>
       <c r="BA207">
         <v>5</v>
@@ -44489,10 +44489,10 @@
         <v>7</v>
       </c>
       <c r="AY208">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ208">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA208">
         <v>5</v>
@@ -44695,10 +44695,10 @@
         <v>3</v>
       </c>
       <c r="AY209">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ209">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA209">
         <v>7</v>
@@ -44901,10 +44901,10 @@
         <v>11</v>
       </c>
       <c r="AY210">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ210">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA210">
         <v>3</v>
@@ -45107,10 +45107,10 @@
         <v>4</v>
       </c>
       <c r="AY211">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ211">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA211">
         <v>9</v>
@@ -45313,7 +45313,7 @@
         <v>4</v>
       </c>
       <c r="AY212">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AZ212">
         <v>7</v>
@@ -45725,7 +45725,7 @@
         <v>7</v>
       </c>
       <c r="AY214">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ214">
         <v>21</v>
@@ -45931,10 +45931,10 @@
         <v>5</v>
       </c>
       <c r="AY215">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ215">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA215">
         <v>6</v>
@@ -46137,10 +46137,10 @@
         <v>3</v>
       </c>
       <c r="AY216">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ216">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA216">
         <v>5</v>
@@ -46343,10 +46343,10 @@
         <v>6</v>
       </c>
       <c r="AY217">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ217">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA217">
         <v>3</v>
@@ -46549,10 +46549,10 @@
         <v>9</v>
       </c>
       <c r="AY218">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ218">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA218">
         <v>3</v>
@@ -46755,10 +46755,10 @@
         <v>10</v>
       </c>
       <c r="AY219">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ219">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA219">
         <v>3</v>
@@ -46961,7 +46961,7 @@
         <v>7</v>
       </c>
       <c r="AY220">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ220">
         <v>10</v>
@@ -47167,10 +47167,10 @@
         <v>2</v>
       </c>
       <c r="AY221">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA221">
         <v>7</v>
@@ -47373,10 +47373,10 @@
         <v>6</v>
       </c>
       <c r="AY222">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ222">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA222">
         <v>6</v>
@@ -47579,10 +47579,10 @@
         <v>7</v>
       </c>
       <c r="AY223">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ223">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA223">
         <v>3</v>
@@ -47785,10 +47785,10 @@
         <v>4</v>
       </c>
       <c r="AY224">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ224">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA224">
         <v>6</v>
@@ -47991,10 +47991,10 @@
         <v>9</v>
       </c>
       <c r="AY225">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ225">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA225">
         <v>5</v>
@@ -48197,10 +48197,10 @@
         <v>3</v>
       </c>
       <c r="AY226">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ226">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA226">
         <v>9</v>
@@ -48403,10 +48403,10 @@
         <v>5</v>
       </c>
       <c r="AY227">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ227">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA227">
         <v>7</v>
@@ -48609,10 +48609,10 @@
         <v>5</v>
       </c>
       <c r="AY228">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ228">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA228">
         <v>3</v>
@@ -48818,7 +48818,7 @@
         <v>7</v>
       </c>
       <c r="AZ229">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA229">
         <v>0</v>
@@ -49021,10 +49021,10 @@
         <v>7</v>
       </c>
       <c r="AY230">
+        <v>10</v>
+      </c>
+      <c r="AZ230">
         <v>13</v>
-      </c>
-      <c r="AZ230">
-        <v>16</v>
       </c>
       <c r="BA230">
         <v>5</v>
@@ -49227,10 +49227,10 @@
         <v>7</v>
       </c>
       <c r="AY231">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ231">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA231">
         <v>4</v>
@@ -49433,10 +49433,10 @@
         <v>8</v>
       </c>
       <c r="AY232">
+        <v>8</v>
+      </c>
+      <c r="AZ232">
         <v>11</v>
-      </c>
-      <c r="AZ232">
-        <v>15</v>
       </c>
       <c r="BA232">
         <v>4</v>
@@ -49639,10 +49639,10 @@
         <v>3</v>
       </c>
       <c r="AY233">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ233">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA233">
         <v>4</v>
@@ -49845,10 +49845,10 @@
         <v>2</v>
       </c>
       <c r="AY234">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ234">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA234">
         <v>4</v>
@@ -50051,10 +50051,10 @@
         <v>9</v>
       </c>
       <c r="AY235">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ235">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA235">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>4</v>
       </c>
       <c r="AY236">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ236">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA236">
         <v>6</v>
@@ -50466,16 +50466,16 @@
         <v>8</v>
       </c>
       <c r="AZ237">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA237">
         <v>0</v>
       </c>
       <c r="BB237">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC237">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD237">
         <v>3.7</v>
@@ -50669,10 +50669,10 @@
         <v>12</v>
       </c>
       <c r="AY238">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ238">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BA238">
         <v>3</v>
@@ -50875,10 +50875,10 @@
         <v>5</v>
       </c>
       <c r="AY239">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ239">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA239">
         <v>7</v>
@@ -51081,7 +51081,7 @@
         <v>2</v>
       </c>
       <c r="AY240">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ240">
         <v>8</v>
@@ -51287,10 +51287,10 @@
         <v>11</v>
       </c>
       <c r="AY241">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AZ241">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA241">
         <v>10</v>
@@ -51493,10 +51493,10 @@
         <v>5</v>
       </c>
       <c r="AY242">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ242">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA242">
         <v>3</v>
@@ -51699,7 +51699,7 @@
         <v>7</v>
       </c>
       <c r="AY243">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ243">
         <v>16</v>
@@ -51905,10 +51905,10 @@
         <v>4</v>
       </c>
       <c r="AY244">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ244">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA244">
         <v>6</v>
@@ -52111,7 +52111,7 @@
         <v>3</v>
       </c>
       <c r="AY245">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ245">
         <v>8</v>
@@ -52317,10 +52317,10 @@
         <v>6</v>
       </c>
       <c r="AY246">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ246">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA246">
         <v>5</v>
@@ -52526,7 +52526,7 @@
         <v>15</v>
       </c>
       <c r="AZ247">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA247">
         <v>2</v>
@@ -52729,10 +52729,10 @@
         <v>6</v>
       </c>
       <c r="AY248">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ248">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA248">
         <v>1</v>
@@ -52938,7 +52938,7 @@
         <v>22</v>
       </c>
       <c r="AZ249">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA249">
         <v>6</v>
@@ -53141,10 +53141,10 @@
         <v>7</v>
       </c>
       <c r="AY250">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ250">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA250">
         <v>4</v>
@@ -53347,10 +53347,10 @@
         <v>9</v>
       </c>
       <c r="AY251">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ251">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA251">
         <v>8</v>
@@ -53553,10 +53553,10 @@
         <v>10</v>
       </c>
       <c r="AY252">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ252">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA252">
         <v>5</v>
@@ -53759,7 +53759,7 @@
         <v>5</v>
       </c>
       <c r="AY253">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ253">
         <v>10</v>
@@ -53965,10 +53965,10 @@
         <v>9</v>
       </c>
       <c r="AY254">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="AZ254">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA254">
         <v>9</v>
@@ -54171,10 +54171,10 @@
         <v>5</v>
       </c>
       <c r="AY255">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ255">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA255">
         <v>4</v>
@@ -54583,10 +54583,10 @@
         <v>17</v>
       </c>
       <c r="AY257">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ257">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BA257">
         <v>2</v>
@@ -54789,10 +54789,10 @@
         <v>9</v>
       </c>
       <c r="AY258">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ258">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA258">
         <v>7</v>
@@ -55201,7 +55201,7 @@
         <v>3</v>
       </c>
       <c r="AY260">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ260">
         <v>10</v>
@@ -55407,10 +55407,10 @@
         <v>5</v>
       </c>
       <c r="AY261">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ261">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA261">
         <v>3</v>
@@ -55613,10 +55613,10 @@
         <v>3</v>
       </c>
       <c r="AY262">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ262">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA262">
         <v>10</v>
@@ -55819,10 +55819,10 @@
         <v>8</v>
       </c>
       <c r="AY263">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ263">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA263">
         <v>7</v>
@@ -56025,7 +56025,7 @@
         <v>3</v>
       </c>
       <c r="AY264">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ264">
         <v>6</v>
@@ -56231,19 +56231,19 @@
         <v>5</v>
       </c>
       <c r="AY265">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ265">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA265">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB265">
         <v>2</v>
       </c>
       <c r="BC265">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD265">
         <v>1.19</v>
@@ -56643,10 +56643,10 @@
         <v>3</v>
       </c>
       <c r="AY267">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ267">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA267">
         <v>4</v>
@@ -56849,7 +56849,7 @@
         <v>9</v>
       </c>
       <c r="AY268">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ268">
         <v>19</v>
@@ -57058,7 +57058,7 @@
         <v>9</v>
       </c>
       <c r="AZ269">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA269">
         <v>0</v>
@@ -57261,19 +57261,19 @@
         <v>13</v>
       </c>
       <c r="AY270">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ270">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA270">
         <v>8</v>
       </c>
       <c r="BB270">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC270">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD270">
         <v>3.05</v>
@@ -57467,10 +57467,10 @@
         <v>5</v>
       </c>
       <c r="AY271">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ271">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA271">
         <v>4</v>
@@ -57673,10 +57673,10 @@
         <v>4</v>
       </c>
       <c r="AY272">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AZ272">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA272">
         <v>17</v>
@@ -57879,10 +57879,10 @@
         <v>11</v>
       </c>
       <c r="AY273">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ273">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA273">
         <v>5</v>
@@ -58085,10 +58085,10 @@
         <v>15</v>
       </c>
       <c r="AY274">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ274">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA274">
         <v>3</v>
@@ -58291,10 +58291,10 @@
         <v>6</v>
       </c>
       <c r="AY275">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ275">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA275">
         <v>7</v>
@@ -58497,10 +58497,10 @@
         <v>4</v>
       </c>
       <c r="AY276">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ276">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA276">
         <v>7</v>
@@ -58703,10 +58703,10 @@
         <v>4</v>
       </c>
       <c r="AY277">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ277">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA277">
         <v>8</v>
@@ -58912,7 +58912,7 @@
         <v>12</v>
       </c>
       <c r="AZ278">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA278">
         <v>3</v>
@@ -59115,10 +59115,10 @@
         <v>5</v>
       </c>
       <c r="AY279">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ279">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA279">
         <v>5</v>
@@ -59321,7 +59321,7 @@
         <v>5</v>
       </c>
       <c r="AY280">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ280">
         <v>10</v>
@@ -59527,10 +59527,10 @@
         <v>14</v>
       </c>
       <c r="AY281">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ281">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA281">
         <v>5</v>
@@ -59733,10 +59733,10 @@
         <v>16</v>
       </c>
       <c r="AY282">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ282">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BA282">
         <v>6</v>
@@ -60145,10 +60145,10 @@
         <v>7</v>
       </c>
       <c r="AY284">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ284">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA284">
         <v>6</v>
@@ -60354,7 +60354,7 @@
         <v>8</v>
       </c>
       <c r="AZ285">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA285">
         <v>4</v>
@@ -60557,10 +60557,10 @@
         <v>4</v>
       </c>
       <c r="AY286">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ286">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA286">
         <v>4</v>
@@ -60766,7 +60766,7 @@
         <v>4</v>
       </c>
       <c r="AZ287">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA287">
         <v>0</v>
@@ -60969,7 +60969,7 @@
         <v>5</v>
       </c>
       <c r="AY288">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ288">
         <v>9</v>
@@ -61175,10 +61175,10 @@
         <v>6</v>
       </c>
       <c r="AY289">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ289">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA289">
         <v>2</v>
@@ -61381,10 +61381,10 @@
         <v>5</v>
       </c>
       <c r="AY290">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ290">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA290">
         <v>3</v>
@@ -61587,10 +61587,10 @@
         <v>17</v>
       </c>
       <c r="AY291">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ291">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA291">
         <v>3</v>
@@ -62002,7 +62002,7 @@
         <v>9</v>
       </c>
       <c r="AZ293">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA293">
         <v>2</v>
@@ -62208,7 +62208,7 @@
         <v>6</v>
       </c>
       <c r="AZ294">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA294">
         <v>2</v>
@@ -62411,10 +62411,10 @@
         <v>4</v>
       </c>
       <c r="AY295">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ295">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA295">
         <v>7</v>
@@ -62617,10 +62617,10 @@
         <v>5</v>
       </c>
       <c r="AY296">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ296">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA296">
         <v>4</v>
@@ -62823,10 +62823,10 @@
         <v>14</v>
       </c>
       <c r="AY297">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ297">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BA297">
         <v>2</v>
@@ -63235,7 +63235,7 @@
         <v>6</v>
       </c>
       <c r="AY299">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ299">
         <v>10</v>
@@ -63441,10 +63441,10 @@
         <v>10</v>
       </c>
       <c r="AY300">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ300">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA300">
         <v>8</v>
@@ -63853,10 +63853,10 @@
         <v>10</v>
       </c>
       <c r="AY302">
+        <v>18</v>
+      </c>
+      <c r="AZ302">
         <v>19</v>
-      </c>
-      <c r="AZ302">
-        <v>20</v>
       </c>
       <c r="BA302">
         <v>7</v>
@@ -64059,7 +64059,7 @@
         <v>2</v>
       </c>
       <c r="AY303">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ303">
         <v>5</v>
@@ -64471,10 +64471,10 @@
         <v>11</v>
       </c>
       <c r="AY305">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ305">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA305">
         <v>7</v>
@@ -64677,10 +64677,10 @@
         <v>3</v>
       </c>
       <c r="AY306">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ306">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA306">
         <v>5</v>
@@ -64883,10 +64883,10 @@
         <v>5</v>
       </c>
       <c r="AY307">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ307">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA307">
         <v>5</v>
